--- a/Result/checksun_type/石化上游原料及相關鑽探設備.xlsx
+++ b/Result/checksun_type/石化上游原料及相關鑽探設備.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>價_量;【c】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>53.4</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>50.95</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>45.16</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>50.95</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>45.16</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>554745012.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>737022951.6</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>737022951.6</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>722290026.4</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>432550164.52</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>432550164.52</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>18557581.47945392</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>554745012</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>554745012.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>54.06</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>50.7</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>44.93</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>50.7</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>44.93</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>788408172.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>744011853.8</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>744011853.8</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>820775940.3</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>425312179.22</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>425312179.22</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>39334024.154495</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>788408172</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>788408172.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>54.46</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>50.37</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>44.69</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>50.37</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>44.69</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>885806096.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>711136410.0</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>711136410</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>841633534.6</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>412172663.7</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>412172663.7</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>42574531.39903605</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>885806096</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>885806096.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>54.34</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>49.89</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>44.39</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>49.89</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>44.39</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>668271837.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>695306190.8</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>695306190.8</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>849322965.9</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>397683648.48</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>397683648.48</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>35247816.62698615</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>668271837</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>668271837.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>54.38</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>49.56</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>44.12</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>49.56</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>44.12</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>787883641.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>674083378.6</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>674083378.6</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>894526103.8</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>386410052.78</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>386410052.78</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>46829472.68023682</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>787883641</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>787883641.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>54.14</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>48.98</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>43.78</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>48.98</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>43.78</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>589689523.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>707557101.2</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>707557101.2</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>878560467.9</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>374087560.62</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>374087560.62</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>48886664.01772928</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>589689523</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>589689523.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>54.5</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>48.48</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>43.51</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>48.48</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>43.51</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>624030953.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>897540026.8</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>897540026.8</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>845078994.9</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>364870429.04</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>364870429.04</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>71314640.57065678</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>624030953</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>624030953.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>54.17999999999999</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>47.96</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>43.21</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>47.96</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>43.21</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>806655000.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>972130659.2</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>972130659.2</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>803973395.4</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>355409680.66</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>355409680.66</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>97128216.69731545</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>806655000</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>806655000.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>53.58</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>47.4</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>42.9</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>47.4</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>42.9</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>562157776.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>1003339741.0</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>1003339741</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>739586306.0</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>343255370.04</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>343255370.04</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>110969026.9604951</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>562157776</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>562157776.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>52.94</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>46.89</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>42.63</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>46.89</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>42.63</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>955252254.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>1114968829.0</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>1114968829</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>707036283.9</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>338029209.8</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>338029209.8</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>152974564.6593055</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>955252254</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>955252254.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>51.51000000000001</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>46.2</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>42.34</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>46.2</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>42.34</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>1539604151.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>1049563834.6</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>1049563834.6</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>636189079.0</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>324215240.94</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>324215240.94</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>165401832.8483452</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>1539604151</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>1539604151.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5669,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5853,15 +5787,11 @@
           <t>75.02000000000001</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>78.97</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>81.51</t>
-        </is>
+      <c r="AM13" t="n">
+        <v>78.97</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>81.51000000000001</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5908,20 +5838,16 @@
           <t>82455044.0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>54894970.2</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>54894970.2</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>43826928.7</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>35350060.16</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>35350060.16</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5864,10 @@
           <t>6700569.163306005</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>82455044</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>82455044.0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6105,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6289,15 +6217,11 @@
           <t>75.7</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>79.39</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>81.66</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>79.39</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>81.66</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6344,20 +6268,16 @@
           <t>83732934.0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>46309061.4</t>
-        </is>
+      <c r="AX14" t="n">
+        <v>46309061.4</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>38056250.1</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>34250910.82</t>
-        </is>
+      <c r="AZ14" t="n">
+        <v>34250910.82</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6374,8 +6294,10 @@
           <t>4448935.272002146</t>
         </is>
       </c>
-      <c r="BD14" t="n">
-        <v>83732934</v>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>83732934.0</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6541,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6725,15 +6647,11 @@
           <t>76.92</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>79.87</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>81.85</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>79.87</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>81.84999999999999</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6780,20 +6698,16 @@
           <t>42275423.0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>37770647.0</t>
-        </is>
+      <c r="AX15" t="n">
+        <v>37770647</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>33547506.6</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>32988097.06</t>
-        </is>
+      <c r="AZ15" t="n">
+        <v>32988097.06</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6810,8 +6724,10 @@
           <t>936508.0961394161</t>
         </is>
       </c>
-      <c r="BD15" t="n">
-        <v>42275423</v>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>42275423.0</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6977,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7161,15 +7077,11 @@
           <t>77.9</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>80.26</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>82.0</t>
-        </is>
+      <c r="AM16" t="n">
+        <v>80.26000000000001</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>82</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7216,20 +7128,16 @@
           <t>40396420.0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>35728397.6</t>
-        </is>
+      <c r="AX16" t="n">
+        <v>35728397.6</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>32885397.6</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>32756986.68</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>32756986.68</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7246,8 +7154,10 @@
           <t>327184.4486162513</t>
         </is>
       </c>
-      <c r="BD16" t="n">
-        <v>40396420</v>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>40396420.0</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7413,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7597,15 +7507,11 @@
           <t>78.67999999999999</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>80.64</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>82.14</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>80.64</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>82.14</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7652,20 +7558,16 @@
           <t>25615030.0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>32809676.6</t>
-        </is>
+      <c r="AX17" t="n">
+        <v>32809676.6</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>31342074.1</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>32292613.84</t>
-        </is>
+      <c r="AZ17" t="n">
+        <v>32292613.84</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7682,8 +7584,10 @@
           <t>-353641.3138674088</t>
         </is>
       </c>
-      <c r="BD17" t="n">
-        <v>25615030</v>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>25615030.0</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7849,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8033,15 +7937,11 @@
           <t>79.24</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>80.98</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>82.26</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>80.98</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>82.26000000000001</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -8088,20 +7988,16 @@
           <t>39525500.0</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>32758887.2</t>
-        </is>
+      <c r="AX18" t="n">
+        <v>32758887.2</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>31206137.4</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>32157569.52</t>
-        </is>
+      <c r="AZ18" t="n">
+        <v>32157569.52</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8118,8 +8014,10 @@
           <t>270100.8580797613</t>
         </is>
       </c>
-      <c r="BD18" t="n">
-        <v>39525500</v>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>39525500.0</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8285,7 +8183,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8469,15 +8367,11 @@
           <t>79.8</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>81.31</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>82.37</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>81.31</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>82.37</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8524,20 +8418,16 @@
           <t>41040862.0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>29803438.8</t>
-        </is>
+      <c r="AX19" t="n">
+        <v>29803438.8</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>30369071.2</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>31948166.24</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>31948166.24</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8554,8 +8444,10 @@
           <t>-338892.855498556</t>
         </is>
       </c>
-      <c r="BD19" t="n">
-        <v>41040862</v>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>41040862.0</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8721,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8905,15 +8797,11 @@
           <t>80.2</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>81.58</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>82.43</t>
-        </is>
+      <c r="AM20" t="n">
+        <v>81.58</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>82.43000000000001</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8960,20 +8848,16 @@
           <t>32064176.0</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>29324366.2</t>
-        </is>
+      <c r="AX20" t="n">
+        <v>29324366.2</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>29811028.5</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>31773476.0</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>31773476</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8990,8 +8874,10 @@
           <t>-1359140.772914063</t>
         </is>
       </c>
-      <c r="BD20" t="n">
-        <v>32064176</v>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>32064176.0</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9157,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9341,15 +9227,11 @@
           <t>80.1</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>81.84</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>82.47</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>81.84</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>82.47</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9396,20 +9278,16 @@
           <t>25802815.0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>30042397.6</t>
-        </is>
+      <c r="AX21" t="n">
+        <v>30042397.6</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>30133020.2</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>31503352.48</t>
-        </is>
+      <c r="AZ21" t="n">
+        <v>31503352.48</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9426,8 +9304,10 @@
           <t>-1806309.270189282</t>
         </is>
       </c>
-      <c r="BD21" t="n">
-        <v>25802815</v>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>25802815.0</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9593,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9777,15 +9657,11 @@
           <t>80.12</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>82.2</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>82.51</t>
-        </is>
+      <c r="AM22" t="n">
+        <v>82.2</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>82.51000000000001</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9832,20 +9708,16 @@
           <t>25361083.0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>29874471.6</t>
-        </is>
+      <c r="AX22" t="n">
+        <v>29874471.6</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>31831792.7</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>31471338.54</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>31471338.54</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9862,8 +9734,10 @@
           <t>-1709750.256647117</t>
         </is>
       </c>
-      <c r="BD22" t="n">
-        <v>25361083</v>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>25361083.0</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10029,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10213,15 +10087,11 @@
           <t>80.2</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>82.67</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>82.55</t>
-        </is>
+      <c r="AM23" t="n">
+        <v>82.67</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>82.55</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10268,20 +10138,16 @@
           <t>24748258.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>29653387.6</t>
-        </is>
+      <c r="AX23" t="n">
+        <v>29653387.6</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>31235489.6</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>31253451.56</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>31253451.56</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10298,8 +10164,10 @@
           <t>-1463417.870992344</t>
         </is>
       </c>
-      <c r="BD23" t="n">
-        <v>24748258</v>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>24748258.0</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10465,7 +10333,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -10649,15 +10517,11 @@
           <t>53.48</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>48.7</t>
-        </is>
-      </c>
-      <c r="AN24" t="inlineStr">
-        <is>
-          <t>43.68</t>
-        </is>
+      <c r="AM24" t="n">
+        <v>48.7</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>43.68</v>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
@@ -10704,20 +10568,16 @@
           <t>3512622548.0</t>
         </is>
       </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>6095469315.0</t>
-        </is>
+      <c r="AX24" t="n">
+        <v>6095469315</v>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
           <t>9544851503.2</t>
         </is>
       </c>
-      <c r="AZ24" t="inlineStr">
-        <is>
-          <t>3663541757.9</t>
-        </is>
+      <c r="AZ24" t="n">
+        <v>3663541757.9</v>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
@@ -10734,8 +10594,10 @@
           <t>98808707.88450241</t>
         </is>
       </c>
-      <c r="BD24" t="n">
-        <v>3512622548</v>
+      <c r="BD24" t="inlineStr">
+        <is>
+          <t>3512622548.0</t>
+        </is>
       </c>
       <c r="BE24" t="inlineStr">
         <is>
@@ -10901,7 +10763,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -11085,15 +10947,11 @@
           <t>54.02</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>48.25</t>
-        </is>
-      </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>43.41</t>
-        </is>
+      <c r="AM25" t="n">
+        <v>48.25</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>43.41</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
@@ -11140,20 +10998,16 @@
           <t>6744255965.0</t>
         </is>
       </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>6936487304.4</t>
-        </is>
+      <c r="AX25" t="n">
+        <v>6936487304.4</v>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
           <t>10032139013.4</t>
         </is>
       </c>
-      <c r="AZ25" t="inlineStr">
-        <is>
-          <t>3632131847.42</t>
-        </is>
+      <c r="AZ25" t="n">
+        <v>3632131847.42</v>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
@@ -11170,8 +11024,10 @@
           <t>468208784.7071676</t>
         </is>
       </c>
-      <c r="BD25" t="n">
-        <v>6744255965</v>
+      <c r="BD25" t="inlineStr">
+        <is>
+          <t>6744255965.0</t>
+        </is>
       </c>
       <c r="BE25" t="inlineStr">
         <is>
@@ -11337,7 +11193,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -11521,15 +11377,11 @@
           <t>55.0</t>
         </is>
       </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>47.74</t>
-        </is>
-      </c>
-      <c r="AN26" t="inlineStr">
-        <is>
-          <t>43.12</t>
-        </is>
+      <c r="AM26" t="n">
+        <v>47.74</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>43.12</v>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
@@ -11576,20 +11428,16 @@
           <t>4850127005.0</t>
         </is>
       </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>8366597065.8</t>
-        </is>
+      <c r="AX26" t="n">
+        <v>8366597065.8</v>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
           <t>9915210649.5</t>
         </is>
       </c>
-      <c r="AZ26" t="inlineStr">
-        <is>
-          <t>3525171118.12</t>
-        </is>
+      <c r="AZ26" t="n">
+        <v>3525171118.12</v>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
@@ -11606,8 +11454,10 @@
           <t>632955000.321434</t>
         </is>
       </c>
-      <c r="BD26" t="n">
-        <v>4850127005</v>
+      <c r="BD26" t="inlineStr">
+        <is>
+          <t>4850127005.0</t>
+        </is>
       </c>
       <c r="BE26" t="inlineStr">
         <is>
@@ -11773,7 +11623,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -11957,15 +11807,11 @@
           <t>55.34</t>
         </is>
       </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>47.15</t>
-        </is>
-      </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>42.8</t>
-        </is>
+      <c r="AM27" t="n">
+        <v>47.15</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>42.8</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
@@ -12012,20 +11858,16 @@
           <t>4661687858.0</t>
         </is>
       </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>9917900867.8</t>
-        </is>
+      <c r="AX27" t="n">
+        <v>9917900867.799999</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
           <t>9646311981.3</t>
         </is>
       </c>
-      <c r="AZ27" t="inlineStr">
-        <is>
-          <t>3483979320.62</t>
-        </is>
+      <c r="AZ27" t="n">
+        <v>3483979320.62</v>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
@@ -12042,8 +11884,10 @@
           <t>1048643589.758906</t>
         </is>
       </c>
-      <c r="BD27" t="n">
-        <v>4661687858</v>
+      <c r="BD27" t="inlineStr">
+        <is>
+          <t>4661687858.0</t>
+        </is>
       </c>
       <c r="BE27" t="inlineStr">
         <is>
@@ -12209,7 +12053,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -12393,15 +12237,11 @@
           <t>55.96</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>46.69</t>
-        </is>
-      </c>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>42.52</t>
-        </is>
+      <c r="AM28" t="n">
+        <v>46.69</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>42.52</v>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
@@ -12448,20 +12288,16 @@
           <t>10708653199.0</t>
         </is>
       </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>11555043688.4</t>
-        </is>
+      <c r="AX28" t="n">
+        <v>11555043688.4</v>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
           <t>9440522375.4</t>
         </is>
       </c>
-      <c r="AZ28" t="inlineStr">
-        <is>
-          <t>3413291777.02</t>
-        </is>
+      <c r="AZ28" t="n">
+        <v>3413291777.02</v>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
@@ -12478,8 +12314,10 @@
           <t>1625222783.642477</t>
         </is>
       </c>
-      <c r="BD28" t="n">
-        <v>10708653199</v>
+      <c r="BD28" t="inlineStr">
+        <is>
+          <t>10708653199.0</t>
+        </is>
       </c>
       <c r="BE28" t="inlineStr">
         <is>
@@ -12645,7 +12483,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -12829,15 +12667,11 @@
           <t>55.4</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>45.98</t>
-        </is>
-      </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>42.16</t>
-        </is>
+      <c r="AM29" t="n">
+        <v>45.98</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>42.16</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
@@ -12884,20 +12718,16 @@
           <t>7717712495.0</t>
         </is>
       </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>12994233691.4</t>
-        </is>
+      <c r="AX29" t="n">
+        <v>12994233691.4</v>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
           <t>8470087592.9</t>
         </is>
       </c>
-      <c r="AZ29" t="inlineStr">
-        <is>
-          <t>3233128694.92</t>
-        </is>
+      <c r="AZ29" t="n">
+        <v>3233128694.92</v>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
@@ -12914,8 +12744,10 @@
           <t>1742974531.810349</t>
         </is>
       </c>
-      <c r="BD29" t="n">
-        <v>7717712495</v>
+      <c r="BD29" t="inlineStr">
+        <is>
+          <t>7717712495.0</t>
+        </is>
       </c>
       <c r="BE29" t="inlineStr">
         <is>
@@ -13081,7 +12913,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -13265,15 +13097,11 @@
           <t>54.6</t>
         </is>
       </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>45.39</t>
-        </is>
-      </c>
-      <c r="AN30" t="inlineStr">
-        <is>
-          <t>41.86</t>
-        </is>
+      <c r="AM30" t="n">
+        <v>45.39</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>41.86</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
@@ -13320,20 +13148,16 @@
           <t>13894804772.0</t>
         </is>
       </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>13127790722.4</t>
-        </is>
+      <c r="AX30" t="n">
+        <v>13127790722.4</v>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
           <t>7823899971.0</t>
         </is>
       </c>
-      <c r="AZ30" t="inlineStr">
-        <is>
-          <t>3109382048.22</t>
-        </is>
+      <c r="AZ30" t="n">
+        <v>3109382048.22</v>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
@@ -13350,8 +13174,10 @@
           <t>2169400157.056937</t>
         </is>
       </c>
-      <c r="BD30" t="n">
-        <v>13894804772</v>
+      <c r="BD30" t="inlineStr">
+        <is>
+          <t>13894804772.0</t>
+        </is>
       </c>
       <c r="BE30" t="inlineStr">
         <is>
@@ -13517,7 +13343,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -13701,15 +13527,11 @@
           <t>52.2</t>
         </is>
       </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>44.62</t>
-        </is>
-      </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>41.5</t>
-        </is>
+      <c r="AM31" t="n">
+        <v>44.62</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>41.5</v>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
@@ -13756,20 +13578,16 @@
           <t>12606646015.0</t>
         </is>
       </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>11463824233.2</t>
-        </is>
+      <c r="AX31" t="n">
+        <v>11463824233.2</v>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
           <t>6558502593.2</t>
         </is>
       </c>
-      <c r="AZ31" t="inlineStr">
-        <is>
-          <t>2879764455.78</t>
-        </is>
+      <c r="AZ31" t="n">
+        <v>2879764455.78</v>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
@@ -13786,8 +13604,10 @@
           <t>2039269729.264316</t>
         </is>
       </c>
-      <c r="BD31" t="n">
-        <v>12606646015</v>
+      <c r="BD31" t="inlineStr">
+        <is>
+          <t>12606646015.0</t>
+        </is>
       </c>
       <c r="BE31" t="inlineStr">
         <is>
@@ -13953,7 +13773,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -14137,15 +13957,11 @@
           <t>49.55</t>
         </is>
       </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>43.9</t>
-        </is>
-      </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>41.17</t>
-        </is>
+      <c r="AM32" t="n">
+        <v>43.9</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>41.17</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
@@ -14192,20 +14008,16 @@
           <t>12847401961.0</t>
         </is>
       </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>9374723094.8</t>
-        </is>
+      <c r="AX32" t="n">
+        <v>9374723094.799999</v>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
           <t>5390815186.5</t>
         </is>
       </c>
-      <c r="AZ32" t="inlineStr">
-        <is>
-          <t>2722439698.1</t>
-        </is>
+      <c r="AZ32" t="n">
+        <v>2722439698.1</v>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
@@ -14222,8 +14034,10 @@
           <t>1918555066.051131</t>
         </is>
       </c>
-      <c r="BD32" t="n">
-        <v>12847401961</v>
+      <c r="BD32" t="inlineStr">
+        <is>
+          <t>12847401961.0</t>
+        </is>
       </c>
       <c r="BE32" t="inlineStr">
         <is>
@@ -14389,7 +14203,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -14573,15 +14387,11 @@
           <t>46.94</t>
         </is>
       </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>43.19</t>
-        </is>
-      </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>40.9</t>
-        </is>
+      <c r="AM33" t="n">
+        <v>43.19</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>40.9</v>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
@@ -14628,20 +14438,16 @@
           <t>17904603214.0</t>
         </is>
       </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>7326001062.4</t>
-        </is>
+      <c r="AX33" t="n">
+        <v>7326001062.4</v>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
           <t>4299803431.4</t>
         </is>
       </c>
-      <c r="AZ33" t="inlineStr">
-        <is>
-          <t>2525457286.94</t>
-        </is>
+      <c r="AZ33" t="n">
+        <v>2525457286.94</v>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
@@ -14658,8 +14464,10 @@
           <t>1651790443.45904</t>
         </is>
       </c>
-      <c r="BD33" t="n">
-        <v>17904603214</v>
+      <c r="BD33" t="inlineStr">
+        <is>
+          <t>17904603214.0</t>
+        </is>
       </c>
       <c r="BE33" t="inlineStr">
         <is>
@@ -14825,7 +14633,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -15009,15 +14817,11 @@
           <t>44.51000000000001</t>
         </is>
       </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>42.52</t>
-        </is>
-      </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>40.69</t>
-        </is>
+      <c r="AM34" t="n">
+        <v>42.52</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>40.69</v>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
@@ -15064,20 +14868,16 @@
           <t>8385497650.0</t>
         </is>
       </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>3945941494.4</t>
-        </is>
+      <c r="AX34" t="n">
+        <v>3945941494.4</v>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
           <t>2599113437.9</t>
         </is>
       </c>
-      <c r="AZ34" t="inlineStr">
-        <is>
-          <t>2229827006.08</t>
-        </is>
+      <c r="AZ34" t="n">
+        <v>2229827006.08</v>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
@@ -15094,8 +14894,10 @@
           <t>669862618.2396603</t>
         </is>
       </c>
-      <c r="BD34" t="n">
-        <v>8385497650</v>
+      <c r="BD34" t="inlineStr">
+        <is>
+          <t>8385497650.0</t>
+        </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>

--- a/Result/checksun_type/石化上游原料及相關鑽探設備.xlsx
+++ b/Result/checksun_type/石化上游原料及相關鑽探設備.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CW34"/>
+  <dimension ref="A1:CW31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -948,12 +948,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>4601.672</t>
+          <t>1316.127</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -978,12 +978,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-3.05</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-3.31</t>
+          <t>-16.57</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-5.37</t>
+          <t>-6.53</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -1073,7 +1073,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -1123,17 +1123,17 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>12.20</t>
+          <t>3.49</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
@@ -1144,66 +1144,66 @@
       <c r="AP2" t="inlineStr"/>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>4602</t>
+          <t>1316</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>61.7</t>
+          <t>36.17</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>37.25</t>
+          <t>43.97</t>
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>1.65</v>
+        <v>-0.1</v>
       </c>
       <c r="AV2" t="n">
-        <v>-4.05</v>
+        <v>-3.09</v>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>2.61</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>7.80</t>
+          <t>7.99</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>48.75</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>50.55</v>
+        <v>50.3</v>
       </c>
       <c r="BA2" t="n">
-        <v>49.26</v>
+        <v>49.57</v>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>45.7</t>
+          <t>45.91</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-1192.49</t>
+          <t>-149.65</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>-0.47</v>
+        <v>-0.51</v>
       </c>
       <c r="BE2" t="n">
-        <v>-0.04</v>
+        <v>-0.21</v>
       </c>
       <c r="BF2" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-101.22</t>
+          <t>-106.92</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1222,43 +1222,43 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>414538193.6427577</t>
+          <t>413789802.2791666</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>226364557.0</t>
+          <t>64138554.0</t>
         </is>
       </c>
       <c r="BK2" t="n">
-        <v>244729109.4</v>
+        <v>180478574.4</v>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>253104275.0</t>
+          <t>216333475.6</t>
         </is>
       </c>
       <c r="BM2" t="n">
-        <v>462234616.36</v>
+        <v>454343174.12</v>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>-8375165</t>
+          <t>-35854901</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>-45494284.39839467</t>
+          <t>-46180765.54027049</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>-39635747.53976309</t>
+          <t>-51094987.65225139</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>226364557.0</t>
+          <t>64138554.0</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>12.43</t>
+          <t>11.06</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1323,22 +1323,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="CI2" t="inlineStr">
         <is>
-          <t>77.03</t>
+          <t>76.09</t>
         </is>
       </c>
       <c r="CJ2" t="inlineStr">
@@ -1363,12 +1363,12 @@
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>27.14</t>
+          <t>26.96</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
         <is>
-          <t>469630</t>
+          <t>463914</t>
         </is>
       </c>
       <c r="CN2" t="inlineStr">
@@ -1388,22 +1388,22 @@
       </c>
       <c r="CQ2" t="inlineStr">
         <is>
-          <t>48.65</t>
+          <t>48.95</t>
         </is>
       </c>
       <c r="CR2" t="inlineStr">
         <is>
-          <t>50.1</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
-          <t>48.15</t>
+          <t>48.45</t>
         </is>
       </c>
       <c r="CT2" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="CU2" t="inlineStr">
@@ -1435,12 +1435,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>3785.684</t>
+          <t>2646.184</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>48.65</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1460,17 +1460,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-3.05</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>-14.41</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1535,7 +1535,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-6.91</t>
+          <t>-6.62</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1610,17 +1610,17 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>10.03</t>
+          <t>7.01</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
@@ -1631,66 +1631,66 @@
       <c r="AP3" t="inlineStr"/>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>4602</t>
+          <t>1316</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>27.66</t>
+          <t>34.04</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>16.68</t>
+          <t>41.13</t>
         </is>
       </c>
       <c r="AU3" t="n">
-        <v>0.02</v>
+        <v>0.14</v>
       </c>
       <c r="AV3" t="n">
-        <v>-4.34</v>
+        <v>-3.74</v>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>7.64</t>
+          <t>7.91</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>48.49</t>
+          <t>48.58</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>50.69</v>
+        <v>50.47</v>
       </c>
       <c r="BA3" t="n">
-        <v>49.09</v>
+        <v>49.42</v>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>45.61</t>
+          <t>45.8</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-780.06</t>
+          <t>-287.52</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>-0.49</v>
+        <v>-0.5</v>
       </c>
       <c r="BE3" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.13</v>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-97.59</t>
+          <t>-104.33</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1709,43 +1709,43 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>414538193.6427577</t>
+          <t>413789802.2791666</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
-          <t>183541718.0</t>
+          <t>129351183.0</t>
         </is>
       </c>
       <c r="BK3" t="n">
-        <v>255848681.6</v>
+        <v>206912922.6</v>
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>250000286.1</t>
+          <t>241751775.8</t>
         </is>
       </c>
       <c r="BM3" t="n">
-        <v>462930721.8</v>
+        <v>459452333.2</v>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>5848395</t>
+          <t>-34838853</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>-46559472.91814587</t>
+          <t>-45287270.61081942</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>-42167407.71421093</t>
+          <t>-44148694.77915558</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>183541718.0</t>
+          <t>129351183.0</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1765,7 +1765,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>10.60</t>
+          <t>10.95</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1825,7 +1825,7 @@
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="CI3" t="inlineStr">
         <is>
-          <t>77.03</t>
+          <t>76.09</t>
         </is>
       </c>
       <c r="CJ3" t="inlineStr">
@@ -1850,12 +1850,12 @@
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>27.14</t>
+          <t>26.96</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
         <is>
-          <t>469630</t>
+          <t>463914</t>
         </is>
       </c>
       <c r="CN3" t="inlineStr">
@@ -1875,22 +1875,22 @@
       </c>
       <c r="CQ3" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="CR3" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>49.45</t>
         </is>
       </c>
       <c r="CS3" t="inlineStr">
         <is>
-          <t>48.15</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="CT3" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>48.65</t>
         </is>
       </c>
       <c r="CU3" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>6166.464</t>
+          <t>4601.672</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1937,7 +1937,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>48.6</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1947,17 +1947,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-3.05</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>9.25</t>
+          <t>-3.31</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -2022,7 +2022,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-6.72</t>
+          <t>-5.37</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -2097,17 +2097,17 @@
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>16.34</t>
+          <t>12.20</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
@@ -2118,66 +2118,66 @@
       <c r="AP4" t="inlineStr"/>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>4602</t>
+          <t>1316</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>22.39</t>
+          <t>61.7</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>7.46</t>
+          <t>37.25</t>
         </is>
       </c>
       <c r="AU4" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>-4.05</v>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>2.61</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>7.80</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>48.5</t>
+        </is>
+      </c>
+      <c r="AZ4" t="n">
+        <v>50.55</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>49.26</v>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>45.7</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>-1192.49</t>
+        </is>
+      </c>
+      <c r="BD4" t="n">
         <v>-0.47</v>
       </c>
-      <c r="AV4" t="n">
-        <v>-4.33</v>
-      </c>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>4.23</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>7.54</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>48.83</t>
-        </is>
-      </c>
-      <c r="AZ4" t="n">
-        <v>51.04</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>48.97</v>
-      </c>
-      <c r="BB4" t="inlineStr">
-        <is>
-          <t>45.53</t>
-        </is>
-      </c>
-      <c r="BC4" t="inlineStr">
-        <is>
-          <t>-300.61</t>
-        </is>
-      </c>
-      <c r="BD4" t="n">
-        <v>-0.42</v>
-      </c>
       <c r="BE4" t="n">
-        <v>0.21</v>
+        <v>-0.04</v>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-92.88</t>
+          <t>-101.22</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2196,43 +2196,43 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>414538193.6427577</t>
+          <t>413789802.2791666</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>298996860.0</t>
+          <t>226364557.0</t>
         </is>
       </c>
       <c r="BK4" t="n">
-        <v>279645957.6</v>
+        <v>244729109.4</v>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>255960435.9</t>
+          <t>253104275.0</t>
         </is>
       </c>
       <c r="BM4" t="n">
-        <v>464661723.26</v>
+        <v>462234616.36</v>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>23685521</t>
+          <t>-8375165</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>-47358030.22795221</t>
+          <t>-45494284.39839467</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>-39689924.93791449</t>
+          <t>-39635747.53976309</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>298996860.0</t>
+          <t>226364557.0</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2252,7 +2252,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>10.83</t>
+          <t>12.43</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2297,7 +2297,7 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
@@ -2307,12 +2307,12 @@
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="CI4" t="inlineStr">
         <is>
-          <t>77.03</t>
+          <t>76.09</t>
         </is>
       </c>
       <c r="CJ4" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>27.14</t>
+          <t>26.96</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
         <is>
-          <t>469630</t>
+          <t>463914</t>
         </is>
       </c>
       <c r="CN4" t="inlineStr">
@@ -2362,22 +2362,22 @@
       </c>
       <c r="CQ4" t="inlineStr">
         <is>
-          <t>47.75</t>
+          <t>48.65</t>
         </is>
       </c>
       <c r="CR4" t="inlineStr">
         <is>
-          <t>48.85</t>
+          <t>50.1</t>
         </is>
       </c>
       <c r="CS4" t="inlineStr">
         <is>
-          <t>47.7</t>
+          <t>48.15</t>
         </is>
       </c>
       <c r="CT4" t="inlineStr">
         <is>
-          <t>48.6</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="CU4" t="inlineStr">
@@ -2409,12 +2409,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>4076.634</t>
+          <t>3785.684</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2424,64 +2424,64 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>48.5</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0.41</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>-0.81</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>2.34</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>-50.0</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2025-11-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2025-11-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>2025-09-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>2025-11-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
           <t>47.85</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>2.94</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>-3.05</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>-4.10</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>-50.0</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>2025-11-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>2025-11-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>2025-09-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>2025-11-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>47.85</t>
-        </is>
-      </c>
       <c r="R5" t="inlineStr">
         <is>
           <t>52.1</t>
@@ -2509,7 +2509,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-8.16</t>
+          <t>-6.91</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -2584,17 +2584,17 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>10.81</t>
+          <t>10.03</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>-2.19</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
@@ -2605,66 +2605,66 @@
       <c r="AP5" t="inlineStr"/>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>4602</t>
+          <t>1316</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>27.66</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>4.21</t>
+          <t>16.68</t>
         </is>
       </c>
       <c r="AU5" t="n">
-        <v>-2.09</v>
+        <v>0.02</v>
       </c>
       <c r="AV5" t="n">
-        <v>-4.66</v>
+        <v>-4.34</v>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>4.96</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>7.41</t>
+          <t>7.64</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>48.87</t>
+          <t>48.49</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>51.26</v>
+        <v>50.69</v>
       </c>
       <c r="BA5" t="n">
-        <v>48.83</v>
+        <v>49.09</v>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>45.46</t>
+          <t>45.61</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-193.82</t>
+          <t>-780.06</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>-0.35</v>
+        <v>-0.49</v>
       </c>
       <c r="BE5" t="n">
-        <v>0.37</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
@@ -2673,7 +2673,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-87.53</t>
+          <t>-97.59</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2683,43 +2683,43 @@
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>414538193.6427577</t>
+          <t>413789802.2791666</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>196310295.0</t>
+          <t>183541718.0</t>
         </is>
       </c>
       <c r="BK5" t="n">
-        <v>252188376.8</v>
+        <v>255848681.6</v>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>262982332.6</t>
+          <t>250000286.1</t>
         </is>
       </c>
       <c r="BM5" t="n">
-        <v>465751913.52</v>
+        <v>462930721.8</v>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>-10793955</t>
+          <t>5848395</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>-48752231.18977726</t>
+          <t>-46559472.91814587</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>-47103360.29542267</t>
+          <t>-42167407.71421093</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>196310295.0</t>
+          <t>183541718.0</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2739,7 +2739,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>9.12</t>
+          <t>10.60</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2784,7 +2784,7 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="CI5" t="inlineStr">
         <is>
-          <t>77.03</t>
+          <t>76.09</t>
         </is>
       </c>
       <c r="CJ5" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>27.14</t>
+          <t>26.96</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
         <is>
-          <t>469630</t>
+          <t>463914</t>
         </is>
       </c>
       <c r="CN5" t="inlineStr">
@@ -2849,22 +2849,22 @@
       </c>
       <c r="CQ5" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="CR5" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="CS5" t="inlineStr">
         <is>
-          <t>47.75</t>
+          <t>48.15</t>
         </is>
       </c>
       <c r="CT5" t="inlineStr">
         <is>
-          <t>47.85</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="CU5" t="inlineStr">
@@ -2896,12 +2896,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-2.02</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>6537.079</t>
+          <t>6166.464</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>48.25</t>
+          <t>48.6</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2921,17 +2921,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-3.05</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>9.25</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-7.39</t>
+          <t>-6.72</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -3071,17 +3071,17 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>17.33</t>
+          <t>16.34</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>-3.83</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -3092,66 +3092,66 @@
       <c r="AP6" t="inlineStr"/>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>4602</t>
+          <t>1316</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>22.39</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>15.09</t>
+          <t>7.46</t>
         </is>
       </c>
       <c r="AU6" t="n">
-        <v>-1.59</v>
+        <v>-0.47</v>
       </c>
       <c r="AV6" t="n">
-        <v>-5.12</v>
+        <v>-4.33</v>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>6.13</t>
+          <t>4.23</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>7.22</t>
+          <t>7.54</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>49.02999999999999</t>
+          <t>48.83</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>51.68</v>
+        <v>51.04</v>
       </c>
       <c r="BA6" t="n">
-        <v>48.69</v>
+        <v>48.97</v>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>45.41</t>
+          <t>45.53</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-130.58</t>
+          <t>-300.61</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>-0.17</v>
+        <v>-0.42</v>
       </c>
       <c r="BE6" t="n">
-        <v>0.55</v>
+        <v>0.21</v>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
@@ -3160,7 +3160,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-81.48</t>
+          <t>-92.88</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -3170,43 +3170,43 @@
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>414538193.6427577</t>
+          <t>413789802.2791666</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
         <is>
-          <t>318432117.0</t>
+          <t>298996860.0</t>
         </is>
       </c>
       <c r="BK6" t="n">
-        <v>276590629</v>
+        <v>279645957.6</v>
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>277420485.8</t>
+          <t>255960435.9</t>
         </is>
       </c>
       <c r="BM6" t="n">
-        <v>468801755</v>
+        <v>464661723.26</v>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>-829856</t>
+          <t>23685521</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>-49052025.89784172</t>
+          <t>-47358030.22795221</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>-45009587.40274072</t>
+          <t>-39689924.93791449</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>318432117.0</t>
+          <t>298996860.0</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>10.03</t>
+          <t>10.83</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -3271,22 +3271,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="CI6" t="inlineStr">
         <is>
-          <t>77.03</t>
+          <t>76.09</t>
         </is>
       </c>
       <c r="CJ6" t="inlineStr">
@@ -3311,12 +3311,12 @@
       </c>
       <c r="CL6" t="inlineStr">
         <is>
-          <t>27.14</t>
+          <t>26.96</t>
         </is>
       </c>
       <c r="CM6" t="inlineStr">
         <is>
-          <t>469630</t>
+          <t>463914</t>
         </is>
       </c>
       <c r="CN6" t="inlineStr">
@@ -3336,22 +3336,22 @@
       </c>
       <c r="CQ6" t="inlineStr">
         <is>
-          <t>49.6</t>
+          <t>47.75</t>
         </is>
       </c>
       <c r="CR6" t="inlineStr">
         <is>
-          <t>50.2</t>
+          <t>48.85</t>
         </is>
       </c>
       <c r="CS6" t="inlineStr">
         <is>
-          <t>48.15</t>
+          <t>47.7</t>
         </is>
       </c>
       <c r="CT6" t="inlineStr">
         <is>
-          <t>48.25</t>
+          <t>48.6</t>
         </is>
       </c>
       <c r="CU6" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>5670.755</t>
+          <t>4076.634</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>49.25</t>
+          <t>47.85</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3408,17 +3408,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-3.05</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-7.22</t>
+          <t>-4.10</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3483,7 +3483,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-5.47</t>
+          <t>-8.16</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -3558,17 +3558,17 @@
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>15.03</t>
+          <t>10.81</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>-2.54</t>
+          <t>-2.19</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -3579,66 +3579,66 @@
       <c r="AP7" t="inlineStr"/>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>4602</t>
+          <t>1316</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>12.63</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>16.04</t>
+          <t>4.21</t>
         </is>
       </c>
       <c r="AU7" t="n">
-        <v>-0.2</v>
+        <v>-2.09</v>
       </c>
       <c r="AV7" t="n">
-        <v>-4.98</v>
+        <v>-4.66</v>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>7.11</t>
+          <t>4.96</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>6.94</t>
+          <t>7.41</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>49.35</t>
+          <t>48.87</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>51.94</v>
+        <v>51.26</v>
       </c>
       <c r="BA7" t="n">
-        <v>48.49</v>
+        <v>48.83</v>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>45.34</t>
+          <t>45.46</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-96.92</t>
+          <t>-193.82</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>0.02</v>
+        <v>-0.35</v>
       </c>
       <c r="BE7" t="n">
-        <v>0.73</v>
+        <v>0.37</v>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
@@ -3647,7 +3647,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-75.44</t>
+          <t>-87.53</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3657,43 +3657,43 @@
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>414538193.6427577</t>
+          <t>413789802.2791666</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
         <is>
-          <t>281962418.0</t>
+          <t>196310295.0</t>
         </is>
       </c>
       <c r="BK7" t="n">
-        <v>261479440.6</v>
+        <v>252188376.8</v>
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>281835618.8</t>
+          <t>262982332.6</t>
         </is>
       </c>
       <c r="BM7" t="n">
-        <v>467776139.32</v>
+        <v>465751913.52</v>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>-20356178</t>
+          <t>-10793955</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>-49787014.71513281</t>
+          <t>-48752231.18977726</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>-53495478.93452573</t>
+          <t>-47103360.29542267</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>281962418.0</t>
+          <t>196310295.0</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3713,7 +3713,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>12.31</t>
+          <t>9.12</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3758,7 +3758,7 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
@@ -3768,12 +3768,12 @@
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="CI7" t="inlineStr">
         <is>
-          <t>77.03</t>
+          <t>76.09</t>
         </is>
       </c>
       <c r="CJ7" t="inlineStr">
@@ -3798,12 +3798,12 @@
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>27.14</t>
+          <t>26.96</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
         <is>
-          <t>469630</t>
+          <t>463914</t>
         </is>
       </c>
       <c r="CN7" t="inlineStr">
@@ -3823,22 +3823,22 @@
       </c>
       <c r="CQ7" t="inlineStr">
         <is>
-          <t>49.45</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="CR7" t="inlineStr">
         <is>
-          <t>50.5</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="CS7" t="inlineStr">
         <is>
-          <t>49.25</t>
+          <t>47.75</t>
         </is>
       </c>
       <c r="CT7" t="inlineStr">
         <is>
-          <t>49.25</t>
+          <t>47.85</t>
         </is>
       </c>
       <c r="CU7" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2.89</t>
+          <t>-2.02</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>6042.766</t>
+          <t>6537.079</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3885,7 +3885,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>50.2</t>
+          <t>48.25</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3895,17 +3895,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-3.05</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-18.31</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3970,7 +3970,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-3.65</t>
+          <t>-7.39</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>16.02</t>
+          <t>17.33</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>3.41</t>
+          <t>-3.83</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -4066,66 +4066,66 @@
       <c r="AP8" t="inlineStr"/>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>4602</t>
+          <t>1316</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>32.63</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>11.83</t>
+          <t>15.09</t>
         </is>
       </c>
       <c r="AU8" t="n">
-        <v>0.92</v>
+        <v>-1.59</v>
       </c>
       <c r="AV8" t="n">
-        <v>-4.68</v>
+        <v>-5.12</v>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>8.03</t>
+          <t>6.13</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>6.81</t>
+          <t>7.22</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>49.73999999999999</t>
+          <t>49.02999999999999</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>52.18</v>
+        <v>51.68</v>
       </c>
       <c r="BA8" t="n">
-        <v>48.3</v>
+        <v>48.69</v>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>45.22</t>
+          <t>45.41</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-81.94</t>
+          <t>-130.58</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>0.16</v>
+        <v>-0.17</v>
       </c>
       <c r="BE8" t="n">
-        <v>0.91</v>
+        <v>0.55</v>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
@@ -4134,7 +4134,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-69.49</t>
+          <t>-81.48</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -4144,43 +4144,43 @@
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>414538193.6427577</t>
+          <t>413789802.2791666</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
         <is>
-          <t>302528098.0</t>
+          <t>318432117.0</t>
         </is>
       </c>
       <c r="BK8" t="n">
-        <v>244151890.6</v>
+        <v>276590629</v>
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>298878172.2</t>
+          <t>277420485.8</t>
         </is>
       </c>
       <c r="BM8" t="n">
-        <v>465434594.7</v>
+        <v>468801755</v>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>-54726281</t>
+          <t>-829856</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>-49112748.49342501</t>
+          <t>-49052025.89784172</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>-59800160.55369985</t>
+          <t>-45009587.40274072</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>302528098.0</t>
+          <t>318432117.0</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -4200,7 +4200,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>14.48</t>
+          <t>10.03</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -4245,22 +4245,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="CI8" t="inlineStr">
         <is>
-          <t>77.03</t>
+          <t>76.09</t>
         </is>
       </c>
       <c r="CJ8" t="inlineStr">
@@ -4285,12 +4285,12 @@
       </c>
       <c r="CL8" t="inlineStr">
         <is>
-          <t>27.14</t>
+          <t>26.96</t>
         </is>
       </c>
       <c r="CM8" t="inlineStr">
         <is>
-          <t>469630</t>
+          <t>463914</t>
         </is>
       </c>
       <c r="CN8" t="inlineStr">
@@ -4310,22 +4310,22 @@
       </c>
       <c r="CQ8" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>49.6</t>
         </is>
       </c>
       <c r="CR8" t="inlineStr">
         <is>
-          <t>50.9</t>
+          <t>50.2</t>
         </is>
       </c>
       <c r="CS8" t="inlineStr">
         <is>
-          <t>47.9</t>
+          <t>48.15</t>
         </is>
       </c>
       <c r="CT8" t="inlineStr">
         <is>
-          <t>50.2</t>
+          <t>48.25</t>
         </is>
       </c>
       <c r="CU8" t="inlineStr">
@@ -4357,12 +4357,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>3311.606</t>
+          <t>5670.755</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4372,7 +4372,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>49.25</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -4382,17 +4382,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-3.05</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-20.68</t>
+          <t>-7.22</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4457,7 +4457,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-6.33</t>
+          <t>-5.47</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4482,7 +4482,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -4532,17 +4532,17 @@
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>8.78</t>
+          <t>15.03</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-2.54</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
@@ -4553,66 +4553,66 @@
       <c r="AP9" t="inlineStr"/>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>4602</t>
+          <t>1316</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>2.86</t>
+          <t>12.63</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>16.04</t>
         </is>
       </c>
       <c r="AU9" t="n">
-        <v>-2.4</v>
+        <v>-0.2</v>
       </c>
       <c r="AV9" t="n">
-        <v>-4.61</v>
+        <v>-4.98</v>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>8.94</t>
+          <t>7.11</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>6.67</t>
+          <t>6.94</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>49.35</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>52.42</v>
+        <v>51.94</v>
       </c>
       <c r="BA9" t="n">
-        <v>48.11</v>
+        <v>48.49</v>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>45.1</t>
+          <t>45.34</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-77.60</t>
+          <t>-96.92</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>0.24</v>
+        <v>0.02</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.09</v>
+        <v>0.73</v>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
@@ -4621,7 +4621,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-63.23</t>
+          <t>-75.44</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4631,43 +4631,43 @@
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>414538193.6427577</t>
+          <t>413789802.2791666</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
         <is>
-          <t>161708956.0</t>
+          <t>281962418.0</t>
         </is>
       </c>
       <c r="BK9" t="n">
-        <v>232274914.2</v>
+        <v>261479440.6</v>
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>292838816.9</t>
+          <t>281835618.8</t>
         </is>
       </c>
       <c r="BM9" t="n">
-        <v>462922104.52</v>
+        <v>467776139.32</v>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>-60563902</t>
+          <t>-20356178</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>-47169582.66428413</t>
+          <t>-49787014.71513281</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>-68874594.2756021</t>
+          <t>-53495478.93452573</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>161708956.0</t>
+          <t>281962418.0</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4687,7 +4687,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>11.29</t>
+          <t>12.31</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4732,22 +4732,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4757,7 +4757,7 @@
       </c>
       <c r="CI9" t="inlineStr">
         <is>
-          <t>77.03</t>
+          <t>76.09</t>
         </is>
       </c>
       <c r="CJ9" t="inlineStr">
@@ -4772,12 +4772,12 @@
       </c>
       <c r="CL9" t="inlineStr">
         <is>
-          <t>27.14</t>
+          <t>26.96</t>
         </is>
       </c>
       <c r="CM9" t="inlineStr">
         <is>
-          <t>469630</t>
+          <t>463914</t>
         </is>
       </c>
       <c r="CN9" t="inlineStr">
@@ -4797,22 +4797,22 @@
       </c>
       <c r="CQ9" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>49.45</t>
         </is>
       </c>
       <c r="CR9" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>50.5</t>
         </is>
       </c>
       <c r="CS9" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>49.25</t>
         </is>
       </c>
       <c r="CT9" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>49.25</t>
         </is>
       </c>
       <c r="CU9" t="inlineStr">
@@ -4844,12 +4844,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-2.4</t>
+          <t>2.89</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>6513.341</t>
+          <t>6042.766</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4859,7 +4859,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>48.65</t>
+          <t>50.2</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4869,17 +4869,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>-3.08</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-3.05</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-9.46</t>
+          <t>-18.31</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4944,7 +4944,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-6.62</t>
+          <t>-3.65</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4969,7 +4969,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -5019,17 +5019,17 @@
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>17.26</t>
+          <t>16.02</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>-2.47</t>
+          <t>3.41</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
@@ -5040,66 +5040,66 @@
       <c r="AP10" t="inlineStr"/>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>4602</t>
+          <t>1316</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>32.63</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>11.83</t>
         </is>
       </c>
       <c r="AU10" t="n">
-        <v>-3.74</v>
+        <v>0.92</v>
       </c>
       <c r="AV10" t="n">
-        <v>-3.98</v>
+        <v>-4.68</v>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>9.77</t>
+          <t>8.03</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>6.52</t>
+          <t>6.81</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>50.54</t>
+          <t>49.73999999999999</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>52.64</v>
+        <v>52.18</v>
       </c>
       <c r="BA10" t="n">
-        <v>47.95</v>
+        <v>48.3</v>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>45.01</t>
+          <t>45.22</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-62.64</t>
+          <t>-81.94</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>0.49</v>
+        <v>0.16</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.3</v>
+        <v>0.91</v>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
@@ -5108,7 +5108,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-56.10</t>
+          <t>-69.49</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -5118,43 +5118,43 @@
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>414538193.6427577</t>
+          <t>413789802.2791666</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
         <is>
-          <t>318321556.0</t>
+          <t>302528098.0</t>
         </is>
       </c>
       <c r="BK10" t="n">
-        <v>273776288.4</v>
+        <v>244151890.6</v>
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>302382316.7</t>
+          <t>298878172.2</t>
         </is>
       </c>
       <c r="BM10" t="n">
-        <v>463824635.9</v>
+        <v>465434594.7</v>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>-28606028</t>
+          <t>-54726281</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>-43223216.91677178</t>
+          <t>-49112748.49342501</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>-64290498.86847669</t>
+          <t>-59800160.55369985</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>318321556.0</t>
+          <t>302528098.0</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -5174,7 +5174,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>10.95</t>
+          <t>14.48</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -5219,22 +5219,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -5244,7 +5244,7 @@
       </c>
       <c r="CI10" t="inlineStr">
         <is>
-          <t>77.03</t>
+          <t>76.09</t>
         </is>
       </c>
       <c r="CJ10" t="inlineStr">
@@ -5259,12 +5259,12 @@
       </c>
       <c r="CL10" t="inlineStr">
         <is>
-          <t>27.14</t>
+          <t>26.96</t>
         </is>
       </c>
       <c r="CM10" t="inlineStr">
         <is>
-          <t>469630</t>
+          <t>463914</t>
         </is>
       </c>
       <c r="CN10" t="inlineStr">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="CQ10" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="CR10" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>50.9</t>
         </is>
       </c>
       <c r="CS10" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>47.9</t>
         </is>
       </c>
       <c r="CT10" t="inlineStr">
         <is>
-          <t>48.65</t>
+          <t>50.2</t>
         </is>
       </c>
       <c r="CU10" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-2.64</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>4830.908</t>
+          <t>3311.606</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5346,7 +5346,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>49.85</t>
+          <t>48.8</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -5356,17 +5356,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-3.05</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-11.98</t>
+          <t>-20.68</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-4.32</t>
+          <t>-6.33</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -5506,17 +5506,17 @@
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>12.80</t>
+          <t>8.78</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
@@ -5527,66 +5527,66 @@
       <c r="AP11" t="inlineStr"/>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>4602</t>
+          <t>1316</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.86</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>11.71</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="AU11" t="n">
-        <v>-3.19</v>
+        <v>-2.4</v>
       </c>
       <c r="AV11" t="n">
-        <v>-2.76</v>
+        <v>-4.61</v>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>10.83</t>
+          <t>8.94</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>6.34</t>
+          <t>6.67</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>51.48999999999999</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>52.95</v>
+        <v>52.42</v>
       </c>
       <c r="BA11" t="n">
-        <v>47.78</v>
+        <v>48.11</v>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>44.93</t>
+          <t>45.1</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-46.63</t>
+          <t>-77.60</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>0.8</v>
+        <v>0.24</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.51</v>
+        <v>1.09</v>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-49.23</t>
+          <t>-63.23</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5605,43 +5605,43 @@
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>414538193.6427577</t>
+          <t>413789802.2791666</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
         <is>
-          <t>242876175.0</t>
+          <t>161708956.0</t>
         </is>
       </c>
       <c r="BK11" t="n">
-        <v>278250342.6</v>
+        <v>232274914.2</v>
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>316128556.2</t>
+          <t>292838816.9</t>
         </is>
       </c>
       <c r="BM11" t="n">
-        <v>460736731.18</v>
+        <v>462922104.52</v>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>-37878213</t>
+          <t>-60563902</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>-39392802.0164618</t>
+          <t>-47169582.66428413</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>-72225623.32728058</t>
+          <t>-68874594.2756021</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>242876175.0</t>
+          <t>161708956.0</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5661,7 +5661,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>13.68</t>
+          <t>11.29</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5706,7 +5706,7 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
@@ -5716,12 +5716,12 @@
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5731,7 +5731,7 @@
       </c>
       <c r="CI11" t="inlineStr">
         <is>
-          <t>77.03</t>
+          <t>76.09</t>
         </is>
       </c>
       <c r="CJ11" t="inlineStr">
@@ -5746,12 +5746,12 @@
       </c>
       <c r="CL11" t="inlineStr">
         <is>
-          <t>27.14</t>
+          <t>26.96</t>
         </is>
       </c>
       <c r="CM11" t="inlineStr">
         <is>
-          <t>469630</t>
+          <t>463914</t>
         </is>
       </c>
       <c r="CN11" t="inlineStr">
@@ -5771,22 +5771,22 @@
       </c>
       <c r="CQ11" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="CR11" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="CS11" t="inlineStr">
         <is>
-          <t>49.75</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="CT11" t="inlineStr">
         <is>
-          <t>49.85</t>
+          <t>48.8</t>
         </is>
       </c>
       <c r="CU11" t="inlineStr">
@@ -5808,22 +5808,22 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>6505</t>
+          <t>1723</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-2.04</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>3830.869</t>
+          <t>839.101</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5833,7 +5833,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>51.2</t>
+          <t>67.1</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5843,17 +5843,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-3.85</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-3.05</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-12.99</t>
+          <t>8.11</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5863,37 +5863,37 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-100.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2025-11-06 00:00:00</t>
+          <t>2025-02-26 00:00:00</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2025-11-25 00:00:00</t>
+          <t>2025-03-12 00:00:00</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>2025-09-26 00:00:00</t>
+          <t>2024-03-28 00:00:00</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2025-11-04 00:00:00</t>
+          <t>2024-04-02 00:00:00</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>47.85</t>
+          <t>99.1</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>98.6</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -5903,12 +5903,12 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>40.15</t>
+          <t>123.5</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>44.5</t>
+          <t>118.0</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -5918,22 +5918,22 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>-31.95</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>7.53</t>
+          <t>-16.02</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025/07/28</t>
+          <t>2025/06/02</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>40.4</t>
+          <t>92.4</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -5943,67 +5943,67 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>2025/09/19</t>
+          <t>2025/11/13</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>38.9</t>
+          <t>79.9</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>2025/07/04</t>
+          <t>2025/06/20</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>37.85</t>
+          <t>90.1</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>2025/11/25</t>
+          <t>2025/10/23</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>2025/11/04</t>
+          <t>2025/07/31</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>44.5</t>
+          <t>86.9</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>2025-11-07 00:00:00</t>
+          <t>2025-11-28 00:00:00</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>10.15</t>
+          <t>44.59</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
@@ -6014,12 +6014,12 @@
       <c r="AP12" t="inlineStr"/>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>4602</t>
+          <t>839</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -6029,106 +6029,106 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>23.42</t>
+          <t>29.63</t>
         </is>
       </c>
       <c r="AU12" t="n">
-        <v>-1.88</v>
+        <v>-1.53</v>
       </c>
       <c r="AV12" t="n">
-        <v>-1.96</v>
+        <v>-1.98</v>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>11.85</t>
+          <t>-8.52</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>6.16</t>
+          <t>-3.21</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>52.18000000000001</t>
+          <t>68.14</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>53.22</v>
+        <v>69.52</v>
       </c>
       <c r="BA12" t="n">
-        <v>47.58</v>
+        <v>75.98999999999999</v>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>44.82</t>
+          <t>78.51</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-36.08</t>
+          <t>8.98</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>1.08</v>
+        <v>-2.23</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.68</v>
+        <v>-2.45</v>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>2.97</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-43.31</t>
+          <t>-241.47</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2025/11/06</t>
+          <t>2025/12/15</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>414538193.6427577</t>
+          <t>67197049.88125001</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
         <is>
-          <t>195324668.0</t>
+          <t>56479383.0</t>
         </is>
       </c>
       <c r="BK12" t="n">
-        <v>302191797</v>
+        <v>30387660</v>
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>347315439.9</t>
+          <t>28107734.3</t>
         </is>
       </c>
       <c r="BM12" t="n">
-        <v>460784361.26</v>
+        <v>38193467.22</v>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>-45123642</t>
+          <t>2279925</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>-33423198.14176747</t>
+          <t>-2693670.6034935</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>-72898595.18531173</t>
+          <t>-2120252.290681858</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>195324668.0</t>
+          <t>56479383.0</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -6138,32 +6138,32 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>43.85</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>2025/10/20</t>
+          <t>2025/10/15</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>16.76</t>
+          <t>-24.86</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>台塑化</t>
+          <t>中碳</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
         <is>
-          <t>台塑化</t>
+          <t>中碳</t>
         </is>
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>油電燃氣業</t>
+          <t>化學工業</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
@@ -6173,117 +6173,117 @@
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
         <is>
-          <t>-16.06351948126612</t>
+          <t>-7.32116827620037</t>
         </is>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>-3.054910686901505</t>
+          <t>-26.54178546817805</t>
         </is>
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>-6.074976069093286</t>
+          <t>-23.30870698662894</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>6.71</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
         <is>
-          <t>17.17</t>
+          <t>5.94</t>
         </is>
       </c>
       <c r="CI12" t="inlineStr">
         <is>
-          <t>77.03</t>
+          <t>21.17</t>
         </is>
       </c>
       <c r="CJ12" t="inlineStr">
         <is>
-          <t>7.31%</t>
+          <t>17.52%</t>
         </is>
       </c>
       <c r="CK12" t="inlineStr">
         <is>
-          <t>5.68%</t>
+          <t>6.35%</t>
         </is>
       </c>
       <c r="CL12" t="inlineStr">
         <is>
-          <t>27.14</t>
+          <t>53.39</t>
         </is>
       </c>
       <c r="CM12" t="inlineStr">
         <is>
-          <t>469630</t>
+          <t>15896</t>
         </is>
       </c>
       <c r="CN12" t="inlineStr">
         <is>
-          <t>汽油,柴油等各項石油製品75.50%、乙烯,丙烯等石油化學品18.10%、電力,蒸汽6.00%、其他0.40% (2024年)</t>
+          <t>煤焦油及化學品系列產品53.20%、輕油及油品系列產品29.03%、精碳材料9.72%、焦碳製品6.62%、其他1.43% (2024年)</t>
         </is>
       </c>
       <c r="CO12" t="inlineStr">
         <is>
-          <t>台塑化-油電燃氣業-上市</t>
+          <t>中碳-化學工業-上市</t>
         </is>
       </c>
       <c r="CP12" t="inlineStr">
         <is>
-          <t>油電燃氣業右下上市</t>
+          <t>化學工業右下上市</t>
         </is>
       </c>
       <c r="CQ12" t="inlineStr">
         <is>
-          <t>51.0</t>
+          <t>68.5</t>
         </is>
       </c>
       <c r="CR12" t="inlineStr">
         <is>
-          <t>51.5</t>
+          <t>68.5</t>
         </is>
       </c>
       <c r="CS12" t="inlineStr">
         <is>
-          <t>50.6</t>
+          <t>66.9</t>
         </is>
       </c>
       <c r="CT12" t="inlineStr">
         <is>
-          <t>51.2</t>
+          <t>67.1</t>
         </is>
       </c>
       <c r="CU12" t="inlineStr">
         <is>
-          <t>32.21</t>
+          <t>33.12</t>
         </is>
       </c>
       <c r="CV12" t="inlineStr">
         <is>
-          <t>** 石化及塑橡膠 - 石化上游原料及相關鑽探設備** 油電燃氣 - 加油站、汽電共生</t>
+          <t>** 石化及塑橡膠 - 石化上游原料及相關鑽探設備** 電動車輛產業 - 鋰電池材料** 能源元件 - 原材料</t>
         </is>
       </c>
       <c r="CW12" t="inlineStr">
@@ -6305,12 +6305,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>261.237</t>
+          <t>251.116</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -6320,7 +6320,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>68.5</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -6330,17 +6330,17 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>5.95</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -6405,7 +6405,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-30.32</t>
+          <t>-30.53</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -6430,7 +6430,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -6480,17 +6480,17 @@
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>13.88</t>
+          <t>13.34</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
@@ -6501,66 +6501,66 @@
       <c r="AP13" t="inlineStr"/>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>261</t>
+          <t>839</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>38.89</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>31.48</t>
+          <t>44.44</t>
         </is>
       </c>
       <c r="AU13" t="n">
-        <v>0.41</v>
+        <v>0.26</v>
       </c>
       <c r="AV13" t="n">
-        <v>-2.42</v>
+        <v>-2.19</v>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>-8.66</t>
+          <t>-8.61</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>-2.67</t>
+          <t>-2.87</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>68.42</t>
+          <t>68.32000000000001</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>70.12</v>
+        <v>69.84999999999999</v>
       </c>
       <c r="BA13" t="n">
-        <v>76.76000000000001</v>
+        <v>76.43000000000001</v>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>78.87</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>9.28</t>
+          <t>11.06</t>
         </is>
       </c>
       <c r="BD13" t="n">
-        <v>-2.34</v>
+        <v>-2.23</v>
       </c>
       <c r="BE13" t="n">
-        <v>-2.58</v>
+        <v>-2.51</v>
       </c>
       <c r="BF13" t="inlineStr">
         <is>
@@ -6569,7 +6569,7 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>-248.65</t>
+          <t>-244.65</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -6579,43 +6579,43 @@
       </c>
       <c r="BI13" t="inlineStr">
         <is>
-          <t>67230192.94011143</t>
+          <t>67197049.88125001</t>
         </is>
       </c>
       <c r="BJ13" t="inlineStr">
         <is>
-          <t>17906877.0</t>
+          <t>17252206.0</t>
         </is>
       </c>
       <c r="BK13" t="n">
-        <v>27813361</v>
+        <v>27906915.2</v>
       </c>
       <c r="BL13" t="inlineStr">
         <is>
-          <t>27215289.8</t>
+          <t>26338712.0</t>
         </is>
       </c>
       <c r="BM13" t="n">
-        <v>41606784.8</v>
+        <v>40395160.94</v>
       </c>
       <c r="BN13" t="inlineStr">
         <is>
-          <t>598071</t>
+          <t>1568203</t>
         </is>
       </c>
       <c r="BO13" t="inlineStr">
         <is>
-          <t>-2412779.841971723</t>
+          <t>-2797928.478550162</t>
         </is>
       </c>
       <c r="BP13" t="inlineStr">
         <is>
-          <t>-4532030.643383615</t>
+          <t>-4916245.979731578</t>
         </is>
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>17906877.0</t>
+          <t>17252206.0</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -6635,7 +6635,7 @@
       </c>
       <c r="BU13" t="inlineStr">
         <is>
-          <t>-23.07</t>
+          <t>-23.29</t>
         </is>
       </c>
       <c r="BV13" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
@@ -6695,7 +6695,7 @@
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>6.55</t>
+          <t>6.71</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6705,7 +6705,7 @@
       </c>
       <c r="CI13" t="inlineStr">
         <is>
-          <t>21.67</t>
+          <t>21.17</t>
         </is>
       </c>
       <c r="CJ13" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="CL13" t="inlineStr">
         <is>
-          <t>55.16</t>
+          <t>53.39</t>
         </is>
       </c>
       <c r="CM13" t="inlineStr">
         <is>
-          <t>16275</t>
+          <t>15896</t>
         </is>
       </c>
       <c r="CN13" t="inlineStr">
@@ -6745,22 +6745,22 @@
       </c>
       <c r="CQ13" t="inlineStr">
         <is>
-          <t>68.6</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="CR13" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>69.4</t>
         </is>
       </c>
       <c r="CS13" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>68.4</t>
         </is>
       </c>
       <c r="CT13" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>68.5</t>
         </is>
       </c>
       <c r="CU13" t="inlineStr">
@@ -6792,12 +6792,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>327.223</t>
+          <t>261.237</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6807,7 +6807,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>68.6</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6817,17 +6817,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>-2.38</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-12.29</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6892,7 +6892,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-30.43</t>
+          <t>-30.32</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6917,7 +6917,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -6967,17 +6967,17 @@
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>17.39</t>
+          <t>13.88</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
@@ -6988,66 +6988,66 @@
       <c r="AP14" t="inlineStr"/>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>261</t>
+          <t>839</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>44.44</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>14.81</t>
+          <t>31.48</t>
         </is>
       </c>
       <c r="AU14" t="n">
-        <v>0.09</v>
+        <v>0.41</v>
       </c>
       <c r="AV14" t="n">
-        <v>-2.54</v>
+        <v>-2.42</v>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>-8.83</t>
+          <t>-8.66</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>-2.40</t>
+          <t>-2.67</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>68.53999999999999</t>
+          <t>68.42</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>70.31999999999999</v>
+        <v>70.12</v>
       </c>
       <c r="BA14" t="n">
-        <v>77.14</v>
+        <v>76.76000000000001</v>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>79.04</t>
+          <t>78.87</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>6.64</t>
+          <t>9.28</t>
         </is>
       </c>
       <c r="BD14" t="n">
-        <v>-2.46</v>
+        <v>-2.34</v>
       </c>
       <c r="BE14" t="n">
-        <v>-2.64</v>
+        <v>-2.58</v>
       </c>
       <c r="BF14" t="inlineStr">
         <is>
@@ -7056,7 +7056,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>-252.10</t>
+          <t>-248.65</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -7066,43 +7066,43 @@
       </c>
       <c r="BI14" t="inlineStr">
         <is>
-          <t>67230192.94011143</t>
+          <t>67197049.88125001</t>
         </is>
       </c>
       <c r="BJ14" t="inlineStr">
         <is>
-          <t>22368625.0</t>
+          <t>17906877.0</t>
         </is>
       </c>
       <c r="BK14" t="n">
-        <v>28384364.6</v>
+        <v>27813361</v>
       </c>
       <c r="BL14" t="inlineStr">
         <is>
-          <t>32361196.0</t>
+          <t>27215289.8</t>
         </is>
       </c>
       <c r="BM14" t="n">
-        <v>43621757.96</v>
+        <v>41606784.8</v>
       </c>
       <c r="BN14" t="inlineStr">
         <is>
-          <t>-3976831</t>
+          <t>598071</t>
         </is>
       </c>
       <c r="BO14" t="inlineStr">
         <is>
-          <t>-2027461.514442288</t>
+          <t>-2412779.841971723</t>
         </is>
       </c>
       <c r="BP14" t="inlineStr">
         <is>
-          <t>-3891436.675622828</t>
+          <t>-4532030.643383615</t>
         </is>
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>22368625.0</t>
+          <t>17906877.0</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -7122,7 +7122,7 @@
       </c>
       <c r="BU14" t="inlineStr">
         <is>
-          <t>-23.18</t>
+          <t>-23.07</t>
         </is>
       </c>
       <c r="BV14" t="inlineStr">
@@ -7167,12 +7167,12 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
@@ -7182,7 +7182,7 @@
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>6.55</t>
+          <t>6.71</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -7192,7 +7192,7 @@
       </c>
       <c r="CI14" t="inlineStr">
         <is>
-          <t>21.67</t>
+          <t>21.17</t>
         </is>
       </c>
       <c r="CJ14" t="inlineStr">
@@ -7207,12 +7207,12 @@
       </c>
       <c r="CL14" t="inlineStr">
         <is>
-          <t>55.16</t>
+          <t>53.39</t>
         </is>
       </c>
       <c r="CM14" t="inlineStr">
         <is>
-          <t>16275</t>
+          <t>15896</t>
         </is>
       </c>
       <c r="CN14" t="inlineStr">
@@ -7232,22 +7232,22 @@
       </c>
       <c r="CQ14" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>68.6</t>
         </is>
       </c>
       <c r="CR14" t="inlineStr">
         <is>
-          <t>68.6</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="CS14" t="inlineStr">
         <is>
-          <t>67.7</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="CT14" t="inlineStr">
         <is>
-          <t>68.6</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="CU14" t="inlineStr">
@@ -7279,12 +7279,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>558.986</t>
+          <t>327.223</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -7294,7 +7294,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>68.6</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -7304,17 +7304,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-27.31</t>
+          <t>-12.29</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -7379,7 +7379,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-31.24</t>
+          <t>-30.43</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -7404,7 +7404,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -7454,17 +7454,17 @@
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>29.70</t>
+          <t>17.39</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
@@ -7475,66 +7475,66 @@
       <c r="AP15" t="inlineStr"/>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>261</t>
+          <t>839</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>44.44</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>14.81</t>
         </is>
       </c>
       <c r="AU15" t="n">
-        <v>-1.37</v>
+        <v>0.09</v>
       </c>
       <c r="AV15" t="n">
-        <v>-2.7</v>
+        <v>-2.54</v>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>-8.8</t>
+          <t>-8.83</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>-2.19</t>
+          <t>-2.40</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>68.74</t>
+          <t>68.53999999999999</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>70.65000000000001</v>
+        <v>70.31999999999999</v>
       </c>
       <c r="BA15" t="n">
-        <v>77.45999999999999</v>
+        <v>77.14</v>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>79.04</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>6.64</t>
         </is>
       </c>
       <c r="BD15" t="n">
-        <v>-2.57</v>
+        <v>-2.46</v>
       </c>
       <c r="BE15" t="n">
-        <v>-2.68</v>
+        <v>-2.64</v>
       </c>
       <c r="BF15" t="inlineStr">
         <is>
@@ -7543,7 +7543,7 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>-254.62</t>
+          <t>-252.10</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -7553,43 +7553,43 @@
       </c>
       <c r="BI15" t="inlineStr">
         <is>
-          <t>67230192.94011143</t>
+          <t>67197049.88125001</t>
         </is>
       </c>
       <c r="BJ15" t="inlineStr">
         <is>
-          <t>37931209.0</t>
+          <t>22368625.0</t>
         </is>
       </c>
       <c r="BK15" t="n">
-        <v>28647934.4</v>
+        <v>28384364.6</v>
       </c>
       <c r="BL15" t="inlineStr">
         <is>
-          <t>39410503.3</t>
+          <t>32361196.0</t>
         </is>
       </c>
       <c r="BM15" t="n">
-        <v>44290902.44</v>
+        <v>43621757.96</v>
       </c>
       <c r="BN15" t="inlineStr">
         <is>
-          <t>-10762568</t>
+          <t>-3976831</t>
         </is>
       </c>
       <c r="BO15" t="inlineStr">
         <is>
-          <t>-1688556.939682189</t>
+          <t>-2027461.514442288</t>
         </is>
       </c>
       <c r="BP15" t="inlineStr">
         <is>
-          <t>-3315366.983263746</t>
+          <t>-3891436.675622828</t>
         </is>
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>37931209.0</t>
+          <t>22368625.0</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
@@ -7609,7 +7609,7 @@
       </c>
       <c r="BU15" t="inlineStr">
         <is>
-          <t>-24.08</t>
+          <t>-23.18</t>
         </is>
       </c>
       <c r="BV15" t="inlineStr">
@@ -7654,7 +7654,7 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
@@ -7664,12 +7664,12 @@
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>6.55</t>
+          <t>6.71</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -7679,7 +7679,7 @@
       </c>
       <c r="CI15" t="inlineStr">
         <is>
-          <t>21.67</t>
+          <t>21.17</t>
         </is>
       </c>
       <c r="CJ15" t="inlineStr">
@@ -7694,12 +7694,12 @@
       </c>
       <c r="CL15" t="inlineStr">
         <is>
-          <t>55.16</t>
+          <t>53.39</t>
         </is>
       </c>
       <c r="CM15" t="inlineStr">
         <is>
-          <t>16275</t>
+          <t>15896</t>
         </is>
       </c>
       <c r="CN15" t="inlineStr">
@@ -7719,22 +7719,22 @@
       </c>
       <c r="CQ15" t="inlineStr">
         <is>
-          <t>67.5</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="CR15" t="inlineStr">
         <is>
-          <t>68.3</t>
+          <t>68.6</t>
         </is>
       </c>
       <c r="CS15" t="inlineStr">
         <is>
-          <t>67.5</t>
+          <t>67.7</t>
         </is>
       </c>
       <c r="CT15" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>68.6</t>
         </is>
       </c>
       <c r="CU15" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>645.775</t>
+          <t>558.986</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -7781,7 +7781,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -7791,17 +7791,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-36.06</t>
+          <t>-27.31</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7866,7 +7866,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-31.03</t>
+          <t>-31.24</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7891,7 +7891,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -7941,17 +7941,17 @@
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>34.31</t>
+          <t>29.70</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
@@ -7962,12 +7962,12 @@
       <c r="AP16" t="inlineStr"/>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>261</t>
+          <t>839</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7977,51 +7977,51 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>17.09</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="AU16" t="n">
-        <v>-1.56</v>
+        <v>-1.37</v>
       </c>
       <c r="AV16" t="n">
-        <v>-2.8</v>
+        <v>-2.7</v>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>-8.65</t>
+          <t>-8.8</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>-1.98</t>
+          <t>-2.19</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>69.08</t>
+          <t>68.74</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>71.06999999999999</v>
+        <v>70.65000000000001</v>
       </c>
       <c r="BA16" t="n">
-        <v>77.8</v>
+        <v>77.45999999999999</v>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>79.37</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>4.07</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="BD16" t="n">
-        <v>-2.6</v>
+        <v>-2.57</v>
       </c>
       <c r="BE16" t="n">
-        <v>-2.71</v>
+        <v>-2.68</v>
       </c>
       <c r="BF16" t="inlineStr">
         <is>
@@ -8030,7 +8030,7 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>-256.17</t>
+          <t>-254.62</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -8040,43 +8040,43 @@
       </c>
       <c r="BI16" t="inlineStr">
         <is>
-          <t>67230192.94011143</t>
+          <t>67197049.88125001</t>
         </is>
       </c>
       <c r="BJ16" t="inlineStr">
         <is>
-          <t>44075659.0</t>
+          <t>37931209.0</t>
         </is>
       </c>
       <c r="BK16" t="n">
-        <v>25827808.6</v>
+        <v>28647934.4</v>
       </c>
       <c r="BL16" t="inlineStr">
         <is>
-          <t>40393503.0</t>
+          <t>39410503.3</t>
         </is>
       </c>
       <c r="BM16" t="n">
-        <v>45004981.12</v>
+        <v>44290902.44</v>
       </c>
       <c r="BN16" t="inlineStr">
         <is>
-          <t>-14565694</t>
+          <t>-10762568</t>
         </is>
       </c>
       <c r="BO16" t="inlineStr">
         <is>
-          <t>-1392773.295394634</t>
+          <t>-1688556.939682189</t>
         </is>
       </c>
       <c r="BP16" t="inlineStr">
         <is>
-          <t>-4041424.030491352</t>
+          <t>-3315366.983263746</t>
         </is>
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>44075659.0</t>
+          <t>37931209.0</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
@@ -8096,7 +8096,7 @@
       </c>
       <c r="BU16" t="inlineStr">
         <is>
-          <t>-23.85</t>
+          <t>-24.08</t>
         </is>
       </c>
       <c r="BV16" t="inlineStr">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>6.55</t>
+          <t>6.71</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -8166,7 +8166,7 @@
       </c>
       <c r="CI16" t="inlineStr">
         <is>
-          <t>21.67</t>
+          <t>21.17</t>
         </is>
       </c>
       <c r="CJ16" t="inlineStr">
@@ -8181,12 +8181,12 @@
       </c>
       <c r="CL16" t="inlineStr">
         <is>
-          <t>55.16</t>
+          <t>53.39</t>
         </is>
       </c>
       <c r="CM16" t="inlineStr">
         <is>
-          <t>16275</t>
+          <t>15896</t>
         </is>
       </c>
       <c r="CN16" t="inlineStr">
@@ -8206,22 +8206,22 @@
       </c>
       <c r="CQ16" t="inlineStr">
         <is>
-          <t>69.2</t>
+          <t>67.5</t>
         </is>
       </c>
       <c r="CR16" t="inlineStr">
         <is>
-          <t>69.2</t>
+          <t>68.3</t>
         </is>
       </c>
       <c r="CS16" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>67.5</t>
         </is>
       </c>
       <c r="CT16" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="CU16" t="inlineStr">
@@ -8253,12 +8253,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>242.836</t>
+          <t>645.775</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -8268,7 +8268,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -8278,17 +8278,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-36.13</t>
+          <t>-36.06</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -8353,7 +8353,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-30.02</t>
+          <t>-31.03</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -8378,7 +8378,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -8428,17 +8428,17 @@
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>12.90</t>
+          <t>34.31</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
@@ -8449,66 +8449,66 @@
       <c r="AP17" t="inlineStr"/>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>261</t>
+          <t>839</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>29.21</t>
+          <t>17.09</t>
         </is>
       </c>
       <c r="AU17" t="n">
-        <v>-0.49</v>
+        <v>-1.56</v>
       </c>
       <c r="AV17" t="n">
-        <v>-3.05</v>
+        <v>-2.8</v>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>-8.4</t>
+          <t>-8.65</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>-1.98</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>69.34</t>
+          <t>69.08</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>71.53</v>
+        <v>71.06999999999999</v>
       </c>
       <c r="BA17" t="n">
-        <v>78.09</v>
+        <v>77.8</v>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>79.54</t>
+          <t>79.37</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>4.56</t>
+          <t>4.07</t>
         </is>
       </c>
       <c r="BD17" t="n">
-        <v>-2.61</v>
+        <v>-2.6</v>
       </c>
       <c r="BE17" t="n">
-        <v>-2.73</v>
+        <v>-2.71</v>
       </c>
       <c r="BF17" t="inlineStr">
         <is>
@@ -8517,7 +8517,7 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>-257.76</t>
+          <t>-256.17</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -8527,43 +8527,43 @@
       </c>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>67230192.94011143</t>
+          <t>67197049.88125001</t>
         </is>
       </c>
       <c r="BJ17" t="inlineStr">
         <is>
-          <t>16784435.0</t>
+          <t>44075659.0</t>
         </is>
       </c>
       <c r="BK17" t="n">
-        <v>24770508.8</v>
+        <v>25827808.6</v>
       </c>
       <c r="BL17" t="inlineStr">
         <is>
-          <t>38781600.1</t>
+          <t>40393503.0</t>
         </is>
       </c>
       <c r="BM17" t="n">
-        <v>44611489.72</v>
+        <v>45004981.12</v>
       </c>
       <c r="BN17" t="inlineStr">
         <is>
-          <t>-14011091</t>
+          <t>-14565694</t>
         </is>
       </c>
       <c r="BO17" t="inlineStr">
         <is>
-          <t>-911200.4344679575</t>
+          <t>-1392773.295394634</t>
         </is>
       </c>
       <c r="BP17" t="inlineStr">
         <is>
-          <t>-5592645.739727527</t>
+          <t>-4041424.030491352</t>
         </is>
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>16784435.0</t>
+          <t>44075659.0</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
@@ -8583,7 +8583,7 @@
       </c>
       <c r="BU17" t="inlineStr">
         <is>
-          <t>-22.73</t>
+          <t>-23.85</t>
         </is>
       </c>
       <c r="BV17" t="inlineStr">
@@ -8628,22 +8628,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>6.55</t>
+          <t>6.71</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -8653,7 +8653,7 @@
       </c>
       <c r="CI17" t="inlineStr">
         <is>
-          <t>21.67</t>
+          <t>21.17</t>
         </is>
       </c>
       <c r="CJ17" t="inlineStr">
@@ -8668,12 +8668,12 @@
       </c>
       <c r="CL17" t="inlineStr">
         <is>
-          <t>55.16</t>
+          <t>53.39</t>
         </is>
       </c>
       <c r="CM17" t="inlineStr">
         <is>
-          <t>16275</t>
+          <t>15896</t>
         </is>
       </c>
       <c r="CN17" t="inlineStr">
@@ -8693,22 +8693,22 @@
       </c>
       <c r="CQ17" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>69.2</t>
         </is>
       </c>
       <c r="CR17" t="inlineStr">
         <is>
-          <t>69.5</t>
+          <t>69.2</t>
         </is>
       </c>
       <c r="CS17" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="CT17" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="CU17" t="inlineStr">
@@ -8745,7 +8745,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>299.387</t>
+          <t>242.836</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -8755,7 +8755,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>69.3</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -8765,17 +8765,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-2.83</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-33.41</t>
+          <t>-36.13</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -8840,7 +8840,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-29.72</t>
+          <t>-30.02</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -8865,7 +8865,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -8915,17 +8915,17 @@
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>15.91</t>
+          <t>12.90</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
@@ -8936,66 +8936,66 @@
       <c r="AP18" t="inlineStr"/>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>261</t>
+          <t>839</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>27.27</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>32.32</t>
+          <t>29.21</t>
         </is>
       </c>
       <c r="AU18" t="n">
-        <v>0.09</v>
+        <v>-0.49</v>
       </c>
       <c r="AV18" t="n">
-        <v>-3.75</v>
+        <v>-3.05</v>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>-8.16</t>
+          <t>-8.4</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>-1.71</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>69.24</t>
+          <t>69.34</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>71.94</v>
+        <v>71.53</v>
       </c>
       <c r="BA18" t="n">
-        <v>78.34</v>
+        <v>78.09</v>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>79.54</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>2.73</t>
+          <t>4.56</t>
         </is>
       </c>
       <c r="BD18" t="n">
-        <v>-2.69</v>
+        <v>-2.61</v>
       </c>
       <c r="BE18" t="n">
-        <v>-2.77</v>
+        <v>-2.73</v>
       </c>
       <c r="BF18" t="inlineStr">
         <is>
@@ -9004,7 +9004,7 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>-259.56</t>
+          <t>-257.76</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -9014,43 +9014,43 @@
       </c>
       <c r="BI18" t="inlineStr">
         <is>
-          <t>67230192.94011143</t>
+          <t>67197049.88125001</t>
         </is>
       </c>
       <c r="BJ18" t="inlineStr">
         <is>
-          <t>20761895.0</t>
+          <t>16784435.0</t>
         </is>
       </c>
       <c r="BK18" t="n">
-        <v>26617218.6</v>
+        <v>24770508.8</v>
       </c>
       <c r="BL18" t="inlineStr">
         <is>
-          <t>39969195.1</t>
+          <t>38781600.1</t>
         </is>
       </c>
       <c r="BM18" t="n">
-        <v>44662589.56</v>
+        <v>44611489.72</v>
       </c>
       <c r="BN18" t="inlineStr">
         <is>
-          <t>-13351976</t>
+          <t>-14011091</t>
         </is>
       </c>
       <c r="BO18" t="inlineStr">
         <is>
-          <t>-60028.56078439939</t>
+          <t>-911200.4344679575</t>
         </is>
       </c>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>-4684879.690788925</t>
+          <t>-5592645.739727527</t>
         </is>
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>20761895.0</t>
+          <t>16784435.0</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
@@ -9070,7 +9070,7 @@
       </c>
       <c r="BU18" t="inlineStr">
         <is>
-          <t>-22.40</t>
+          <t>-22.73</t>
         </is>
       </c>
       <c r="BV18" t="inlineStr">
@@ -9115,22 +9115,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>6.55</t>
+          <t>6.71</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -9140,7 +9140,7 @@
       </c>
       <c r="CI18" t="inlineStr">
         <is>
-          <t>21.67</t>
+          <t>21.17</t>
         </is>
       </c>
       <c r="CJ18" t="inlineStr">
@@ -9155,12 +9155,12 @@
       </c>
       <c r="CL18" t="inlineStr">
         <is>
-          <t>55.16</t>
+          <t>53.39</t>
         </is>
       </c>
       <c r="CM18" t="inlineStr">
         <is>
-          <t>16275</t>
+          <t>15896</t>
         </is>
       </c>
       <c r="CN18" t="inlineStr">
@@ -9180,22 +9180,22 @@
       </c>
       <c r="CQ18" t="inlineStr">
         <is>
+          <t>69.0</t>
+        </is>
+      </c>
+      <c r="CR18" t="inlineStr">
+        <is>
           <t>69.5</t>
         </is>
       </c>
-      <c r="CR18" t="inlineStr">
-        <is>
-          <t>69.8</t>
-        </is>
-      </c>
       <c r="CS18" t="inlineStr">
         <is>
-          <t>68.8</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="CT18" t="inlineStr">
         <is>
-          <t>69.3</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="CU18" t="inlineStr">
@@ -9227,12 +9227,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>339.165</t>
+          <t>299.387</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -9242,7 +9242,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>69.6</t>
+          <t>69.3</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -9252,17 +9252,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>-3.28</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-11.75</t>
+          <t>-33.41</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -9327,7 +9327,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-29.41</t>
+          <t>-29.72</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -9352,7 +9352,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -9402,17 +9402,17 @@
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>18.02</t>
+          <t>15.91</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
@@ -9423,17 +9423,17 @@
       <c r="AP19" t="inlineStr"/>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>261</t>
+          <t>839</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>36.36</t>
+          <t>27.27</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr">
@@ -9442,47 +9442,47 @@
         </is>
       </c>
       <c r="AU19" t="n">
-        <v>0.78</v>
+        <v>0.09</v>
       </c>
       <c r="AV19" t="n">
-        <v>-4.64</v>
+        <v>-3.75</v>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>-7.84</t>
+          <t>-8.16</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>-1.60</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>69.06</t>
+          <t>69.24</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>72.42</v>
+        <v>71.94</v>
       </c>
       <c r="BA19" t="n">
-        <v>78.58</v>
+        <v>78.34</v>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>79.85</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>2.73</t>
         </is>
       </c>
       <c r="BD19" t="n">
-        <v>-2.78</v>
+        <v>-2.69</v>
       </c>
       <c r="BE19" t="n">
-        <v>-2.78</v>
+        <v>-2.77</v>
       </c>
       <c r="BF19" t="inlineStr">
         <is>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>-260.64</t>
+          <t>-259.56</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -9501,43 +9501,43 @@
       </c>
       <c r="BI19" t="inlineStr">
         <is>
-          <t>67230192.94011143</t>
+          <t>67197049.88125001</t>
         </is>
       </c>
       <c r="BJ19" t="inlineStr">
         <is>
-          <t>23686474.0</t>
+          <t>20761895.0</t>
         </is>
       </c>
       <c r="BK19" t="n">
-        <v>36338027.4</v>
+        <v>26617218.6</v>
       </c>
       <c r="BL19" t="inlineStr">
         <is>
-          <t>41176634.1</t>
+          <t>39969195.1</t>
         </is>
       </c>
       <c r="BM19" t="n">
-        <v>44635885.7</v>
+        <v>44662589.56</v>
       </c>
       <c r="BN19" t="inlineStr">
         <is>
-          <t>-4838606</t>
+          <t>-13351976</t>
         </is>
       </c>
       <c r="BO19" t="inlineStr">
         <is>
-          <t>780853.4628527871</t>
+          <t>-60028.56078439939</t>
         </is>
       </c>
       <c r="BP19" t="inlineStr">
         <is>
-          <t>-3646910.346205607</t>
+          <t>-4684879.690788925</t>
         </is>
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>23686474.0</t>
+          <t>20761895.0</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
@@ -9557,7 +9557,7 @@
       </c>
       <c r="BU19" t="inlineStr">
         <is>
-          <t>-22.06</t>
+          <t>-22.40</t>
         </is>
       </c>
       <c r="BV19" t="inlineStr">
@@ -9602,22 +9602,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>6.55</t>
+          <t>6.71</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -9627,7 +9627,7 @@
       </c>
       <c r="CI19" t="inlineStr">
         <is>
-          <t>21.67</t>
+          <t>21.17</t>
         </is>
       </c>
       <c r="CJ19" t="inlineStr">
@@ -9642,12 +9642,12 @@
       </c>
       <c r="CL19" t="inlineStr">
         <is>
-          <t>55.16</t>
+          <t>53.39</t>
         </is>
       </c>
       <c r="CM19" t="inlineStr">
         <is>
-          <t>16275</t>
+          <t>15896</t>
         </is>
       </c>
       <c r="CN19" t="inlineStr">
@@ -9672,17 +9672,17 @@
       </c>
       <c r="CR19" t="inlineStr">
         <is>
-          <t>70.3</t>
+          <t>69.8</t>
         </is>
       </c>
       <c r="CS19" t="inlineStr">
         <is>
+          <t>68.8</t>
+        </is>
+      </c>
+      <c r="CT19" t="inlineStr">
+        <is>
           <t>69.3</t>
-        </is>
-      </c>
-      <c r="CT19" t="inlineStr">
-        <is>
-          <t>69.6</t>
         </is>
       </c>
       <c r="CU19" t="inlineStr">
@@ -9704,7 +9704,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -9714,12 +9714,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>342.577</t>
+          <t>339.165</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -9729,7 +9729,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>69.5</t>
+          <t>69.6</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -9739,17 +9739,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-1.16</t>
+          <t>-3.73</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>13.93</t>
+          <t>-11.75</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-29.51</t>
+          <t>-29.41</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -9839,7 +9839,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -9889,17 +9889,17 @@
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>18.20</t>
+          <t>18.02</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
@@ -9910,63 +9910,63 @@
       <c r="AP20" t="inlineStr"/>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>261</t>
+          <t>839</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>36.36</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>21.21</t>
+          <t>32.32</t>
         </is>
       </c>
       <c r="AU20" t="n">
-        <v>0.52</v>
+        <v>0.78</v>
       </c>
       <c r="AV20" t="n">
-        <v>-5.21</v>
+        <v>-4.64</v>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>-7.47</t>
+          <t>-7.84</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>-1.60</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>69.14000000000001</t>
+          <t>69.06</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>72.94</v>
+        <v>72.42</v>
       </c>
       <c r="BA20" t="n">
-        <v>78.83</v>
+        <v>78.58</v>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>80.02</t>
+          <t>79.85</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>-3.95</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BD20" t="n">
-        <v>-2.89</v>
+        <v>-2.78</v>
       </c>
       <c r="BE20" t="n">
         <v>-2.78</v>
@@ -9988,43 +9988,43 @@
       </c>
       <c r="BI20" t="inlineStr">
         <is>
-          <t>67230192.94011143</t>
+          <t>67197049.88125001</t>
         </is>
       </c>
       <c r="BJ20" t="inlineStr">
         <is>
-          <t>23830580.0</t>
+          <t>23686474.0</t>
         </is>
       </c>
       <c r="BK20" t="n">
-        <v>50173072.2</v>
+        <v>36338027.4</v>
       </c>
       <c r="BL20" t="inlineStr">
         <is>
-          <t>44037538.5</t>
+          <t>41176634.1</t>
         </is>
       </c>
       <c r="BM20" t="n">
-        <v>44370710.28</v>
+        <v>44635885.7</v>
       </c>
       <c r="BN20" t="inlineStr">
         <is>
-          <t>6135533</t>
+          <t>-4838606</t>
         </is>
       </c>
       <c r="BO20" t="inlineStr">
         <is>
-          <t>1585901.428136131</t>
+          <t>780853.4628527871</t>
         </is>
       </c>
       <c r="BP20" t="inlineStr">
         <is>
-          <t>-2347197.948722087</t>
+          <t>-3646910.346205607</t>
         </is>
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>23830580.0</t>
+          <t>23686474.0</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
@@ -10044,7 +10044,7 @@
       </c>
       <c r="BU20" t="inlineStr">
         <is>
-          <t>-22.17</t>
+          <t>-22.06</t>
         </is>
       </c>
       <c r="BV20" t="inlineStr">
@@ -10089,12 +10089,12 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
@@ -10104,7 +10104,7 @@
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>6.55</t>
+          <t>6.71</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -10114,7 +10114,7 @@
       </c>
       <c r="CI20" t="inlineStr">
         <is>
-          <t>21.67</t>
+          <t>21.17</t>
         </is>
       </c>
       <c r="CJ20" t="inlineStr">
@@ -10129,12 +10129,12 @@
       </c>
       <c r="CL20" t="inlineStr">
         <is>
-          <t>55.16</t>
+          <t>53.39</t>
         </is>
       </c>
       <c r="CM20" t="inlineStr">
         <is>
-          <t>16275</t>
+          <t>15896</t>
         </is>
       </c>
       <c r="CN20" t="inlineStr">
@@ -10159,17 +10159,17 @@
       </c>
       <c r="CR20" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>70.3</t>
         </is>
       </c>
       <c r="CS20" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>69.3</t>
         </is>
       </c>
       <c r="CT20" t="inlineStr">
         <is>
-          <t>69.5</t>
+          <t>69.6</t>
         </is>
       </c>
       <c r="CU20" t="inlineStr">
@@ -10201,12 +10201,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>563.0</t>
+          <t>342.577</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -10216,7 +10216,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>69.3</t>
+          <t>69.5</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -10226,17 +10226,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-3.58</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>13.93</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -10301,7 +10301,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-29.72</t>
+          <t>-29.51</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -10326,7 +10326,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -10376,17 +10376,17 @@
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>29.91</t>
+          <t>18.20</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
@@ -10397,66 +10397,66 @@
       <c r="AP21" t="inlineStr"/>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>261</t>
+          <t>839</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
         <is>
-          <t>27.27</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>21.21</t>
         </is>
       </c>
       <c r="AU21" t="n">
-        <v>-0.17</v>
+        <v>0.52</v>
       </c>
       <c r="AV21" t="n">
-        <v>-5.51</v>
+        <v>-5.21</v>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>-7.09</t>
+          <t>-7.47</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>69.42</t>
+          <t>69.14000000000001</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>73.47</v>
+        <v>72.94</v>
       </c>
       <c r="BA21" t="n">
-        <v>79.06999999999999</v>
+        <v>78.83</v>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>80.17</t>
+          <t>80.02</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>-8.19</t>
+          <t>-3.95</t>
         </is>
       </c>
       <c r="BD21" t="n">
-        <v>-2.98</v>
+        <v>-2.89</v>
       </c>
       <c r="BE21" t="n">
-        <v>-2.76</v>
+        <v>-2.78</v>
       </c>
       <c r="BF21" t="inlineStr">
         <is>
@@ -10465,7 +10465,7 @@
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>-259.06</t>
+          <t>-260.64</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
@@ -10475,43 +10475,43 @@
       </c>
       <c r="BI21" t="inlineStr">
         <is>
-          <t>67230192.94011143</t>
+          <t>67197049.88125001</t>
         </is>
       </c>
       <c r="BJ21" t="inlineStr">
         <is>
-          <t>38789160.0</t>
+          <t>23830580.0</t>
         </is>
       </c>
       <c r="BK21" t="n">
-        <v>54959197.4</v>
+        <v>50173072.2</v>
       </c>
       <c r="BL21" t="inlineStr">
         <is>
-          <t>54407795.1</t>
+          <t>44037538.5</t>
         </is>
       </c>
       <c r="BM21" t="n">
-        <v>44300854.06</v>
+        <v>44370710.28</v>
       </c>
       <c r="BN21" t="inlineStr">
         <is>
-          <t>551402</t>
+          <t>6135533</t>
         </is>
       </c>
       <c r="BO21" t="inlineStr">
         <is>
-          <t>2301010.405746717</t>
+          <t>1585901.428136131</t>
         </is>
       </c>
       <c r="BP21" t="inlineStr">
         <is>
-          <t>-422077.382719852</t>
+          <t>-2347197.948722087</t>
         </is>
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>38789160.0</t>
+          <t>23830580.0</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -10531,7 +10531,7 @@
       </c>
       <c r="BU21" t="inlineStr">
         <is>
-          <t>-22.40</t>
+          <t>-22.17</t>
         </is>
       </c>
       <c r="BV21" t="inlineStr">
@@ -10576,22 +10576,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>6.55</t>
+          <t>6.71</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -10601,7 +10601,7 @@
       </c>
       <c r="CI21" t="inlineStr">
         <is>
-          <t>21.67</t>
+          <t>21.17</t>
         </is>
       </c>
       <c r="CJ21" t="inlineStr">
@@ -10616,12 +10616,12 @@
       </c>
       <c r="CL21" t="inlineStr">
         <is>
-          <t>55.16</t>
+          <t>53.39</t>
         </is>
       </c>
       <c r="CM21" t="inlineStr">
         <is>
-          <t>16275</t>
+          <t>15896</t>
         </is>
       </c>
       <c r="CN21" t="inlineStr">
@@ -10641,22 +10641,22 @@
       </c>
       <c r="CQ21" t="inlineStr">
         <is>
-          <t>68.6</t>
+          <t>69.5</t>
         </is>
       </c>
       <c r="CR21" t="inlineStr">
         <is>
-          <t>69.4</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="CS21" t="inlineStr">
         <is>
-          <t>68.3</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="CT21" t="inlineStr">
         <is>
-          <t>69.3</t>
+          <t>69.5</t>
         </is>
       </c>
       <c r="CU21" t="inlineStr">
@@ -10678,22 +10678,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>1723</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>379.745</t>
+          <t>37995.984</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -10703,7 +10703,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>68.5</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -10713,17 +10713,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-8.80</t>
+          <t>22.11</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -10733,37 +10733,37 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-100.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2025-02-26 00:00:00</t>
+          <t>2025-11-27 00:00:00</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>2025-03-12 00:00:00</t>
+          <t>2025-12-10 00:00:00</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>2024-03-28 00:00:00</t>
+          <t>2025-11-11 00:00:00</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>2024-04-02 00:00:00</t>
+          <t>2025-11-26 00:00:00</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>99.1</t>
+          <t>56.2</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>98.6</t>
+          <t>61.4</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -10773,12 +10773,12 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>123.5</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>118.0</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
@@ -10788,22 +10788,22 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-30.53</t>
+          <t>-6.35</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>-16.02</t>
+          <t>9.98</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025/06/02</t>
+          <t>2025/07/28</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>92.4</t>
+          <t>37.0</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -10813,67 +10813,67 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>2025/11/13</t>
+          <t>2025/09/26</t>
         </is>
       </c>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>79.9</t>
+          <t>39.6</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>2025/06/20</t>
+          <t>2025/04/08</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>90.1</t>
+          <t>28.85</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>2025/10/23</t>
+          <t>2025/12/10</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>61.4</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>2025/07/31</t>
+          <t>2025/11/26</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>86.9</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>2025-11-28 00:00:00</t>
+          <t>2025-11-10 00:00:00</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>20.18</t>
+          <t>11.28</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>-2.96</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
@@ -10884,121 +10884,121 @@
       <c r="AP22" t="inlineStr"/>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>440</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>261</t>
+          <t>37996</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>19.99</t>
         </is>
       </c>
       <c r="AU22" t="n">
-        <v>-2</v>
+        <v>-2.44</v>
       </c>
       <c r="AV22" t="n">
-        <v>-5.54</v>
+        <v>-2.99</v>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>-6.72</t>
+          <t>15.7</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>-1.24</t>
+          <t>10.35</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>69.9</t>
+          <t>58.94</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>74</v>
+        <v>60.76</v>
       </c>
       <c r="BA22" t="n">
-        <v>79.33</v>
+        <v>52.51</v>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>80.33</t>
+          <t>47.59</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>-12.27</t>
+          <t>-40.98</t>
         </is>
       </c>
       <c r="BD22" t="n">
-        <v>-3.03</v>
+        <v>1.34</v>
       </c>
       <c r="BE22" t="n">
-        <v>-2.7</v>
+        <v>2.26</v>
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>4.51</t>
         </is>
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>-255.80</t>
+          <t>-49.81</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2025/12/15</t>
+          <t>2025/11/27</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
         <is>
-          <t>67230192.94011143</t>
+          <t>1598977155.522917</t>
         </is>
       </c>
       <c r="BJ22" t="inlineStr">
         <is>
-          <t>26017984.0</t>
+          <t>2204976767.0</t>
         </is>
       </c>
       <c r="BK22" t="n">
-        <v>52792691.4</v>
+        <v>4154560976.4</v>
       </c>
       <c r="BL22" t="inlineStr">
         <is>
-          <t>57889533.1</t>
+          <t>3402420209.8</t>
         </is>
       </c>
       <c r="BM22" t="n">
-        <v>43830679.68</v>
+        <v>5711824024.86</v>
       </c>
       <c r="BN22" t="inlineStr">
         <is>
-          <t>-5096841</t>
+          <t>752140766</t>
         </is>
       </c>
       <c r="BO22" t="inlineStr">
         <is>
-          <t>2796117.276377002</t>
+          <t>-639556274.0913253</t>
         </is>
       </c>
       <c r="BP22" t="inlineStr">
         <is>
-          <t>740464.04666619</t>
+          <t>-835422234.4695697</t>
         </is>
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>26017984.0</t>
+          <t>2204976767.0</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -11008,32 +11008,32 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>41.9</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>2025/10/15</t>
+          <t>2025/10/21</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
         <is>
-          <t>-23.29</t>
+          <t>37.23</t>
         </is>
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>中碳</t>
+          <t>南亞</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
         <is>
-          <t>中碳</t>
+          <t>南亞</t>
         </is>
       </c>
       <c r="BX22" t="inlineStr">
         <is>
-          <t>化學工業</t>
+          <t>塑膠工業</t>
         </is>
       </c>
       <c r="BY22" t="inlineStr">
@@ -11043,27 +11043,27 @@
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
         <is>
-          <t>-7.32116827620037</t>
+          <t>-4.249662585945642</t>
         </is>
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>-26.54178546817805</t>
+          <t>-6.718506037644686</t>
         </is>
       </c>
       <c r="CC22" t="inlineStr">
         <is>
-          <t>-23.30870698662894</t>
+          <t>1.146736876787111</t>
         </is>
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
@@ -11073,87 +11073,87 @@
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>6.55</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
         <is>
-          <t>5.94</t>
+          <t>8.09</t>
         </is>
       </c>
       <c r="CI22" t="inlineStr">
         <is>
-          <t>21.67</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CJ22" t="inlineStr">
         <is>
-          <t>17.52%</t>
+          <t>8.29%</t>
         </is>
       </c>
       <c r="CK22" t="inlineStr">
         <is>
-          <t>6.35%</t>
+          <t>1.61%</t>
         </is>
       </c>
       <c r="CL22" t="inlineStr">
         <is>
-          <t>55.16</t>
+          <t>63.34</t>
         </is>
       </c>
       <c r="CM22" t="inlineStr">
         <is>
-          <t>16275</t>
+          <t>456022</t>
         </is>
       </c>
       <c r="CN22" t="inlineStr">
         <is>
-          <t>煤焦油及化學品系列產品53.20%、輕油及油品系列產品29.03%、精碳材料9.72%、焦碳製品6.62%、其他1.43% (2024年)</t>
+          <t>聚酯纖維16.60%、其他16.28%、印刷電路板(PCB)12.09%、銅箔基板(CCL)10.47%、環氧樹脂8.29%、丙二酚(BPA)5.67%、乙二醇(EG)5.60%、銅箔5.01%、可塑劑(DOP)及硬化劑3.38%、硬質管2.55%、硬質膠布2.48%、塑膠門窗2.20%、軟質膠布1.85%、麩酸酐(PA)1.55%、玻璃纖維布1.32%、聚酯薄膜1.30%、膠乳皮0.92%、PU合成皮(人造皮)0.69%、BOPP膜0.64%、玻璃纖維絲0.60%、丁二醇(BDO)0.54% (2024年)</t>
         </is>
       </c>
       <c r="CO22" t="inlineStr">
         <is>
-          <t>中碳-化學工業-上市</t>
+          <t>南亞-塑膠工業-上市</t>
         </is>
       </c>
       <c r="CP22" t="inlineStr">
         <is>
-          <t>化學工業右下上市</t>
+          <t>塑膠工業平上市</t>
         </is>
       </c>
       <c r="CQ22" t="inlineStr">
         <is>
-          <t>68.1</t>
+          <t>58.8</t>
         </is>
       </c>
       <c r="CR22" t="inlineStr">
         <is>
-          <t>68.8</t>
+          <t>59.2</t>
         </is>
       </c>
       <c r="CS22" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="CT22" t="inlineStr">
         <is>
-          <t>68.5</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="CU22" t="inlineStr">
         <is>
-          <t>33.12</t>
+          <t>41.48</t>
         </is>
       </c>
       <c r="CV22" t="inlineStr">
         <is>
-          <t>** 石化及塑橡膠 - 石化上游原料及相關鑽探設備** 電動車輛產業 - 鋰電池材料** 能源元件 - 原材料</t>
+          <t>** 印刷電路板 - 玻璃纖維/玻纖布、環氧樹脂、酚醛樹脂、銅箔、銅箔基板** 石化及塑橡膠 - 石化上游原料及相關鑽探設備、人造纖維** 紡織 - 石化原料(例如純對苯二甲酸、乙二醇、己內醯胺、丙烯腈等)、人造纖維產品(例如尼龍纖維、聚酯纖維、嫘縈纖維等)、染整** 電機機械 - 電控元件、機械設備之沖壓零組件</t>
         </is>
       </c>
       <c r="CW22" t="inlineStr">
@@ -11165,22 +11165,22 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>1723</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-2.3</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1010.558</t>
+          <t>51548.933</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -11190,7 +11190,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>68.4</t>
+          <t>58.1</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -11200,17 +11200,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-16.07</t>
+          <t>17.04</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -11220,37 +11220,37 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>-100.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2025-02-26 00:00:00</t>
+          <t>2025-11-27 00:00:00</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>2025-03-12 00:00:00</t>
+          <t>2025-12-10 00:00:00</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>2024-03-28 00:00:00</t>
+          <t>2025-11-11 00:00:00</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>2024-04-02 00:00:00</t>
+          <t>2025-11-26 00:00:00</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>99.1</t>
+          <t>56.2</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>98.6</t>
+          <t>61.4</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -11260,12 +11260,12 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>123.5</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>118.0</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
@@ -11275,22 +11275,22 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-30.63</t>
+          <t>-5.37</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>-16.02</t>
+          <t>9.98</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025/06/02</t>
+          <t>2025/07/28</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>92.4</t>
+          <t>37.0</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -11300,67 +11300,67 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>2025/11/13</t>
+          <t>2025/09/26</t>
         </is>
       </c>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>79.9</t>
+          <t>39.6</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>2025/06/20</t>
+          <t>2025/04/08</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>90.1</t>
+          <t>28.85</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>2025/10/23</t>
+          <t>2025/12/10</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>61.4</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>2025/07/31</t>
+          <t>2025/11/26</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>86.9</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>2025-11-28 00:00:00</t>
+          <t>2025-11-10 00:00:00</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>53.70</t>
+          <t>15.30</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>-4.99</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
@@ -11371,121 +11371,121 @@
       <c r="AP23" t="inlineStr"/>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>440</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>261</t>
+          <t>37996</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>18.92</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>43.92</t>
         </is>
       </c>
       <c r="AU23" t="n">
-        <v>-2.84</v>
+        <v>-1.39</v>
       </c>
       <c r="AV23" t="n">
-        <v>-5.6</v>
+        <v>-2.92</v>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>-6.29</t>
+          <t>16.32</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>10.05</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>70.4</t>
+          <t>58.92</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>74.58</v>
+        <v>60.69</v>
       </c>
       <c r="BA23" t="n">
-        <v>79.59</v>
+        <v>52.17</v>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>80.51</t>
+          <t>47.41</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>-13.42</t>
+          <t>-36.04</t>
         </is>
       </c>
       <c r="BD23" t="n">
-        <v>-2.97</v>
+        <v>1.6</v>
       </c>
       <c r="BE23" t="n">
-        <v>-2.62</v>
+        <v>2.49</v>
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>4.51</t>
         </is>
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>-251.02</t>
+          <t>-44.66</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2025/12/15</t>
+          <t>2025/11/27</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
         <is>
-          <t>67230192.94011143</t>
+          <t>1598977155.522917</t>
         </is>
       </c>
       <c r="BJ23" t="inlineStr">
         <is>
-          <t>69365939.0</t>
+          <t>3040538846.0</t>
         </is>
       </c>
       <c r="BK23" t="n">
-        <v>53321171.6</v>
+        <v>4242264725.6</v>
       </c>
       <c r="BL23" t="inlineStr">
         <is>
-          <t>63533239.1</t>
+          <t>3624559420.8</t>
         </is>
       </c>
       <c r="BM23" t="n">
-        <v>43619025.94</v>
+        <v>5691886697.32</v>
       </c>
       <c r="BN23" t="inlineStr">
         <is>
-          <t>-10212067</t>
+          <t>617705304</t>
         </is>
       </c>
       <c r="BO23" t="inlineStr">
         <is>
-          <t>3169872.409051695</t>
+          <t>-603944281.2952808</t>
         </is>
       </c>
       <c r="BP23" t="inlineStr">
         <is>
-          <t>3743132.658408165</t>
+          <t>-775145884.3949137</t>
         </is>
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>69365939.0</t>
+          <t>3040538846.0</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -11495,32 +11495,32 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>41.9</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>2025/10/15</t>
+          <t>2025/10/21</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
         <is>
-          <t>-23.40</t>
+          <t>38.66</t>
         </is>
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>中碳</t>
+          <t>南亞</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
         <is>
-          <t>中碳</t>
+          <t>南亞</t>
         </is>
       </c>
       <c r="BX23" t="inlineStr">
         <is>
-          <t>化學工業</t>
+          <t>塑膠工業</t>
         </is>
       </c>
       <c r="BY23" t="inlineStr">
@@ -11530,117 +11530,117 @@
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
         <is>
-          <t>-7.32116827620037</t>
+          <t>-4.249662585945642</t>
         </is>
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>-26.54178546817805</t>
+          <t>-6.718506037644686</t>
         </is>
       </c>
       <c r="CC23" t="inlineStr">
         <is>
-          <t>-23.30870698662894</t>
+          <t>1.146736876787111</t>
         </is>
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>6.55</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">
         <is>
-          <t>5.94</t>
+          <t>8.09</t>
         </is>
       </c>
       <c r="CI23" t="inlineStr">
         <is>
-          <t>21.67</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CJ23" t="inlineStr">
         <is>
-          <t>17.52%</t>
+          <t>8.29%</t>
         </is>
       </c>
       <c r="CK23" t="inlineStr">
         <is>
-          <t>6.35%</t>
+          <t>1.61%</t>
         </is>
       </c>
       <c r="CL23" t="inlineStr">
         <is>
-          <t>55.16</t>
+          <t>63.34</t>
         </is>
       </c>
       <c r="CM23" t="inlineStr">
         <is>
-          <t>16275</t>
+          <t>456022</t>
         </is>
       </c>
       <c r="CN23" t="inlineStr">
         <is>
-          <t>煤焦油及化學品系列產品53.20%、輕油及油品系列產品29.03%、精碳材料9.72%、焦碳製品6.62%、其他1.43% (2024年)</t>
+          <t>聚酯纖維16.60%、其他16.28%、印刷電路板(PCB)12.09%、銅箔基板(CCL)10.47%、環氧樹脂8.29%、丙二酚(BPA)5.67%、乙二醇(EG)5.60%、銅箔5.01%、可塑劑(DOP)及硬化劑3.38%、硬質管2.55%、硬質膠布2.48%、塑膠門窗2.20%、軟質膠布1.85%、麩酸酐(PA)1.55%、玻璃纖維布1.32%、聚酯薄膜1.30%、膠乳皮0.92%、PU合成皮(人造皮)0.69%、BOPP膜0.64%、玻璃纖維絲0.60%、丁二醇(BDO)0.54% (2024年)</t>
         </is>
       </c>
       <c r="CO23" t="inlineStr">
         <is>
-          <t>中碳-化學工業-上市</t>
+          <t>南亞-塑膠工業-上市</t>
         </is>
       </c>
       <c r="CP23" t="inlineStr">
         <is>
-          <t>化學工業右下上市</t>
+          <t>塑膠工業平上市</t>
         </is>
       </c>
       <c r="CQ23" t="inlineStr">
         <is>
-          <t>69.5</t>
+          <t>59.7</t>
         </is>
       </c>
       <c r="CR23" t="inlineStr">
         <is>
-          <t>69.5</t>
+          <t>61.0</t>
         </is>
       </c>
       <c r="CS23" t="inlineStr">
         <is>
-          <t>68.2</t>
+          <t>58.1</t>
         </is>
       </c>
       <c r="CT23" t="inlineStr">
         <is>
-          <t>68.4</t>
+          <t>58.1</t>
         </is>
       </c>
       <c r="CU23" t="inlineStr">
         <is>
-          <t>33.12</t>
+          <t>41.48</t>
         </is>
       </c>
       <c r="CV23" t="inlineStr">
         <is>
-          <t>** 石化及塑橡膠 - 石化上游原料及相關鑽探設備** 電動車輛產業 - 鋰電池材料** 能源元件 - 原材料</t>
+          <t>** 印刷電路板 - 玻璃纖維/玻纖布、環氧樹脂、酚醛樹脂、銅箔、銅箔基板** 石化及塑橡膠 - 石化上游原料及相關鑽探設備、人造纖維** 紡織 - 石化原料(例如純對苯二甲酸、乙二醇、己內醯胺、丙烯腈等)、人造纖維產品(例如尼龍纖維、聚酯纖維、嫘縈纖維等)、染整** 電機機械 - 電控元件、機械設備之沖壓零組件</t>
         </is>
       </c>
       <c r="CW23" t="inlineStr">
@@ -11687,12 +11687,12 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-2.26</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>-3.63</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -11858,12 +11858,12 @@
       <c r="AP24" t="inlineStr"/>
       <c r="AQ24" t="inlineStr">
         <is>
-          <t>764</t>
+          <t>440</t>
         </is>
       </c>
       <c r="AR24" t="inlineStr">
         <is>
-          <t>62689</t>
+          <t>37996</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr">
@@ -11936,7 +11936,7 @@
       </c>
       <c r="BI24" t="inlineStr">
         <is>
-          <t>1592472532.809192</t>
+          <t>1598977155.522917</t>
         </is>
       </c>
       <c r="BJ24" t="inlineStr">
@@ -12052,7 +12052,7 @@
       </c>
       <c r="CG24" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="CH24" t="inlineStr">
@@ -12077,12 +12077,12 @@
       </c>
       <c r="CL24" t="inlineStr">
         <is>
-          <t>63.62</t>
+          <t>63.34</t>
         </is>
       </c>
       <c r="CM24" t="inlineStr">
         <is>
-          <t>466332</t>
+          <t>456022</t>
         </is>
       </c>
       <c r="CN24" t="inlineStr">
@@ -12174,12 +12174,12 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>-5.04</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>-3.63</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -12345,12 +12345,12 @@
       <c r="AP25" t="inlineStr"/>
       <c r="AQ25" t="inlineStr">
         <is>
-          <t>764</t>
+          <t>440</t>
         </is>
       </c>
       <c r="AR25" t="inlineStr">
         <is>
-          <t>62689</t>
+          <t>37996</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr">
@@ -12423,7 +12423,7 @@
       </c>
       <c r="BI25" t="inlineStr">
         <is>
-          <t>1592472532.809192</t>
+          <t>1598977155.522917</t>
         </is>
       </c>
       <c r="BJ25" t="inlineStr">
@@ -12539,7 +12539,7 @@
       </c>
       <c r="CG25" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="CH25" t="inlineStr">
@@ -12564,12 +12564,12 @@
       </c>
       <c r="CL25" t="inlineStr">
         <is>
-          <t>63.62</t>
+          <t>63.34</t>
         </is>
       </c>
       <c r="CM25" t="inlineStr">
         <is>
-          <t>466332</t>
+          <t>456022</t>
         </is>
       </c>
       <c r="CN25" t="inlineStr">
@@ -12661,12 +12661,12 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-4.17</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>-3.63</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -12832,12 +12832,12 @@
       <c r="AP26" t="inlineStr"/>
       <c r="AQ26" t="inlineStr">
         <is>
-          <t>764</t>
+          <t>440</t>
         </is>
       </c>
       <c r="AR26" t="inlineStr">
         <is>
-          <t>62689</t>
+          <t>37996</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr">
@@ -12910,7 +12910,7 @@
       </c>
       <c r="BI26" t="inlineStr">
         <is>
-          <t>1592472532.809192</t>
+          <t>1598977155.522917</t>
         </is>
       </c>
       <c r="BJ26" t="inlineStr">
@@ -13026,7 +13026,7 @@
       </c>
       <c r="CG26" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="CH26" t="inlineStr">
@@ -13051,12 +13051,12 @@
       </c>
       <c r="CL26" t="inlineStr">
         <is>
-          <t>63.62</t>
+          <t>63.34</t>
         </is>
       </c>
       <c r="CM26" t="inlineStr">
         <is>
-          <t>466332</t>
+          <t>456022</t>
         </is>
       </c>
       <c r="CN26" t="inlineStr">
@@ -13148,12 +13148,12 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>-3.63</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -13319,12 +13319,12 @@
       <c r="AP27" t="inlineStr"/>
       <c r="AQ27" t="inlineStr">
         <is>
-          <t>764</t>
+          <t>440</t>
         </is>
       </c>
       <c r="AR27" t="inlineStr">
         <is>
-          <t>62689</t>
+          <t>37996</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr">
@@ -13397,7 +13397,7 @@
       </c>
       <c r="BI27" t="inlineStr">
         <is>
-          <t>1592472532.809192</t>
+          <t>1598977155.522917</t>
         </is>
       </c>
       <c r="BJ27" t="inlineStr">
@@ -13513,7 +13513,7 @@
       </c>
       <c r="CG27" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="CH27" t="inlineStr">
@@ -13538,12 +13538,12 @@
       </c>
       <c r="CL27" t="inlineStr">
         <is>
-          <t>63.62</t>
+          <t>63.34</t>
         </is>
       </c>
       <c r="CM27" t="inlineStr">
         <is>
-          <t>466332</t>
+          <t>456022</t>
         </is>
       </c>
       <c r="CN27" t="inlineStr">
@@ -13635,12 +13635,12 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>-3.63</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -13806,12 +13806,12 @@
       <c r="AP28" t="inlineStr"/>
       <c r="AQ28" t="inlineStr">
         <is>
-          <t>764</t>
+          <t>440</t>
         </is>
       </c>
       <c r="AR28" t="inlineStr">
         <is>
-          <t>62689</t>
+          <t>37996</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr">
@@ -13884,7 +13884,7 @@
       </c>
       <c r="BI28" t="inlineStr">
         <is>
-          <t>1592472532.809192</t>
+          <t>1598977155.522917</t>
         </is>
       </c>
       <c r="BJ28" t="inlineStr">
@@ -14000,7 +14000,7 @@
       </c>
       <c r="CG28" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="CH28" t="inlineStr">
@@ -14025,12 +14025,12 @@
       </c>
       <c r="CL28" t="inlineStr">
         <is>
-          <t>63.62</t>
+          <t>63.34</t>
         </is>
       </c>
       <c r="CM28" t="inlineStr">
         <is>
-          <t>466332</t>
+          <t>456022</t>
         </is>
       </c>
       <c r="CN28" t="inlineStr">
@@ -14122,12 +14122,12 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>-3.63</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -14293,12 +14293,12 @@
       <c r="AP29" t="inlineStr"/>
       <c r="AQ29" t="inlineStr">
         <is>
-          <t>764</t>
+          <t>440</t>
         </is>
       </c>
       <c r="AR29" t="inlineStr">
         <is>
-          <t>62689</t>
+          <t>37996</t>
         </is>
       </c>
       <c r="AS29" t="inlineStr">
@@ -14371,7 +14371,7 @@
       </c>
       <c r="BI29" t="inlineStr">
         <is>
-          <t>1592472532.809192</t>
+          <t>1598977155.522917</t>
         </is>
       </c>
       <c r="BJ29" t="inlineStr">
@@ -14477,7 +14477,7 @@
       </c>
       <c r="CE29" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF29" t="inlineStr">
@@ -14487,7 +14487,7 @@
       </c>
       <c r="CG29" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="CH29" t="inlineStr">
@@ -14512,12 +14512,12 @@
       </c>
       <c r="CL29" t="inlineStr">
         <is>
-          <t>63.62</t>
+          <t>63.34</t>
         </is>
       </c>
       <c r="CM29" t="inlineStr">
         <is>
-          <t>466332</t>
+          <t>456022</t>
         </is>
       </c>
       <c r="CN29" t="inlineStr">
@@ -14609,12 +14609,12 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-2.89</t>
+          <t>-5.22</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>-3.63</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -14780,12 +14780,12 @@
       <c r="AP30" t="inlineStr"/>
       <c r="AQ30" t="inlineStr">
         <is>
-          <t>764</t>
+          <t>440</t>
         </is>
       </c>
       <c r="AR30" t="inlineStr">
         <is>
-          <t>62689</t>
+          <t>37996</t>
         </is>
       </c>
       <c r="AS30" t="inlineStr">
@@ -14858,7 +14858,7 @@
       </c>
       <c r="BI30" t="inlineStr">
         <is>
-          <t>1592472532.809192</t>
+          <t>1598977155.522917</t>
         </is>
       </c>
       <c r="BJ30" t="inlineStr">
@@ -14964,7 +14964,7 @@
       </c>
       <c r="CE30" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF30" t="inlineStr">
@@ -14974,7 +14974,7 @@
       </c>
       <c r="CG30" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="CH30" t="inlineStr">
@@ -14999,12 +14999,12 @@
       </c>
       <c r="CL30" t="inlineStr">
         <is>
-          <t>63.62</t>
+          <t>63.34</t>
         </is>
       </c>
       <c r="CM30" t="inlineStr">
         <is>
-          <t>466332</t>
+          <t>456022</t>
         </is>
       </c>
       <c r="CN30" t="inlineStr">
@@ -15096,12 +15096,12 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>-3.91</t>
+          <t>-6.26</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>-3.63</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -15267,12 +15267,12 @@
       <c r="AP31" t="inlineStr"/>
       <c r="AQ31" t="inlineStr">
         <is>
-          <t>764</t>
+          <t>440</t>
         </is>
       </c>
       <c r="AR31" t="inlineStr">
         <is>
-          <t>62689</t>
+          <t>37996</t>
         </is>
       </c>
       <c r="AS31" t="inlineStr">
@@ -15345,7 +15345,7 @@
       </c>
       <c r="BI31" t="inlineStr">
         <is>
-          <t>1592472532.809192</t>
+          <t>1598977155.522917</t>
         </is>
       </c>
       <c r="BJ31" t="inlineStr">
@@ -15451,7 +15451,7 @@
       </c>
       <c r="CE31" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF31" t="inlineStr">
@@ -15461,7 +15461,7 @@
       </c>
       <c r="CG31" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="CH31" t="inlineStr">
@@ -15486,12 +15486,12 @@
       </c>
       <c r="CL31" t="inlineStr">
         <is>
-          <t>63.62</t>
+          <t>63.34</t>
         </is>
       </c>
       <c r="CM31" t="inlineStr">
         <is>
-          <t>466332</t>
+          <t>456022</t>
         </is>
       </c>
       <c r="CN31" t="inlineStr">
@@ -15540,1467 +15540,6 @@
         </is>
       </c>
       <c r="CW31" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>【c】</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>1303</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>-2.43</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>73179.542</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>59.9</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>-1.87</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>-3.63</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>-47.68</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>2025-11-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>2025-12-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>2025-11-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="P32" t="inlineStr">
-        <is>
-          <t>2025-11-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q32" t="inlineStr">
-        <is>
-          <t>56.2</t>
-        </is>
-      </c>
-      <c r="R32" t="inlineStr">
-        <is>
-          <t>61.4</t>
-        </is>
-      </c>
-      <c r="S32" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T32" t="inlineStr">
-        <is>
-          <t>45.3</t>
-        </is>
-      </c>
-      <c r="U32" t="inlineStr">
-        <is>
-          <t>51.1</t>
-        </is>
-      </c>
-      <c r="V32" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W32" t="inlineStr">
-        <is>
-          <t>-2.44</t>
-        </is>
-      </c>
-      <c r="X32" t="inlineStr">
-        <is>
-          <t>9.98</t>
-        </is>
-      </c>
-      <c r="Y32" t="inlineStr">
-        <is>
-          <t>2025/07/28</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>37.0</t>
-        </is>
-      </c>
-      <c r="AA32" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>-0.31</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>2025/09/26</t>
-        </is>
-      </c>
-      <c r="AD32" t="inlineStr">
-        <is>
-          <t>39.6</t>
-        </is>
-      </c>
-      <c r="AE32" t="inlineStr">
-        <is>
-          <t>2025/04/08</t>
-        </is>
-      </c>
-      <c r="AF32" t="inlineStr">
-        <is>
-          <t>28.85</t>
-        </is>
-      </c>
-      <c r="AG32" t="inlineStr">
-        <is>
-          <t>2025/12/10</t>
-        </is>
-      </c>
-      <c r="AH32" t="inlineStr">
-        <is>
-          <t>61.4</t>
-        </is>
-      </c>
-      <c r="AI32" t="inlineStr">
-        <is>
-          <t>2025/11/26</t>
-        </is>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>51.1</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>2025-11-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="AL32" t="inlineStr">
-        <is>
-          <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>21.72</t>
-        </is>
-      </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>-3.34</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AP32" t="inlineStr"/>
-      <c r="AQ32" t="inlineStr">
-        <is>
-          <t>764</t>
-        </is>
-      </c>
-      <c r="AR32" t="inlineStr">
-        <is>
-          <t>62689</t>
-        </is>
-      </c>
-      <c r="AS32" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AT32" t="inlineStr">
-        <is>
-          <t>26.3</t>
-        </is>
-      </c>
-      <c r="AU32" t="n">
-        <v>-3.45</v>
-      </c>
-      <c r="AV32" t="n">
-        <v>5.82</v>
-      </c>
-      <c r="AW32" t="inlineStr">
-        <is>
-          <t>20.1</t>
-        </is>
-      </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>7.05</t>
-        </is>
-      </c>
-      <c r="AY32" t="inlineStr">
-        <is>
-          <t>62.04</t>
-        </is>
-      </c>
-      <c r="AZ32" t="n">
-        <v>58.63</v>
-      </c>
-      <c r="BA32" t="n">
-        <v>48.82</v>
-      </c>
-      <c r="BB32" t="inlineStr">
-        <is>
-          <t>45.6</t>
-        </is>
-      </c>
-      <c r="BC32" t="inlineStr">
-        <is>
-          <t>-7.15</t>
-        </is>
-      </c>
-      <c r="BD32" t="n">
-        <v>4.11</v>
-      </c>
-      <c r="BE32" t="n">
-        <v>4.43</v>
-      </c>
-      <c r="BF32" t="inlineStr">
-        <is>
-          <t>4.51</t>
-        </is>
-      </c>
-      <c r="BG32" t="inlineStr">
-        <is>
-          <t>-1.81</t>
-        </is>
-      </c>
-      <c r="BH32" t="inlineStr">
-        <is>
-          <t>2025/11/27</t>
-        </is>
-      </c>
-      <c r="BI32" t="inlineStr">
-        <is>
-          <t>1592472532.809192</t>
-        </is>
-      </c>
-      <c r="BJ32" t="inlineStr">
-        <is>
-          <t>4426368877.0</t>
-        </is>
-      </c>
-      <c r="BK32" t="n">
-        <v>5421472756.6</v>
-      </c>
-      <c r="BL32" t="inlineStr">
-        <is>
-          <t>10362427279.8</t>
-        </is>
-      </c>
-      <c r="BM32" t="n">
-        <v>5422126731.62</v>
-      </c>
-      <c r="BN32" t="inlineStr">
-        <is>
-          <t>-2147483648</t>
-        </is>
-      </c>
-      <c r="BO32" t="inlineStr">
-        <is>
-          <t>471693525.0193826</t>
-        </is>
-      </c>
-      <c r="BP32" t="inlineStr">
-        <is>
-          <t>-586385784.6035738</t>
-        </is>
-      </c>
-      <c r="BQ32" t="inlineStr">
-        <is>
-          <t>4426368877.0</t>
-        </is>
-      </c>
-      <c r="BR32" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BS32" t="inlineStr">
-        <is>
-          <t>41.9</t>
-        </is>
-      </c>
-      <c r="BT32" t="inlineStr">
-        <is>
-          <t>2025/10/21</t>
-        </is>
-      </c>
-      <c r="BU32" t="inlineStr">
-        <is>
-          <t>42.96</t>
-        </is>
-      </c>
-      <c r="BV32" t="inlineStr">
-        <is>
-          <t>南亞</t>
-        </is>
-      </c>
-      <c r="BW32" t="inlineStr">
-        <is>
-          <t>南亞</t>
-        </is>
-      </c>
-      <c r="BX32" t="inlineStr">
-        <is>
-          <t>塑膠工業</t>
-        </is>
-      </c>
-      <c r="BY32" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BZ32" t="inlineStr">
-        <is>
-          <t>0.93</t>
-        </is>
-      </c>
-      <c r="CA32" t="inlineStr">
-        <is>
-          <t>-4.249662585945642</t>
-        </is>
-      </c>
-      <c r="CB32" t="inlineStr">
-        <is>
-          <t>-6.718506037644686</t>
-        </is>
-      </c>
-      <c r="CC32" t="inlineStr">
-        <is>
-          <t>1.146736876787111</t>
-        </is>
-      </c>
-      <c r="CD32" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="CE32" t="inlineStr">
-        <is>
-          <t>價跌量增</t>
-        </is>
-      </c>
-      <c r="CF32" t="inlineStr">
-        <is>
-          <t>1.44</t>
-        </is>
-      </c>
-      <c r="CG32" t="inlineStr">
-        <is>
-          <t>1.19</t>
-        </is>
-      </c>
-      <c r="CH32" t="inlineStr">
-        <is>
-          <t>8.09</t>
-        </is>
-      </c>
-      <c r="CI32" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CJ32" t="inlineStr">
-        <is>
-          <t>8.29%</t>
-        </is>
-      </c>
-      <c r="CK32" t="inlineStr">
-        <is>
-          <t>1.61%</t>
-        </is>
-      </c>
-      <c r="CL32" t="inlineStr">
-        <is>
-          <t>63.62</t>
-        </is>
-      </c>
-      <c r="CM32" t="inlineStr">
-        <is>
-          <t>466332</t>
-        </is>
-      </c>
-      <c r="CN32" t="inlineStr">
-        <is>
-          <t>聚酯纖維16.60%、其他16.28%、印刷電路板(PCB)12.09%、銅箔基板(CCL)10.47%、環氧樹脂8.29%、丙二酚(BPA)5.67%、乙二醇(EG)5.60%、銅箔5.01%、可塑劑(DOP)及硬化劑3.38%、硬質管2.55%、硬質膠布2.48%、塑膠門窗2.20%、軟質膠布1.85%、麩酸酐(PA)1.55%、玻璃纖維布1.32%、聚酯薄膜1.30%、膠乳皮0.92%、PU合成皮(人造皮)0.69%、BOPP膜0.64%、玻璃纖維絲0.60%、丁二醇(BDO)0.54% (2024年)</t>
-        </is>
-      </c>
-      <c r="CO32" t="inlineStr">
-        <is>
-          <t>南亞-塑膠工業-上市</t>
-        </is>
-      </c>
-      <c r="CP32" t="inlineStr">
-        <is>
-          <t>塑膠工業平上市</t>
-        </is>
-      </c>
-      <c r="CQ32" t="inlineStr">
-        <is>
-          <t>61.8</t>
-        </is>
-      </c>
-      <c r="CR32" t="inlineStr">
-        <is>
-          <t>62.1</t>
-        </is>
-      </c>
-      <c r="CS32" t="inlineStr">
-        <is>
-          <t>59.7</t>
-        </is>
-      </c>
-      <c r="CT32" t="inlineStr">
-        <is>
-          <t>59.9</t>
-        </is>
-      </c>
-      <c r="CU32" t="inlineStr">
-        <is>
-          <t>41.48</t>
-        </is>
-      </c>
-      <c r="CV32" t="inlineStr">
-        <is>
-          <t>** 印刷電路板 - 玻璃纖維/玻纖布、環氧樹脂、酚醛樹脂、銅箔、銅箔基板** 石化及塑橡膠 - 石化上游原料及相關鑽探設備、人造纖維** 紡織 - 石化原料(例如純對苯二甲酸、乙二醇、己內醯胺、丙烯腈等)、人造纖維產品(例如尼龍纖維、聚酯纖維、嫘縈纖維等)、染整** 電機機械 - 電控元件、機械設備之沖壓零組件</t>
-        </is>
-      </c>
-      <c r="CW32" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>【c】</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>1303</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>-1.12</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>72310.843</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>61.4</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>-4.42</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>-3.63</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>-30.65</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>2025-11-27</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>2025-11-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>2025-12-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>2025-11-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>2025-11-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>56.2</t>
-        </is>
-      </c>
-      <c r="R33" t="inlineStr">
-        <is>
-          <t>61.4</t>
-        </is>
-      </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>56.2</t>
-        </is>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>45.3</t>
-        </is>
-      </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>51.1</t>
-        </is>
-      </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>9.25</t>
-        </is>
-      </c>
-      <c r="W33" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>9.98</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>2025/07/28</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>37.0</t>
-        </is>
-      </c>
-      <c r="AA33" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>-0.27</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>2025/09/26</t>
-        </is>
-      </c>
-      <c r="AD33" t="inlineStr">
-        <is>
-          <t>39.6</t>
-        </is>
-      </c>
-      <c r="AE33" t="inlineStr">
-        <is>
-          <t>2025/04/08</t>
-        </is>
-      </c>
-      <c r="AF33" t="inlineStr">
-        <is>
-          <t>28.85</t>
-        </is>
-      </c>
-      <c r="AG33" t="inlineStr">
-        <is>
-          <t>2025/12/10</t>
-        </is>
-      </c>
-      <c r="AH33" t="inlineStr">
-        <is>
-          <t>61.4</t>
-        </is>
-      </c>
-      <c r="AI33" t="inlineStr">
-        <is>
-          <t>2025/11/26</t>
-        </is>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>51.1</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>2025-11-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="AL33" t="inlineStr">
-        <is>
-          <t>2025-12-10</t>
-        </is>
-      </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>21.46</t>
-        </is>
-      </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>-3.25</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AP33" t="inlineStr"/>
-      <c r="AQ33" t="inlineStr">
-        <is>
-          <t>764</t>
-        </is>
-      </c>
-      <c r="AR33" t="inlineStr">
-        <is>
-          <t>62689</t>
-        </is>
-      </c>
-      <c r="AS33" t="inlineStr">
-        <is>
-          <t>27.59</t>
-        </is>
-      </c>
-      <c r="AT33" t="inlineStr">
-        <is>
-          <t>51.0</t>
-        </is>
-      </c>
-      <c r="AU33" t="n">
-        <v>-2.14</v>
-      </c>
-      <c r="AV33" t="n">
-        <v>7.57</v>
-      </c>
-      <c r="AW33" t="inlineStr">
-        <is>
-          <t>20.48</t>
-        </is>
-      </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>6.65</t>
-        </is>
-      </c>
-      <c r="AY33" t="inlineStr">
-        <is>
-          <t>62.73999999999999</t>
-        </is>
-      </c>
-      <c r="AZ33" t="n">
-        <v>58.32</v>
-      </c>
-      <c r="BA33" t="n">
-        <v>48.41</v>
-      </c>
-      <c r="BB33" t="inlineStr">
-        <is>
-          <t>45.39</t>
-        </is>
-      </c>
-      <c r="BC33" t="inlineStr">
-        <is>
-          <t>-0.21</t>
-        </is>
-      </c>
-      <c r="BD33" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BE33" t="n">
-        <v>4.51</v>
-      </c>
-      <c r="BF33" t="inlineStr">
-        <is>
-          <t>4.51</t>
-        </is>
-      </c>
-      <c r="BG33" t="inlineStr">
-        <is>
-          <t>-0.05</t>
-        </is>
-      </c>
-      <c r="BH33" t="inlineStr">
-        <is>
-          <t>2025/11/27</t>
-        </is>
-      </c>
-      <c r="BI33" t="inlineStr">
-        <is>
-          <t>1592472532.809192</t>
-        </is>
-      </c>
-      <c r="BJ33" t="inlineStr">
-        <is>
-          <t>4499648716.0</t>
-        </is>
-      </c>
-      <c r="BK33" t="n">
-        <v>7463766717.6</v>
-      </c>
-      <c r="BL33" t="inlineStr">
-        <is>
-          <t>10762151611.7</t>
-        </is>
-      </c>
-      <c r="BM33" t="n">
-        <v>5364535684.78</v>
-      </c>
-      <c r="BN33" t="inlineStr">
-        <is>
-          <t>-2147483648</t>
-        </is>
-      </c>
-      <c r="BO33" t="inlineStr">
-        <is>
-          <t>664071581.3144655</t>
-        </is>
-      </c>
-      <c r="BP33" t="inlineStr">
-        <is>
-          <t>-324318180.6293612</t>
-        </is>
-      </c>
-      <c r="BQ33" t="inlineStr">
-        <is>
-          <t>4499648716.0</t>
-        </is>
-      </c>
-      <c r="BR33" t="inlineStr">
-        <is>
-          <t>2025-12-10</t>
-        </is>
-      </c>
-      <c r="BS33" t="inlineStr">
-        <is>
-          <t>41.9</t>
-        </is>
-      </c>
-      <c r="BT33" t="inlineStr">
-        <is>
-          <t>2025/10/21</t>
-        </is>
-      </c>
-      <c r="BU33" t="inlineStr">
-        <is>
-          <t>46.54</t>
-        </is>
-      </c>
-      <c r="BV33" t="inlineStr">
-        <is>
-          <t>南亞</t>
-        </is>
-      </c>
-      <c r="BW33" t="inlineStr">
-        <is>
-          <t>南亞</t>
-        </is>
-      </c>
-      <c r="BX33" t="inlineStr">
-        <is>
-          <t>塑膠工業</t>
-        </is>
-      </c>
-      <c r="BY33" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BZ33" t="inlineStr">
-        <is>
-          <t>0.93</t>
-        </is>
-      </c>
-      <c r="CA33" t="inlineStr">
-        <is>
-          <t>-4.249662585945642</t>
-        </is>
-      </c>
-      <c r="CB33" t="inlineStr">
-        <is>
-          <t>-6.718506037644686</t>
-        </is>
-      </c>
-      <c r="CC33" t="inlineStr">
-        <is>
-          <t>1.146736876787111</t>
-        </is>
-      </c>
-      <c r="CD33" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="CE33" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="CF33" t="inlineStr">
-        <is>
-          <t>1.48</t>
-        </is>
-      </c>
-      <c r="CG33" t="inlineStr">
-        <is>
-          <t>1.19</t>
-        </is>
-      </c>
-      <c r="CH33" t="inlineStr">
-        <is>
-          <t>8.09</t>
-        </is>
-      </c>
-      <c r="CI33" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CJ33" t="inlineStr">
-        <is>
-          <t>8.29%</t>
-        </is>
-      </c>
-      <c r="CK33" t="inlineStr">
-        <is>
-          <t>1.61%</t>
-        </is>
-      </c>
-      <c r="CL33" t="inlineStr">
-        <is>
-          <t>63.62</t>
-        </is>
-      </c>
-      <c r="CM33" t="inlineStr">
-        <is>
-          <t>466332</t>
-        </is>
-      </c>
-      <c r="CN33" t="inlineStr">
-        <is>
-          <t>聚酯纖維16.60%、其他16.28%、印刷電路板(PCB)12.09%、銅箔基板(CCL)10.47%、環氧樹脂8.29%、丙二酚(BPA)5.67%、乙二醇(EG)5.60%、銅箔5.01%、可塑劑(DOP)及硬化劑3.38%、硬質管2.55%、硬質膠布2.48%、塑膠門窗2.20%、軟質膠布1.85%、麩酸酐(PA)1.55%、玻璃纖維布1.32%、聚酯薄膜1.30%、膠乳皮0.92%、PU合成皮(人造皮)0.69%、BOPP膜0.64%、玻璃纖維絲0.60%、丁二醇(BDO)0.54% (2024年)</t>
-        </is>
-      </c>
-      <c r="CO33" t="inlineStr">
-        <is>
-          <t>南亞-塑膠工業-上市</t>
-        </is>
-      </c>
-      <c r="CP33" t="inlineStr">
-        <is>
-          <t>塑膠工業平上市</t>
-        </is>
-      </c>
-      <c r="CQ33" t="inlineStr">
-        <is>
-          <t>62.6</t>
-        </is>
-      </c>
-      <c r="CR33" t="inlineStr">
-        <is>
-          <t>63.7</t>
-        </is>
-      </c>
-      <c r="CS33" t="inlineStr">
-        <is>
-          <t>61.1</t>
-        </is>
-      </c>
-      <c r="CT33" t="inlineStr">
-        <is>
-          <t>61.4</t>
-        </is>
-      </c>
-      <c r="CU33" t="inlineStr">
-        <is>
-          <t>41.48</t>
-        </is>
-      </c>
-      <c r="CV33" t="inlineStr">
-        <is>
-          <t>** 印刷電路板 - 玻璃纖維/玻纖布、環氧樹脂、酚醛樹脂、銅箔、銅箔基板** 石化及塑橡膠 - 石化上游原料及相關鑽探設備、人造纖維** 紡織 - 石化原料(例如純對苯二甲酸、乙二醇、己內醯胺、丙烯腈等)、人造纖維產品(例如尼龍纖維、聚酯纖維、嫘縈纖維等)、染整** 電機機械 - 電控元件、機械設備之沖壓零組件</t>
-        </is>
-      </c>
-      <c r="CW33" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>【b1】</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>1303</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>-2.09</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>91971.053</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>62.1</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>-5.61</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>-3.63</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>-5.58</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>2025-11-27</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>2025-11-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>2025-12-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t>2025-11-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>2025-11-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q34" t="inlineStr">
-        <is>
-          <t>56.2</t>
-        </is>
-      </c>
-      <c r="R34" t="inlineStr">
-        <is>
-          <t>61.4</t>
-        </is>
-      </c>
-      <c r="S34" t="inlineStr">
-        <is>
-          <t>56.2</t>
-        </is>
-      </c>
-      <c r="T34" t="inlineStr">
-        <is>
-          <t>45.3</t>
-        </is>
-      </c>
-      <c r="U34" t="inlineStr">
-        <is>
-          <t>51.1</t>
-        </is>
-      </c>
-      <c r="V34" t="inlineStr">
-        <is>
-          <t>10.50</t>
-        </is>
-      </c>
-      <c r="W34" t="inlineStr">
-        <is>
-          <t>1.14</t>
-        </is>
-      </c>
-      <c r="X34" t="inlineStr">
-        <is>
-          <t>9.98</t>
-        </is>
-      </c>
-      <c r="Y34" t="inlineStr">
-        <is>
-          <t>2025/07/28</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>37.0</t>
-        </is>
-      </c>
-      <c r="AA34" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>-0.28</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>2025/09/26</t>
-        </is>
-      </c>
-      <c r="AD34" t="inlineStr">
-        <is>
-          <t>39.6</t>
-        </is>
-      </c>
-      <c r="AE34" t="inlineStr">
-        <is>
-          <t>2025/04/08</t>
-        </is>
-      </c>
-      <c r="AF34" t="inlineStr">
-        <is>
-          <t>28.85</t>
-        </is>
-      </c>
-      <c r="AG34" t="inlineStr">
-        <is>
-          <t>2025/12/10</t>
-        </is>
-      </c>
-      <c r="AH34" t="inlineStr">
-        <is>
-          <t>61.4</t>
-        </is>
-      </c>
-      <c r="AI34" t="inlineStr">
-        <is>
-          <t>2025/11/26</t>
-        </is>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>51.1</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>2025-11-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="AL34" t="inlineStr">
-        <is>
-          <t>2025-12-09</t>
-        </is>
-      </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>27.30</t>
-        </is>
-      </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>1.36</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AP34" t="inlineStr"/>
-      <c r="AQ34" t="inlineStr">
-        <is>
-          <t>764</t>
-        </is>
-      </c>
-      <c r="AR34" t="inlineStr">
-        <is>
-          <t>62689</t>
-        </is>
-      </c>
-      <c r="AS34" t="inlineStr">
-        <is>
-          <t>51.3</t>
-        </is>
-      </c>
-      <c r="AT34" t="inlineStr">
-        <is>
-          <t>66.5</t>
-        </is>
-      </c>
-      <c r="AU34" t="n">
-        <v>-2.97</v>
-      </c>
-      <c r="AV34" t="n">
-        <v>10.83</v>
-      </c>
-      <c r="AW34" t="inlineStr">
-        <is>
-          <t>20.3</t>
-        </is>
-      </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>6.32</t>
-        </is>
-      </c>
-      <c r="AY34" t="inlineStr">
-        <is>
-          <t>64.0</t>
-        </is>
-      </c>
-      <c r="AZ34" t="n">
-        <v>57.74</v>
-      </c>
-      <c r="BA34" t="n">
-        <v>48</v>
-      </c>
-      <c r="BB34" t="inlineStr">
-        <is>
-          <t>45.15</t>
-        </is>
-      </c>
-      <c r="BC34" t="inlineStr">
-        <is>
-          <t>5.84</t>
-        </is>
-      </c>
-      <c r="BD34" t="n">
-        <v>4.77</v>
-      </c>
-      <c r="BE34" t="n">
-        <v>4.51</v>
-      </c>
-      <c r="BF34" t="inlineStr">
-        <is>
-          <t>4.51</t>
-        </is>
-      </c>
-      <c r="BG34" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="BH34" t="inlineStr">
-        <is>
-          <t>2025/11/27</t>
-        </is>
-      </c>
-      <c r="BI34" t="inlineStr">
-        <is>
-          <t>1592472532.809192</t>
-        </is>
-      </c>
-      <c r="BJ34" t="inlineStr">
-        <is>
-          <t>5676097071.0</t>
-        </is>
-      </c>
-      <c r="BK34" t="n">
-        <v>10068354662</v>
-      </c>
-      <c r="BL34" t="inlineStr">
-        <is>
-          <t>10663448994.9</t>
-        </is>
-      </c>
-      <c r="BM34" t="n">
-        <v>5342883430.56</v>
-      </c>
-      <c r="BN34" t="inlineStr">
-        <is>
-          <t>-595094332</t>
-        </is>
-      </c>
-      <c r="BO34" t="inlineStr">
-        <is>
-          <t>843778810.7587978</t>
-        </is>
-      </c>
-      <c r="BP34" t="inlineStr">
-        <is>
-          <t>53795491.60627747</t>
-        </is>
-      </c>
-      <c r="BQ34" t="inlineStr">
-        <is>
-          <t>5676097071.0</t>
-        </is>
-      </c>
-      <c r="BR34" t="inlineStr">
-        <is>
-          <t>2025-12-10</t>
-        </is>
-      </c>
-      <c r="BS34" t="inlineStr">
-        <is>
-          <t>41.9</t>
-        </is>
-      </c>
-      <c r="BT34" t="inlineStr">
-        <is>
-          <t>2025/10/21</t>
-        </is>
-      </c>
-      <c r="BU34" t="inlineStr">
-        <is>
-          <t>48.21</t>
-        </is>
-      </c>
-      <c r="BV34" t="inlineStr">
-        <is>
-          <t>南亞</t>
-        </is>
-      </c>
-      <c r="BW34" t="inlineStr">
-        <is>
-          <t>南亞</t>
-        </is>
-      </c>
-      <c r="BX34" t="inlineStr">
-        <is>
-          <t>塑膠工業</t>
-        </is>
-      </c>
-      <c r="BY34" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BZ34" t="inlineStr">
-        <is>
-          <t>0.93</t>
-        </is>
-      </c>
-      <c r="CA34" t="inlineStr">
-        <is>
-          <t>-4.249662585945642</t>
-        </is>
-      </c>
-      <c r="CB34" t="inlineStr">
-        <is>
-          <t>-6.718506037644686</t>
-        </is>
-      </c>
-      <c r="CC34" t="inlineStr">
-        <is>
-          <t>1.146736876787111</t>
-        </is>
-      </c>
-      <c r="CD34" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="CE34" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="CF34" t="inlineStr">
-        <is>
-          <t>1.50</t>
-        </is>
-      </c>
-      <c r="CG34" t="inlineStr">
-        <is>
-          <t>1.19</t>
-        </is>
-      </c>
-      <c r="CH34" t="inlineStr">
-        <is>
-          <t>8.09</t>
-        </is>
-      </c>
-      <c r="CI34" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CJ34" t="inlineStr">
-        <is>
-          <t>8.29%</t>
-        </is>
-      </c>
-      <c r="CK34" t="inlineStr">
-        <is>
-          <t>1.61%</t>
-        </is>
-      </c>
-      <c r="CL34" t="inlineStr">
-        <is>
-          <t>63.62</t>
-        </is>
-      </c>
-      <c r="CM34" t="inlineStr">
-        <is>
-          <t>466332</t>
-        </is>
-      </c>
-      <c r="CN34" t="inlineStr">
-        <is>
-          <t>聚酯纖維16.60%、其他16.28%、印刷電路板(PCB)12.09%、銅箔基板(CCL)10.47%、環氧樹脂8.29%、丙二酚(BPA)5.67%、乙二醇(EG)5.60%、銅箔5.01%、可塑劑(DOP)及硬化劑3.38%、硬質管2.55%、硬質膠布2.48%、塑膠門窗2.20%、軟質膠布1.85%、麩酸酐(PA)1.55%、玻璃纖維布1.32%、聚酯薄膜1.30%、膠乳皮0.92%、PU合成皮(人造皮)0.69%、BOPP膜0.64%、玻璃纖維絲0.60%、丁二醇(BDO)0.54% (2024年)</t>
-        </is>
-      </c>
-      <c r="CO34" t="inlineStr">
-        <is>
-          <t>南亞-塑膠工業-上市</t>
-        </is>
-      </c>
-      <c r="CP34" t="inlineStr">
-        <is>
-          <t>塑膠工業平上市</t>
-        </is>
-      </c>
-      <c r="CQ34" t="inlineStr">
-        <is>
-          <t>62.1</t>
-        </is>
-      </c>
-      <c r="CR34" t="inlineStr">
-        <is>
-          <t>62.9</t>
-        </is>
-      </c>
-      <c r="CS34" t="inlineStr">
-        <is>
-          <t>60.5</t>
-        </is>
-      </c>
-      <c r="CT34" t="inlineStr">
-        <is>
-          <t>62.1</t>
-        </is>
-      </c>
-      <c r="CU34" t="inlineStr">
-        <is>
-          <t>41.48</t>
-        </is>
-      </c>
-      <c r="CV34" t="inlineStr">
-        <is>
-          <t>** 印刷電路板 - 玻璃纖維/玻纖布、環氧樹脂、酚醛樹脂、銅箔、銅箔基板** 石化及塑橡膠 - 石化上游原料及相關鑽探設備、人造纖維** 紡織 - 石化原料(例如純對苯二甲酸、乙二醇、己內醯胺、丙烯腈等)、人造纖維產品(例如尼龍纖維、聚酯纖維、嫘縈纖維等)、染整** 電機機械 - 電控元件、機械設備之沖壓零組件</t>
-        </is>
-      </c>
-      <c r="CW34" t="inlineStr">
         <is>
           <t>False</t>
         </is>

--- a/Result/checksun_type/石化上游原料及相關鑽探設備.xlsx
+++ b/Result/checksun_type/石化上游原料及相關鑽探設備.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CW22"/>
+  <dimension ref="A1:CW21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -938,22 +938,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>6505</t>
+          <t>1723</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2623.606</t>
+          <t>673.593</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>68.5</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -978,12 +978,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-31.27</t>
+          <t>12.26</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -993,37 +993,37 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-99.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2025-11-06 00:00:00</t>
+          <t>2025-02-26 00:00:00</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2025-11-25 00:00:00</t>
+          <t>2025-03-12 00:00:00</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>2025-09-26 00:00:00</t>
+          <t>2024-03-28 00:00:00</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2025-11-04 00:00:00</t>
+          <t>2024-04-02 00:00:00</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>47.85</t>
+          <t>99.1</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>98.6</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -1033,12 +1033,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>40.15</t>
+          <t>123.5</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>44.5</t>
+          <t>118.0</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -1048,22 +1048,22 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-5.95</t>
+          <t>-30.53</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>7.53</t>
+          <t>-16.02</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025/07/28</t>
+          <t>2025/06/02</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>40.4</t>
+          <t>92.4</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -1073,67 +1073,67 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>2025/09/19</t>
+          <t>2025/11/13</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>38.9</t>
+          <t>79.9</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>2025/07/04</t>
+          <t>2025/06/20</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>37.85</t>
+          <t>90.1</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>2025/11/25</t>
+          <t>2025/10/23</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2025/11/04</t>
+          <t>2025/07/31</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>44.5</t>
+          <t>86.9</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>2025-11-07 00:00:00</t>
+          <t>2025-11-28 00:00:00</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>6.95</t>
+          <t>35.79</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>3.01</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
@@ -1144,121 +1144,121 @@
       <c r="AP2" t="inlineStr"/>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>2624</t>
+          <t>674</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>79.31</t>
+          <t>73.68</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>49.84</t>
+          <t>35.17</t>
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>0.35</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AV2" t="n">
-        <v>-2.61</v>
+        <v>-1.55</v>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>-8.07</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>7.98</t>
+          <t>-3.71</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>48.83</t>
+          <t>68.12</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>50.14</v>
+        <v>69.19</v>
       </c>
       <c r="BA2" t="n">
-        <v>49.69</v>
+        <v>75.27</v>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>46.02</t>
+          <t>78.16</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-87.85</t>
+          <t>13.22</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>-0.49</v>
+        <v>-2.01</v>
       </c>
       <c r="BE2" t="n">
-        <v>-0.26</v>
+        <v>-2.32</v>
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>2.97</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-108.87</t>
+          <t>-233.60</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2025/11/06</t>
+          <t>2025/12/15</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>413483698.6976421</t>
+          <t>67197780.36772853</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>128726080.0</t>
+          <t>45290917.0</t>
         </is>
       </c>
       <c r="BK2" t="n">
-        <v>146424418.4</v>
+        <v>36317228</v>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>213035188.0</t>
+          <t>32350796.3</t>
         </is>
       </c>
       <c r="BM2" t="n">
-        <v>446858256.1</v>
+        <v>38135166.56</v>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>-66610769</t>
+          <t>3966431</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>-46743102.15286153</t>
+          <t>-2079560.521867446</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>-49835953.52211222</t>
+          <t>-137813.2095817178</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>128726080.0</t>
+          <t>45290917.0</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1268,32 +1268,32 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>43.85</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>2025/10/20</t>
+          <t>2025/10/15</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>11.74</t>
+          <t>-23.29</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>台塑化</t>
+          <t>中碳</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
         <is>
-          <t>台塑化</t>
+          <t>中碳</t>
         </is>
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>油電燃氣業</t>
+          <t>化學工業</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
@@ -1303,117 +1303,117 @@
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
         <is>
-          <t>-16.06351948126612</t>
+          <t>-7.32116827620037</t>
         </is>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>-3.054910686901505</t>
+          <t>-26.54178546817805</t>
         </is>
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>-6.074976069093286</t>
+          <t>-23.30870698662894</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>6.57</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
         <is>
-          <t>17.17</t>
+          <t>5.94</t>
         </is>
       </c>
       <c r="CI2" t="inlineStr">
         <is>
-          <t>76.56</t>
+          <t>21.61</t>
         </is>
       </c>
       <c r="CJ2" t="inlineStr">
         <is>
-          <t>7.31%</t>
+          <t>17.52%</t>
         </is>
       </c>
       <c r="CK2" t="inlineStr">
         <is>
-          <t>5.68%</t>
+          <t>6.35%</t>
         </is>
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>27.06</t>
+          <t>52.23</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
         <is>
-          <t>466772</t>
+          <t>16228</t>
         </is>
       </c>
       <c r="CN2" t="inlineStr">
         <is>
-          <t>汽油,柴油等各項石油製品75.50%、乙烯,丙烯等石油化學品18.10%、電力,蒸汽6.00%、其他0.40% (2024年)</t>
+          <t>煤焦油及化學品系列產品53.20%、輕油及油品系列產品29.03%、精碳材料9.72%、焦碳製品6.62%、其他1.43% (2024年)</t>
         </is>
       </c>
       <c r="CO2" t="inlineStr">
         <is>
-          <t>台塑化-油電燃氣業-上市</t>
+          <t>中碳-化學工業-上市</t>
         </is>
       </c>
       <c r="CP2" t="inlineStr">
         <is>
-          <t>油電燃氣業右下上市</t>
+          <t>化學工業右下上市</t>
         </is>
       </c>
       <c r="CQ2" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>67.5</t>
         </is>
       </c>
       <c r="CR2" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>68.5</t>
         </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>66.5</t>
         </is>
       </c>
       <c r="CT2" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>68.5</t>
         </is>
       </c>
       <c r="CU2" t="inlineStr">
         <is>
-          <t>32.21</t>
+          <t>33.12</t>
         </is>
       </c>
       <c r="CV2" t="inlineStr">
         <is>
-          <t>** 石化及塑橡膠 - 石化上游原料及相關鑽探設備** 油電燃氣 - 加油站、汽電共生</t>
+          <t>** 石化及塑橡膠 - 石化上游原料及相關鑽探設備** 電動車輛產業 - 鋰電池材料** 能源元件 - 原材料</t>
         </is>
       </c>
       <c r="CW2" t="inlineStr">
@@ -1425,22 +1425,22 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>6505</t>
+          <t>1723</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1316.127</t>
+          <t>658.104</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1460,167 +1460,167 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
+          <t>1.02</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>-1.63</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>5.11</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>-99.0</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2025-02-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2025-03-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>2024-03-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2024-04-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>99.1</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>98.6</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>123.5</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>118.0</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>-31.24</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>-16.02</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025/06/02</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>92.4</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>2025/11/13</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>79.9</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>2025/06/20</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>90.1</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>2025/10/23</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>83.8</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>2025/07/31</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>86.9</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>2025-11-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>34.97</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
           <t>0.61</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>-0.72</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>-16.57</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>-50.0</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>2025-11-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>2025-11-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>2025-09-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>2025-11-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>47.85</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>52.1</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>40.15</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>44.5</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>-6.53</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>7.53</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>2025/07/28</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>40.4</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>0.06</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>2025/09/19</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>38.9</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>2025/07/04</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>37.85</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>2025/11/25</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>52.1</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>2025/11/04</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>44.5</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>2025-11-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t>2025-12-26</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>3.49</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>-0.31</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
@@ -1631,121 +1631,121 @@
       <c r="AP3" t="inlineStr"/>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>2624</t>
+          <t>674</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>36.17</t>
+          <t>31.82</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>43.97</t>
+          <t>23.57</t>
         </is>
       </c>
       <c r="AU3" t="n">
-        <v>-0.1</v>
+        <v>-0.5</v>
       </c>
       <c r="AV3" t="n">
-        <v>-3.09</v>
+        <v>-1.72</v>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>-8.29</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>7.99</t>
+          <t>-3.49</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>48.75</t>
+          <t>68.14</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>50.3</v>
+        <v>69.33</v>
       </c>
       <c r="BA3" t="n">
-        <v>49.57</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>45.91</t>
+          <t>78.33</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-149.65</t>
+          <t>10.03</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>-0.51</v>
+        <v>-2.15</v>
       </c>
       <c r="BE3" t="n">
-        <v>-0.21</v>
+        <v>-2.39</v>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>2.97</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-106.92</t>
+          <t>-238.01</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2025/11/06</t>
+          <t>2025/12/15</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>413483698.6976421</t>
+          <t>67197780.36772853</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
-          <t>64138554.0</t>
+          <t>44656757.0</t>
         </is>
       </c>
       <c r="BK3" t="n">
-        <v>180478574.4</v>
+        <v>31732769.6</v>
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>216333475.6</t>
+          <t>30190352.0</t>
         </is>
       </c>
       <c r="BM3" t="n">
-        <v>454343174.12</v>
+        <v>37849613.32</v>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>-35854901</t>
+          <t>1542417</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>-46180765.54027049</t>
+          <t>-2432605.487737579</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>-51094987.65225139</t>
+          <t>-996747.3510800153</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>64138554.0</t>
+          <t>44656757.0</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1755,32 +1755,32 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>43.85</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>2025/10/20</t>
+          <t>2025/10/15</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>11.06</t>
+          <t>-24.08</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>台塑化</t>
+          <t>中碳</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
         <is>
-          <t>台塑化</t>
+          <t>中碳</t>
         </is>
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>油電燃氣業</t>
+          <t>化學工業</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
@@ -1790,117 +1790,117 @@
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
         <is>
-          <t>-16.06351948126612</t>
+          <t>-7.32116827620037</t>
         </is>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>-3.054910686901505</t>
+          <t>-26.54178546817805</t>
         </is>
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>-6.074976069093286</t>
+          <t>-23.30870698662894</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>6.57</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
         <is>
-          <t>17.17</t>
+          <t>5.94</t>
         </is>
       </c>
       <c r="CI3" t="inlineStr">
         <is>
-          <t>76.56</t>
+          <t>21.61</t>
         </is>
       </c>
       <c r="CJ3" t="inlineStr">
         <is>
-          <t>7.31%</t>
+          <t>17.52%</t>
         </is>
       </c>
       <c r="CK3" t="inlineStr">
         <is>
-          <t>5.68%</t>
+          <t>6.35%</t>
         </is>
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>27.06</t>
+          <t>52.23</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
         <is>
-          <t>466772</t>
+          <t>16228</t>
         </is>
       </c>
       <c r="CN3" t="inlineStr">
         <is>
-          <t>汽油,柴油等各項石油製品75.50%、乙烯,丙烯等石油化學品18.10%、電力,蒸汽6.00%、其他0.40% (2024年)</t>
+          <t>煤焦油及化學品系列產品53.20%、輕油及油品系列產品29.03%、精碳材料9.72%、焦碳製品6.62%、其他1.43% (2024年)</t>
         </is>
       </c>
       <c r="CO3" t="inlineStr">
         <is>
-          <t>台塑化-油電燃氣業-上市</t>
+          <t>中碳-化學工業-上市</t>
         </is>
       </c>
       <c r="CP3" t="inlineStr">
         <is>
-          <t>油電燃氣業右下上市</t>
+          <t>化學工業右下上市</t>
         </is>
       </c>
       <c r="CQ3" t="inlineStr">
         <is>
-          <t>48.95</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="CR3" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>68.4</t>
         </is>
       </c>
       <c r="CS3" t="inlineStr">
         <is>
-          <t>48.45</t>
+          <t>66.8</t>
         </is>
       </c>
       <c r="CT3" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="CU3" t="inlineStr">
         <is>
-          <t>32.21</t>
+          <t>33.12</t>
         </is>
       </c>
       <c r="CV3" t="inlineStr">
         <is>
-          <t>** 石化及塑橡膠 - 石化上游原料及相關鑽探設備** 油電燃氣 - 加油站、汽電共生</t>
+          <t>** 石化及塑橡膠 - 石化上游原料及相關鑽探設備** 電動車輛產業 - 鋰電池材料** 能源元件 - 原材料</t>
         </is>
       </c>
       <c r="CW3" t="inlineStr">
@@ -1912,22 +1912,22 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>6505</t>
+          <t>1723</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-2.04</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2646.184</t>
+          <t>839.101</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1937,7 +1937,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>48.65</t>
+          <t>67.1</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1947,17 +1947,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-14.41</t>
+          <t>8.11</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1967,37 +1967,37 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-99.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2025-11-06 00:00:00</t>
+          <t>2025-02-26 00:00:00</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2025-11-25 00:00:00</t>
+          <t>2025-03-12 00:00:00</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>2025-09-26 00:00:00</t>
+          <t>2024-03-28 00:00:00</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2025-11-04 00:00:00</t>
+          <t>2024-04-02 00:00:00</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>47.85</t>
+          <t>99.1</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>98.6</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -2007,12 +2007,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>40.15</t>
+          <t>123.5</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>44.5</t>
+          <t>118.0</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -2022,22 +2022,22 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-6.62</t>
+          <t>-31.95</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>7.53</t>
+          <t>-16.02</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025/07/28</t>
+          <t>2025/06/02</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>40.4</t>
+          <t>92.4</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -2047,67 +2047,67 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>2025/09/19</t>
+          <t>2025/11/13</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>38.9</t>
+          <t>79.9</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>2025/07/04</t>
+          <t>2025/06/20</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>37.85</t>
+          <t>90.1</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>2025/11/25</t>
+          <t>2025/10/23</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>2025/11/04</t>
+          <t>2025/07/31</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>44.5</t>
+          <t>86.9</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>2025-11-07 00:00:00</t>
+          <t>2025-11-28 00:00:00</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>7.01</t>
+          <t>44.59</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
@@ -2118,121 +2118,121 @@
       <c r="AP4" t="inlineStr"/>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>2624</t>
+          <t>674</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>34.04</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>41.13</t>
+          <t>29.63</t>
         </is>
       </c>
       <c r="AU4" t="n">
-        <v>0.14</v>
+        <v>-1.53</v>
       </c>
       <c r="AV4" t="n">
-        <v>-3.74</v>
+        <v>-1.98</v>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>-8.52</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>7.91</t>
+          <t>-3.21</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>48.58</t>
+          <t>68.14</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>50.47</v>
+        <v>69.52</v>
       </c>
       <c r="BA4" t="n">
-        <v>49.42</v>
+        <v>75.98999999999999</v>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>45.8</t>
+          <t>78.51</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-287.52</t>
+          <t>8.98</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>-0.5</v>
+        <v>-2.23</v>
       </c>
       <c r="BE4" t="n">
-        <v>-0.13</v>
+        <v>-2.45</v>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>2.97</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-104.33</t>
+          <t>-241.47</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2025/11/06</t>
+          <t>2025/12/15</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>413483698.6976421</t>
+          <t>67197780.36772853</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>129351183.0</t>
+          <t>56479383.0</t>
         </is>
       </c>
       <c r="BK4" t="n">
-        <v>206912922.6</v>
+        <v>30387660</v>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>241751775.8</t>
+          <t>28107734.3</t>
         </is>
       </c>
       <c r="BM4" t="n">
-        <v>459452333.2</v>
+        <v>38193467.22</v>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>-34838853</t>
+          <t>2279925</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>-45287270.61081942</t>
+          <t>-2693670.6034935</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>-44148694.77915558</t>
+          <t>-2120252.290681858</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>129351183.0</t>
+          <t>56479383.0</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2242,32 +2242,32 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>43.85</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>2025/10/20</t>
+          <t>2025/10/15</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>10.95</t>
+          <t>-24.86</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>台塑化</t>
+          <t>中碳</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
         <is>
-          <t>台塑化</t>
+          <t>中碳</t>
         </is>
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>油電燃氣業</t>
+          <t>化學工業</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
@@ -2277,117 +2277,117 @@
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
         <is>
-          <t>-16.06351948126612</t>
+          <t>-7.32116827620037</t>
         </is>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>-3.054910686901505</t>
+          <t>-26.54178546817805</t>
         </is>
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>-6.074976069093286</t>
+          <t>-23.30870698662894</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>6.57</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
         <is>
-          <t>17.17</t>
+          <t>5.94</t>
         </is>
       </c>
       <c r="CI4" t="inlineStr">
         <is>
-          <t>76.56</t>
+          <t>21.61</t>
         </is>
       </c>
       <c r="CJ4" t="inlineStr">
         <is>
-          <t>7.31%</t>
+          <t>17.52%</t>
         </is>
       </c>
       <c r="CK4" t="inlineStr">
         <is>
-          <t>5.68%</t>
+          <t>6.35%</t>
         </is>
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>27.06</t>
+          <t>52.23</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
         <is>
-          <t>466772</t>
+          <t>16228</t>
         </is>
       </c>
       <c r="CN4" t="inlineStr">
         <is>
-          <t>汽油,柴油等各項石油製品75.50%、乙烯,丙烯等石油化學品18.10%、電力,蒸汽6.00%、其他0.40% (2024年)</t>
+          <t>煤焦油及化學品系列產品53.20%、輕油及油品系列產品29.03%、精碳材料9.72%、焦碳製品6.62%、其他1.43% (2024年)</t>
         </is>
       </c>
       <c r="CO4" t="inlineStr">
         <is>
-          <t>台塑化-油電燃氣業-上市</t>
+          <t>中碳-化學工業-上市</t>
         </is>
       </c>
       <c r="CP4" t="inlineStr">
         <is>
-          <t>油電燃氣業右下上市</t>
+          <t>化學工業右下上市</t>
         </is>
       </c>
       <c r="CQ4" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>68.5</t>
         </is>
       </c>
       <c r="CR4" t="inlineStr">
         <is>
-          <t>49.45</t>
+          <t>68.5</t>
         </is>
       </c>
       <c r="CS4" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>66.9</t>
         </is>
       </c>
       <c r="CT4" t="inlineStr">
         <is>
-          <t>48.65</t>
+          <t>67.1</t>
         </is>
       </c>
       <c r="CU4" t="inlineStr">
         <is>
-          <t>32.21</t>
+          <t>33.12</t>
         </is>
       </c>
       <c r="CV4" t="inlineStr">
         <is>
-          <t>** 石化及塑橡膠 - 石化上游原料及相關鑽探設備** 油電燃氣 - 加油站、汽電共生</t>
+          <t>** 石化及塑橡膠 - 石化上游原料及相關鑽探設備** 電動車輛產業 - 鋰電池材料** 能源元件 - 原材料</t>
         </is>
       </c>
       <c r="CW4" t="inlineStr">
@@ -2399,22 +2399,22 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>6505</t>
+          <t>1723</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>4601.672</t>
+          <t>251.116</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>68.5</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2434,17 +2434,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-3.31</t>
+          <t>5.95</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2454,37 +2454,37 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-99.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2025-11-06 00:00:00</t>
+          <t>2025-02-26 00:00:00</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2025-11-25 00:00:00</t>
+          <t>2025-03-12 00:00:00</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>2025-09-26 00:00:00</t>
+          <t>2024-03-28 00:00:00</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2025-11-04 00:00:00</t>
+          <t>2024-04-02 00:00:00</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>47.85</t>
+          <t>99.1</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>98.6</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -2494,12 +2494,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>40.15</t>
+          <t>123.5</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>44.5</t>
+          <t>118.0</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -2509,22 +2509,22 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-5.37</t>
+          <t>-30.53</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>7.53</t>
+          <t>-16.02</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025/07/28</t>
+          <t>2025/06/02</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>40.4</t>
+          <t>92.4</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -2534,67 +2534,67 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>2025/09/19</t>
+          <t>2025/11/13</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>38.9</t>
+          <t>79.9</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>2025/07/04</t>
+          <t>2025/06/20</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>37.85</t>
+          <t>90.1</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>2025/11/25</t>
+          <t>2025/10/23</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>2025/11/04</t>
+          <t>2025/07/31</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>44.5</t>
+          <t>86.9</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>2025-11-07 00:00:00</t>
+          <t>2025-11-28 00:00:00</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>12.20</t>
+          <t>13.34</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
@@ -2605,121 +2605,121 @@
       <c r="AP5" t="inlineStr"/>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>2624</t>
+          <t>674</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>61.7</t>
+          <t>38.89</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>37.25</t>
+          <t>44.44</t>
         </is>
       </c>
       <c r="AU5" t="n">
-        <v>1.65</v>
+        <v>0.26</v>
       </c>
       <c r="AV5" t="n">
-        <v>-4.05</v>
+        <v>-2.19</v>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>2.61</t>
+          <t>-8.61</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>7.80</t>
+          <t>-2.87</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>68.32000000000001</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>50.55</v>
+        <v>69.84999999999999</v>
       </c>
       <c r="BA5" t="n">
-        <v>49.26</v>
+        <v>76.43000000000001</v>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>45.7</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-1192.49</t>
+          <t>11.06</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>-0.47</v>
+        <v>-2.23</v>
       </c>
       <c r="BE5" t="n">
-        <v>-0.04</v>
+        <v>-2.51</v>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>2.97</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-101.22</t>
+          <t>-244.65</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2025/11/06</t>
+          <t>2025/12/15</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>413483698.6976421</t>
+          <t>67197780.36772853</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>226364557.0</t>
+          <t>17252206.0</t>
         </is>
       </c>
       <c r="BK5" t="n">
-        <v>244729109.4</v>
+        <v>27906915.2</v>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>253104275.0</t>
+          <t>26338712.0</t>
         </is>
       </c>
       <c r="BM5" t="n">
-        <v>462234616.36</v>
+        <v>40395160.94</v>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>-8375165</t>
+          <t>1568203</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>-45494284.39839467</t>
+          <t>-2797928.478550162</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>-39635747.53976309</t>
+          <t>-4916245.979731578</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>226364557.0</t>
+          <t>17252206.0</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2729,32 +2729,32 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>43.85</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>2025/10/20</t>
+          <t>2025/10/15</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>12.43</t>
+          <t>-23.29</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>台塑化</t>
+          <t>中碳</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
         <is>
-          <t>台塑化</t>
+          <t>中碳</t>
         </is>
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>油電燃氣業</t>
+          <t>化學工業</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
@@ -2764,117 +2764,117 @@
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
         <is>
-          <t>-16.06351948126612</t>
+          <t>-7.32116827620037</t>
         </is>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>-3.054910686901505</t>
+          <t>-26.54178546817805</t>
         </is>
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>-6.074976069093286</t>
+          <t>-23.30870698662894</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>6.57</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
         <is>
-          <t>17.17</t>
+          <t>5.94</t>
         </is>
       </c>
       <c r="CI5" t="inlineStr">
         <is>
-          <t>76.56</t>
+          <t>21.61</t>
         </is>
       </c>
       <c r="CJ5" t="inlineStr">
         <is>
-          <t>7.31%</t>
+          <t>17.52%</t>
         </is>
       </c>
       <c r="CK5" t="inlineStr">
         <is>
-          <t>5.68%</t>
+          <t>6.35%</t>
         </is>
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>27.06</t>
+          <t>52.23</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
         <is>
-          <t>466772</t>
+          <t>16228</t>
         </is>
       </c>
       <c r="CN5" t="inlineStr">
         <is>
-          <t>汽油,柴油等各項石油製品75.50%、乙烯,丙烯等石油化學品18.10%、電力,蒸汽6.00%、其他0.40% (2024年)</t>
+          <t>煤焦油及化學品系列產品53.20%、輕油及油品系列產品29.03%、精碳材料9.72%、焦碳製品6.62%、其他1.43% (2024年)</t>
         </is>
       </c>
       <c r="CO5" t="inlineStr">
         <is>
-          <t>台塑化-油電燃氣業-上市</t>
+          <t>中碳-化學工業-上市</t>
         </is>
       </c>
       <c r="CP5" t="inlineStr">
         <is>
-          <t>油電燃氣業右下上市</t>
+          <t>化學工業右下上市</t>
         </is>
       </c>
       <c r="CQ5" t="inlineStr">
         <is>
-          <t>48.65</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="CR5" t="inlineStr">
         <is>
-          <t>50.1</t>
+          <t>69.4</t>
         </is>
       </c>
       <c r="CS5" t="inlineStr">
         <is>
-          <t>48.15</t>
+          <t>68.4</t>
         </is>
       </c>
       <c r="CT5" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>68.5</t>
         </is>
       </c>
       <c r="CU5" t="inlineStr">
         <is>
-          <t>32.21</t>
+          <t>33.12</t>
         </is>
       </c>
       <c r="CV5" t="inlineStr">
         <is>
-          <t>** 石化及塑橡膠 - 石化上游原料及相關鑽探設備** 油電燃氣 - 加油站、汽電共生</t>
+          <t>** 石化及塑橡膠 - 石化上游原料及相關鑽探設備** 電動車輛產業 - 鋰電池材料** 能源元件 - 原材料</t>
         </is>
       </c>
       <c r="CW5" t="inlineStr">
@@ -2886,22 +2886,22 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>6505</t>
+          <t>1723</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>3785.684</t>
+          <t>261.237</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2921,17 +2921,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2941,37 +2941,37 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-99.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2025-11-06 00:00:00</t>
+          <t>2025-02-26 00:00:00</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2025-11-25 00:00:00</t>
+          <t>2025-03-12 00:00:00</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>2025-09-26 00:00:00</t>
+          <t>2024-03-28 00:00:00</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2025-11-04 00:00:00</t>
+          <t>2024-04-02 00:00:00</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>47.85</t>
+          <t>99.1</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>98.6</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -2981,12 +2981,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>40.15</t>
+          <t>123.5</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>44.5</t>
+          <t>118.0</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -2996,22 +2996,22 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-6.91</t>
+          <t>-30.32</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>7.53</t>
+          <t>-16.02</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025/07/28</t>
+          <t>2025/06/02</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>40.4</t>
+          <t>92.4</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -3021,67 +3021,67 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>2025/09/19</t>
+          <t>2025/11/13</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>38.9</t>
+          <t>79.9</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>2025/07/04</t>
+          <t>2025/06/20</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>37.85</t>
+          <t>90.1</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>2025/11/25</t>
+          <t>2025/10/23</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>2025/11/04</t>
+          <t>2025/07/31</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>44.5</t>
+          <t>86.9</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>2025-11-07 00:00:00</t>
+          <t>2025-11-28 00:00:00</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>10.03</t>
+          <t>13.88</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -3092,121 +3092,121 @@
       <c r="AP6" t="inlineStr"/>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>2624</t>
+          <t>674</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>27.66</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>16.68</t>
+          <t>31.48</t>
         </is>
       </c>
       <c r="AU6" t="n">
-        <v>0.02</v>
+        <v>0.41</v>
       </c>
       <c r="AV6" t="n">
-        <v>-4.34</v>
+        <v>-2.42</v>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>-8.66</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>7.64</t>
+          <t>-2.67</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>48.49</t>
+          <t>68.42</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>50.69</v>
+        <v>70.12</v>
       </c>
       <c r="BA6" t="n">
-        <v>49.09</v>
+        <v>76.76000000000001</v>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>45.61</t>
+          <t>78.87</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-780.06</t>
+          <t>9.28</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>-0.49</v>
+        <v>-2.34</v>
       </c>
       <c r="BE6" t="n">
-        <v>0.07000000000000001</v>
+        <v>-2.58</v>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>2.97</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-97.59</t>
+          <t>-248.65</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2025/11/06</t>
+          <t>2025/12/15</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>413483698.6976421</t>
+          <t>67197780.36772853</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
         <is>
-          <t>183541718.0</t>
+          <t>17906877.0</t>
         </is>
       </c>
       <c r="BK6" t="n">
-        <v>255848681.6</v>
+        <v>27813361</v>
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>250000286.1</t>
+          <t>27215289.8</t>
         </is>
       </c>
       <c r="BM6" t="n">
-        <v>462930721.8</v>
+        <v>41606784.8</v>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>5848395</t>
+          <t>598071</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>-46559472.91814587</t>
+          <t>-2412779.841971723</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>-42167407.71421093</t>
+          <t>-4532030.643383615</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>183541718.0</t>
+          <t>17906877.0</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -3216,32 +3216,32 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>43.85</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>2025/10/20</t>
+          <t>2025/10/15</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>10.60</t>
+          <t>-23.07</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>台塑化</t>
+          <t>中碳</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
         <is>
-          <t>台塑化</t>
+          <t>中碳</t>
         </is>
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>油電燃氣業</t>
+          <t>化學工業</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
@@ -3251,117 +3251,117 @@
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
         <is>
-          <t>-16.06351948126612</t>
+          <t>-7.32116827620037</t>
         </is>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>-3.054910686901505</t>
+          <t>-26.54178546817805</t>
         </is>
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>-6.074976069093286</t>
+          <t>-23.30870698662894</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>6.57</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
         <is>
-          <t>17.17</t>
+          <t>5.94</t>
         </is>
       </c>
       <c r="CI6" t="inlineStr">
         <is>
-          <t>76.56</t>
+          <t>21.61</t>
         </is>
       </c>
       <c r="CJ6" t="inlineStr">
         <is>
-          <t>7.31%</t>
+          <t>17.52%</t>
         </is>
       </c>
       <c r="CK6" t="inlineStr">
         <is>
-          <t>5.68%</t>
+          <t>6.35%</t>
         </is>
       </c>
       <c r="CL6" t="inlineStr">
         <is>
-          <t>27.06</t>
+          <t>52.23</t>
         </is>
       </c>
       <c r="CM6" t="inlineStr">
         <is>
-          <t>466772</t>
+          <t>16228</t>
         </is>
       </c>
       <c r="CN6" t="inlineStr">
         <is>
-          <t>汽油,柴油等各項石油製品75.50%、乙烯,丙烯等石油化學品18.10%、電力,蒸汽6.00%、其他0.40% (2024年)</t>
+          <t>煤焦油及化學品系列產品53.20%、輕油及油品系列產品29.03%、精碳材料9.72%、焦碳製品6.62%、其他1.43% (2024年)</t>
         </is>
       </c>
       <c r="CO6" t="inlineStr">
         <is>
-          <t>台塑化-油電燃氣業-上市</t>
+          <t>中碳-化學工業-上市</t>
         </is>
       </c>
       <c r="CP6" t="inlineStr">
         <is>
-          <t>油電燃氣業右下上市</t>
+          <t>化學工業右下上市</t>
         </is>
       </c>
       <c r="CQ6" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>68.6</t>
         </is>
       </c>
       <c r="CR6" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="CS6" t="inlineStr">
         <is>
-          <t>48.15</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="CT6" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="CU6" t="inlineStr">
         <is>
-          <t>32.21</t>
+          <t>33.12</t>
         </is>
       </c>
       <c r="CV6" t="inlineStr">
         <is>
-          <t>** 石化及塑橡膠 - 石化上游原料及相關鑽探設備** 油電燃氣 - 加油站、汽電共生</t>
+          <t>** 石化及塑橡膠 - 石化上游原料及相關鑽探設備** 電動車輛產業 - 鋰電池材料** 能源元件 - 原材料</t>
         </is>
       </c>
       <c r="CW6" t="inlineStr">
@@ -3373,22 +3373,22 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>6505</t>
+          <t>1723</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>6166.464</t>
+          <t>327.223</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>48.6</t>
+          <t>68.6</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3408,17 +3408,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>9.25</t>
+          <t>-12.29</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3428,37 +3428,37 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-99.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2025-11-06 00:00:00</t>
+          <t>2025-02-26 00:00:00</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2025-11-25 00:00:00</t>
+          <t>2025-03-12 00:00:00</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>2025-09-26 00:00:00</t>
+          <t>2024-03-28 00:00:00</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2025-11-04 00:00:00</t>
+          <t>2024-04-02 00:00:00</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>47.85</t>
+          <t>99.1</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>98.6</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -3468,12 +3468,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>40.15</t>
+          <t>123.5</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>44.5</t>
+          <t>118.0</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -3483,22 +3483,22 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-6.72</t>
+          <t>-30.43</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>7.53</t>
+          <t>-16.02</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025/07/28</t>
+          <t>2025/06/02</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>40.4</t>
+          <t>92.4</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -3508,67 +3508,67 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>2025/09/19</t>
+          <t>2025/11/13</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>38.9</t>
+          <t>79.9</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>2025/07/04</t>
+          <t>2025/06/20</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>37.85</t>
+          <t>90.1</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>2025/11/25</t>
+          <t>2025/10/23</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>2025/11/04</t>
+          <t>2025/07/31</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>44.5</t>
+          <t>86.9</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>2025-11-07 00:00:00</t>
+          <t>2025-11-28 00:00:00</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>16.34</t>
+          <t>17.39</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -3579,121 +3579,121 @@
       <c r="AP7" t="inlineStr"/>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>2624</t>
+          <t>674</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>22.39</t>
+          <t>44.44</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>7.46</t>
+          <t>14.81</t>
         </is>
       </c>
       <c r="AU7" t="n">
-        <v>-0.47</v>
+        <v>0.09</v>
       </c>
       <c r="AV7" t="n">
-        <v>-4.33</v>
+        <v>-2.54</v>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>4.23</t>
+          <t>-8.83</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>7.54</t>
+          <t>-2.40</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>48.83</t>
+          <t>68.53999999999999</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>51.04</v>
+        <v>70.31999999999999</v>
       </c>
       <c r="BA7" t="n">
-        <v>48.97</v>
+        <v>77.14</v>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>45.53</t>
+          <t>79.04</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-300.61</t>
+          <t>6.64</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>-0.42</v>
+        <v>-2.46</v>
       </c>
       <c r="BE7" t="n">
-        <v>0.21</v>
+        <v>-2.64</v>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>2.97</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-92.88</t>
+          <t>-252.10</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2025/11/06</t>
+          <t>2025/12/15</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>413483698.6976421</t>
+          <t>67197780.36772853</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
         <is>
-          <t>298996860.0</t>
+          <t>22368625.0</t>
         </is>
       </c>
       <c r="BK7" t="n">
-        <v>279645957.6</v>
+        <v>28384364.6</v>
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>255960435.9</t>
+          <t>32361196.0</t>
         </is>
       </c>
       <c r="BM7" t="n">
-        <v>464661723.26</v>
+        <v>43621757.96</v>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>23685521</t>
+          <t>-3976831</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>-47358030.22795221</t>
+          <t>-2027461.514442288</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>-39689924.93791449</t>
+          <t>-3891436.675622828</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>298996860.0</t>
+          <t>22368625.0</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3703,32 +3703,32 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>43.85</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>2025/10/20</t>
+          <t>2025/10/15</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>10.83</t>
+          <t>-23.18</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>台塑化</t>
+          <t>中碳</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
         <is>
-          <t>台塑化</t>
+          <t>中碳</t>
         </is>
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>油電燃氣業</t>
+          <t>化學工業</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
@@ -3738,117 +3738,117 @@
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
         <is>
-          <t>-16.06351948126612</t>
+          <t>-7.32116827620037</t>
         </is>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>-3.054910686901505</t>
+          <t>-26.54178546817805</t>
         </is>
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>-6.074976069093286</t>
+          <t>-23.30870698662894</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>6.57</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
         <is>
-          <t>17.17</t>
+          <t>5.94</t>
         </is>
       </c>
       <c r="CI7" t="inlineStr">
         <is>
-          <t>76.56</t>
+          <t>21.61</t>
         </is>
       </c>
       <c r="CJ7" t="inlineStr">
         <is>
-          <t>7.31%</t>
+          <t>17.52%</t>
         </is>
       </c>
       <c r="CK7" t="inlineStr">
         <is>
-          <t>5.68%</t>
+          <t>6.35%</t>
         </is>
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>27.06</t>
+          <t>52.23</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
         <is>
-          <t>466772</t>
+          <t>16228</t>
         </is>
       </c>
       <c r="CN7" t="inlineStr">
         <is>
-          <t>汽油,柴油等各項石油製品75.50%、乙烯,丙烯等石油化學品18.10%、電力,蒸汽6.00%、其他0.40% (2024年)</t>
+          <t>煤焦油及化學品系列產品53.20%、輕油及油品系列產品29.03%、精碳材料9.72%、焦碳製品6.62%、其他1.43% (2024年)</t>
         </is>
       </c>
       <c r="CO7" t="inlineStr">
         <is>
-          <t>台塑化-油電燃氣業-上市</t>
+          <t>中碳-化學工業-上市</t>
         </is>
       </c>
       <c r="CP7" t="inlineStr">
         <is>
-          <t>油電燃氣業右下上市</t>
+          <t>化學工業右下上市</t>
         </is>
       </c>
       <c r="CQ7" t="inlineStr">
         <is>
-          <t>47.75</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="CR7" t="inlineStr">
         <is>
-          <t>48.85</t>
+          <t>68.6</t>
         </is>
       </c>
       <c r="CS7" t="inlineStr">
         <is>
-          <t>47.7</t>
+          <t>67.7</t>
         </is>
       </c>
       <c r="CT7" t="inlineStr">
         <is>
-          <t>48.6</t>
+          <t>68.6</t>
         </is>
       </c>
       <c r="CU7" t="inlineStr">
         <is>
-          <t>32.21</t>
+          <t>33.12</t>
         </is>
       </c>
       <c r="CV7" t="inlineStr">
         <is>
-          <t>** 石化及塑橡膠 - 石化上游原料及相關鑽探設備** 油電燃氣 - 加油站、汽電共生</t>
+          <t>** 石化及塑橡膠 - 石化上游原料及相關鑽探設備** 電動車輛產業 - 鋰電池材料** 能源元件 - 原材料</t>
         </is>
       </c>
       <c r="CW7" t="inlineStr">
@@ -3860,22 +3860,22 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>6505</t>
+          <t>1723</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>4076.634</t>
+          <t>558.986</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3885,7 +3885,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>47.85</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3895,17 +3895,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-4.10</t>
+          <t>-27.31</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3915,37 +3915,37 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-99.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2025-11-06 00:00:00</t>
+          <t>2025-02-26 00:00:00</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2025-11-25 00:00:00</t>
+          <t>2025-03-12 00:00:00</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>2025-09-26 00:00:00</t>
+          <t>2024-03-28 00:00:00</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2025-11-04 00:00:00</t>
+          <t>2024-04-02 00:00:00</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>47.85</t>
+          <t>99.1</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>98.6</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -3955,12 +3955,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>40.15</t>
+          <t>123.5</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>44.5</t>
+          <t>118.0</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -3970,22 +3970,22 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-8.16</t>
+          <t>-31.24</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>7.53</t>
+          <t>-16.02</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025/07/28</t>
+          <t>2025/06/02</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>40.4</t>
+          <t>92.4</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -3995,67 +3995,67 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>2025/09/19</t>
+          <t>2025/11/13</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>38.9</t>
+          <t>79.9</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>2025/07/04</t>
+          <t>2025/06/20</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>37.85</t>
+          <t>90.1</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>2025/11/25</t>
+          <t>2025/10/23</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>2025/11/04</t>
+          <t>2025/07/31</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>44.5</t>
+          <t>86.9</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>2025-11-07 00:00:00</t>
+          <t>2025-11-28 00:00:00</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>10.81</t>
+          <t>29.70</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>-2.19</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -4066,12 +4066,12 @@
       <c r="AP8" t="inlineStr"/>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>2624</t>
+          <t>674</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -4081,106 +4081,106 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>4.21</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="AU8" t="n">
-        <v>-2.09</v>
+        <v>-1.37</v>
       </c>
       <c r="AV8" t="n">
-        <v>-4.66</v>
+        <v>-2.7</v>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>4.96</t>
+          <t>-8.8</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>7.41</t>
+          <t>-2.19</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>48.87</t>
+          <t>68.74</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>51.26</v>
+        <v>70.65000000000001</v>
       </c>
       <c r="BA8" t="n">
-        <v>48.83</v>
+        <v>77.45999999999999</v>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>45.46</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-193.82</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>-0.35</v>
+        <v>-2.57</v>
       </c>
       <c r="BE8" t="n">
-        <v>0.37</v>
+        <v>-2.68</v>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>2.97</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-87.53</t>
+          <t>-254.62</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2025/11/06</t>
+          <t>2025/12/15</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>413483698.6976421</t>
+          <t>67197780.36772853</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
         <is>
-          <t>196310295.0</t>
+          <t>37931209.0</t>
         </is>
       </c>
       <c r="BK8" t="n">
-        <v>252188376.8</v>
+        <v>28647934.4</v>
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>262982332.6</t>
+          <t>39410503.3</t>
         </is>
       </c>
       <c r="BM8" t="n">
-        <v>465751913.52</v>
+        <v>44290902.44</v>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>-10793955</t>
+          <t>-10762568</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>-48752231.18977726</t>
+          <t>-1688556.939682189</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>-47103360.29542267</t>
+          <t>-3315366.983263746</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>196310295.0</t>
+          <t>37931209.0</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -4190,32 +4190,32 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>43.85</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>2025/10/20</t>
+          <t>2025/10/15</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>9.12</t>
+          <t>-24.08</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>台塑化</t>
+          <t>中碳</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
         <is>
-          <t>台塑化</t>
+          <t>中碳</t>
         </is>
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>油電燃氣業</t>
+          <t>化學工業</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
@@ -4225,117 +4225,117 @@
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
         <is>
-          <t>-16.06351948126612</t>
+          <t>-7.32116827620037</t>
         </is>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>-3.054910686901505</t>
+          <t>-26.54178546817805</t>
         </is>
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>-6.074976069093286</t>
+          <t>-23.30870698662894</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>6.57</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
         <is>
-          <t>17.17</t>
+          <t>5.94</t>
         </is>
       </c>
       <c r="CI8" t="inlineStr">
         <is>
-          <t>76.56</t>
+          <t>21.61</t>
         </is>
       </c>
       <c r="CJ8" t="inlineStr">
         <is>
-          <t>7.31%</t>
+          <t>17.52%</t>
         </is>
       </c>
       <c r="CK8" t="inlineStr">
         <is>
-          <t>5.68%</t>
+          <t>6.35%</t>
         </is>
       </c>
       <c r="CL8" t="inlineStr">
         <is>
-          <t>27.06</t>
+          <t>52.23</t>
         </is>
       </c>
       <c r="CM8" t="inlineStr">
         <is>
-          <t>466772</t>
+          <t>16228</t>
         </is>
       </c>
       <c r="CN8" t="inlineStr">
         <is>
-          <t>汽油,柴油等各項石油製品75.50%、乙烯,丙烯等石油化學品18.10%、電力,蒸汽6.00%、其他0.40% (2024年)</t>
+          <t>煤焦油及化學品系列產品53.20%、輕油及油品系列產品29.03%、精碳材料9.72%、焦碳製品6.62%、其他1.43% (2024年)</t>
         </is>
       </c>
       <c r="CO8" t="inlineStr">
         <is>
-          <t>台塑化-油電燃氣業-上市</t>
+          <t>中碳-化學工業-上市</t>
         </is>
       </c>
       <c r="CP8" t="inlineStr">
         <is>
-          <t>油電燃氣業右下上市</t>
+          <t>化學工業右下上市</t>
         </is>
       </c>
       <c r="CQ8" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>67.5</t>
         </is>
       </c>
       <c r="CR8" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>68.3</t>
         </is>
       </c>
       <c r="CS8" t="inlineStr">
         <is>
-          <t>47.75</t>
+          <t>67.5</t>
         </is>
       </c>
       <c r="CT8" t="inlineStr">
         <is>
-          <t>47.85</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="CU8" t="inlineStr">
         <is>
-          <t>32.21</t>
+          <t>33.12</t>
         </is>
       </c>
       <c r="CV8" t="inlineStr">
         <is>
-          <t>** 石化及塑橡膠 - 石化上游原料及相關鑽探設備** 油電燃氣 - 加油站、汽電共生</t>
+          <t>** 石化及塑橡膠 - 石化上游原料及相關鑽探設備** 電動車輛產業 - 鋰電池材料** 能源元件 - 原材料</t>
         </is>
       </c>
       <c r="CW8" t="inlineStr">
@@ -4347,22 +4347,22 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>6505</t>
+          <t>1723</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-2.02</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>6537.079</t>
+          <t>645.775</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4372,7 +4372,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>48.25</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -4382,17 +4382,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-36.06</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4402,37 +4402,37 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-99.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2025-11-06 00:00:00</t>
+          <t>2025-02-26 00:00:00</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2025-11-25 00:00:00</t>
+          <t>2025-03-12 00:00:00</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>2025-09-26 00:00:00</t>
+          <t>2024-03-28 00:00:00</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2025-11-04 00:00:00</t>
+          <t>2024-04-02 00:00:00</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>47.85</t>
+          <t>99.1</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>98.6</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -4442,12 +4442,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>40.15</t>
+          <t>123.5</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>44.5</t>
+          <t>118.0</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -4457,22 +4457,22 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-7.39</t>
+          <t>-31.03</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>7.53</t>
+          <t>-16.02</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025/07/28</t>
+          <t>2025/06/02</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>40.4</t>
+          <t>92.4</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -4487,62 +4487,62 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>2025/09/19</t>
+          <t>2025/11/13</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>38.9</t>
+          <t>79.9</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>2025/07/04</t>
+          <t>2025/06/20</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>37.85</t>
+          <t>90.1</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>2025/11/25</t>
+          <t>2025/10/23</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>2025/11/04</t>
+          <t>2025/07/31</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>44.5</t>
+          <t>86.9</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>2025-11-07 00:00:00</t>
+          <t>2025-11-28 00:00:00</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>17.33</t>
+          <t>34.31</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>-3.83</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
@@ -4553,12 +4553,12 @@
       <c r="AP9" t="inlineStr"/>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>2624</t>
+          <t>674</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4568,106 +4568,106 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>15.09</t>
+          <t>17.09</t>
         </is>
       </c>
       <c r="AU9" t="n">
-        <v>-1.59</v>
+        <v>-1.56</v>
       </c>
       <c r="AV9" t="n">
-        <v>-5.12</v>
+        <v>-2.8</v>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>6.13</t>
+          <t>-8.65</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>7.22</t>
+          <t>-1.98</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>49.02999999999999</t>
+          <t>69.08</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>51.68</v>
+        <v>71.06999999999999</v>
       </c>
       <c r="BA9" t="n">
-        <v>48.69</v>
+        <v>77.8</v>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>45.41</t>
+          <t>79.37</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-130.58</t>
+          <t>4.07</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>-0.17</v>
+        <v>-2.6</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.55</v>
+        <v>-2.71</v>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>2.97</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-81.48</t>
+          <t>-256.17</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2025/11/06</t>
+          <t>2025/12/15</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>413483698.6976421</t>
+          <t>67197780.36772853</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
         <is>
-          <t>318432117.0</t>
+          <t>44075659.0</t>
         </is>
       </c>
       <c r="BK9" t="n">
-        <v>276590629</v>
+        <v>25827808.6</v>
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>277420485.8</t>
+          <t>40393503.0</t>
         </is>
       </c>
       <c r="BM9" t="n">
-        <v>468801755</v>
+        <v>45004981.12</v>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>-829856</t>
+          <t>-14565694</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>-49052025.89784172</t>
+          <t>-1392773.295394634</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>-45009587.40274072</t>
+          <t>-4041424.030491352</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>318432117.0</t>
+          <t>44075659.0</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4677,32 +4677,32 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>43.85</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>2025/10/20</t>
+          <t>2025/10/15</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>10.03</t>
+          <t>-23.85</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>台塑化</t>
+          <t>中碳</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
         <is>
-          <t>台塑化</t>
+          <t>中碳</t>
         </is>
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>油電燃氣業</t>
+          <t>化學工業</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
@@ -4712,27 +4712,27 @@
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
         <is>
-          <t>-16.06351948126612</t>
+          <t>-7.32116827620037</t>
         </is>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>-3.054910686901505</t>
+          <t>-26.54178546817805</t>
         </is>
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>-6.074976069093286</t>
+          <t>-23.30870698662894</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
@@ -4742,87 +4742,87 @@
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>6.57</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
         <is>
-          <t>17.17</t>
+          <t>5.94</t>
         </is>
       </c>
       <c r="CI9" t="inlineStr">
         <is>
-          <t>76.56</t>
+          <t>21.61</t>
         </is>
       </c>
       <c r="CJ9" t="inlineStr">
         <is>
-          <t>7.31%</t>
+          <t>17.52%</t>
         </is>
       </c>
       <c r="CK9" t="inlineStr">
         <is>
-          <t>5.68%</t>
+          <t>6.35%</t>
         </is>
       </c>
       <c r="CL9" t="inlineStr">
         <is>
-          <t>27.06</t>
+          <t>52.23</t>
         </is>
       </c>
       <c r="CM9" t="inlineStr">
         <is>
-          <t>466772</t>
+          <t>16228</t>
         </is>
       </c>
       <c r="CN9" t="inlineStr">
         <is>
-          <t>汽油,柴油等各項石油製品75.50%、乙烯,丙烯等石油化學品18.10%、電力,蒸汽6.00%、其他0.40% (2024年)</t>
+          <t>煤焦油及化學品系列產品53.20%、輕油及油品系列產品29.03%、精碳材料9.72%、焦碳製品6.62%、其他1.43% (2024年)</t>
         </is>
       </c>
       <c r="CO9" t="inlineStr">
         <is>
-          <t>台塑化-油電燃氣業-上市</t>
+          <t>中碳-化學工業-上市</t>
         </is>
       </c>
       <c r="CP9" t="inlineStr">
         <is>
-          <t>油電燃氣業右下上市</t>
+          <t>化學工業右下上市</t>
         </is>
       </c>
       <c r="CQ9" t="inlineStr">
         <is>
-          <t>49.6</t>
+          <t>69.2</t>
         </is>
       </c>
       <c r="CR9" t="inlineStr">
         <is>
-          <t>50.2</t>
+          <t>69.2</t>
         </is>
       </c>
       <c r="CS9" t="inlineStr">
         <is>
-          <t>48.15</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="CT9" t="inlineStr">
         <is>
-          <t>48.25</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="CU9" t="inlineStr">
         <is>
-          <t>32.21</t>
+          <t>33.12</t>
         </is>
       </c>
       <c r="CV9" t="inlineStr">
         <is>
-          <t>** 石化及塑橡膠 - 石化上游原料及相關鑽探設備** 油電燃氣 - 加油站、汽電共生</t>
+          <t>** 石化及塑橡膠 - 石化上游原料及相關鑽探設備** 電動車輛產業 - 鋰電池材料** 能源元件 - 原材料</t>
         </is>
       </c>
       <c r="CW9" t="inlineStr">
@@ -4834,22 +4834,22 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>6505</t>
+          <t>1723</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>5670.755</t>
+          <t>242.836</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4859,7 +4859,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>49.25</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4869,167 +4869,167 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
+          <t>-1.63</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>-36.13</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>-99.0</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>2025-02-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>2025-03-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>2024-03-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>2024-04-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>99.1</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>98.6</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>123.5</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>118.0</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>-30.02</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>-16.02</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025/06/02</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>92.4</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>2025/11/13</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>79.9</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>2025/06/20</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>90.1</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>2025/10/23</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>83.8</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>2025/07/31</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>86.9</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>2025-11-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>2025-12-17</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>12.90</t>
+        </is>
+      </c>
+      <c r="AN10" t="inlineStr">
+        <is>
           <t>-0.72</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>-7.22</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>-50.0</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>2025-11-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>2025-11-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>2025-09-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>2025-11-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>47.85</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>52.1</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>40.15</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>44.5</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>-5.47</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>7.53</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>2025/07/28</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>40.4</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>0.04</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>2025/09/19</t>
-        </is>
-      </c>
-      <c r="AD10" t="inlineStr">
-        <is>
-          <t>38.9</t>
-        </is>
-      </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>2025/07/04</t>
-        </is>
-      </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>37.85</t>
-        </is>
-      </c>
-      <c r="AG10" t="inlineStr">
-        <is>
-          <t>2025/11/25</t>
-        </is>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>52.1</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>2025/11/04</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>44.5</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>2025-11-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="AL10" t="inlineStr">
-        <is>
-          <t>2025-12-16</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>15.03</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>-2.54</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
@@ -5040,121 +5040,121 @@
       <c r="AP10" t="inlineStr"/>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>2624</t>
+          <t>674</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>12.63</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>16.04</t>
+          <t>29.21</t>
         </is>
       </c>
       <c r="AU10" t="n">
-        <v>-0.2</v>
+        <v>-0.49</v>
       </c>
       <c r="AV10" t="n">
-        <v>-4.98</v>
+        <v>-3.05</v>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>7.11</t>
+          <t>-8.4</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>6.94</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>49.35</t>
+          <t>69.34</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>51.94</v>
+        <v>71.53</v>
       </c>
       <c r="BA10" t="n">
-        <v>48.49</v>
+        <v>78.09</v>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>45.34</t>
+          <t>79.54</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-96.92</t>
+          <t>4.56</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>0.02</v>
+        <v>-2.61</v>
       </c>
       <c r="BE10" t="n">
-        <v>0.73</v>
+        <v>-2.73</v>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>2.97</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-75.44</t>
+          <t>-257.76</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2025/11/06</t>
+          <t>2025/12/15</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>413483698.6976421</t>
+          <t>67197780.36772853</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
         <is>
-          <t>281962418.0</t>
+          <t>16784435.0</t>
         </is>
       </c>
       <c r="BK10" t="n">
-        <v>261479440.6</v>
+        <v>24770508.8</v>
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>281835618.8</t>
+          <t>38781600.1</t>
         </is>
       </c>
       <c r="BM10" t="n">
-        <v>467776139.32</v>
+        <v>44611489.72</v>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>-20356178</t>
+          <t>-14011091</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>-49787014.71513281</t>
+          <t>-911200.4344679575</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>-53495478.93452573</t>
+          <t>-5592645.739727527</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>281962418.0</t>
+          <t>16784435.0</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -5164,32 +5164,32 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>43.85</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>2025/10/20</t>
+          <t>2025/10/15</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>12.31</t>
+          <t>-22.73</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>台塑化</t>
+          <t>中碳</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
         <is>
-          <t>台塑化</t>
+          <t>中碳</t>
         </is>
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>油電燃氣業</t>
+          <t>化學工業</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
@@ -5199,27 +5199,27 @@
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
         <is>
-          <t>-16.06351948126612</t>
+          <t>-7.32116827620037</t>
         </is>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>-3.054910686901505</t>
+          <t>-26.54178546817805</t>
         </is>
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>-6.074976069093286</t>
+          <t>-23.30870698662894</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
@@ -5229,87 +5229,87 @@
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>6.57</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
         <is>
-          <t>17.17</t>
+          <t>5.94</t>
         </is>
       </c>
       <c r="CI10" t="inlineStr">
         <is>
-          <t>76.56</t>
+          <t>21.61</t>
         </is>
       </c>
       <c r="CJ10" t="inlineStr">
         <is>
-          <t>7.31%</t>
+          <t>17.52%</t>
         </is>
       </c>
       <c r="CK10" t="inlineStr">
         <is>
-          <t>5.68%</t>
+          <t>6.35%</t>
         </is>
       </c>
       <c r="CL10" t="inlineStr">
         <is>
-          <t>27.06</t>
+          <t>52.23</t>
         </is>
       </c>
       <c r="CM10" t="inlineStr">
         <is>
-          <t>466772</t>
+          <t>16228</t>
         </is>
       </c>
       <c r="CN10" t="inlineStr">
         <is>
-          <t>汽油,柴油等各項石油製品75.50%、乙烯,丙烯等石油化學品18.10%、電力,蒸汽6.00%、其他0.40% (2024年)</t>
+          <t>煤焦油及化學品系列產品53.20%、輕油及油品系列產品29.03%、精碳材料9.72%、焦碳製品6.62%、其他1.43% (2024年)</t>
         </is>
       </c>
       <c r="CO10" t="inlineStr">
         <is>
-          <t>台塑化-油電燃氣業-上市</t>
+          <t>中碳-化學工業-上市</t>
         </is>
       </c>
       <c r="CP10" t="inlineStr">
         <is>
-          <t>油電燃氣業右下上市</t>
+          <t>化學工業右下上市</t>
         </is>
       </c>
       <c r="CQ10" t="inlineStr">
         <is>
-          <t>49.45</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="CR10" t="inlineStr">
         <is>
-          <t>50.5</t>
+          <t>69.5</t>
         </is>
       </c>
       <c r="CS10" t="inlineStr">
         <is>
-          <t>49.25</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="CT10" t="inlineStr">
         <is>
-          <t>49.25</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="CU10" t="inlineStr">
         <is>
-          <t>32.21</t>
+          <t>33.12</t>
         </is>
       </c>
       <c r="CV10" t="inlineStr">
         <is>
-          <t>** 石化及塑橡膠 - 石化上游原料及相關鑽探設備** 油電燃氣 - 加油站、汽電共生</t>
+          <t>** 石化及塑橡膠 - 石化上游原料及相關鑽探設備** 電動車輛產業 - 鋰電池材料** 能源元件 - 原材料</t>
         </is>
       </c>
       <c r="CW10" t="inlineStr">
@@ -5321,22 +5321,22 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>6505</t>
+          <t>1723</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2.89</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>6042.766</t>
+          <t>299.387</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5346,7 +5346,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>50.2</t>
+          <t>69.3</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -5356,17 +5356,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-2.45</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-18.31</t>
+          <t>-33.41</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -5376,37 +5376,37 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-99.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2025-11-06 00:00:00</t>
+          <t>2025-02-26 00:00:00</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2025-11-25 00:00:00</t>
+          <t>2025-03-12 00:00:00</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>2025-09-26 00:00:00</t>
+          <t>2024-03-28 00:00:00</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2025-11-04 00:00:00</t>
+          <t>2024-04-02 00:00:00</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>47.85</t>
+          <t>99.1</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>98.6</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>40.15</t>
+          <t>123.5</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>44.5</t>
+          <t>118.0</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -5431,22 +5431,22 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-3.65</t>
+          <t>-29.72</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>7.53</t>
+          <t>-16.02</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025/07/28</t>
+          <t>2025/06/02</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>40.4</t>
+          <t>92.4</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -5456,67 +5456,67 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>2025/09/19</t>
+          <t>2025/11/13</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>38.9</t>
+          <t>79.9</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>2025/07/04</t>
+          <t>2025/06/20</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>37.85</t>
+          <t>90.1</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>2025/11/25</t>
+          <t>2025/10/23</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>2025/11/04</t>
+          <t>2025/07/31</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>44.5</t>
+          <t>86.9</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>2025-11-07 00:00:00</t>
+          <t>2025-11-28 00:00:00</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>16.02</t>
+          <t>15.91</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>3.41</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
@@ -5527,121 +5527,121 @@
       <c r="AP11" t="inlineStr"/>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>2624</t>
+          <t>674</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>32.63</t>
+          <t>27.27</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>11.83</t>
+          <t>32.32</t>
         </is>
       </c>
       <c r="AU11" t="n">
-        <v>0.92</v>
+        <v>0.09</v>
       </c>
       <c r="AV11" t="n">
-        <v>-4.68</v>
+        <v>-3.75</v>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>8.03</t>
+          <t>-8.16</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>6.81</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>49.73999999999999</t>
+          <t>69.24</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>52.18</v>
+        <v>71.94</v>
       </c>
       <c r="BA11" t="n">
-        <v>48.3</v>
+        <v>78.34</v>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>45.22</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-81.94</t>
+          <t>2.73</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>0.16</v>
+        <v>-2.69</v>
       </c>
       <c r="BE11" t="n">
-        <v>0.91</v>
+        <v>-2.77</v>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>2.97</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-69.49</t>
+          <t>-259.56</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2025/11/06</t>
+          <t>2025/12/15</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>413483698.6976421</t>
+          <t>67197780.36772853</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
         <is>
-          <t>302528098.0</t>
+          <t>20761895.0</t>
         </is>
       </c>
       <c r="BK11" t="n">
-        <v>244151890.6</v>
+        <v>26617218.6</v>
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>298878172.2</t>
+          <t>39969195.1</t>
         </is>
       </c>
       <c r="BM11" t="n">
-        <v>465434594.7</v>
+        <v>44662589.56</v>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>-54726281</t>
+          <t>-13351976</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>-49112748.49342501</t>
+          <t>-60028.56078439939</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>-59800160.55369985</t>
+          <t>-4684879.690788925</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>302528098.0</t>
+          <t>20761895.0</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5651,32 +5651,32 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>43.85</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>2025/10/20</t>
+          <t>2025/10/15</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>14.48</t>
+          <t>-22.40</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>台塑化</t>
+          <t>中碳</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
         <is>
-          <t>台塑化</t>
+          <t>中碳</t>
         </is>
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>油電燃氣業</t>
+          <t>化學工業</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
@@ -5686,27 +5686,27 @@
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
         <is>
-          <t>-16.06351948126612</t>
+          <t>-7.32116827620037</t>
         </is>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>-3.054910686901505</t>
+          <t>-26.54178546817805</t>
         </is>
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>-6.074976069093286</t>
+          <t>-23.30870698662894</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
@@ -5716,87 +5716,87 @@
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>6.57</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
         <is>
-          <t>17.17</t>
+          <t>5.94</t>
         </is>
       </c>
       <c r="CI11" t="inlineStr">
         <is>
-          <t>76.56</t>
+          <t>21.61</t>
         </is>
       </c>
       <c r="CJ11" t="inlineStr">
         <is>
-          <t>7.31%</t>
+          <t>17.52%</t>
         </is>
       </c>
       <c r="CK11" t="inlineStr">
         <is>
-          <t>5.68%</t>
+          <t>6.35%</t>
         </is>
       </c>
       <c r="CL11" t="inlineStr">
         <is>
-          <t>27.06</t>
+          <t>52.23</t>
         </is>
       </c>
       <c r="CM11" t="inlineStr">
         <is>
-          <t>466772</t>
+          <t>16228</t>
         </is>
       </c>
       <c r="CN11" t="inlineStr">
         <is>
-          <t>汽油,柴油等各項石油製品75.50%、乙烯,丙烯等石油化學品18.10%、電力,蒸汽6.00%、其他0.40% (2024年)</t>
+          <t>煤焦油及化學品系列產品53.20%、輕油及油品系列產品29.03%、精碳材料9.72%、焦碳製品6.62%、其他1.43% (2024年)</t>
         </is>
       </c>
       <c r="CO11" t="inlineStr">
         <is>
-          <t>台塑化-油電燃氣業-上市</t>
+          <t>中碳-化學工業-上市</t>
         </is>
       </c>
       <c r="CP11" t="inlineStr">
         <is>
-          <t>油電燃氣業右下上市</t>
+          <t>化學工業右下上市</t>
         </is>
       </c>
       <c r="CQ11" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>69.5</t>
         </is>
       </c>
       <c r="CR11" t="inlineStr">
         <is>
-          <t>50.9</t>
+          <t>69.8</t>
         </is>
       </c>
       <c r="CS11" t="inlineStr">
         <is>
-          <t>47.9</t>
+          <t>68.8</t>
         </is>
       </c>
       <c r="CT11" t="inlineStr">
         <is>
-          <t>50.2</t>
+          <t>69.3</t>
         </is>
       </c>
       <c r="CU11" t="inlineStr">
         <is>
-          <t>32.21</t>
+          <t>33.12</t>
         </is>
       </c>
       <c r="CV11" t="inlineStr">
         <is>
-          <t>** 石化及塑橡膠 - 石化上游原料及相關鑽探設備** 油電燃氣 - 加油站、汽電共生</t>
+          <t>** 石化及塑橡膠 - 石化上游原料及相關鑽探設備** 電動車輛產業 - 鋰電池材料** 能源元件 - 原材料</t>
         </is>
       </c>
       <c r="CW11" t="inlineStr">
@@ -5806,50 +5806,54 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr"/>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1723</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
+          <t>-0.68</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>26487.92</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>58.3</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-19.23</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5859,37 +5863,37 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-27 00:00:00</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-10 00:00:00</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-11 00:00:00</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-26 00:00:00</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>56.2</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>61.4</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -5899,12 +5903,12 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -5914,217 +5918,217 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-5.05</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9.98</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025/07/28</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>37.0</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025/09/26</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>39.6</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025/04/08</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>28.85</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025/12/10</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>61.4</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025/11/26</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-10 00:00:00</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7.86</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr"/>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>319</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>658</t>
+          <t>26488</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>25.52</t>
         </is>
       </c>
       <c r="AU12" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="AV12" t="n">
-        <v>0</v>
+        <v>-3.83</v>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>13.94</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10.75</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>58.27999999999999</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>0</v>
+        <v>60.6</v>
       </c>
       <c r="BA12" t="n">
-        <v>0</v>
+        <v>53.18</v>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>48.02</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-42.35</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="BE12" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.51</t>
         </is>
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-58.82</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025/11/27</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1605256682.65097</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1545925762.0</t>
         </is>
       </c>
       <c r="BK12" t="n">
-        <v>0</v>
+        <v>2816775873.8</v>
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3487467287.4</t>
         </is>
       </c>
       <c r="BM12" t="n">
-        <v>0</v>
+        <v>5761704538.5</v>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-670691413</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-683206907.0130951</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-828598323.6169515</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1545925762.0</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -6134,32 +6138,32 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>41.9</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025/10/21</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>39.14</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>中碳</t>
+          <t>南亞</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
         <is>
-          <t>中碳</t>
+          <t>南亞</t>
         </is>
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>化學工業</t>
+          <t>塑膠工業</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
@@ -6169,27 +6173,27 @@
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
         <is>
-          <t>-7.32116827620037</t>
+          <t>-4.249662585945642</t>
         </is>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>-26.54178546817805</t>
+          <t>-6.718506037644686</t>
         </is>
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>-23.30870698662894</t>
+          <t>1.146736876787111</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
@@ -6199,87 +6203,87 @@
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>6.64</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
         <is>
-          <t>5.94</t>
+          <t>8.09</t>
         </is>
       </c>
       <c r="CI12" t="inlineStr">
         <is>
-          <t>21.39</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CJ12" t="inlineStr">
         <is>
-          <t>17.52%</t>
+          <t>8.29%</t>
         </is>
       </c>
       <c r="CK12" t="inlineStr">
         <is>
-          <t>6.35%</t>
+          <t>1.61%</t>
         </is>
       </c>
       <c r="CL12" t="inlineStr">
         <is>
-          <t>52.77</t>
+          <t>63.41</t>
         </is>
       </c>
       <c r="CM12" t="inlineStr">
         <is>
-          <t>16062</t>
+          <t>462367</t>
         </is>
       </c>
       <c r="CN12" t="inlineStr">
         <is>
-          <t>煤焦油及化學品系列產品53.20%、輕油及油品系列產品29.03%、精碳材料9.72%、焦碳製品6.62%、其他1.43% (2024年)</t>
+          <t>聚酯纖維16.60%、其他16.28%、印刷電路板(PCB)12.09%、銅箔基板(CCL)10.47%、環氧樹脂8.29%、丙二酚(BPA)5.67%、乙二醇(EG)5.60%、銅箔5.01%、可塑劑(DOP)及硬化劑3.38%、硬質管2.55%、硬質膠布2.48%、塑膠門窗2.20%、軟質膠布1.85%、麩酸酐(PA)1.55%、玻璃纖維布1.32%、聚酯薄膜1.30%、膠乳皮0.92%、PU合成皮(人造皮)0.69%、BOPP膜0.64%、玻璃纖維絲0.60%、丁二醇(BDO)0.54% (2024年)</t>
         </is>
       </c>
       <c r="CO12" t="inlineStr">
         <is>
-          <t>中碳-化學工業-上市</t>
+          <t>南亞-塑膠工業-上市</t>
         </is>
       </c>
       <c r="CP12" t="inlineStr">
         <is>
-          <t>化學工業右下上市</t>
+          <t>塑膠工業平上市</t>
         </is>
       </c>
       <c r="CQ12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>58.7</t>
         </is>
       </c>
       <c r="CR12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>59.0</t>
         </is>
       </c>
       <c r="CS12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>58.0</t>
         </is>
       </c>
       <c r="CT12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>58.3</t>
         </is>
       </c>
       <c r="CU12" t="inlineStr">
         <is>
-          <t>33.12</t>
+          <t>41.48</t>
         </is>
       </c>
       <c r="CV12" t="inlineStr">
         <is>
-          <t>** 石化及塑橡膠 - 石化上游原料及相關鑽探設備** 電動車輛產業 - 鋰電池材料** 能源元件 - 原材料</t>
+          <t>** 印刷電路板 - 玻璃纖維/玻纖布、環氧樹脂、酚醛樹脂、銅箔、銅箔基板** 石化及塑橡膠 - 石化上游原料及相關鑽探設備、人造纖維** 紡織 - 石化原料(例如純對苯二甲酸、乙二醇、己內醯胺、丙烯腈等)、人造纖維產品(例如尼龍纖維、聚酯纖維、嫘縈纖維等)、染整** 電機機械 - 電控元件、機械設備之沖壓零組件</t>
         </is>
       </c>
       <c r="CW12" t="inlineStr">
@@ -6326,12 +6330,12 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -6497,12 +6501,12 @@
       <c r="AP13" t="inlineStr"/>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>512</t>
+          <t>319</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>60874</t>
+          <t>26488</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -6575,7 +6579,7 @@
       </c>
       <c r="BI13" t="inlineStr">
         <is>
-          <t>1604266901.846047</t>
+          <t>1605256682.65097</t>
         </is>
       </c>
       <c r="BJ13" t="inlineStr">
@@ -6656,7 +6660,7 @@
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -6691,7 +6695,7 @@
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6716,12 +6720,12 @@
       </c>
       <c r="CL13" t="inlineStr">
         <is>
-          <t>63.29</t>
+          <t>63.41</t>
         </is>
       </c>
       <c r="CM13" t="inlineStr">
         <is>
-          <t>465539</t>
+          <t>462367</t>
         </is>
       </c>
       <c r="CN13" t="inlineStr">
@@ -6813,12 +6817,12 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -6984,12 +6988,12 @@
       <c r="AP14" t="inlineStr"/>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>512</t>
+          <t>319</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>60874</t>
+          <t>26488</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -7062,7 +7066,7 @@
       </c>
       <c r="BI14" t="inlineStr">
         <is>
-          <t>1604266901.846047</t>
+          <t>1605256682.65097</t>
         </is>
       </c>
       <c r="BJ14" t="inlineStr">
@@ -7143,7 +7147,7 @@
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -7178,7 +7182,7 @@
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -7203,12 +7207,12 @@
       </c>
       <c r="CL14" t="inlineStr">
         <is>
-          <t>63.29</t>
+          <t>63.41</t>
         </is>
       </c>
       <c r="CM14" t="inlineStr">
         <is>
-          <t>465539</t>
+          <t>462367</t>
         </is>
       </c>
       <c r="CN14" t="inlineStr">
@@ -7300,12 +7304,12 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -7471,12 +7475,12 @@
       <c r="AP15" t="inlineStr"/>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>512</t>
+          <t>319</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>60874</t>
+          <t>26488</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -7549,7 +7553,7 @@
       </c>
       <c r="BI15" t="inlineStr">
         <is>
-          <t>1604266901.846047</t>
+          <t>1605256682.65097</t>
         </is>
       </c>
       <c r="BJ15" t="inlineStr">
@@ -7630,7 +7634,7 @@
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -7665,7 +7669,7 @@
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -7690,12 +7694,12 @@
       </c>
       <c r="CL15" t="inlineStr">
         <is>
-          <t>63.29</t>
+          <t>63.41</t>
         </is>
       </c>
       <c r="CM15" t="inlineStr">
         <is>
-          <t>465539</t>
+          <t>462367</t>
         </is>
       </c>
       <c r="CN15" t="inlineStr">
@@ -7787,12 +7791,12 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -7958,12 +7962,12 @@
       <c r="AP16" t="inlineStr"/>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>512</t>
+          <t>319</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>60874</t>
+          <t>26488</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -8036,7 +8040,7 @@
       </c>
       <c r="BI16" t="inlineStr">
         <is>
-          <t>1604266901.846047</t>
+          <t>1605256682.65097</t>
         </is>
       </c>
       <c r="BJ16" t="inlineStr">
@@ -8117,7 +8121,7 @@
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -8152,7 +8156,7 @@
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -8177,12 +8181,12 @@
       </c>
       <c r="CL16" t="inlineStr">
         <is>
-          <t>63.29</t>
+          <t>63.41</t>
         </is>
       </c>
       <c r="CM16" t="inlineStr">
         <is>
-          <t>465539</t>
+          <t>462367</t>
         </is>
       </c>
       <c r="CN16" t="inlineStr">
@@ -8274,12 +8278,12 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-2.9</t>
+          <t>-3.6</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -8445,12 +8449,12 @@
       <c r="AP17" t="inlineStr"/>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>512</t>
+          <t>319</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>60874</t>
+          <t>26488</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -8523,7 +8527,7 @@
       </c>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>1604266901.846047</t>
+          <t>1605256682.65097</t>
         </is>
       </c>
       <c r="BJ17" t="inlineStr">
@@ -8604,7 +8608,7 @@
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -8639,7 +8643,7 @@
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -8664,12 +8668,12 @@
       </c>
       <c r="CL17" t="inlineStr">
         <is>
-          <t>63.29</t>
+          <t>63.41</t>
         </is>
       </c>
       <c r="CM17" t="inlineStr">
         <is>
-          <t>465539</t>
+          <t>462367</t>
         </is>
       </c>
       <c r="CN17" t="inlineStr">
@@ -8761,12 +8765,12 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-2.04</t>
+          <t>-2.74</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -8932,12 +8936,12 @@
       <c r="AP18" t="inlineStr"/>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>512</t>
+          <t>319</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>60874</t>
+          <t>26488</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -9010,7 +9014,7 @@
       </c>
       <c r="BI18" t="inlineStr">
         <is>
-          <t>1604266901.846047</t>
+          <t>1605256682.65097</t>
         </is>
       </c>
       <c r="BJ18" t="inlineStr">
@@ -9091,7 +9095,7 @@
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -9126,7 +9130,7 @@
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -9151,12 +9155,12 @@
       </c>
       <c r="CL18" t="inlineStr">
         <is>
-          <t>63.29</t>
+          <t>63.41</t>
         </is>
       </c>
       <c r="CM18" t="inlineStr">
         <is>
-          <t>465539</t>
+          <t>462367</t>
         </is>
       </c>
       <c r="CN18" t="inlineStr">
@@ -9248,12 +9252,12 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -9419,12 +9423,12 @@
       <c r="AP19" t="inlineStr"/>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>512</t>
+          <t>319</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>60874</t>
+          <t>26488</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -9497,7 +9501,7 @@
       </c>
       <c r="BI19" t="inlineStr">
         <is>
-          <t>1604266901.846047</t>
+          <t>1605256682.65097</t>
         </is>
       </c>
       <c r="BJ19" t="inlineStr">
@@ -9578,7 +9582,7 @@
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -9603,7 +9607,7 @@
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
@@ -9613,7 +9617,7 @@
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -9638,12 +9642,12 @@
       </c>
       <c r="CL19" t="inlineStr">
         <is>
-          <t>63.29</t>
+          <t>63.41</t>
         </is>
       </c>
       <c r="CM19" t="inlineStr">
         <is>
-          <t>465539</t>
+          <t>462367</t>
         </is>
       </c>
       <c r="CN19" t="inlineStr">
@@ -9735,12 +9739,12 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -9906,12 +9910,12 @@
       <c r="AP20" t="inlineStr"/>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>512</t>
+          <t>319</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>60874</t>
+          <t>26488</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -9984,7 +9988,7 @@
       </c>
       <c r="BI20" t="inlineStr">
         <is>
-          <t>1604266901.846047</t>
+          <t>1605256682.65097</t>
         </is>
       </c>
       <c r="BJ20" t="inlineStr">
@@ -10065,7 +10069,7 @@
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -10090,7 +10094,7 @@
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
@@ -10100,7 +10104,7 @@
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -10125,12 +10129,12 @@
       </c>
       <c r="CL20" t="inlineStr">
         <is>
-          <t>63.29</t>
+          <t>63.41</t>
         </is>
       </c>
       <c r="CM20" t="inlineStr">
         <is>
-          <t>465539</t>
+          <t>462367</t>
         </is>
       </c>
       <c r="CN20" t="inlineStr">
@@ -10222,12 +10226,12 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -10393,12 +10397,12 @@
       <c r="AP21" t="inlineStr"/>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>512</t>
+          <t>319</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>60874</t>
+          <t>26488</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -10471,7 +10475,7 @@
       </c>
       <c r="BI21" t="inlineStr">
         <is>
-          <t>1604266901.846047</t>
+          <t>1605256682.65097</t>
         </is>
       </c>
       <c r="BJ21" t="inlineStr">
@@ -10552,7 +10556,7 @@
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -10587,7 +10591,7 @@
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -10612,12 +10616,12 @@
       </c>
       <c r="CL21" t="inlineStr">
         <is>
-          <t>63.29</t>
+          <t>63.41</t>
         </is>
       </c>
       <c r="CM21" t="inlineStr">
         <is>
-          <t>465539</t>
+          <t>462367</t>
         </is>
       </c>
       <c r="CN21" t="inlineStr">
@@ -10666,493 +10670,6 @@
         </is>
       </c>
       <c r="CW21" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>【c】</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>1303</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>32503.687</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>60.5</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>-3.07</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>-0.77</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>-51.89</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>2025-11-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>2025-12-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>2025-11-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>2025-11-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>56.2</t>
-        </is>
-      </c>
-      <c r="R22" t="inlineStr">
-        <is>
-          <t>61.4</t>
-        </is>
-      </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>45.3</t>
-        </is>
-      </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>51.1</t>
-        </is>
-      </c>
-      <c r="V22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>-1.47</t>
-        </is>
-      </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>9.98</t>
-        </is>
-      </c>
-      <c r="Y22" t="inlineStr">
-        <is>
-          <t>2025/07/28</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>37.0</t>
-        </is>
-      </c>
-      <c r="AA22" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>-0.14</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>2025/09/26</t>
-        </is>
-      </c>
-      <c r="AD22" t="inlineStr">
-        <is>
-          <t>39.6</t>
-        </is>
-      </c>
-      <c r="AE22" t="inlineStr">
-        <is>
-          <t>2025/04/08</t>
-        </is>
-      </c>
-      <c r="AF22" t="inlineStr">
-        <is>
-          <t>28.85</t>
-        </is>
-      </c>
-      <c r="AG22" t="inlineStr">
-        <is>
-          <t>2025/12/10</t>
-        </is>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>61.4</t>
-        </is>
-      </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>2025/11/26</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>51.1</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>2025-11-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="AL22" t="inlineStr">
-        <is>
-          <t>2025-12-15</t>
-        </is>
-      </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>9.65</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>0.71</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AP22" t="inlineStr"/>
-      <c r="AQ22" t="inlineStr">
-        <is>
-          <t>512</t>
-        </is>
-      </c>
-      <c r="AR22" t="inlineStr">
-        <is>
-          <t>60874</t>
-        </is>
-      </c>
-      <c r="AS22" t="inlineStr">
-        <is>
-          <t>7.69</t>
-        </is>
-      </c>
-      <c r="AT22" t="inlineStr">
-        <is>
-          <t>7.69</t>
-        </is>
-      </c>
-      <c r="AU22" t="n">
-        <v>-0.82</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>3.21</v>
-      </c>
-      <c r="AW22" t="inlineStr">
-        <is>
-          <t>18.99</t>
-        </is>
-      </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>7.94</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr">
-        <is>
-          <t>61.0</t>
-        </is>
-      </c>
-      <c r="AZ22" t="n">
-        <v>59.1</v>
-      </c>
-      <c r="BA22" t="n">
-        <v>49.67</v>
-      </c>
-      <c r="BB22" t="inlineStr">
-        <is>
-          <t>46.02</t>
-        </is>
-      </c>
-      <c r="BC22" t="inlineStr">
-        <is>
-          <t>-14.36</t>
-        </is>
-      </c>
-      <c r="BD22" t="n">
-        <v>3.57</v>
-      </c>
-      <c r="BE22" t="n">
-        <v>4.16</v>
-      </c>
-      <c r="BF22" t="inlineStr">
-        <is>
-          <t>4.51</t>
-        </is>
-      </c>
-      <c r="BG22" t="inlineStr">
-        <is>
-          <t>-7.65</t>
-        </is>
-      </c>
-      <c r="BH22" t="inlineStr">
-        <is>
-          <t>2025/11/27</t>
-        </is>
-      </c>
-      <c r="BI22" t="inlineStr">
-        <is>
-          <t>1604266901.846047</t>
-        </is>
-      </c>
-      <c r="BJ22" t="inlineStr">
-        <is>
-          <t>1961003405.0</t>
-        </is>
-      </c>
-      <c r="BK22" t="n">
-        <v>3781231830.6</v>
-      </c>
-      <c r="BL22" t="inlineStr">
-        <is>
-          <t>7859920944.9</t>
-        </is>
-      </c>
-      <c r="BM22" t="n">
-        <v>5470453576.18</v>
-      </c>
-      <c r="BN22" t="inlineStr">
-        <is>
-          <t>-2147483648</t>
-        </is>
-      </c>
-      <c r="BO22" t="inlineStr">
-        <is>
-          <t>42949015.30261654</t>
-        </is>
-      </c>
-      <c r="BP22" t="inlineStr">
-        <is>
-          <t>-1144816380.838599</t>
-        </is>
-      </c>
-      <c r="BQ22" t="inlineStr">
-        <is>
-          <t>1961003405.0</t>
-        </is>
-      </c>
-      <c r="BR22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BS22" t="inlineStr">
-        <is>
-          <t>41.9</t>
-        </is>
-      </c>
-      <c r="BT22" t="inlineStr">
-        <is>
-          <t>2025/10/21</t>
-        </is>
-      </c>
-      <c r="BU22" t="inlineStr">
-        <is>
-          <t>44.39</t>
-        </is>
-      </c>
-      <c r="BV22" t="inlineStr">
-        <is>
-          <t>南亞</t>
-        </is>
-      </c>
-      <c r="BW22" t="inlineStr">
-        <is>
-          <t>南亞</t>
-        </is>
-      </c>
-      <c r="BX22" t="inlineStr">
-        <is>
-          <t>塑膠工業</t>
-        </is>
-      </c>
-      <c r="BY22" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BZ22" t="inlineStr">
-        <is>
-          <t>0.92</t>
-        </is>
-      </c>
-      <c r="CA22" t="inlineStr">
-        <is>
-          <t>-4.249662585945642</t>
-        </is>
-      </c>
-      <c r="CB22" t="inlineStr">
-        <is>
-          <t>-6.718506037644686</t>
-        </is>
-      </c>
-      <c r="CC22" t="inlineStr">
-        <is>
-          <t>1.146736876787111</t>
-        </is>
-      </c>
-      <c r="CD22" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="CE22" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="CF22" t="inlineStr">
-        <is>
-          <t>1.46</t>
-        </is>
-      </c>
-      <c r="CG22" t="inlineStr">
-        <is>
-          <t>1.19</t>
-        </is>
-      </c>
-      <c r="CH22" t="inlineStr">
-        <is>
-          <t>8.09</t>
-        </is>
-      </c>
-      <c r="CI22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CJ22" t="inlineStr">
-        <is>
-          <t>8.29%</t>
-        </is>
-      </c>
-      <c r="CK22" t="inlineStr">
-        <is>
-          <t>1.61%</t>
-        </is>
-      </c>
-      <c r="CL22" t="inlineStr">
-        <is>
-          <t>63.29</t>
-        </is>
-      </c>
-      <c r="CM22" t="inlineStr">
-        <is>
-          <t>465539</t>
-        </is>
-      </c>
-      <c r="CN22" t="inlineStr">
-        <is>
-          <t>聚酯纖維16.60%、其他16.28%、印刷電路板(PCB)12.09%、銅箔基板(CCL)10.47%、環氧樹脂8.29%、丙二酚(BPA)5.67%、乙二醇(EG)5.60%、銅箔5.01%、可塑劑(DOP)及硬化劑3.38%、硬質管2.55%、硬質膠布2.48%、塑膠門窗2.20%、軟質膠布1.85%、麩酸酐(PA)1.55%、玻璃纖維布1.32%、聚酯薄膜1.30%、膠乳皮0.92%、PU合成皮(人造皮)0.69%、BOPP膜0.64%、玻璃纖維絲0.60%、丁二醇(BDO)0.54% (2024年)</t>
-        </is>
-      </c>
-      <c r="CO22" t="inlineStr">
-        <is>
-          <t>南亞-塑膠工業-上市</t>
-        </is>
-      </c>
-      <c r="CP22" t="inlineStr">
-        <is>
-          <t>塑膠工業平上市</t>
-        </is>
-      </c>
-      <c r="CQ22" t="inlineStr">
-        <is>
-          <t>60.0</t>
-        </is>
-      </c>
-      <c r="CR22" t="inlineStr">
-        <is>
-          <t>61.4</t>
-        </is>
-      </c>
-      <c r="CS22" t="inlineStr">
-        <is>
-          <t>59.2</t>
-        </is>
-      </c>
-      <c r="CT22" t="inlineStr">
-        <is>
-          <t>60.5</t>
-        </is>
-      </c>
-      <c r="CU22" t="inlineStr">
-        <is>
-          <t>41.48</t>
-        </is>
-      </c>
-      <c r="CV22" t="inlineStr">
-        <is>
-          <t>** 印刷電路板 - 玻璃纖維/玻纖布、環氧樹脂、酚醛樹脂、銅箔、銅箔基板** 石化及塑橡膠 - 石化上游原料及相關鑽探設備、人造纖維** 紡織 - 石化原料(例如純對苯二甲酸、乙二醇、己內醯胺、丙烯腈等)、人造纖維產品(例如尼龍纖維、聚酯纖維、嫘縈纖維等)、染整** 電機機械 - 電控元件、機械設備之沖壓零組件</t>
-        </is>
-      </c>
-      <c r="CW22" t="inlineStr">
         <is>
           <t>False</t>
         </is>

--- a/Result/checksun_type/石化上游原料及相關鑽探設備.xlsx
+++ b/Result/checksun_type/石化上游原料及相關鑽探設備.xlsx
@@ -948,12 +948,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>4700.034</t>
+          <t>3638.546</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>46.9</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -978,12 +978,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.82</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>4.37</t>
+          <t>16.80</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-9.60</t>
+          <t>-9.98</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -1073,7 +1073,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -1123,17 +1123,17 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>12.46</t>
+          <t>9.64</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
@@ -1144,66 +1144,66 @@
       <c r="AP2" t="inlineStr"/>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>41</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>4700</t>
+          <t>3639</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>18.52</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>6.17</t>
+          <t>9.88</t>
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>-1.67</v>
+        <v>-1.22</v>
       </c>
       <c r="AV2" t="n">
-        <v>-2.27</v>
+        <v>-2.68</v>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>-2.43</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>7.68</t>
+          <t>7.48</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>47.9</t>
+          <t>47.48</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>49.02</v>
+        <v>48.78</v>
       </c>
       <c r="BA2" t="n">
-        <v>49.99</v>
+        <v>50</v>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>46.43</t>
+          <t>46.52</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-55.75</t>
+          <t>-47.93</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>-0.77</v>
+        <v>-0.83</v>
       </c>
       <c r="BE2" t="n">
-        <v>-0.49</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="BF2" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-116.56</t>
+          <t>-118.81</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1222,43 +1222,43 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>412973818.0924138</t>
+          <t>412759570.7561983</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>222017076.0</t>
+          <t>171620168.0</t>
         </is>
       </c>
       <c r="BK2" t="n">
-        <v>196981396.8</v>
+        <v>205560214.4</v>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>188729985.6</t>
+          <t>175992316.4</t>
         </is>
       </c>
       <c r="BM2" t="n">
-        <v>441739824.86</v>
+        <v>429198766.1</v>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>8251411</t>
+          <t>29567898</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>-39079262.28408828</t>
+          <t>-36347578.56177494</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>-21438639.1844793</t>
+          <t>-21323318.08905157</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>222017076.0</t>
+          <t>171620168.0</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>7.41</t>
+          <t>6.96</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="CI2" t="inlineStr">
         <is>
-          <t>73.59</t>
+          <t>73.28</t>
         </is>
       </c>
       <c r="CJ2" t="inlineStr">
@@ -1363,12 +1363,12 @@
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>26.65</t>
+          <t>26.59</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
         <is>
-          <t>448673</t>
+          <t>446767</t>
         </is>
       </c>
       <c r="CN2" t="inlineStr">
@@ -1388,22 +1388,22 @@
       </c>
       <c r="CQ2" t="inlineStr">
         <is>
-          <t>47.4</t>
+          <t>47.25</t>
         </is>
       </c>
       <c r="CR2" t="inlineStr">
         <is>
-          <t>47.7</t>
+          <t>47.95</t>
         </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
-          <t>46.95</t>
+          <t>46.85</t>
         </is>
       </c>
       <c r="CT2" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>46.9</t>
         </is>
       </c>
       <c r="CU2" t="inlineStr">
@@ -1435,12 +1435,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>5142.181</t>
+          <t>4700.034</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>46.6</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1460,17 +1460,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.82</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-11.15</t>
+          <t>4.37</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1535,7 +1535,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-10.56</t>
+          <t>-9.60</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1610,17 +1610,17 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>13.63</t>
+          <t>12.46</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>-3.22</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
@@ -1631,66 +1631,66 @@
       <c r="AP3" t="inlineStr"/>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>41</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>4700</t>
+          <t>3639</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>18.52</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>26.44</t>
+          <t>6.17</t>
         </is>
       </c>
       <c r="AU3" t="n">
-        <v>-3.36</v>
+        <v>-1.67</v>
       </c>
       <c r="AV3" t="n">
-        <v>-2.25</v>
+        <v>-2.27</v>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>-1.96</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>7.78</t>
+          <t>7.68</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>48.22</t>
+          <t>47.9</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>49.33</v>
+        <v>49.02</v>
       </c>
       <c r="BA3" t="n">
-        <v>49.94</v>
+        <v>49.99</v>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>46.33</t>
+          <t>46.43</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-64.87</t>
+          <t>-55.75</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>-0.7</v>
+        <v>-0.77</v>
       </c>
       <c r="BE3" t="n">
-        <v>-0.42</v>
+        <v>-0.49</v>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-114.25</t>
+          <t>-116.56</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1709,43 +1709,43 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>412973818.0924138</t>
+          <t>412759570.7561983</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
-          <t>241897797.0</t>
+          <t>222017076.0</t>
         </is>
       </c>
       <c r="BK3" t="n">
-        <v>165405692.4</v>
+        <v>196981396.8</v>
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>186159307.5</t>
+          <t>188729985.6</t>
         </is>
       </c>
       <c r="BM3" t="n">
-        <v>443312295.6</v>
+        <v>441739824.86</v>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>-20753615</t>
+          <t>8251411</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>-42286648.30219901</t>
+          <t>-39079262.28408828</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>-26237386.63564461</t>
+          <t>-21438639.1844793</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>241897797.0</t>
+          <t>222017076.0</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1765,7 +1765,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>6.27</t>
+          <t>7.41</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
@@ -1820,12 +1820,12 @@
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="CI3" t="inlineStr">
         <is>
-          <t>73.59</t>
+          <t>73.28</t>
         </is>
       </c>
       <c r="CJ3" t="inlineStr">
@@ -1850,12 +1850,12 @@
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>26.65</t>
+          <t>26.59</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
         <is>
-          <t>448673</t>
+          <t>446767</t>
         </is>
       </c>
       <c r="CN3" t="inlineStr">
@@ -1875,22 +1875,22 @@
       </c>
       <c r="CQ3" t="inlineStr">
         <is>
-          <t>48.1</t>
+          <t>47.4</t>
         </is>
       </c>
       <c r="CR3" t="inlineStr">
         <is>
-          <t>48.1</t>
+          <t>47.7</t>
         </is>
       </c>
       <c r="CS3" t="inlineStr">
         <is>
-          <t>46.6</t>
+          <t>46.95</t>
         </is>
       </c>
       <c r="CT3" t="inlineStr">
         <is>
-          <t>46.6</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="CU3" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-2.45</t>
+          <t>-2.49</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>6031.976</t>
+          <t>5142.181</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1937,159 +1937,159 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>46.6</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0.64</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>-1.65</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>-11.15</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>-65.0</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2025-11-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2025-11-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>2025-09-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>2025-11-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>47.85</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>52.1</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>40.15</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>44.5</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>-10.56</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>7.53</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025/07/28</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>40.4</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>-0.08</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>2025/12/31</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
           <t>47.8</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>-1.49</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>-1.82</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>-26.27</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>-65.0</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>2025-11-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>2025-11-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>2025-09-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>2025-11-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>47.85</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>2025/09/19</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>38.9</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>2025/11/25</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
         <is>
           <t>52.1</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>40.15</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>2025/11/04</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
         <is>
           <t>44.5</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>-8.25</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>7.53</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>2025/07/28</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>40.4</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>-0.03</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>2025/12/31</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>47.8</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>2025/09/19</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>38.9</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>2025/11/25</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>52.1</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>2025/11/04</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>44.5</t>
-        </is>
-      </c>
       <c r="AK4" t="inlineStr">
         <is>
           <t>2025-11-07 00:00:00</t>
@@ -2097,17 +2097,17 @@
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>15.99</t>
+          <t>13.63</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>-2.30</t>
+          <t>-3.22</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
@@ -2118,12 +2118,12 @@
       <c r="AP4" t="inlineStr"/>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>41</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>4700</t>
+          <t>3639</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -2133,51 +2133,51 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>52.87</t>
+          <t>26.44</t>
         </is>
       </c>
       <c r="AU4" t="n">
-        <v>-1.71</v>
+        <v>-3.36</v>
       </c>
       <c r="AV4" t="n">
-        <v>-2.08</v>
+        <v>-2.25</v>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>7.85</t>
+          <t>7.78</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>48.63</t>
+          <t>48.22</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>49.66</v>
+        <v>49.33</v>
       </c>
       <c r="BA4" t="n">
-        <v>49.88</v>
+        <v>49.94</v>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>46.25</t>
+          <t>46.33</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-55.03</t>
+          <t>-64.87</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>-0.55</v>
+        <v>-0.7</v>
       </c>
       <c r="BE4" t="n">
-        <v>-0.35</v>
+        <v>-0.42</v>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-111.94</t>
+          <t>-114.25</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2196,43 +2196,43 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>412973818.0924138</t>
+          <t>412759570.7561983</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>289392194.0</t>
+          <t>241897797.0</t>
         </is>
       </c>
       <c r="BK4" t="n">
-        <v>142896369.6</v>
+        <v>165405692.4</v>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>193812739.5</t>
+          <t>186159307.5</t>
         </is>
       </c>
       <c r="BM4" t="n">
-        <v>442436106.5</v>
+        <v>443312295.6</v>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>-50916369</t>
+          <t>-20753615</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>-45204695.87793616</t>
+          <t>-42286648.30219901</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>-34285767.86460775</t>
+          <t>-26237386.63564461</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>289392194.0</t>
+          <t>241897797.0</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2252,7 +2252,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>9.01</t>
+          <t>6.27</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2297,7 +2297,7 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
@@ -2307,12 +2307,12 @@
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="CI4" t="inlineStr">
         <is>
-          <t>73.59</t>
+          <t>73.28</t>
         </is>
       </c>
       <c r="CJ4" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>26.65</t>
+          <t>26.59</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
         <is>
-          <t>448673</t>
+          <t>446767</t>
         </is>
       </c>
       <c r="CN4" t="inlineStr">
@@ -2362,22 +2362,22 @@
       </c>
       <c r="CQ4" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>48.1</t>
         </is>
       </c>
       <c r="CR4" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>48.1</t>
         </is>
       </c>
       <c r="CS4" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>46.6</t>
         </is>
       </c>
       <c r="CT4" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>46.6</t>
         </is>
       </c>
       <c r="CU4" t="inlineStr">
@@ -2399,7 +2399,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2409,12 +2409,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-2.45</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2103.849</t>
+          <t>6031.976</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>47.8</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2434,17 +2434,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-4.03</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.82</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-32.52</t>
+          <t>-26.27</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2509,7 +2509,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-5.95</t>
+          <t>-8.25</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2529,12 +2529,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -2584,17 +2584,17 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>5.58</t>
+          <t>15.99</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>-2.30</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
@@ -2605,66 +2605,66 @@
       <c r="AP5" t="inlineStr"/>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>41</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>4700</t>
+          <t>3639</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>79.31</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>64.93</t>
+          <t>52.87</t>
         </is>
       </c>
       <c r="AU5" t="n">
-        <v>0.14</v>
+        <v>-1.71</v>
       </c>
       <c r="AV5" t="n">
         <v>-2.08</v>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>7.93</t>
+          <t>7.85</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>48.92999999999999</t>
+          <t>48.63</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>49.97</v>
+        <v>49.66</v>
       </c>
       <c r="BA5" t="n">
-        <v>49.8</v>
+        <v>49.88</v>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>46.14</t>
+          <t>46.25</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-55.33</t>
+          <t>-55.03</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>-0.47</v>
+        <v>-0.55</v>
       </c>
       <c r="BE5" t="n">
-        <v>-0.31</v>
+        <v>-0.35</v>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
@@ -2673,7 +2673,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-110.30</t>
+          <t>-111.94</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2683,43 +2683,43 @@
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>412973818.0924138</t>
+          <t>412759570.7561983</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>102873837.0</t>
+          <t>289392194.0</t>
         </is>
       </c>
       <c r="BK5" t="n">
-        <v>130290842.2</v>
+        <v>142896369.6</v>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>193069761.9</t>
+          <t>193812739.5</t>
         </is>
       </c>
       <c r="BM5" t="n">
-        <v>440991024.68</v>
+        <v>442436106.5</v>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>-62778919</t>
+          <t>-50916369</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>-47189955.51672314</t>
+          <t>-45204695.87793616</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>-49647649.01796198</t>
+          <t>-34285767.86460775</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>102873837.0</t>
+          <t>289392194.0</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2739,7 +2739,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>11.74</t>
+          <t>9.01</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2784,22 +2784,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="CI5" t="inlineStr">
         <is>
-          <t>73.59</t>
+          <t>73.28</t>
         </is>
       </c>
       <c r="CJ5" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>26.65</t>
+          <t>26.59</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
         <is>
-          <t>448673</t>
+          <t>446767</t>
         </is>
       </c>
       <c r="CN5" t="inlineStr">
@@ -2849,22 +2849,22 @@
       </c>
       <c r="CQ5" t="inlineStr">
         <is>
+          <t>49.0</t>
+        </is>
+      </c>
+      <c r="CR5" t="inlineStr">
+        <is>
           <t>49.2</t>
         </is>
       </c>
-      <c r="CR5" t="inlineStr">
-        <is>
-          <t>49.35</t>
-        </is>
-      </c>
       <c r="CS5" t="inlineStr">
         <is>
-          <t>48.35</t>
+          <t>47.5</t>
         </is>
       </c>
       <c r="CT5" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>47.8</t>
         </is>
       </c>
       <c r="CU5" t="inlineStr">
@@ -2896,12 +2896,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2623.606</t>
+          <t>2103.849</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2921,17 +2921,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-4.03</t>
+          <t>-4.48</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.82</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-31.27</t>
+          <t>-32.52</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -3071,17 +3071,17 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>6.95</t>
+          <t>5.58</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -3092,12 +3092,12 @@
       <c r="AP6" t="inlineStr"/>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>41</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>4700</t>
+          <t>3639</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -3107,51 +3107,51 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>49.84</t>
+          <t>64.93</t>
         </is>
       </c>
       <c r="AU6" t="n">
-        <v>0.35</v>
+        <v>0.14</v>
       </c>
       <c r="AV6" t="n">
-        <v>-2.61</v>
+        <v>-2.08</v>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>7.98</t>
+          <t>7.93</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>48.83</t>
+          <t>48.92999999999999</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>50.14</v>
+        <v>49.97</v>
       </c>
       <c r="BA6" t="n">
-        <v>49.69</v>
+        <v>49.8</v>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>46.02</t>
+          <t>46.14</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-87.85</t>
+          <t>-55.33</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>-0.49</v>
+        <v>-0.47</v>
       </c>
       <c r="BE6" t="n">
-        <v>-0.26</v>
+        <v>-0.31</v>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
@@ -3160,7 +3160,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-108.87</t>
+          <t>-110.30</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -3170,43 +3170,43 @@
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>412973818.0924138</t>
+          <t>412759570.7561983</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
         <is>
-          <t>128726080.0</t>
+          <t>102873837.0</t>
         </is>
       </c>
       <c r="BK6" t="n">
-        <v>146424418.4</v>
+        <v>130290842.2</v>
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>213035188.0</t>
+          <t>193069761.9</t>
         </is>
       </c>
       <c r="BM6" t="n">
-        <v>446858256.1</v>
+        <v>440991024.68</v>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>-66610769</t>
+          <t>-62778919</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>-46743102.15286153</t>
+          <t>-47189955.51672314</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>-49835953.52211222</t>
+          <t>-49647649.01796198</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>128726080.0</t>
+          <t>102873837.0</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -3271,7 +3271,7 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="CI6" t="inlineStr">
         <is>
-          <t>73.59</t>
+          <t>73.28</t>
         </is>
       </c>
       <c r="CJ6" t="inlineStr">
@@ -3311,12 +3311,12 @@
       </c>
       <c r="CL6" t="inlineStr">
         <is>
-          <t>26.65</t>
+          <t>26.59</t>
         </is>
       </c>
       <c r="CM6" t="inlineStr">
         <is>
-          <t>448673</t>
+          <t>446767</t>
         </is>
       </c>
       <c r="CN6" t="inlineStr">
@@ -3336,17 +3336,17 @@
       </c>
       <c r="CQ6" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="CR6" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>49.35</t>
         </is>
       </c>
       <c r="CS6" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>48.35</t>
         </is>
       </c>
       <c r="CT6" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1316.127</t>
+          <t>2623.606</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3408,17 +3408,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-3.4</t>
+          <t>-4.48</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.82</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-16.57</t>
+          <t>-31.27</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3483,7 +3483,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-6.53</t>
+          <t>-5.95</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -3558,17 +3558,17 @@
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>3.49</t>
+          <t>6.95</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -3579,66 +3579,66 @@
       <c r="AP7" t="inlineStr"/>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>41</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>4700</t>
+          <t>3639</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>36.17</t>
+          <t>79.31</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>43.97</t>
+          <t>49.84</t>
         </is>
       </c>
       <c r="AU7" t="n">
-        <v>-0.1</v>
+        <v>0.35</v>
       </c>
       <c r="AV7" t="n">
-        <v>-3.09</v>
+        <v>-2.61</v>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>7.99</t>
+          <t>7.98</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>48.75</t>
+          <t>48.83</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>50.3</v>
+        <v>50.14</v>
       </c>
       <c r="BA7" t="n">
-        <v>49.57</v>
+        <v>49.69</v>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>45.91</t>
+          <t>46.02</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-149.65</t>
+          <t>-87.85</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>-0.51</v>
+        <v>-0.49</v>
       </c>
       <c r="BE7" t="n">
-        <v>-0.21</v>
+        <v>-0.26</v>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
@@ -3647,7 +3647,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-106.92</t>
+          <t>-108.87</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3657,43 +3657,43 @@
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>412973818.0924138</t>
+          <t>412759570.7561983</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
         <is>
-          <t>64138554.0</t>
+          <t>128726080.0</t>
         </is>
       </c>
       <c r="BK7" t="n">
-        <v>180478574.4</v>
+        <v>146424418.4</v>
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>216333475.6</t>
+          <t>213035188.0</t>
         </is>
       </c>
       <c r="BM7" t="n">
-        <v>454343174.12</v>
+        <v>446858256.1</v>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>-35854901</t>
+          <t>-66610769</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>-46180765.54027049</t>
+          <t>-46743102.15286153</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>-51094987.65225139</t>
+          <t>-49835953.52211222</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>64138554.0</t>
+          <t>128726080.0</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3713,7 +3713,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>11.06</t>
+          <t>11.74</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3758,7 +3758,7 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
@@ -3768,12 +3768,12 @@
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="CI7" t="inlineStr">
         <is>
-          <t>73.59</t>
+          <t>73.28</t>
         </is>
       </c>
       <c r="CJ7" t="inlineStr">
@@ -3798,12 +3798,12 @@
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>26.65</t>
+          <t>26.59</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
         <is>
-          <t>448673</t>
+          <t>446767</t>
         </is>
       </c>
       <c r="CN7" t="inlineStr">
@@ -3823,22 +3823,22 @@
       </c>
       <c r="CQ7" t="inlineStr">
         <is>
-          <t>48.95</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="CR7" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>49.5</t>
         </is>
       </c>
       <c r="CS7" t="inlineStr">
         <is>
-          <t>48.45</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="CT7" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="CU7" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2646.184</t>
+          <t>1316.127</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3885,7 +3885,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>48.65</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3895,17 +3895,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-3.29</t>
+          <t>-3.84</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.82</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-14.41</t>
+          <t>-16.57</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3970,7 +3970,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-6.62</t>
+          <t>-6.53</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>7.01</t>
+          <t>3.49</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -4066,66 +4066,66 @@
       <c r="AP8" t="inlineStr"/>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>41</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>4700</t>
+          <t>3639</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>34.04</t>
+          <t>36.17</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>41.13</t>
+          <t>43.97</t>
         </is>
       </c>
       <c r="AU8" t="n">
-        <v>0.14</v>
+        <v>-0.1</v>
       </c>
       <c r="AV8" t="n">
-        <v>-3.74</v>
+        <v>-3.09</v>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>7.91</t>
+          <t>7.99</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>48.58</t>
+          <t>48.75</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>50.47</v>
+        <v>50.3</v>
       </c>
       <c r="BA8" t="n">
-        <v>49.42</v>
+        <v>49.57</v>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>45.8</t>
+          <t>45.91</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-287.52</t>
+          <t>-149.65</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>-0.5</v>
+        <v>-0.51</v>
       </c>
       <c r="BE8" t="n">
-        <v>-0.13</v>
+        <v>-0.21</v>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
@@ -4134,7 +4134,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-104.33</t>
+          <t>-106.92</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -4144,43 +4144,43 @@
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>412973818.0924138</t>
+          <t>412759570.7561983</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
         <is>
-          <t>129351183.0</t>
+          <t>64138554.0</t>
         </is>
       </c>
       <c r="BK8" t="n">
-        <v>206912922.6</v>
+        <v>180478574.4</v>
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>241751775.8</t>
+          <t>216333475.6</t>
         </is>
       </c>
       <c r="BM8" t="n">
-        <v>459452333.2</v>
+        <v>454343174.12</v>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>-34838853</t>
+          <t>-35854901</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>-45287270.61081942</t>
+          <t>-46180765.54027049</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>-44148694.77915558</t>
+          <t>-51094987.65225139</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>129351183.0</t>
+          <t>64138554.0</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -4200,7 +4200,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>10.95</t>
+          <t>11.06</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -4260,7 +4260,7 @@
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="CI8" t="inlineStr">
         <is>
-          <t>73.59</t>
+          <t>73.28</t>
         </is>
       </c>
       <c r="CJ8" t="inlineStr">
@@ -4285,12 +4285,12 @@
       </c>
       <c r="CL8" t="inlineStr">
         <is>
-          <t>26.65</t>
+          <t>26.59</t>
         </is>
       </c>
       <c r="CM8" t="inlineStr">
         <is>
-          <t>448673</t>
+          <t>446767</t>
         </is>
       </c>
       <c r="CN8" t="inlineStr">
@@ -4310,22 +4310,22 @@
       </c>
       <c r="CQ8" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>48.95</t>
         </is>
       </c>
       <c r="CR8" t="inlineStr">
         <is>
-          <t>49.45</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="CS8" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>48.45</t>
         </is>
       </c>
       <c r="CT8" t="inlineStr">
         <is>
-          <t>48.65</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="CU8" t="inlineStr">
@@ -4357,12 +4357,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>4601.672</t>
+          <t>2646.184</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4372,7 +4372,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>48.65</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -4382,17 +4382,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-4.67</t>
+          <t>-3.73</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.82</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-3.31</t>
+          <t>-14.41</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4457,7 +4457,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-5.37</t>
+          <t>-6.62</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4482,7 +4482,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -4532,17 +4532,17 @@
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>12.20</t>
+          <t>7.01</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
@@ -4553,266 +4553,266 @@
       <c r="AP9" t="inlineStr"/>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>41</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>4700</t>
+          <t>3639</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>61.7</t>
+          <t>34.04</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>37.25</t>
+          <t>41.13</t>
         </is>
       </c>
       <c r="AU9" t="n">
-        <v>1.65</v>
+        <v>0.14</v>
       </c>
       <c r="AV9" t="n">
-        <v>-4.05</v>
+        <v>-3.74</v>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>2.61</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>7.80</t>
+          <t>7.91</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
+          <t>48.58</t>
+        </is>
+      </c>
+      <c r="AZ9" t="n">
+        <v>50.47</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>49.42</v>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>45.8</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>-287.52</t>
+        </is>
+      </c>
+      <c r="BD9" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>-0.13</v>
+      </c>
+      <c r="BF9" t="inlineStr">
+        <is>
+          <t>2.97</t>
+        </is>
+      </c>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>-104.33</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>2025/11/06</t>
+        </is>
+      </c>
+      <c r="BI9" t="inlineStr">
+        <is>
+          <t>412759570.7561983</t>
+        </is>
+      </c>
+      <c r="BJ9" t="inlineStr">
+        <is>
+          <t>129351183.0</t>
+        </is>
+      </c>
+      <c r="BK9" t="n">
+        <v>206912922.6</v>
+      </c>
+      <c r="BL9" t="inlineStr">
+        <is>
+          <t>241751775.8</t>
+        </is>
+      </c>
+      <c r="BM9" t="n">
+        <v>459452333.2</v>
+      </c>
+      <c r="BN9" t="inlineStr">
+        <is>
+          <t>-34838853</t>
+        </is>
+      </c>
+      <c r="BO9" t="inlineStr">
+        <is>
+          <t>-45287270.61081942</t>
+        </is>
+      </c>
+      <c r="BP9" t="inlineStr">
+        <is>
+          <t>-44148694.77915558</t>
+        </is>
+      </c>
+      <c r="BQ9" t="inlineStr">
+        <is>
+          <t>129351183.0</t>
+        </is>
+      </c>
+      <c r="BR9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BS9" t="inlineStr">
+        <is>
+          <t>43.85</t>
+        </is>
+      </c>
+      <c r="BT9" t="inlineStr">
+        <is>
+          <t>2025/10/20</t>
+        </is>
+      </c>
+      <c r="BU9" t="inlineStr">
+        <is>
+          <t>10.95</t>
+        </is>
+      </c>
+      <c r="BV9" t="inlineStr">
+        <is>
+          <t>台塑化</t>
+        </is>
+      </c>
+      <c r="BW9" t="inlineStr">
+        <is>
+          <t>台塑化</t>
+        </is>
+      </c>
+      <c r="BX9" t="inlineStr">
+        <is>
+          <t>油電燃氣業</t>
+        </is>
+      </c>
+      <c r="BY9" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BZ9" t="inlineStr">
+        <is>
+          <t>0.78</t>
+        </is>
+      </c>
+      <c r="CA9" t="inlineStr">
+        <is>
+          <t>6.224057236717059</t>
+        </is>
+      </c>
+      <c r="CB9" t="inlineStr">
+        <is>
+          <t>-8.662170551815038</t>
+        </is>
+      </c>
+      <c r="CC9" t="inlineStr">
+        <is>
+          <t>-6.291713809683439</t>
+        </is>
+      </c>
+      <c r="CD9" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="CE9" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="CF9" t="inlineStr">
+        <is>
+          <t>1.51</t>
+        </is>
+      </c>
+      <c r="CG9" t="inlineStr">
+        <is>
+          <t>1.71</t>
+        </is>
+      </c>
+      <c r="CH9" t="inlineStr">
+        <is>
+          <t>17.17</t>
+        </is>
+      </c>
+      <c r="CI9" t="inlineStr">
+        <is>
+          <t>73.28</t>
+        </is>
+      </c>
+      <c r="CJ9" t="inlineStr">
+        <is>
+          <t>7.31%</t>
+        </is>
+      </c>
+      <c r="CK9" t="inlineStr">
+        <is>
+          <t>5.68%</t>
+        </is>
+      </c>
+      <c r="CL9" t="inlineStr">
+        <is>
+          <t>26.59</t>
+        </is>
+      </c>
+      <c r="CM9" t="inlineStr">
+        <is>
+          <t>446767</t>
+        </is>
+      </c>
+      <c r="CN9" t="inlineStr">
+        <is>
+          <t>汽油,柴油等各項石油製品75.50%、乙烯,丙烯等石油化學品18.10%、電力,蒸汽6.00%、其他0.40% (2024年)</t>
+        </is>
+      </c>
+      <c r="CO9" t="inlineStr">
+        <is>
+          <t>台塑化-油電燃氣業-上市</t>
+        </is>
+      </c>
+      <c r="CP9" t="inlineStr">
+        <is>
+          <t>油電燃氣業右下上市</t>
+        </is>
+      </c>
+      <c r="CQ9" t="inlineStr">
+        <is>
+          <t>49.3</t>
+        </is>
+      </c>
+      <c r="CR9" t="inlineStr">
+        <is>
+          <t>49.45</t>
+        </is>
+      </c>
+      <c r="CS9" t="inlineStr">
+        <is>
           <t>48.5</t>
         </is>
       </c>
-      <c r="AZ9" t="n">
-        <v>50.55</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>49.26</v>
-      </c>
-      <c r="BB9" t="inlineStr">
-        <is>
-          <t>45.7</t>
-        </is>
-      </c>
-      <c r="BC9" t="inlineStr">
-        <is>
-          <t>-1192.49</t>
-        </is>
-      </c>
-      <c r="BD9" t="n">
-        <v>-0.47</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="BF9" t="inlineStr">
-        <is>
-          <t>2.97</t>
-        </is>
-      </c>
-      <c r="BG9" t="inlineStr">
-        <is>
-          <t>-101.22</t>
-        </is>
-      </c>
-      <c r="BH9" t="inlineStr">
-        <is>
-          <t>2025/11/06</t>
-        </is>
-      </c>
-      <c r="BI9" t="inlineStr">
-        <is>
-          <t>412973818.0924138</t>
-        </is>
-      </c>
-      <c r="BJ9" t="inlineStr">
-        <is>
-          <t>226364557.0</t>
-        </is>
-      </c>
-      <c r="BK9" t="n">
-        <v>244729109.4</v>
-      </c>
-      <c r="BL9" t="inlineStr">
-        <is>
-          <t>253104275.0</t>
-        </is>
-      </c>
-      <c r="BM9" t="n">
-        <v>462234616.36</v>
-      </c>
-      <c r="BN9" t="inlineStr">
-        <is>
-          <t>-8375165</t>
-        </is>
-      </c>
-      <c r="BO9" t="inlineStr">
-        <is>
-          <t>-45494284.39839467</t>
-        </is>
-      </c>
-      <c r="BP9" t="inlineStr">
-        <is>
-          <t>-39635747.53976309</t>
-        </is>
-      </c>
-      <c r="BQ9" t="inlineStr">
-        <is>
-          <t>226364557.0</t>
-        </is>
-      </c>
-      <c r="BR9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BS9" t="inlineStr">
-        <is>
-          <t>43.85</t>
-        </is>
-      </c>
-      <c r="BT9" t="inlineStr">
-        <is>
-          <t>2025/10/20</t>
-        </is>
-      </c>
-      <c r="BU9" t="inlineStr">
-        <is>
-          <t>12.43</t>
-        </is>
-      </c>
-      <c r="BV9" t="inlineStr">
-        <is>
-          <t>台塑化</t>
-        </is>
-      </c>
-      <c r="BW9" t="inlineStr">
-        <is>
-          <t>台塑化</t>
-        </is>
-      </c>
-      <c r="BX9" t="inlineStr">
-        <is>
-          <t>油電燃氣業</t>
-        </is>
-      </c>
-      <c r="BY9" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BZ9" t="inlineStr">
-        <is>
-          <t>0.78</t>
-        </is>
-      </c>
-      <c r="CA9" t="inlineStr">
-        <is>
-          <t>6.224057236717059</t>
-        </is>
-      </c>
-      <c r="CB9" t="inlineStr">
-        <is>
-          <t>-8.662170551815038</t>
-        </is>
-      </c>
-      <c r="CC9" t="inlineStr">
-        <is>
-          <t>-6.291713809683439</t>
-        </is>
-      </c>
-      <c r="CD9" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="CE9" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="CF9" t="inlineStr">
-        <is>
-          <t>1.53</t>
-        </is>
-      </c>
-      <c r="CG9" t="inlineStr">
-        <is>
-          <t>1.7</t>
-        </is>
-      </c>
-      <c r="CH9" t="inlineStr">
-        <is>
-          <t>17.17</t>
-        </is>
-      </c>
-      <c r="CI9" t="inlineStr">
-        <is>
-          <t>73.59</t>
-        </is>
-      </c>
-      <c r="CJ9" t="inlineStr">
-        <is>
-          <t>7.31%</t>
-        </is>
-      </c>
-      <c r="CK9" t="inlineStr">
-        <is>
-          <t>5.68%</t>
-        </is>
-      </c>
-      <c r="CL9" t="inlineStr">
-        <is>
-          <t>26.65</t>
-        </is>
-      </c>
-      <c r="CM9" t="inlineStr">
-        <is>
-          <t>448673</t>
-        </is>
-      </c>
-      <c r="CN9" t="inlineStr">
-        <is>
-          <t>汽油,柴油等各項石油製品75.50%、乙烯,丙烯等石油化學品18.10%、電力,蒸汽6.00%、其他0.40% (2024年)</t>
-        </is>
-      </c>
-      <c r="CO9" t="inlineStr">
-        <is>
-          <t>台塑化-油電燃氣業-上市</t>
-        </is>
-      </c>
-      <c r="CP9" t="inlineStr">
-        <is>
-          <t>油電燃氣業右下上市</t>
-        </is>
-      </c>
-      <c r="CQ9" t="inlineStr">
+      <c r="CT9" t="inlineStr">
         <is>
           <t>48.65</t>
-        </is>
-      </c>
-      <c r="CR9" t="inlineStr">
-        <is>
-          <t>50.1</t>
-        </is>
-      </c>
-      <c r="CS9" t="inlineStr">
-        <is>
-          <t>48.15</t>
-        </is>
-      </c>
-      <c r="CT9" t="inlineStr">
-        <is>
-          <t>49.3</t>
         </is>
       </c>
       <c r="CU9" t="inlineStr">
@@ -4844,12 +4844,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>3785.684</t>
+          <t>4601.672</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4859,7 +4859,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4869,17 +4869,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-2.97</t>
+          <t>-5.12</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.82</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>-3.31</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4944,7 +4944,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-6.91</t>
+          <t>-5.37</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4969,7 +4969,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -5019,17 +5019,17 @@
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>10.03</t>
+          <t>12.20</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
@@ -5040,66 +5040,66 @@
       <c r="AP10" t="inlineStr"/>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>41</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>4700</t>
+          <t>3639</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>27.66</t>
+          <t>61.7</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>16.68</t>
+          <t>37.25</t>
         </is>
       </c>
       <c r="AU10" t="n">
-        <v>0.02</v>
+        <v>1.65</v>
       </c>
       <c r="AV10" t="n">
-        <v>-4.34</v>
+        <v>-4.05</v>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>7.64</t>
+          <t>7.80</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>48.49</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>50.69</v>
+        <v>50.55</v>
       </c>
       <c r="BA10" t="n">
-        <v>49.09</v>
+        <v>49.26</v>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>45.61</t>
+          <t>45.7</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-780.06</t>
+          <t>-1192.49</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>-0.49</v>
+        <v>-0.47</v>
       </c>
       <c r="BE10" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.04</v>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
@@ -5108,7 +5108,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-97.59</t>
+          <t>-101.22</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -5118,43 +5118,43 @@
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>412973818.0924138</t>
+          <t>412759570.7561983</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
         <is>
-          <t>183541718.0</t>
+          <t>226364557.0</t>
         </is>
       </c>
       <c r="BK10" t="n">
-        <v>255848681.6</v>
+        <v>244729109.4</v>
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>250000286.1</t>
+          <t>253104275.0</t>
         </is>
       </c>
       <c r="BM10" t="n">
-        <v>462930721.8</v>
+        <v>462234616.36</v>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>5848395</t>
+          <t>-8375165</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>-46559472.91814587</t>
+          <t>-45494284.39839467</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>-42167407.71421093</t>
+          <t>-39635747.53976309</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>183541718.0</t>
+          <t>226364557.0</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -5174,7 +5174,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>10.60</t>
+          <t>12.43</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -5219,7 +5219,7 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
@@ -5229,12 +5229,12 @@
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -5244,7 +5244,7 @@
       </c>
       <c r="CI10" t="inlineStr">
         <is>
-          <t>73.59</t>
+          <t>73.28</t>
         </is>
       </c>
       <c r="CJ10" t="inlineStr">
@@ -5259,12 +5259,12 @@
       </c>
       <c r="CL10" t="inlineStr">
         <is>
-          <t>26.65</t>
+          <t>26.59</t>
         </is>
       </c>
       <c r="CM10" t="inlineStr">
         <is>
-          <t>448673</t>
+          <t>446767</t>
         </is>
       </c>
       <c r="CN10" t="inlineStr">
@@ -5284,12 +5284,12 @@
       </c>
       <c r="CQ10" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>48.65</t>
         </is>
       </c>
       <c r="CR10" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>50.1</t>
         </is>
       </c>
       <c r="CS10" t="inlineStr">
@@ -5299,7 +5299,7 @@
       </c>
       <c r="CT10" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="CU10" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>643.584</t>
+          <t>485.313</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5346,7 +5346,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>66.4</t>
+          <t>67.1</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -5361,12 +5361,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>11.71</t>
+          <t>6.33</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-32.66</t>
+          <t>-31.95</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -5506,17 +5506,17 @@
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>34.20</t>
+          <t>25.79</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
@@ -5527,66 +5527,66 @@
       <c r="AP11" t="inlineStr"/>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>644</t>
+          <t>485</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>30.43</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>20.83</t>
+          <t>10.14</t>
         </is>
       </c>
       <c r="AU11" t="n">
-        <v>-1.75</v>
+        <v>-0.5</v>
       </c>
       <c r="AV11" t="n">
-        <v>-1.42</v>
+        <v>-1.35</v>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>-7.68</t>
+          <t>-7.52</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>-4.29</t>
+          <t>-4.47</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>67.58</t>
+          <t>67.44</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>68.55</v>
+        <v>68.36</v>
       </c>
       <c r="BA11" t="n">
-        <v>74.26000000000001</v>
+        <v>73.92</v>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>77.59</t>
+          <t>77.39</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>9.97</t>
+          <t>10.70</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>-1.9</v>
+        <v>-1.84</v>
       </c>
       <c r="BE11" t="n">
-        <v>-2.11</v>
+        <v>-2.06</v>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-221.81</t>
+          <t>-218.63</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5605,43 +5605,43 @@
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>67131363.81310345</t>
+          <t>67106092.04545455</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
         <is>
-          <t>42761898.0</t>
+          <t>32522707.0</t>
         </is>
       </c>
       <c r="BK11" t="n">
-        <v>38448380</v>
+        <v>36021570</v>
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>34418020.0</t>
+          <t>33877169.8</t>
         </is>
       </c>
       <c r="BM11" t="n">
-        <v>38733021.6</v>
+        <v>39098673.78</v>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>4030360</t>
+          <t>2144400</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>-1545714.322361908</t>
+          <t>-1379274.545714302</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>-183826.1974112913</t>
+          <t>-463855.7741524726</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>42761898.0</t>
+          <t>32522707.0</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5661,7 +5661,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>-25.64</t>
+          <t>-24.86</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5711,17 +5711,17 @@
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>6.78</t>
+          <t>6.71</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5731,7 +5731,7 @@
       </c>
       <c r="CI11" t="inlineStr">
         <is>
-          <t>20.95</t>
+          <t>21.17</t>
         </is>
       </c>
       <c r="CJ11" t="inlineStr">
@@ -5746,12 +5746,12 @@
       </c>
       <c r="CL11" t="inlineStr">
         <is>
-          <t>55.85</t>
+          <t>56.13</t>
         </is>
       </c>
       <c r="CM11" t="inlineStr">
         <is>
-          <t>15730</t>
+          <t>15896</t>
         </is>
       </c>
       <c r="CN11" t="inlineStr">
@@ -5771,22 +5771,22 @@
       </c>
       <c r="CQ11" t="inlineStr">
         <is>
+          <t>66.2</t>
+        </is>
+      </c>
+      <c r="CR11" t="inlineStr">
+        <is>
+          <t>67.6</t>
+        </is>
+      </c>
+      <c r="CS11" t="inlineStr">
+        <is>
+          <t>66.2</t>
+        </is>
+      </c>
+      <c r="CT11" t="inlineStr">
+        <is>
           <t>67.1</t>
-        </is>
-      </c>
-      <c r="CR11" t="inlineStr">
-        <is>
-          <t>67.3</t>
-        </is>
-      </c>
-      <c r="CS11" t="inlineStr">
-        <is>
-          <t>66.0</t>
-        </is>
-      </c>
-      <c r="CT11" t="inlineStr">
-        <is>
-          <t>66.4</t>
         </is>
       </c>
       <c r="CU11" t="inlineStr">
@@ -5818,12 +5818,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>561.716</t>
+          <t>643.584</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5833,7 +5833,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>67.1</t>
+          <t>66.4</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5843,17 +5843,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>19.23</t>
+          <t>11.71</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5918,7 +5918,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-31.95</t>
+          <t>-32.66</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5943,7 +5943,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -5993,17 +5993,17 @@
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>29.85</t>
+          <t>34.20</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
@@ -6014,12 +6014,12 @@
       <c r="AP12" t="inlineStr"/>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>644</t>
+          <t>485</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -6029,51 +6029,51 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>45.39</t>
+          <t>20.83</t>
         </is>
       </c>
       <c r="AU12" t="n">
-        <v>-0.92</v>
+        <v>-1.75</v>
       </c>
       <c r="AV12" t="n">
-        <v>-1.6</v>
+        <v>-1.42</v>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>-7.76</t>
+          <t>-7.68</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>-4.10</t>
+          <t>-4.29</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>67.72</t>
+          <t>67.58</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>68.81999999999999</v>
+        <v>68.55</v>
       </c>
       <c r="BA12" t="n">
-        <v>74.61</v>
+        <v>74.26000000000001</v>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>77.79</t>
+          <t>77.59</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>12.93</t>
+          <t>9.97</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>-1.88</v>
+        <v>-1.9</v>
       </c>
       <c r="BE12" t="n">
-        <v>-2.16</v>
+        <v>-2.11</v>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
@@ -6082,7 +6082,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-224.84</t>
+          <t>-221.81</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -6092,43 +6092,43 @@
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>67131363.81310345</t>
+          <t>67106092.04545455</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
         <is>
-          <t>37869502.0</t>
+          <t>42761898.0</t>
         </is>
       </c>
       <c r="BK12" t="n">
-        <v>41191877</v>
+        <v>38448380</v>
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>34549396.1</t>
+          <t>34418020.0</t>
         </is>
       </c>
       <c r="BM12" t="n">
-        <v>38283283.38</v>
+        <v>38733021.6</v>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>6642480</t>
+          <t>4030360</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>-1793330.345080202</t>
+          <t>-1545714.322361908</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>-874274.9021591917</t>
+          <t>-183826.1974112913</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>37869502.0</t>
+          <t>42761898.0</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -6148,7 +6148,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>-24.86</t>
+          <t>-25.64</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -6193,7 +6193,7 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
@@ -6203,12 +6203,12 @@
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>6.78</t>
+          <t>6.71</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -6218,7 +6218,7 @@
       </c>
       <c r="CI12" t="inlineStr">
         <is>
-          <t>20.95</t>
+          <t>21.17</t>
         </is>
       </c>
       <c r="CJ12" t="inlineStr">
@@ -6233,12 +6233,12 @@
       </c>
       <c r="CL12" t="inlineStr">
         <is>
-          <t>55.85</t>
+          <t>56.13</t>
         </is>
       </c>
       <c r="CM12" t="inlineStr">
         <is>
-          <t>15730</t>
+          <t>15896</t>
         </is>
       </c>
       <c r="CN12" t="inlineStr">
@@ -6258,22 +6258,22 @@
       </c>
       <c r="CQ12" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>67.1</t>
         </is>
       </c>
       <c r="CR12" t="inlineStr">
         <is>
-          <t>68.4</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="CS12" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="CT12" t="inlineStr">
         <is>
-          <t>67.1</t>
+          <t>66.4</t>
         </is>
       </c>
       <c r="CU12" t="inlineStr">
@@ -6305,12 +6305,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>316.85</t>
+          <t>561.716</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -6320,7 +6320,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>68.1</t>
+          <t>67.1</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -6330,17 +6330,17 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-2.56</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>14.26</t>
+          <t>19.23</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -6405,7 +6405,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-30.93</t>
+          <t>-31.95</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -6430,7 +6430,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -6480,17 +6480,17 @@
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>16.84</t>
+          <t>29.85</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
@@ -6501,66 +6501,66 @@
       <c r="AP13" t="inlineStr"/>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>644</t>
+          <t>485</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>62.5</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>56.0</t>
+          <t>45.39</t>
         </is>
       </c>
       <c r="AU13" t="n">
-        <v>0.15</v>
+        <v>-0.92</v>
       </c>
       <c r="AV13" t="n">
-        <v>-1.47</v>
+        <v>-1.6</v>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>-7.91</t>
+          <t>-7.76</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>-3.92</t>
+          <t>-4.10</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>67.99999999999999</t>
+          <t>67.72</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>69.02</v>
+        <v>68.81999999999999</v>
       </c>
       <c r="BA13" t="n">
-        <v>74.94</v>
+        <v>74.61</v>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>77.99</t>
+          <t>77.79</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>14.65</t>
+          <t>12.93</t>
         </is>
       </c>
       <c r="BD13" t="n">
-        <v>-1.91</v>
+        <v>-1.88</v>
       </c>
       <c r="BE13" t="n">
-        <v>-2.23</v>
+        <v>-2.16</v>
       </c>
       <c r="BF13" t="inlineStr">
         <is>
@@ -6569,7 +6569,7 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>-228.88</t>
+          <t>-224.84</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -6579,43 +6579,43 @@
       </c>
       <c r="BI13" t="inlineStr">
         <is>
-          <t>67131363.81310345</t>
+          <t>67106092.04545455</t>
         </is>
       </c>
       <c r="BJ13" t="inlineStr">
         <is>
-          <t>21662826.0</t>
+          <t>37869502.0</t>
         </is>
       </c>
       <c r="BK13" t="n">
-        <v>37068417.8</v>
+        <v>41191877</v>
       </c>
       <c r="BL13" t="inlineStr">
         <is>
-          <t>32440889.4</t>
+          <t>34549396.1</t>
         </is>
       </c>
       <c r="BM13" t="n">
-        <v>37992857.32</v>
+        <v>38283283.38</v>
       </c>
       <c r="BN13" t="inlineStr">
         <is>
-          <t>4627528</t>
+          <t>6642480</t>
         </is>
       </c>
       <c r="BO13" t="inlineStr">
         <is>
-          <t>-1960431.334702203</t>
+          <t>-1793330.345080202</t>
         </is>
       </c>
       <c r="BP13" t="inlineStr">
         <is>
-          <t>-1305220.805293366</t>
+          <t>-874274.9021591917</t>
         </is>
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>21662826.0</t>
+          <t>37869502.0</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -6635,7 +6635,7 @@
       </c>
       <c r="BU13" t="inlineStr">
         <is>
-          <t>-23.74</t>
+          <t>-24.86</t>
         </is>
       </c>
       <c r="BV13" t="inlineStr">
@@ -6680,22 +6680,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>6.78</t>
+          <t>6.71</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6705,7 +6705,7 @@
       </c>
       <c r="CI13" t="inlineStr">
         <is>
-          <t>20.95</t>
+          <t>21.17</t>
         </is>
       </c>
       <c r="CJ13" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="CL13" t="inlineStr">
         <is>
-          <t>55.85</t>
+          <t>56.13</t>
         </is>
       </c>
       <c r="CM13" t="inlineStr">
         <is>
-          <t>15730</t>
+          <t>15896</t>
         </is>
       </c>
       <c r="CN13" t="inlineStr">
@@ -6745,22 +6745,22 @@
       </c>
       <c r="CQ13" t="inlineStr">
         <is>
-          <t>68.1</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="CR13" t="inlineStr">
         <is>
-          <t>69.1</t>
+          <t>68.4</t>
         </is>
       </c>
       <c r="CS13" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="CT13" t="inlineStr">
         <is>
-          <t>68.1</t>
+          <t>67.1</t>
         </is>
       </c>
       <c r="CU13" t="inlineStr">
@@ -6792,12 +6792,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>673.593</t>
+          <t>316.85</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6807,7 +6807,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>68.5</t>
+          <t>68.1</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6817,17 +6817,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-3.16</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>12.26</t>
+          <t>14.26</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6892,7 +6892,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-30.53</t>
+          <t>-30.93</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6917,7 +6917,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -6967,17 +6967,17 @@
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>35.79</t>
+          <t>16.84</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>3.01</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
@@ -6988,66 +6988,66 @@
       <c r="AP14" t="inlineStr"/>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>644</t>
+          <t>485</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>73.68</t>
+          <t>62.5</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>35.17</t>
+          <t>56.0</t>
         </is>
       </c>
       <c r="AU14" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.15</v>
       </c>
       <c r="AV14" t="n">
-        <v>-1.55</v>
+        <v>-1.47</v>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>-8.07</t>
+          <t>-7.91</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>-3.71</t>
+          <t>-3.92</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>68.12</t>
+          <t>67.99999999999999</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>69.19</v>
+        <v>69.02</v>
       </c>
       <c r="BA14" t="n">
-        <v>75.27</v>
+        <v>74.94</v>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>78.16</t>
+          <t>77.99</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>13.22</t>
+          <t>14.65</t>
         </is>
       </c>
       <c r="BD14" t="n">
-        <v>-2.01</v>
+        <v>-1.91</v>
       </c>
       <c r="BE14" t="n">
-        <v>-2.32</v>
+        <v>-2.23</v>
       </c>
       <c r="BF14" t="inlineStr">
         <is>
@@ -7056,7 +7056,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>-233.60</t>
+          <t>-228.88</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -7066,43 +7066,43 @@
       </c>
       <c r="BI14" t="inlineStr">
         <is>
-          <t>67131363.81310345</t>
+          <t>67106092.04545455</t>
         </is>
       </c>
       <c r="BJ14" t="inlineStr">
         <is>
-          <t>45290917.0</t>
+          <t>21662826.0</t>
         </is>
       </c>
       <c r="BK14" t="n">
-        <v>36317228</v>
+        <v>37068417.8</v>
       </c>
       <c r="BL14" t="inlineStr">
         <is>
-          <t>32350796.3</t>
+          <t>32440889.4</t>
         </is>
       </c>
       <c r="BM14" t="n">
-        <v>38135166.56</v>
+        <v>37992857.32</v>
       </c>
       <c r="BN14" t="inlineStr">
         <is>
-          <t>3966431</t>
+          <t>4627528</t>
         </is>
       </c>
       <c r="BO14" t="inlineStr">
         <is>
-          <t>-2079560.521867446</t>
+          <t>-1960431.334702203</t>
         </is>
       </c>
       <c r="BP14" t="inlineStr">
         <is>
-          <t>-137813.2095817178</t>
+          <t>-1305220.805293366</t>
         </is>
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>45290917.0</t>
+          <t>21662826.0</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -7122,7 +7122,7 @@
       </c>
       <c r="BU14" t="inlineStr">
         <is>
-          <t>-23.29</t>
+          <t>-23.74</t>
         </is>
       </c>
       <c r="BV14" t="inlineStr">
@@ -7167,22 +7167,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>6.78</t>
+          <t>6.71</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -7192,7 +7192,7 @@
       </c>
       <c r="CI14" t="inlineStr">
         <is>
-          <t>20.95</t>
+          <t>21.17</t>
         </is>
       </c>
       <c r="CJ14" t="inlineStr">
@@ -7207,12 +7207,12 @@
       </c>
       <c r="CL14" t="inlineStr">
         <is>
-          <t>55.85</t>
+          <t>56.13</t>
         </is>
       </c>
       <c r="CM14" t="inlineStr">
         <is>
-          <t>15730</t>
+          <t>15896</t>
         </is>
       </c>
       <c r="CN14" t="inlineStr">
@@ -7232,22 +7232,22 @@
       </c>
       <c r="CQ14" t="inlineStr">
         <is>
-          <t>67.5</t>
+          <t>68.1</t>
         </is>
       </c>
       <c r="CR14" t="inlineStr">
         <is>
-          <t>68.5</t>
+          <t>69.1</t>
         </is>
       </c>
       <c r="CS14" t="inlineStr">
         <is>
-          <t>66.5</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="CT14" t="inlineStr">
         <is>
-          <t>68.5</t>
+          <t>68.1</t>
         </is>
       </c>
       <c r="CU14" t="inlineStr">
@@ -7284,7 +7284,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>658.104</t>
+          <t>673.593</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -7294,7 +7294,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>68.5</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -7304,17 +7304,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-2.11</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>5.11</t>
+          <t>12.26</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -7379,7 +7379,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-31.24</t>
+          <t>-30.53</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -7404,7 +7404,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -7454,17 +7454,17 @@
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>34.97</t>
+          <t>35.79</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>3.01</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
@@ -7475,66 +7475,66 @@
       <c r="AP15" t="inlineStr"/>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>644</t>
+          <t>485</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>31.82</t>
+          <t>73.68</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>23.57</t>
+          <t>35.17</t>
         </is>
       </c>
       <c r="AU15" t="n">
-        <v>-0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AV15" t="n">
-        <v>-1.72</v>
+        <v>-1.55</v>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>-8.29</t>
+          <t>-8.07</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>-3.49</t>
+          <t>-3.71</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>68.14</t>
+          <t>68.12</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>69.33</v>
+        <v>69.19</v>
       </c>
       <c r="BA15" t="n">
-        <v>75.59999999999999</v>
+        <v>75.27</v>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>78.33</t>
+          <t>78.16</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>10.03</t>
+          <t>13.22</t>
         </is>
       </c>
       <c r="BD15" t="n">
-        <v>-2.15</v>
+        <v>-2.01</v>
       </c>
       <c r="BE15" t="n">
-        <v>-2.39</v>
+        <v>-2.32</v>
       </c>
       <c r="BF15" t="inlineStr">
         <is>
@@ -7543,7 +7543,7 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>-238.01</t>
+          <t>-233.60</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -7553,43 +7553,43 @@
       </c>
       <c r="BI15" t="inlineStr">
         <is>
-          <t>67131363.81310345</t>
+          <t>67106092.04545455</t>
         </is>
       </c>
       <c r="BJ15" t="inlineStr">
         <is>
-          <t>44656757.0</t>
+          <t>45290917.0</t>
         </is>
       </c>
       <c r="BK15" t="n">
-        <v>31732769.6</v>
+        <v>36317228</v>
       </c>
       <c r="BL15" t="inlineStr">
         <is>
-          <t>30190352.0</t>
+          <t>32350796.3</t>
         </is>
       </c>
       <c r="BM15" t="n">
-        <v>37849613.32</v>
+        <v>38135166.56</v>
       </c>
       <c r="BN15" t="inlineStr">
         <is>
-          <t>1542417</t>
+          <t>3966431</t>
         </is>
       </c>
       <c r="BO15" t="inlineStr">
         <is>
-          <t>-2432605.487737579</t>
+          <t>-2079560.521867446</t>
         </is>
       </c>
       <c r="BP15" t="inlineStr">
         <is>
-          <t>-996747.3510800153</t>
+          <t>-137813.2095817178</t>
         </is>
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>44656757.0</t>
+          <t>45290917.0</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
@@ -7609,7 +7609,7 @@
       </c>
       <c r="BU15" t="inlineStr">
         <is>
-          <t>-24.08</t>
+          <t>-23.29</t>
         </is>
       </c>
       <c r="BV15" t="inlineStr">
@@ -7654,7 +7654,7 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
@@ -7664,12 +7664,12 @@
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>6.78</t>
+          <t>6.71</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -7679,7 +7679,7 @@
       </c>
       <c r="CI15" t="inlineStr">
         <is>
-          <t>20.95</t>
+          <t>21.17</t>
         </is>
       </c>
       <c r="CJ15" t="inlineStr">
@@ -7694,12 +7694,12 @@
       </c>
       <c r="CL15" t="inlineStr">
         <is>
-          <t>55.85</t>
+          <t>56.13</t>
         </is>
       </c>
       <c r="CM15" t="inlineStr">
         <is>
-          <t>15730</t>
+          <t>15896</t>
         </is>
       </c>
       <c r="CN15" t="inlineStr">
@@ -7719,22 +7719,22 @@
       </c>
       <c r="CQ15" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>67.5</t>
         </is>
       </c>
       <c r="CR15" t="inlineStr">
         <is>
-          <t>68.4</t>
+          <t>68.5</t>
         </is>
       </c>
       <c r="CS15" t="inlineStr">
         <is>
-          <t>66.8</t>
+          <t>66.5</t>
         </is>
       </c>
       <c r="CT15" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>68.5</t>
         </is>
       </c>
       <c r="CU15" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-2.04</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>839.101</t>
+          <t>658.104</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -7781,7 +7781,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>67.1</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -7791,17 +7791,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>8.11</t>
+          <t>5.11</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7866,7 +7866,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-31.95</t>
+          <t>-31.24</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7891,7 +7891,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -7941,17 +7941,17 @@
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>44.59</t>
+          <t>34.97</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
@@ -7962,38 +7962,38 @@
       <c r="AP16" t="inlineStr"/>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>644</t>
+          <t>485</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>31.82</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>29.63</t>
+          <t>23.57</t>
         </is>
       </c>
       <c r="AU16" t="n">
-        <v>-1.53</v>
+        <v>-0.5</v>
       </c>
       <c r="AV16" t="n">
-        <v>-1.98</v>
+        <v>-1.72</v>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>-8.52</t>
+          <t>-8.29</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>-3.21</t>
+          <t>-3.49</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -8002,26 +8002,26 @@
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>69.52</v>
+        <v>69.33</v>
       </c>
       <c r="BA16" t="n">
-        <v>75.98999999999999</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>78.51</t>
+          <t>78.33</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>8.98</t>
+          <t>10.03</t>
         </is>
       </c>
       <c r="BD16" t="n">
-        <v>-2.23</v>
+        <v>-2.15</v>
       </c>
       <c r="BE16" t="n">
-        <v>-2.45</v>
+        <v>-2.39</v>
       </c>
       <c r="BF16" t="inlineStr">
         <is>
@@ -8030,7 +8030,7 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>-241.47</t>
+          <t>-238.01</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -8040,43 +8040,43 @@
       </c>
       <c r="BI16" t="inlineStr">
         <is>
-          <t>67131363.81310345</t>
+          <t>67106092.04545455</t>
         </is>
       </c>
       <c r="BJ16" t="inlineStr">
         <is>
-          <t>56479383.0</t>
+          <t>44656757.0</t>
         </is>
       </c>
       <c r="BK16" t="n">
-        <v>30387660</v>
+        <v>31732769.6</v>
       </c>
       <c r="BL16" t="inlineStr">
         <is>
-          <t>28107734.3</t>
+          <t>30190352.0</t>
         </is>
       </c>
       <c r="BM16" t="n">
-        <v>38193467.22</v>
+        <v>37849613.32</v>
       </c>
       <c r="BN16" t="inlineStr">
         <is>
-          <t>2279925</t>
+          <t>1542417</t>
         </is>
       </c>
       <c r="BO16" t="inlineStr">
         <is>
-          <t>-2693670.6034935</t>
+          <t>-2432605.487737579</t>
         </is>
       </c>
       <c r="BP16" t="inlineStr">
         <is>
-          <t>-2120252.290681858</t>
+          <t>-996747.3510800153</t>
         </is>
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>56479383.0</t>
+          <t>44656757.0</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
@@ -8096,7 +8096,7 @@
       </c>
       <c r="BU16" t="inlineStr">
         <is>
-          <t>-24.86</t>
+          <t>-24.08</t>
         </is>
       </c>
       <c r="BV16" t="inlineStr">
@@ -8141,7 +8141,7 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
@@ -8151,12 +8151,12 @@
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>6.78</t>
+          <t>6.71</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -8166,7 +8166,7 @@
       </c>
       <c r="CI16" t="inlineStr">
         <is>
-          <t>20.95</t>
+          <t>21.17</t>
         </is>
       </c>
       <c r="CJ16" t="inlineStr">
@@ -8181,12 +8181,12 @@
       </c>
       <c r="CL16" t="inlineStr">
         <is>
-          <t>55.85</t>
+          <t>56.13</t>
         </is>
       </c>
       <c r="CM16" t="inlineStr">
         <is>
-          <t>15730</t>
+          <t>15896</t>
         </is>
       </c>
       <c r="CN16" t="inlineStr">
@@ -8206,22 +8206,22 @@
       </c>
       <c r="CQ16" t="inlineStr">
         <is>
-          <t>68.5</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="CR16" t="inlineStr">
         <is>
-          <t>68.5</t>
+          <t>68.4</t>
         </is>
       </c>
       <c r="CS16" t="inlineStr">
         <is>
-          <t>66.9</t>
+          <t>66.8</t>
         </is>
       </c>
       <c r="CT16" t="inlineStr">
         <is>
-          <t>67.1</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="CU16" t="inlineStr">
@@ -8253,12 +8253,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-2.04</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>251.116</t>
+          <t>839.101</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -8268,7 +8268,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>68.5</t>
+          <t>67.1</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -8278,17 +8278,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-3.16</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>5.95</t>
+          <t>8.11</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -8353,7 +8353,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-30.53</t>
+          <t>-31.95</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -8378,7 +8378,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -8428,17 +8428,17 @@
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>13.34</t>
+          <t>44.59</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
@@ -8449,66 +8449,66 @@
       <c r="AP17" t="inlineStr"/>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>644</t>
+          <t>485</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>38.89</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>44.44</t>
+          <t>29.63</t>
         </is>
       </c>
       <c r="AU17" t="n">
-        <v>0.26</v>
+        <v>-1.53</v>
       </c>
       <c r="AV17" t="n">
-        <v>-2.19</v>
+        <v>-1.98</v>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>-8.61</t>
+          <t>-8.52</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>-2.87</t>
+          <t>-3.21</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>68.32000000000001</t>
+          <t>68.14</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>69.84999999999999</v>
+        <v>69.52</v>
       </c>
       <c r="BA17" t="n">
-        <v>76.43000000000001</v>
+        <v>75.98999999999999</v>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>78.51</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>11.06</t>
+          <t>8.98</t>
         </is>
       </c>
       <c r="BD17" t="n">
         <v>-2.23</v>
       </c>
       <c r="BE17" t="n">
-        <v>-2.51</v>
+        <v>-2.45</v>
       </c>
       <c r="BF17" t="inlineStr">
         <is>
@@ -8517,7 +8517,7 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>-244.65</t>
+          <t>-241.47</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -8527,43 +8527,43 @@
       </c>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>67131363.81310345</t>
+          <t>67106092.04545455</t>
         </is>
       </c>
       <c r="BJ17" t="inlineStr">
         <is>
-          <t>17252206.0</t>
+          <t>56479383.0</t>
         </is>
       </c>
       <c r="BK17" t="n">
-        <v>27906915.2</v>
+        <v>30387660</v>
       </c>
       <c r="BL17" t="inlineStr">
         <is>
-          <t>26338712.0</t>
+          <t>28107734.3</t>
         </is>
       </c>
       <c r="BM17" t="n">
-        <v>40395160.94</v>
+        <v>38193467.22</v>
       </c>
       <c r="BN17" t="inlineStr">
         <is>
-          <t>1568203</t>
+          <t>2279925</t>
         </is>
       </c>
       <c r="BO17" t="inlineStr">
         <is>
-          <t>-2797928.478550162</t>
+          <t>-2693670.6034935</t>
         </is>
       </c>
       <c r="BP17" t="inlineStr">
         <is>
-          <t>-4916245.979731578</t>
+          <t>-2120252.290681858</t>
         </is>
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>17252206.0</t>
+          <t>56479383.0</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
@@ -8583,7 +8583,7 @@
       </c>
       <c r="BU17" t="inlineStr">
         <is>
-          <t>-23.29</t>
+          <t>-24.86</t>
         </is>
       </c>
       <c r="BV17" t="inlineStr">
@@ -8638,12 +8638,12 @@
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>6.78</t>
+          <t>6.71</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -8653,7 +8653,7 @@
       </c>
       <c r="CI17" t="inlineStr">
         <is>
-          <t>20.95</t>
+          <t>21.17</t>
         </is>
       </c>
       <c r="CJ17" t="inlineStr">
@@ -8668,12 +8668,12 @@
       </c>
       <c r="CL17" t="inlineStr">
         <is>
-          <t>55.85</t>
+          <t>56.13</t>
         </is>
       </c>
       <c r="CM17" t="inlineStr">
         <is>
-          <t>15730</t>
+          <t>15896</t>
         </is>
       </c>
       <c r="CN17" t="inlineStr">
@@ -8693,22 +8693,22 @@
       </c>
       <c r="CQ17" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>68.5</t>
         </is>
       </c>
       <c r="CR17" t="inlineStr">
         <is>
-          <t>69.4</t>
+          <t>68.5</t>
         </is>
       </c>
       <c r="CS17" t="inlineStr">
         <is>
-          <t>68.4</t>
+          <t>66.9</t>
         </is>
       </c>
       <c r="CT17" t="inlineStr">
         <is>
-          <t>68.5</t>
+          <t>67.1</t>
         </is>
       </c>
       <c r="CU17" t="inlineStr">
@@ -8740,12 +8740,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>261.237</t>
+          <t>251.116</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -8755,7 +8755,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>68.5</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -8765,17 +8765,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-3.46</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>5.95</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -8840,7 +8840,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-30.32</t>
+          <t>-30.53</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -8865,7 +8865,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -8915,17 +8915,17 @@
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>13.88</t>
+          <t>13.34</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
@@ -8936,66 +8936,66 @@
       <c r="AP18" t="inlineStr"/>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>644</t>
+          <t>485</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>38.89</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>31.48</t>
+          <t>44.44</t>
         </is>
       </c>
       <c r="AU18" t="n">
-        <v>0.41</v>
+        <v>0.26</v>
       </c>
       <c r="AV18" t="n">
-        <v>-2.42</v>
+        <v>-2.19</v>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>-8.66</t>
+          <t>-8.61</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>-2.67</t>
+          <t>-2.87</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>68.42</t>
+          <t>68.32000000000001</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>70.12</v>
+        <v>69.84999999999999</v>
       </c>
       <c r="BA18" t="n">
-        <v>76.76000000000001</v>
+        <v>76.43000000000001</v>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>78.87</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>9.28</t>
+          <t>11.06</t>
         </is>
       </c>
       <c r="BD18" t="n">
-        <v>-2.34</v>
+        <v>-2.23</v>
       </c>
       <c r="BE18" t="n">
-        <v>-2.58</v>
+        <v>-2.51</v>
       </c>
       <c r="BF18" t="inlineStr">
         <is>
@@ -9004,7 +9004,7 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>-248.65</t>
+          <t>-244.65</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -9014,43 +9014,43 @@
       </c>
       <c r="BI18" t="inlineStr">
         <is>
-          <t>67131363.81310345</t>
+          <t>67106092.04545455</t>
         </is>
       </c>
       <c r="BJ18" t="inlineStr">
         <is>
-          <t>17906877.0</t>
+          <t>17252206.0</t>
         </is>
       </c>
       <c r="BK18" t="n">
-        <v>27813361</v>
+        <v>27906915.2</v>
       </c>
       <c r="BL18" t="inlineStr">
         <is>
-          <t>27215289.8</t>
+          <t>26338712.0</t>
         </is>
       </c>
       <c r="BM18" t="n">
-        <v>41606784.8</v>
+        <v>40395160.94</v>
       </c>
       <c r="BN18" t="inlineStr">
         <is>
-          <t>598071</t>
+          <t>1568203</t>
         </is>
       </c>
       <c r="BO18" t="inlineStr">
         <is>
-          <t>-2412779.841971723</t>
+          <t>-2797928.478550162</t>
         </is>
       </c>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>-4532030.643383615</t>
+          <t>-4916245.979731578</t>
         </is>
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>17906877.0</t>
+          <t>17252206.0</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
@@ -9070,7 +9070,7 @@
       </c>
       <c r="BU18" t="inlineStr">
         <is>
-          <t>-23.07</t>
+          <t>-23.29</t>
         </is>
       </c>
       <c r="BV18" t="inlineStr">
@@ -9115,7 +9115,7 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
@@ -9130,7 +9130,7 @@
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>6.78</t>
+          <t>6.71</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -9140,7 +9140,7 @@
       </c>
       <c r="CI18" t="inlineStr">
         <is>
-          <t>20.95</t>
+          <t>21.17</t>
         </is>
       </c>
       <c r="CJ18" t="inlineStr">
@@ -9155,12 +9155,12 @@
       </c>
       <c r="CL18" t="inlineStr">
         <is>
-          <t>55.85</t>
+          <t>56.13</t>
         </is>
       </c>
       <c r="CM18" t="inlineStr">
         <is>
-          <t>15730</t>
+          <t>15896</t>
         </is>
       </c>
       <c r="CN18" t="inlineStr">
@@ -9180,22 +9180,22 @@
       </c>
       <c r="CQ18" t="inlineStr">
         <is>
-          <t>68.6</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="CR18" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>69.4</t>
         </is>
       </c>
       <c r="CS18" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>68.4</t>
         </is>
       </c>
       <c r="CT18" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>68.5</t>
         </is>
       </c>
       <c r="CU18" t="inlineStr">
@@ -9227,12 +9227,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>327.223</t>
+          <t>261.237</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -9242,7 +9242,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>68.6</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -9252,17 +9252,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-3.31</t>
+          <t>-2.38</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-12.29</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -9327,7 +9327,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-30.43</t>
+          <t>-30.32</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -9352,7 +9352,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -9402,17 +9402,17 @@
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>17.39</t>
+          <t>13.88</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
@@ -9423,66 +9423,66 @@
       <c r="AP19" t="inlineStr"/>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>644</t>
+          <t>485</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>44.44</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>14.81</t>
+          <t>31.48</t>
         </is>
       </c>
       <c r="AU19" t="n">
-        <v>0.09</v>
+        <v>0.41</v>
       </c>
       <c r="AV19" t="n">
-        <v>-2.54</v>
+        <v>-2.42</v>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>-8.83</t>
+          <t>-8.66</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>-2.40</t>
+          <t>-2.67</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>68.53999999999999</t>
+          <t>68.42</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>70.31999999999999</v>
+        <v>70.12</v>
       </c>
       <c r="BA19" t="n">
-        <v>77.14</v>
+        <v>76.76000000000001</v>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>79.04</t>
+          <t>78.87</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>6.64</t>
+          <t>9.28</t>
         </is>
       </c>
       <c r="BD19" t="n">
-        <v>-2.46</v>
+        <v>-2.34</v>
       </c>
       <c r="BE19" t="n">
-        <v>-2.64</v>
+        <v>-2.58</v>
       </c>
       <c r="BF19" t="inlineStr">
         <is>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>-252.10</t>
+          <t>-248.65</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -9501,43 +9501,43 @@
       </c>
       <c r="BI19" t="inlineStr">
         <is>
-          <t>67131363.81310345</t>
+          <t>67106092.04545455</t>
         </is>
       </c>
       <c r="BJ19" t="inlineStr">
         <is>
-          <t>22368625.0</t>
+          <t>17906877.0</t>
         </is>
       </c>
       <c r="BK19" t="n">
-        <v>28384364.6</v>
+        <v>27813361</v>
       </c>
       <c r="BL19" t="inlineStr">
         <is>
-          <t>32361196.0</t>
+          <t>27215289.8</t>
         </is>
       </c>
       <c r="BM19" t="n">
-        <v>43621757.96</v>
+        <v>41606784.8</v>
       </c>
       <c r="BN19" t="inlineStr">
         <is>
-          <t>-3976831</t>
+          <t>598071</t>
         </is>
       </c>
       <c r="BO19" t="inlineStr">
         <is>
-          <t>-2027461.514442288</t>
+          <t>-2412779.841971723</t>
         </is>
       </c>
       <c r="BP19" t="inlineStr">
         <is>
-          <t>-3891436.675622828</t>
+          <t>-4532030.643383615</t>
         </is>
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>22368625.0</t>
+          <t>17906877.0</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
@@ -9557,7 +9557,7 @@
       </c>
       <c r="BU19" t="inlineStr">
         <is>
-          <t>-23.18</t>
+          <t>-23.07</t>
         </is>
       </c>
       <c r="BV19" t="inlineStr">
@@ -9602,7 +9602,7 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
@@ -9617,7 +9617,7 @@
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>6.78</t>
+          <t>6.71</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -9627,7 +9627,7 @@
       </c>
       <c r="CI19" t="inlineStr">
         <is>
-          <t>20.95</t>
+          <t>21.17</t>
         </is>
       </c>
       <c r="CJ19" t="inlineStr">
@@ -9642,12 +9642,12 @@
       </c>
       <c r="CL19" t="inlineStr">
         <is>
-          <t>55.85</t>
+          <t>56.13</t>
         </is>
       </c>
       <c r="CM19" t="inlineStr">
         <is>
-          <t>15730</t>
+          <t>15896</t>
         </is>
       </c>
       <c r="CN19" t="inlineStr">
@@ -9667,22 +9667,22 @@
       </c>
       <c r="CQ19" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>68.6</t>
         </is>
       </c>
       <c r="CR19" t="inlineStr">
         <is>
-          <t>68.6</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="CS19" t="inlineStr">
         <is>
-          <t>67.7</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="CT19" t="inlineStr">
         <is>
-          <t>68.6</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="CU19" t="inlineStr">
@@ -9714,12 +9714,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-2.45</t>
+          <t>5.86</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>82573.213</t>
+          <t>83828.18</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -9729,7 +9729,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>55.6</t>
+          <t>58.9</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -9744,12 +9744,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-2.5</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>13.99</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-9.45</t>
+          <t>-4.07</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -9839,7 +9839,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -9889,17 +9889,17 @@
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>24.51</t>
+          <t>24.88</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>-2.69</t>
+          <t>3.77</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
@@ -9910,66 +9910,66 @@
       <c r="AP20" t="inlineStr"/>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>656</t>
+          <t>679</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>82573</t>
+          <t>83828</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>71.74</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>31.11</t>
+          <t>23.91</t>
         </is>
       </c>
       <c r="AU20" t="n">
-        <v>-4.07</v>
+        <v>1.55</v>
       </c>
       <c r="AV20" t="n">
-        <v>-2.53</v>
+        <v>-2.09</v>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>9.89</t>
+          <t>8.85</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>11.07</t>
+          <t>11.12</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>57.96</t>
+          <t>58.0</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>59.46</v>
+        <v>59.24</v>
       </c>
       <c r="BA20" t="n">
-        <v>54.12</v>
+        <v>54.42</v>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>48.72</t>
+          <t>48.98</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>-59.69</t>
+          <t>-53.37</t>
         </is>
       </c>
       <c r="BD20" t="n">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="BF20" t="inlineStr">
         <is>
@@ -9978,7 +9978,7 @@
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>-70.39</t>
+          <t>-73.88</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
@@ -9988,43 +9988,43 @@
       </c>
       <c r="BI20" t="inlineStr">
         <is>
-          <t>1631368124.406207</t>
+          <t>1639172660.568182</t>
         </is>
       </c>
       <c r="BJ20" t="inlineStr">
         <is>
-          <t>4619110598.0</t>
+          <t>4864974252.0</t>
         </is>
       </c>
       <c r="BK20" t="n">
-        <v>4197111762.4</v>
+        <v>4448388712.2</v>
       </c>
       <c r="BL20" t="inlineStr">
         <is>
-          <t>4175836369.4</t>
+          <t>3902292857.5</t>
         </is>
       </c>
       <c r="BM20" t="n">
-        <v>5968956549.88</v>
+        <v>5988755892.86</v>
       </c>
       <c r="BN20" t="inlineStr">
         <is>
-          <t>21275393</t>
+          <t>546095854</t>
         </is>
       </c>
       <c r="BO20" t="inlineStr">
         <is>
-          <t>-564368963.728064</t>
+          <t>-507260011.6889273</t>
         </is>
       </c>
       <c r="BP20" t="inlineStr">
         <is>
-          <t>-271577338.4025931</t>
+          <t>-193160775.4736757</t>
         </is>
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>4619110598.0</t>
+          <t>4864974252.0</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
@@ -10044,7 +10044,7 @@
       </c>
       <c r="BU20" t="inlineStr">
         <is>
-          <t>32.70</t>
+          <t>40.57</t>
         </is>
       </c>
       <c r="BV20" t="inlineStr">
@@ -10069,7 +10069,7 @@
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -10089,22 +10089,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -10129,12 +10129,12 @@
       </c>
       <c r="CL20" t="inlineStr">
         <is>
-          <t>62.95</t>
+          <t>63.05</t>
         </is>
       </c>
       <c r="CM20" t="inlineStr">
         <is>
-          <t>440954</t>
+          <t>467125</t>
         </is>
       </c>
       <c r="CN20" t="inlineStr">
@@ -10154,22 +10154,22 @@
       </c>
       <c r="CQ20" t="inlineStr">
         <is>
-          <t>57.2</t>
+          <t>56.3</t>
         </is>
       </c>
       <c r="CR20" t="inlineStr">
         <is>
-          <t>57.6</t>
+          <t>59.4</t>
         </is>
       </c>
       <c r="CS20" t="inlineStr">
         <is>
-          <t>55.1</t>
+          <t>56.3</t>
         </is>
       </c>
       <c r="CT20" t="inlineStr">
         <is>
-          <t>55.6</t>
+          <t>58.9</t>
         </is>
       </c>
       <c r="CU20" t="inlineStr">
@@ -10184,7 +10184,7 @@
       </c>
       <c r="CW20" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -10201,12 +10201,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-5.32</t>
+          <t>-2.45</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>101489.286</t>
+          <t>82573.213</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -10216,7 +10216,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>57.0</t>
+          <t>55.6</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -10226,17 +10226,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-2.52</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-2.5</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-6.64</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -10301,7 +10301,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-7.17</t>
+          <t>-9.45</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -10326,7 +10326,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -10376,17 +10376,17 @@
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>30.12</t>
+          <t>24.51</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>-5.61</t>
+          <t>-2.69</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
@@ -10397,12 +10397,12 @@
       <c r="AP21" t="inlineStr"/>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>656</t>
+          <t>679</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>82573</t>
+          <t>83828</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -10412,51 +10412,51 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>41.11</t>
+          <t>31.11</t>
         </is>
       </c>
       <c r="AU21" t="n">
-        <v>-2.3</v>
+        <v>-4.07</v>
       </c>
       <c r="AV21" t="n">
         <v>-2.53</v>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>11.15</t>
+          <t>9.89</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>11.01</t>
+          <t>11.07</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>58.34</t>
+          <t>57.96</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>59.86</v>
+        <v>59.46</v>
       </c>
       <c r="BA21" t="n">
-        <v>53.85</v>
+        <v>54.12</v>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>48.51</t>
+          <t>48.72</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>-44.45</t>
+          <t>-59.69</t>
         </is>
       </c>
       <c r="BD21" t="n">
-        <v>0.85</v>
+        <v>0.54</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.53</v>
+        <v>1.33</v>
       </c>
       <c r="BF21" t="inlineStr">
         <is>
@@ -10465,7 +10465,7 @@
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>-65.97</t>
+          <t>-70.39</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
@@ -10475,43 +10475,43 @@
       </c>
       <c r="BI21" t="inlineStr">
         <is>
-          <t>1631368124.406207</t>
+          <t>1639172660.568182</t>
         </is>
       </c>
       <c r="BJ21" t="inlineStr">
         <is>
-          <t>5853333897.0</t>
+          <t>4619110598.0</t>
         </is>
       </c>
       <c r="BK21" t="n">
-        <v>3714284996.2</v>
+        <v>4197111762.4</v>
       </c>
       <c r="BL21" t="inlineStr">
         <is>
-          <t>3978274860.9</t>
+          <t>4175836369.4</t>
         </is>
       </c>
       <c r="BM21" t="n">
-        <v>5935432936.84</v>
+        <v>5968956549.88</v>
       </c>
       <c r="BN21" t="inlineStr">
         <is>
-          <t>-263989864</t>
+          <t>21275393</t>
         </is>
       </c>
       <c r="BO21" t="inlineStr">
         <is>
-          <t>-617603804.6963314</t>
+          <t>-564368963.728064</t>
         </is>
       </c>
       <c r="BP21" t="inlineStr">
         <is>
-          <t>-347559274.7152386</t>
+          <t>-271577338.4025931</t>
         </is>
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>5853333897.0</t>
+          <t>4619110598.0</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -10531,7 +10531,7 @@
       </c>
       <c r="BU21" t="inlineStr">
         <is>
-          <t>36.04</t>
+          <t>32.70</t>
         </is>
       </c>
       <c r="BV21" t="inlineStr">
@@ -10556,7 +10556,7 @@
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -10576,22 +10576,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -10616,12 +10616,12 @@
       </c>
       <c r="CL21" t="inlineStr">
         <is>
-          <t>62.95</t>
+          <t>63.05</t>
         </is>
       </c>
       <c r="CM21" t="inlineStr">
         <is>
-          <t>440954</t>
+          <t>467125</t>
         </is>
       </c>
       <c r="CN21" t="inlineStr">
@@ -10641,22 +10641,22 @@
       </c>
       <c r="CQ21" t="inlineStr">
         <is>
-          <t>60.2</t>
+          <t>57.2</t>
         </is>
       </c>
       <c r="CR21" t="inlineStr">
         <is>
-          <t>60.2</t>
+          <t>57.6</t>
         </is>
       </c>
       <c r="CS21" t="inlineStr">
         <is>
-          <t>57.0</t>
+          <t>55.1</t>
         </is>
       </c>
       <c r="CT21" t="inlineStr">
         <is>
-          <t>57.0</t>
+          <t>55.6</t>
         </is>
       </c>
       <c r="CU21" t="inlineStr">
@@ -10671,7 +10671,7 @@
       </c>
       <c r="CW21" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -10688,12 +10688,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>-5.32</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>90915.325</t>
+          <t>101489.286</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -10703,7 +10703,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>60.2</t>
+          <t>57.0</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -10713,17 +10713,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-8.27</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-2.5</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-15.89</t>
+          <t>-6.64</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -10788,7 +10788,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>-7.17</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -10813,7 +10813,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -10863,17 +10863,17 @@
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>26.98</t>
+          <t>30.12</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>4.16</t>
+          <t>-5.61</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
@@ -10884,66 +10884,66 @@
       <c r="AP22" t="inlineStr"/>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>656</t>
+          <t>679</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>82573</t>
+          <t>83828</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
         <is>
-          <t>93.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>55.56</t>
+          <t>41.11</t>
         </is>
       </c>
       <c r="AU22" t="n">
-        <v>2.8</v>
+        <v>-2.3</v>
       </c>
       <c r="AV22" t="n">
-        <v>-3.03</v>
+        <v>-2.53</v>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>12.78</t>
+          <t>11.15</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>10.91</t>
+          <t>11.01</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>58.56</t>
+          <t>58.34</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>60.39</v>
+        <v>59.86</v>
       </c>
       <c r="BA22" t="n">
-        <v>53.55</v>
+        <v>53.85</v>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>48.28</t>
+          <t>48.51</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>-35.58</t>
+          <t>-44.45</t>
         </is>
       </c>
       <c r="BD22" t="n">
-        <v>1.1</v>
+        <v>0.85</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.7</v>
+        <v>1.53</v>
       </c>
       <c r="BF22" t="inlineStr">
         <is>
@@ -10952,7 +10952,7 @@
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>-62.19</t>
+          <t>-65.97</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
@@ -10962,43 +10962,43 @@
       </c>
       <c r="BI22" t="inlineStr">
         <is>
-          <t>1631368124.406207</t>
+          <t>1639172660.568182</t>
         </is>
       </c>
       <c r="BJ22" t="inlineStr">
         <is>
-          <t>5358599052.0</t>
+          <t>5853333897.0</t>
         </is>
       </c>
       <c r="BK22" t="n">
-        <v>3151725986</v>
+        <v>3714284996.2</v>
       </c>
       <c r="BL22" t="inlineStr">
         <is>
-          <t>3746963129.5</t>
+          <t>3978274860.9</t>
         </is>
       </c>
       <c r="BM22" t="n">
-        <v>5841022551.14</v>
+        <v>5935432936.84</v>
       </c>
       <c r="BN22" t="inlineStr">
         <is>
-          <t>-595237143</t>
+          <t>-263989864</t>
         </is>
       </c>
       <c r="BO22" t="inlineStr">
         <is>
-          <t>-666702810.1474391</t>
+          <t>-617603804.6963314</t>
         </is>
       </c>
       <c r="BP22" t="inlineStr">
         <is>
-          <t>-575930277.3863311</t>
+          <t>-347559274.7152386</t>
         </is>
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>5358599052.0</t>
+          <t>5853333897.0</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -11018,7 +11018,7 @@
       </c>
       <c r="BU22" t="inlineStr">
         <is>
-          <t>43.68</t>
+          <t>36.04</t>
         </is>
       </c>
       <c r="BV22" t="inlineStr">
@@ -11043,7 +11043,7 @@
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -11063,22 +11063,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -11103,12 +11103,12 @@
       </c>
       <c r="CL22" t="inlineStr">
         <is>
-          <t>62.95</t>
+          <t>63.05</t>
         </is>
       </c>
       <c r="CM22" t="inlineStr">
         <is>
-          <t>440954</t>
+          <t>467125</t>
         </is>
       </c>
       <c r="CN22" t="inlineStr">
@@ -11128,22 +11128,22 @@
       </c>
       <c r="CQ22" t="inlineStr">
         <is>
-          <t>58.4</t>
+          <t>60.2</t>
         </is>
       </c>
       <c r="CR22" t="inlineStr">
         <is>
-          <t>61.3</t>
+          <t>60.2</t>
         </is>
       </c>
       <c r="CS22" t="inlineStr">
         <is>
-          <t>56.8</t>
+          <t>57.0</t>
         </is>
       </c>
       <c r="CT22" t="inlineStr">
         <is>
-          <t>60.2</t>
+          <t>57.0</t>
         </is>
       </c>
       <c r="CU22" t="inlineStr">
@@ -11158,7 +11158,7 @@
       </c>
       <c r="CW22" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -11175,12 +11175,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>26487.92</t>
+          <t>90915.325</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -11190,7 +11190,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>58.3</t>
+          <t>60.2</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -11200,17 +11200,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-4.86</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-2.5</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-19.23</t>
+          <t>-15.89</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -11275,7 +11275,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-5.05</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -11300,7 +11300,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -11350,17 +11350,17 @@
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>7.86</t>
+          <t>26.98</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>4.16</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
@@ -11371,66 +11371,66 @@
       <c r="AP23" t="inlineStr"/>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>656</t>
+          <t>679</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>82573</t>
+          <t>83828</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>93.33</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>25.52</t>
+          <t>55.56</t>
         </is>
       </c>
       <c r="AU23" t="n">
-        <v>0.03</v>
+        <v>2.8</v>
       </c>
       <c r="AV23" t="n">
-        <v>-3.83</v>
+        <v>-3.03</v>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>13.94</t>
+          <t>12.78</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>10.75</t>
+          <t>10.91</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>58.27999999999999</t>
+          <t>58.56</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>60.6</v>
+        <v>60.39</v>
       </c>
       <c r="BA23" t="n">
-        <v>53.18</v>
+        <v>53.55</v>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>48.02</t>
+          <t>48.28</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>-42.35</t>
+          <t>-35.58</t>
         </is>
       </c>
       <c r="BD23" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.86</v>
+        <v>1.7</v>
       </c>
       <c r="BF23" t="inlineStr">
         <is>
@@ -11439,7 +11439,7 @@
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>-58.82</t>
+          <t>-62.19</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
@@ -11449,43 +11449,43 @@
       </c>
       <c r="BI23" t="inlineStr">
         <is>
-          <t>1631368124.406207</t>
+          <t>1639172660.568182</t>
         </is>
       </c>
       <c r="BJ23" t="inlineStr">
         <is>
-          <t>1545925762.0</t>
+          <t>5358599052.0</t>
         </is>
       </c>
       <c r="BK23" t="n">
-        <v>2816775873.8</v>
+        <v>3151725986</v>
       </c>
       <c r="BL23" t="inlineStr">
         <is>
-          <t>3487467287.4</t>
+          <t>3746963129.5</t>
         </is>
       </c>
       <c r="BM23" t="n">
-        <v>5761704538.5</v>
+        <v>5841022551.14</v>
       </c>
       <c r="BN23" t="inlineStr">
         <is>
-          <t>-670691413</t>
+          <t>-595237143</t>
         </is>
       </c>
       <c r="BO23" t="inlineStr">
         <is>
-          <t>-683206907.0130951</t>
+          <t>-666702810.1474391</t>
         </is>
       </c>
       <c r="BP23" t="inlineStr">
         <is>
-          <t>-828598323.6169515</t>
+          <t>-575930277.3863311</t>
         </is>
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>1545925762.0</t>
+          <t>5358599052.0</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -11505,7 +11505,7 @@
       </c>
       <c r="BU23" t="inlineStr">
         <is>
-          <t>39.14</t>
+          <t>43.68</t>
         </is>
       </c>
       <c r="BV23" t="inlineStr">
@@ -11530,7 +11530,7 @@
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -11550,22 +11550,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">
@@ -11590,12 +11590,12 @@
       </c>
       <c r="CL23" t="inlineStr">
         <is>
-          <t>62.95</t>
+          <t>63.05</t>
         </is>
       </c>
       <c r="CM23" t="inlineStr">
         <is>
-          <t>440954</t>
+          <t>467125</t>
         </is>
       </c>
       <c r="CN23" t="inlineStr">
@@ -11615,22 +11615,22 @@
       </c>
       <c r="CQ23" t="inlineStr">
         <is>
-          <t>58.7</t>
+          <t>58.4</t>
         </is>
       </c>
       <c r="CR23" t="inlineStr">
         <is>
-          <t>59.0</t>
+          <t>61.3</t>
         </is>
       </c>
       <c r="CS23" t="inlineStr">
         <is>
-          <t>58.0</t>
+          <t>56.8</t>
         </is>
       </c>
       <c r="CT23" t="inlineStr">
         <is>
-          <t>58.3</t>
+          <t>60.2</t>
         </is>
       </c>
       <c r="CU23" t="inlineStr">
@@ -11645,7 +11645,7 @@
       </c>
       <c r="CW23" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -11662,12 +11662,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>60874.354</t>
+          <t>26487.92</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -11677,7 +11677,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>58.7</t>
+          <t>58.3</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -11687,17 +11687,17 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-5.58</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>-2.5</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>-4.90</t>
+          <t>-19.23</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -11762,7 +11762,7 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>-4.40</t>
+          <t>-5.05</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
@@ -11787,7 +11787,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -11837,17 +11837,17 @@
       </c>
       <c r="AL24" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>18.07</t>
+          <t>7.86</t>
         </is>
       </c>
       <c r="AN24" t="inlineStr">
         <is>
-          <t>-1.69</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
@@ -11858,266 +11858,266 @@
       <c r="AP24" t="inlineStr"/>
       <c r="AQ24" t="inlineStr">
         <is>
-          <t>656</t>
+          <t>679</t>
         </is>
       </c>
       <c r="AR24" t="inlineStr">
         <is>
-          <t>82573</t>
+          <t>83828</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr">
         <is>
-          <t>43.33</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr">
         <is>
-          <t>21.83</t>
+          <t>25.52</t>
         </is>
       </c>
       <c r="AU24" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="AV24" t="n">
-        <v>-3.36</v>
+        <v>-3.83</v>
       </c>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>14.91</t>
+          <t>13.94</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>10.60</t>
+          <t>10.75</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
+          <t>58.27999999999999</t>
+        </is>
+      </c>
+      <c r="AZ24" t="n">
+        <v>60.6</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>53.18</v>
+      </c>
+      <c r="BB24" t="inlineStr">
+        <is>
+          <t>48.02</t>
+        </is>
+      </c>
+      <c r="BC24" t="inlineStr">
+        <is>
+          <t>-42.35</t>
+        </is>
+      </c>
+      <c r="BD24" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="BF24" t="inlineStr">
+        <is>
+          <t>4.51</t>
+        </is>
+      </c>
+      <c r="BG24" t="inlineStr">
+        <is>
+          <t>-58.82</t>
+        </is>
+      </c>
+      <c r="BH24" t="inlineStr">
+        <is>
+          <t>2025/11/27</t>
+        </is>
+      </c>
+      <c r="BI24" t="inlineStr">
+        <is>
+          <t>1639172660.568182</t>
+        </is>
+      </c>
+      <c r="BJ24" t="inlineStr">
+        <is>
+          <t>1545925762.0</t>
+        </is>
+      </c>
+      <c r="BK24" t="n">
+        <v>2816775873.8</v>
+      </c>
+      <c r="BL24" t="inlineStr">
+        <is>
+          <t>3487467287.4</t>
+        </is>
+      </c>
+      <c r="BM24" t="n">
+        <v>5761704538.5</v>
+      </c>
+      <c r="BN24" t="inlineStr">
+        <is>
+          <t>-670691413</t>
+        </is>
+      </c>
+      <c r="BO24" t="inlineStr">
+        <is>
+          <t>-683206907.0130951</t>
+        </is>
+      </c>
+      <c r="BP24" t="inlineStr">
+        <is>
+          <t>-828598323.6169515</t>
+        </is>
+      </c>
+      <c r="BQ24" t="inlineStr">
+        <is>
+          <t>1545925762.0</t>
+        </is>
+      </c>
+      <c r="BR24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BS24" t="inlineStr">
+        <is>
+          <t>41.9</t>
+        </is>
+      </c>
+      <c r="BT24" t="inlineStr">
+        <is>
+          <t>2025/10/21</t>
+        </is>
+      </c>
+      <c r="BU24" t="inlineStr">
+        <is>
+          <t>39.14</t>
+        </is>
+      </c>
+      <c r="BV24" t="inlineStr">
+        <is>
+          <t>南亞</t>
+        </is>
+      </c>
+      <c r="BW24" t="inlineStr">
+        <is>
+          <t>南亞</t>
+        </is>
+      </c>
+      <c r="BX24" t="inlineStr">
+        <is>
+          <t>塑膠工業</t>
+        </is>
+      </c>
+      <c r="BY24" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BZ24" t="inlineStr">
+        <is>
+          <t>0.88</t>
+        </is>
+      </c>
+      <c r="CA24" t="inlineStr">
+        <is>
+          <t>-0.4646396463764443</t>
+        </is>
+      </c>
+      <c r="CB24" t="inlineStr">
+        <is>
+          <t>-3.800318800328133</t>
+        </is>
+      </c>
+      <c r="CC24" t="inlineStr">
+        <is>
+          <t>0.6866519744403886</t>
+        </is>
+      </c>
+      <c r="CD24" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="CE24" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="CF24" t="inlineStr">
+        <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="CG24" t="inlineStr">
+        <is>
+          <t>1.19</t>
+        </is>
+      </c>
+      <c r="CH24" t="inlineStr">
+        <is>
+          <t>8.09</t>
+        </is>
+      </c>
+      <c r="CI24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CJ24" t="inlineStr">
+        <is>
+          <t>8.29%</t>
+        </is>
+      </c>
+      <c r="CK24" t="inlineStr">
+        <is>
+          <t>1.61%</t>
+        </is>
+      </c>
+      <c r="CL24" t="inlineStr">
+        <is>
+          <t>63.05</t>
+        </is>
+      </c>
+      <c r="CM24" t="inlineStr">
+        <is>
+          <t>467125</t>
+        </is>
+      </c>
+      <c r="CN24" t="inlineStr">
+        <is>
+          <t>聚酯纖維16.60%、其他16.28%、印刷電路板(PCB)12.09%、銅箔基板(CCL)10.47%、環氧樹脂8.29%、丙二酚(BPA)5.67%、乙二醇(EG)5.60%、銅箔5.01%、可塑劑(DOP)及硬化劑3.38%、硬質管2.55%、硬質膠布2.48%、塑膠門窗2.20%、軟質膠布1.85%、麩酸酐(PA)1.55%、玻璃纖維布1.32%、聚酯薄膜1.30%、膠乳皮0.92%、PU合成皮(人造皮)0.69%、BOPP膜0.64%、玻璃纖維絲0.60%、丁二醇(BDO)0.54% (2024年)</t>
+        </is>
+      </c>
+      <c r="CO24" t="inlineStr">
+        <is>
+          <t>南亞-塑膠工業-上市</t>
+        </is>
+      </c>
+      <c r="CP24" t="inlineStr">
+        <is>
+          <t>塑膠工業平上市</t>
+        </is>
+      </c>
+      <c r="CQ24" t="inlineStr">
+        <is>
           <t>58.7</t>
         </is>
       </c>
-      <c r="AZ24" t="n">
-        <v>60.74</v>
-      </c>
-      <c r="BA24" t="n">
-        <v>52.86</v>
-      </c>
-      <c r="BB24" t="inlineStr">
-        <is>
-          <t>47.79</t>
-        </is>
-      </c>
-      <c r="BC24" t="inlineStr">
-        <is>
-          <t>-40.94</t>
-        </is>
-      </c>
-      <c r="BD24" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="BE24" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="BF24" t="inlineStr">
-        <is>
-          <t>4.51</t>
-        </is>
-      </c>
-      <c r="BG24" t="inlineStr">
-        <is>
-          <t>-54.47</t>
-        </is>
-      </c>
-      <c r="BH24" t="inlineStr">
-        <is>
-          <t>2025/11/27</t>
-        </is>
-      </c>
-      <c r="BI24" t="inlineStr">
-        <is>
-          <t>1631368124.406207</t>
-        </is>
-      </c>
-      <c r="BJ24" t="inlineStr">
-        <is>
-          <t>3608589503.0</t>
-        </is>
-      </c>
-      <c r="BK24" t="n">
-        <v>3356197002.8</v>
-      </c>
-      <c r="BL24" t="inlineStr">
-        <is>
-          <t>3528975051.7</t>
-        </is>
-      </c>
-      <c r="BM24" t="n">
-        <v>5761226342.04</v>
-      </c>
-      <c r="BN24" t="inlineStr">
-        <is>
-          <t>-172778048</t>
-        </is>
-      </c>
-      <c r="BO24" t="inlineStr">
-        <is>
-          <t>-656772103.9942122</t>
-        </is>
-      </c>
-      <c r="BP24" t="inlineStr">
-        <is>
-          <t>-751459168.4600897</t>
-        </is>
-      </c>
-      <c r="BQ24" t="inlineStr">
-        <is>
-          <t>3608589503.0</t>
-        </is>
-      </c>
-      <c r="BR24" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BS24" t="inlineStr">
-        <is>
-          <t>41.9</t>
-        </is>
-      </c>
-      <c r="BT24" t="inlineStr">
-        <is>
-          <t>2025/10/21</t>
-        </is>
-      </c>
-      <c r="BU24" t="inlineStr">
-        <is>
-          <t>40.10</t>
-        </is>
-      </c>
-      <c r="BV24" t="inlineStr">
-        <is>
-          <t>南亞</t>
-        </is>
-      </c>
-      <c r="BW24" t="inlineStr">
-        <is>
-          <t>南亞</t>
-        </is>
-      </c>
-      <c r="BX24" t="inlineStr">
-        <is>
-          <t>塑膠工業</t>
-        </is>
-      </c>
-      <c r="BY24" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BZ24" t="inlineStr">
-        <is>
-          <t>0.89</t>
-        </is>
-      </c>
-      <c r="CA24" t="inlineStr">
-        <is>
-          <t>-0.4646396463764443</t>
-        </is>
-      </c>
-      <c r="CB24" t="inlineStr">
-        <is>
-          <t>-3.800318800328133</t>
-        </is>
-      </c>
-      <c r="CC24" t="inlineStr">
-        <is>
-          <t>0.6866519744403886</t>
-        </is>
-      </c>
-      <c r="CD24" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="CE24" t="inlineStr">
-        <is>
-          <t>價漲量-</t>
-        </is>
-      </c>
-      <c r="CF24" t="inlineStr">
-        <is>
-          <t>1.42</t>
-        </is>
-      </c>
-      <c r="CG24" t="inlineStr">
-        <is>
-          <t>1.26</t>
-        </is>
-      </c>
-      <c r="CH24" t="inlineStr">
-        <is>
-          <t>8.09</t>
-        </is>
-      </c>
-      <c r="CI24" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CJ24" t="inlineStr">
-        <is>
-          <t>8.29%</t>
-        </is>
-      </c>
-      <c r="CK24" t="inlineStr">
-        <is>
-          <t>1.61%</t>
-        </is>
-      </c>
-      <c r="CL24" t="inlineStr">
-        <is>
-          <t>62.95</t>
-        </is>
-      </c>
-      <c r="CM24" t="inlineStr">
-        <is>
-          <t>440954</t>
-        </is>
-      </c>
-      <c r="CN24" t="inlineStr">
-        <is>
-          <t>聚酯纖維16.60%、其他16.28%、印刷電路板(PCB)12.09%、銅箔基板(CCL)10.47%、環氧樹脂8.29%、丙二酚(BPA)5.67%、乙二醇(EG)5.60%、銅箔5.01%、可塑劑(DOP)及硬化劑3.38%、硬質管2.55%、硬質膠布2.48%、塑膠門窗2.20%、軟質膠布1.85%、麩酸酐(PA)1.55%、玻璃纖維布1.32%、聚酯薄膜1.30%、膠乳皮0.92%、PU合成皮(人造皮)0.69%、BOPP膜0.64%、玻璃纖維絲0.60%、丁二醇(BDO)0.54% (2024年)</t>
-        </is>
-      </c>
-      <c r="CO24" t="inlineStr">
-        <is>
-          <t>南亞-塑膠工業-上市</t>
-        </is>
-      </c>
-      <c r="CP24" t="inlineStr">
-        <is>
-          <t>塑膠工業平上市</t>
-        </is>
-      </c>
-      <c r="CQ24" t="inlineStr">
-        <is>
-          <t>58.2</t>
-        </is>
-      </c>
       <c r="CR24" t="inlineStr">
         <is>
-          <t>60.3</t>
+          <t>59.0</t>
         </is>
       </c>
       <c r="CS24" t="inlineStr">
         <is>
-          <t>58.1</t>
+          <t>58.0</t>
         </is>
       </c>
       <c r="CT24" t="inlineStr">
         <is>
-          <t>58.7</t>
+          <t>58.3</t>
         </is>
       </c>
       <c r="CU24" t="inlineStr">
@@ -12132,7 +12132,7 @@
       </c>
       <c r="CW24" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -12149,12 +12149,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>37995.984</t>
+          <t>60874.354</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -12164,7 +12164,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>58.7</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -12174,17 +12174,17 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-3.42</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>-2.5</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>22.11</t>
+          <t>-4.90</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -12249,7 +12249,7 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>-6.35</t>
+          <t>-4.40</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
@@ -12274,7 +12274,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -12324,17 +12324,17 @@
       </c>
       <c r="AL25" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>11.28</t>
+          <t>18.07</t>
         </is>
       </c>
       <c r="AN25" t="inlineStr">
         <is>
-          <t>-2.96</t>
+          <t>-1.69</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
@@ -12345,66 +12345,66 @@
       <c r="AP25" t="inlineStr"/>
       <c r="AQ25" t="inlineStr">
         <is>
-          <t>656</t>
+          <t>679</t>
         </is>
       </c>
       <c r="AR25" t="inlineStr">
         <is>
-          <t>82573</t>
+          <t>83828</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>43.33</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr">
         <is>
-          <t>19.99</t>
+          <t>21.83</t>
         </is>
       </c>
       <c r="AU25" t="n">
-        <v>-2.44</v>
+        <v>0</v>
       </c>
       <c r="AV25" t="n">
-        <v>-2.99</v>
+        <v>-3.36</v>
       </c>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>15.7</t>
+          <t>14.91</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>10.35</t>
+          <t>10.60</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
-          <t>58.94</t>
+          <t>58.7</t>
         </is>
       </c>
       <c r="AZ25" t="n">
-        <v>60.76</v>
+        <v>60.74</v>
       </c>
       <c r="BA25" t="n">
-        <v>52.51</v>
+        <v>52.86</v>
       </c>
       <c r="BB25" t="inlineStr">
         <is>
-          <t>47.59</t>
+          <t>47.79</t>
         </is>
       </c>
       <c r="BC25" t="inlineStr">
         <is>
-          <t>-40.98</t>
+          <t>-40.94</t>
         </is>
       </c>
       <c r="BD25" t="n">
-        <v>1.34</v>
+        <v>1.21</v>
       </c>
       <c r="BE25" t="n">
-        <v>2.26</v>
+        <v>2.05</v>
       </c>
       <c r="BF25" t="inlineStr">
         <is>
@@ -12413,7 +12413,7 @@
       </c>
       <c r="BG25" t="inlineStr">
         <is>
-          <t>-49.81</t>
+          <t>-54.47</t>
         </is>
       </c>
       <c r="BH25" t="inlineStr">
@@ -12423,43 +12423,43 @@
       </c>
       <c r="BI25" t="inlineStr">
         <is>
-          <t>1631368124.406207</t>
+          <t>1639172660.568182</t>
         </is>
       </c>
       <c r="BJ25" t="inlineStr">
         <is>
-          <t>2204976767.0</t>
+          <t>3608589503.0</t>
         </is>
       </c>
       <c r="BK25" t="n">
-        <v>4154560976.4</v>
+        <v>3356197002.8</v>
       </c>
       <c r="BL25" t="inlineStr">
         <is>
-          <t>3402420209.8</t>
+          <t>3528975051.7</t>
         </is>
       </c>
       <c r="BM25" t="n">
-        <v>5711824024.86</v>
+        <v>5761226342.04</v>
       </c>
       <c r="BN25" t="inlineStr">
         <is>
-          <t>752140766</t>
+          <t>-172778048</t>
         </is>
       </c>
       <c r="BO25" t="inlineStr">
         <is>
-          <t>-639556274.0913253</t>
+          <t>-656772103.9942122</t>
         </is>
       </c>
       <c r="BP25" t="inlineStr">
         <is>
-          <t>-835422234.4695697</t>
+          <t>-751459168.4600897</t>
         </is>
       </c>
       <c r="BQ25" t="inlineStr">
         <is>
-          <t>2204976767.0</t>
+          <t>3608589503.0</t>
         </is>
       </c>
       <c r="BR25" t="inlineStr">
@@ -12479,7 +12479,7 @@
       </c>
       <c r="BU25" t="inlineStr">
         <is>
-          <t>37.23</t>
+          <t>40.10</t>
         </is>
       </c>
       <c r="BV25" t="inlineStr">
@@ -12504,7 +12504,7 @@
       </c>
       <c r="BZ25" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="CA25" t="inlineStr">
@@ -12524,22 +12524,22 @@
       </c>
       <c r="CD25" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE25" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="CF25" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="CG25" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="CH25" t="inlineStr">
@@ -12564,12 +12564,12 @@
       </c>
       <c r="CL25" t="inlineStr">
         <is>
-          <t>62.95</t>
+          <t>63.05</t>
         </is>
       </c>
       <c r="CM25" t="inlineStr">
         <is>
-          <t>440954</t>
+          <t>467125</t>
         </is>
       </c>
       <c r="CN25" t="inlineStr">
@@ -12589,22 +12589,22 @@
       </c>
       <c r="CQ25" t="inlineStr">
         <is>
-          <t>58.8</t>
+          <t>58.2</t>
         </is>
       </c>
       <c r="CR25" t="inlineStr">
         <is>
-          <t>59.2</t>
+          <t>60.3</t>
         </is>
       </c>
       <c r="CS25" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>58.1</t>
         </is>
       </c>
       <c r="CT25" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>58.7</t>
         </is>
       </c>
       <c r="CU25" t="inlineStr">
@@ -12619,7 +12619,7 @@
       </c>
       <c r="CW25" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -12636,12 +12636,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>51548.933</t>
+          <t>37995.984</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -12651,7 +12651,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>58.1</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -12661,17 +12661,17 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-4.5</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>-2.5</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>17.04</t>
+          <t>22.11</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -12736,7 +12736,7 @@
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>-5.37</t>
+          <t>-6.35</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
@@ -12761,7 +12761,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -12811,17 +12811,17 @@
       </c>
       <c r="AL26" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>15.30</t>
+          <t>11.28</t>
         </is>
       </c>
       <c r="AN26" t="inlineStr">
         <is>
-          <t>-4.99</t>
+          <t>-2.96</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
@@ -12832,66 +12832,66 @@
       <c r="AP26" t="inlineStr"/>
       <c r="AQ26" t="inlineStr">
         <is>
-          <t>656</t>
+          <t>679</t>
         </is>
       </c>
       <c r="AR26" t="inlineStr">
         <is>
-          <t>82573</t>
+          <t>83828</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr">
         <is>
-          <t>18.92</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr">
         <is>
-          <t>43.92</t>
+          <t>19.99</t>
         </is>
       </c>
       <c r="AU26" t="n">
-        <v>-1.39</v>
+        <v>-2.44</v>
       </c>
       <c r="AV26" t="n">
-        <v>-2.92</v>
+        <v>-2.99</v>
       </c>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>16.32</t>
+          <t>15.7</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>10.05</t>
+          <t>10.35</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
-          <t>58.92</t>
+          <t>58.94</t>
         </is>
       </c>
       <c r="AZ26" t="n">
-        <v>60.69</v>
+        <v>60.76</v>
       </c>
       <c r="BA26" t="n">
-        <v>52.17</v>
+        <v>52.51</v>
       </c>
       <c r="BB26" t="inlineStr">
         <is>
-          <t>47.41</t>
+          <t>47.59</t>
         </is>
       </c>
       <c r="BC26" t="inlineStr">
         <is>
-          <t>-36.04</t>
+          <t>-40.98</t>
         </is>
       </c>
       <c r="BD26" t="n">
-        <v>1.6</v>
+        <v>1.34</v>
       </c>
       <c r="BE26" t="n">
-        <v>2.49</v>
+        <v>2.26</v>
       </c>
       <c r="BF26" t="inlineStr">
         <is>
@@ -12900,7 +12900,7 @@
       </c>
       <c r="BG26" t="inlineStr">
         <is>
-          <t>-44.66</t>
+          <t>-49.81</t>
         </is>
       </c>
       <c r="BH26" t="inlineStr">
@@ -12910,43 +12910,43 @@
       </c>
       <c r="BI26" t="inlineStr">
         <is>
-          <t>1631368124.406207</t>
+          <t>1639172660.568182</t>
         </is>
       </c>
       <c r="BJ26" t="inlineStr">
         <is>
-          <t>3040538846.0</t>
+          <t>2204976767.0</t>
         </is>
       </c>
       <c r="BK26" t="n">
-        <v>4242264725.6</v>
+        <v>4154560976.4</v>
       </c>
       <c r="BL26" t="inlineStr">
         <is>
-          <t>3624559420.8</t>
+          <t>3402420209.8</t>
         </is>
       </c>
       <c r="BM26" t="n">
-        <v>5691886697.32</v>
+        <v>5711824024.86</v>
       </c>
       <c r="BN26" t="inlineStr">
         <is>
-          <t>617705304</t>
+          <t>752140766</t>
         </is>
       </c>
       <c r="BO26" t="inlineStr">
         <is>
-          <t>-603944281.2952808</t>
+          <t>-639556274.0913253</t>
         </is>
       </c>
       <c r="BP26" t="inlineStr">
         <is>
-          <t>-775145884.3949137</t>
+          <t>-835422234.4695697</t>
         </is>
       </c>
       <c r="BQ26" t="inlineStr">
         <is>
-          <t>3040538846.0</t>
+          <t>2204976767.0</t>
         </is>
       </c>
       <c r="BR26" t="inlineStr">
@@ -12966,7 +12966,7 @@
       </c>
       <c r="BU26" t="inlineStr">
         <is>
-          <t>38.66</t>
+          <t>37.23</t>
         </is>
       </c>
       <c r="BV26" t="inlineStr">
@@ -12991,7 +12991,7 @@
       </c>
       <c r="BZ26" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="CA26" t="inlineStr">
@@ -13011,22 +13011,22 @@
       </c>
       <c r="CD26" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE26" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="CF26" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="CG26" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="CH26" t="inlineStr">
@@ -13051,12 +13051,12 @@
       </c>
       <c r="CL26" t="inlineStr">
         <is>
-          <t>62.95</t>
+          <t>63.05</t>
         </is>
       </c>
       <c r="CM26" t="inlineStr">
         <is>
-          <t>440954</t>
+          <t>467125</t>
         </is>
       </c>
       <c r="CN26" t="inlineStr">
@@ -13076,22 +13076,22 @@
       </c>
       <c r="CQ26" t="inlineStr">
         <is>
-          <t>59.7</t>
+          <t>58.8</t>
         </is>
       </c>
       <c r="CR26" t="inlineStr">
         <is>
-          <t>61.0</t>
+          <t>59.2</t>
         </is>
       </c>
       <c r="CS26" t="inlineStr">
         <is>
-          <t>58.1</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="CT26" t="inlineStr">
         <is>
-          <t>58.1</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="CU26" t="inlineStr">
@@ -13106,7 +13106,7 @@
       </c>
       <c r="CW26" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -13123,12 +13123,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>-2.65</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>62689.338</t>
+          <t>51548.933</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -13138,7 +13138,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>58.8</t>
+          <t>58.1</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -13148,17 +13148,17 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-5.76</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>-2.5</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>15.16</t>
+          <t>17.04</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -13223,7 +13223,7 @@
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>-4.23</t>
+          <t>-5.37</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
@@ -13248,7 +13248,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -13298,17 +13298,17 @@
       </c>
       <c r="AL27" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>18.61</t>
+          <t>15.30</t>
         </is>
       </c>
       <c r="AN27" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-4.99</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
@@ -13319,66 +13319,66 @@
       <c r="AP27" t="inlineStr"/>
       <c r="AQ27" t="inlineStr">
         <is>
-          <t>656</t>
+          <t>679</t>
         </is>
       </c>
       <c r="AR27" t="inlineStr">
         <is>
-          <t>82573</t>
+          <t>83828</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr">
         <is>
-          <t>37.84</t>
+          <t>18.92</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr">
         <is>
-          <t>55.34</t>
+          <t>43.92</t>
         </is>
       </c>
       <c r="AU27" t="n">
-        <v>0.03</v>
+        <v>-1.39</v>
       </c>
       <c r="AV27" t="n">
-        <v>-2.59</v>
+        <v>-2.92</v>
       </c>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>16.45</t>
+          <t>16.32</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>9.73</t>
+          <t>10.05</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
-          <t>58.77999999999999</t>
+          <t>58.92</t>
         </is>
       </c>
       <c r="AZ27" t="n">
-        <v>60.34</v>
+        <v>60.69</v>
       </c>
       <c r="BA27" t="n">
-        <v>51.82</v>
+        <v>52.17</v>
       </c>
       <c r="BB27" t="inlineStr">
         <is>
-          <t>47.22</t>
+          <t>47.41</t>
         </is>
       </c>
       <c r="BC27" t="inlineStr">
         <is>
-          <t>-32.22</t>
+          <t>-36.04</t>
         </is>
       </c>
       <c r="BD27" t="n">
-        <v>1.84</v>
+        <v>1.6</v>
       </c>
       <c r="BE27" t="n">
-        <v>2.72</v>
+        <v>2.49</v>
       </c>
       <c r="BF27" t="inlineStr">
         <is>
@@ -13387,7 +13387,7 @@
       </c>
       <c r="BG27" t="inlineStr">
         <is>
-          <t>-39.68</t>
+          <t>-44.66</t>
         </is>
       </c>
       <c r="BH27" t="inlineStr">
@@ -13397,43 +13397,43 @@
       </c>
       <c r="BI27" t="inlineStr">
         <is>
-          <t>1631368124.406207</t>
+          <t>1639172660.568182</t>
         </is>
       </c>
       <c r="BJ27" t="inlineStr">
         <is>
-          <t>3683848491.0</t>
+          <t>3040538846.0</t>
         </is>
       </c>
       <c r="BK27" t="n">
-        <v>4342200273</v>
+        <v>4242264725.6</v>
       </c>
       <c r="BL27" t="inlineStr">
         <is>
-          <t>3770470407.8</t>
+          <t>3624559420.8</t>
         </is>
       </c>
       <c r="BM27" t="n">
-        <v>5679083897.76</v>
+        <v>5691886697.32</v>
       </c>
       <c r="BN27" t="inlineStr">
         <is>
-          <t>571729865</t>
+          <t>617705304</t>
         </is>
       </c>
       <c r="BO27" t="inlineStr">
         <is>
-          <t>-572816717.0953475</t>
+          <t>-603944281.2952808</t>
         </is>
       </c>
       <c r="BP27" t="inlineStr">
         <is>
-          <t>-750877539.7384434</t>
+          <t>-775145884.3949137</t>
         </is>
       </c>
       <c r="BQ27" t="inlineStr">
         <is>
-          <t>3683848491.0</t>
+          <t>3040538846.0</t>
         </is>
       </c>
       <c r="BR27" t="inlineStr">
@@ -13453,7 +13453,7 @@
       </c>
       <c r="BU27" t="inlineStr">
         <is>
-          <t>40.33</t>
+          <t>38.66</t>
         </is>
       </c>
       <c r="BV27" t="inlineStr">
@@ -13478,7 +13478,7 @@
       </c>
       <c r="BZ27" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="CA27" t="inlineStr">
@@ -13498,7 +13498,7 @@
       </c>
       <c r="CD27" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE27" t="inlineStr">
@@ -13508,12 +13508,12 @@
       </c>
       <c r="CF27" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="CG27" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="CH27" t="inlineStr">
@@ -13538,12 +13538,12 @@
       </c>
       <c r="CL27" t="inlineStr">
         <is>
-          <t>62.95</t>
+          <t>63.05</t>
         </is>
       </c>
       <c r="CM27" t="inlineStr">
         <is>
-          <t>440954</t>
+          <t>467125</t>
         </is>
       </c>
       <c r="CN27" t="inlineStr">
@@ -13563,22 +13563,22 @@
       </c>
       <c r="CQ27" t="inlineStr">
         <is>
-          <t>60.4</t>
+          <t>59.7</t>
         </is>
       </c>
       <c r="CR27" t="inlineStr">
         <is>
-          <t>60.4</t>
+          <t>61.0</t>
         </is>
       </c>
       <c r="CS27" t="inlineStr">
         <is>
-          <t>57.8</t>
+          <t>58.1</t>
         </is>
       </c>
       <c r="CT27" t="inlineStr">
         <is>
-          <t>58.8</t>
+          <t>58.1</t>
         </is>
       </c>
       <c r="CU27" t="inlineStr">
@@ -13593,7 +13593,7 @@
       </c>
       <c r="CW27" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -13610,12 +13610,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>-2.65</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>69732.905</t>
+          <t>62689.338</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -13625,7 +13625,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>60.4</t>
+          <t>58.8</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -13635,17 +13635,17 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-8.63</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>-2.5</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>15.16</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -13710,7 +13710,7 @@
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>-4.23</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
@@ -13735,7 +13735,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -13785,17 +13785,17 @@
       </c>
       <c r="AL28" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>20.70</t>
+          <t>18.61</t>
         </is>
       </c>
       <c r="AN28" t="inlineStr">
         <is>
-          <t>-1.82</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
@@ -13806,66 +13806,66 @@
       <c r="AP28" t="inlineStr"/>
       <c r="AQ28" t="inlineStr">
         <is>
-          <t>656</t>
+          <t>679</t>
         </is>
       </c>
       <c r="AR28" t="inlineStr">
         <is>
-          <t>82573</t>
+          <t>83828</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>37.84</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr">
         <is>
-          <t>42.73</t>
+          <t>55.34</t>
         </is>
       </c>
       <c r="AU28" t="n">
-        <v>2.97</v>
+        <v>0.03</v>
       </c>
       <c r="AV28" t="n">
-        <v>-2.27</v>
+        <v>-2.59</v>
       </c>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>16.6</t>
+          <t>16.45</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>9.73</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
-          <t>58.66</t>
+          <t>58.77999999999999</t>
         </is>
       </c>
       <c r="AZ28" t="n">
-        <v>60.02</v>
+        <v>60.34</v>
       </c>
       <c r="BA28" t="n">
-        <v>51.48</v>
+        <v>51.82</v>
       </c>
       <c r="BB28" t="inlineStr">
         <is>
-          <t>47.05</t>
+          <t>47.22</t>
         </is>
       </c>
       <c r="BC28" t="inlineStr">
         <is>
-          <t>-29.86</t>
+          <t>-32.22</t>
         </is>
       </c>
       <c r="BD28" t="n">
-        <v>2.06</v>
+        <v>1.84</v>
       </c>
       <c r="BE28" t="n">
-        <v>2.94</v>
+        <v>2.72</v>
       </c>
       <c r="BF28" t="inlineStr">
         <is>
@@ -13874,7 +13874,7 @@
       </c>
       <c r="BG28" t="inlineStr">
         <is>
-          <t>-34.82</t>
+          <t>-39.68</t>
         </is>
       </c>
       <c r="BH28" t="inlineStr">
@@ -13884,43 +13884,43 @@
       </c>
       <c r="BI28" t="inlineStr">
         <is>
-          <t>1631368124.406207</t>
+          <t>1639172660.568182</t>
         </is>
       </c>
       <c r="BJ28" t="inlineStr">
         <is>
-          <t>4243031407.0</t>
+          <t>3683848491.0</t>
         </is>
       </c>
       <c r="BK28" t="n">
-        <v>4158158701</v>
+        <v>4342200273</v>
       </c>
       <c r="BL28" t="inlineStr">
         <is>
-          <t>3969695265.8</t>
+          <t>3770470407.8</t>
         </is>
       </c>
       <c r="BM28" t="n">
-        <v>5642533638.26</v>
+        <v>5679083897.76</v>
       </c>
       <c r="BN28" t="inlineStr">
         <is>
-          <t>188463435</t>
+          <t>571729865</t>
         </is>
       </c>
       <c r="BO28" t="inlineStr">
         <is>
-          <t>-540442022.0693301</t>
+          <t>-572816717.0953475</t>
         </is>
       </c>
       <c r="BP28" t="inlineStr">
         <is>
-          <t>-758317454.345684</t>
+          <t>-750877539.7384434</t>
         </is>
       </c>
       <c r="BQ28" t="inlineStr">
         <is>
-          <t>4243031407.0</t>
+          <t>3683848491.0</t>
         </is>
       </c>
       <c r="BR28" t="inlineStr">
@@ -13940,7 +13940,7 @@
       </c>
       <c r="BU28" t="inlineStr">
         <is>
-          <t>44.15</t>
+          <t>40.33</t>
         </is>
       </c>
       <c r="BV28" t="inlineStr">
@@ -13965,7 +13965,7 @@
       </c>
       <c r="BZ28" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="CA28" t="inlineStr">
@@ -13985,7 +13985,7 @@
       </c>
       <c r="CD28" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE28" t="inlineStr">
@@ -13995,12 +13995,12 @@
       </c>
       <c r="CF28" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="CG28" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="CH28" t="inlineStr">
@@ -14025,12 +14025,12 @@
       </c>
       <c r="CL28" t="inlineStr">
         <is>
-          <t>62.95</t>
+          <t>63.05</t>
         </is>
       </c>
       <c r="CM28" t="inlineStr">
         <is>
-          <t>440954</t>
+          <t>467125</t>
         </is>
       </c>
       <c r="CN28" t="inlineStr">
@@ -14050,22 +14050,22 @@
       </c>
       <c r="CQ28" t="inlineStr">
         <is>
-          <t>60.7</t>
+          <t>60.4</t>
         </is>
       </c>
       <c r="CR28" t="inlineStr">
         <is>
-          <t>61.6</t>
+          <t>60.4</t>
         </is>
       </c>
       <c r="CS28" t="inlineStr">
         <is>
-          <t>60.3</t>
+          <t>57.8</t>
         </is>
       </c>
       <c r="CT28" t="inlineStr">
         <is>
-          <t>60.4</t>
+          <t>58.8</t>
         </is>
       </c>
       <c r="CU28" t="inlineStr">
@@ -14080,7 +14080,7 @@
       </c>
       <c r="CW28" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>

--- a/Result/checksun_type/石化上游原料及相關鑽探設備.xlsx
+++ b/Result/checksun_type/石化上游原料及相關鑽探設備.xlsx
@@ -948,12 +948,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>-2.57</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>3709.041</t>
+          <t>6392.719</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>48.55</t>
+          <t>47.3</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -978,12 +978,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>19.02</t>
+          <t>21.13</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-6.81</t>
+          <t>-9.21</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -1073,7 +1073,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -1123,17 +1123,17 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>9.83</t>
+          <t>16.94</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
@@ -1144,63 +1144,63 @@
       <c r="AP2" t="inlineStr"/>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>48</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>3709</t>
+          <t>6393</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>81.25</t>
+          <t>35.9</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>54.86</t>
+          <t>52.94</t>
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>1.85</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="AV2" t="n">
-        <v>-1.3</v>
+        <v>-0.98</v>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>-3.76</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>6.92</t>
+          <t>6.79</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>47.67</t>
+          <t>47.75</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>48.3</v>
+        <v>48.22</v>
       </c>
       <c r="BA2" t="n">
-        <v>50.19</v>
+        <v>50.24</v>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>46.94</t>
+          <t>47.04</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>-0.65</v>
+        <v>-0.66</v>
       </c>
       <c r="BE2" t="n">
         <v>-0.66</v>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-122.26</t>
+          <t>-122.25</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1222,43 +1222,43 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>504922909.0967413</t>
+          <t>504818691.2743902</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>179344290.0</t>
+          <t>302431827.0</t>
         </is>
       </c>
       <c r="BK2" t="n">
-        <v>289518116.4</v>
+        <v>315680448.2</v>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>243249756.6</t>
+          <t>260620331.3</t>
         </is>
       </c>
       <c r="BM2" t="n">
-        <v>428269005.78</v>
+        <v>429584491.22</v>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>46268359</t>
+          <t>55060116</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>-16512398.52220696</t>
+          <t>-13317754.76861903</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>919559.001555562</t>
+          <t>4252785.876114607</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>179344290.0</t>
+          <t>302431827.0</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>10.72</t>
+          <t>7.87</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1323,22 +1323,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="CI2" t="inlineStr">
         <is>
-          <t>75.86</t>
+          <t>73.91</t>
         </is>
       </c>
       <c r="CJ2" t="inlineStr">
@@ -1363,12 +1363,12 @@
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>26.91</t>
+          <t>26.63</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
         <is>
-          <t>462485</t>
+          <t>450578</t>
         </is>
       </c>
       <c r="CN2" t="inlineStr">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="CQ2" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="CR2" t="inlineStr">
@@ -1398,12 +1398,12 @@
       </c>
       <c r="CS2" t="inlineStr">
         <is>
-          <t>47.95</t>
+          <t>46.65</t>
         </is>
       </c>
       <c r="CT2" t="inlineStr">
         <is>
-          <t>48.55</t>
+          <t>47.3</t>
         </is>
       </c>
       <c r="CU2" t="inlineStr">
@@ -1425,7 +1425,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1435,12 +1435,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>5994.042</t>
+          <t>3709.041</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>47.6</t>
+          <t>48.55</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1460,17 +1460,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>-2.64</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>28.62</t>
+          <t>19.02</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1535,7 +1535,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-8.64</t>
+          <t>-6.81</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1610,17 +1610,17 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>15.89</t>
+          <t>9.83</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>-2.19</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
@@ -1631,63 +1631,63 @@
       <c r="AP3" t="inlineStr"/>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>48</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>3709</t>
+          <t>6393</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>41.67</t>
+          <t>81.25</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>43.06</t>
+          <t>54.86</t>
         </is>
       </c>
       <c r="AU3" t="n">
-        <v>0.46</v>
+        <v>1.85</v>
       </c>
       <c r="AV3" t="n">
-        <v>-1.91</v>
+        <v>-1.3</v>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>-3.64</t>
+          <t>-3.76</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>7.07</t>
+          <t>6.92</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>47.38</t>
+          <t>47.67</t>
         </is>
       </c>
       <c r="AZ3" t="n">
         <v>48.3</v>
       </c>
       <c r="BA3" t="n">
-        <v>50.13</v>
+        <v>50.19</v>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>46.82</t>
+          <t>46.94</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-13.52</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>-0.75</v>
+        <v>-0.65</v>
       </c>
       <c r="BE3" t="n">
         <v>-0.66</v>
@@ -1699,7 +1699,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-122.36</t>
+          <t>-122.26</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1709,43 +1709,43 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>504922909.0967413</t>
+          <t>504818691.2743902</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
-          <t>287225273.0</t>
+          <t>179344290.0</t>
         </is>
       </c>
       <c r="BK3" t="n">
-        <v>298052673.6</v>
+        <v>289518116.4</v>
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>231729183.0</t>
+          <t>243249756.6</t>
         </is>
       </c>
       <c r="BM3" t="n">
-        <v>429617724.08</v>
+        <v>428269005.78</v>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>66323490</t>
+          <t>46268359</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>-19681845.34470924</t>
+          <t>-16512398.52220696</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>9312915.32355851</t>
+          <t>919559.001555562</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>287225273.0</t>
+          <t>179344290.0</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1765,7 +1765,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>8.55</t>
+          <t>10.72</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1810,22 +1810,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="CI3" t="inlineStr">
         <is>
-          <t>75.86</t>
+          <t>73.91</t>
         </is>
       </c>
       <c r="CJ3" t="inlineStr">
@@ -1850,12 +1850,12 @@
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>26.91</t>
+          <t>26.63</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
         <is>
-          <t>462485</t>
+          <t>450578</t>
         </is>
       </c>
       <c r="CN3" t="inlineStr">
@@ -1875,22 +1875,22 @@
       </c>
       <c r="CQ3" t="inlineStr">
         <is>
-          <t>48.3</t>
+          <t>48.2</t>
         </is>
       </c>
       <c r="CR3" t="inlineStr">
         <is>
-          <t>49.15</t>
+          <t>48.75</t>
         </is>
       </c>
       <c r="CS3" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>47.95</t>
         </is>
       </c>
       <c r="CT3" t="inlineStr">
         <is>
-          <t>47.6</t>
+          <t>48.55</t>
         </is>
       </c>
       <c r="CU3" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>8255.567</t>
+          <t>5994.042</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1947,17 +1947,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>33.83</t>
+          <t>28.62</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -2097,17 +2097,17 @@
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>21.88</t>
+          <t>15.89</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>-3.68</t>
+          <t>-2.19</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
@@ -2118,12 +2118,12 @@
       <c r="AP4" t="inlineStr"/>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>48</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>3709</t>
+          <t>6393</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -2133,51 +2133,51 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>32.87</t>
+          <t>43.06</t>
         </is>
       </c>
       <c r="AU4" t="n">
-        <v>0.89</v>
+        <v>0.46</v>
       </c>
       <c r="AV4" t="n">
-        <v>-2.55</v>
+        <v>-1.91</v>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>-3.32</t>
+          <t>-3.64</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>7.22</t>
+          <t>7.07</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>47.18</t>
+          <t>47.38</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>48.42</v>
+        <v>48.3</v>
       </c>
       <c r="BA4" t="n">
-        <v>50.08</v>
+        <v>50.13</v>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>46.71</t>
+          <t>46.82</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-21.48</t>
+          <t>-13.52</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>-0.78</v>
+        <v>-0.75</v>
       </c>
       <c r="BE4" t="n">
-        <v>-0.64</v>
+        <v>-0.66</v>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-121.60</t>
+          <t>-122.36</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2196,43 +2196,43 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>504922909.0967413</t>
+          <t>504818691.2743902</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>400332973.0</t>
+          <t>287225273.0</t>
         </is>
       </c>
       <c r="BK4" t="n">
-        <v>288987178.4</v>
+        <v>298052673.6</v>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>215941774.0</t>
+          <t>231729183.0</t>
         </is>
       </c>
       <c r="BM4" t="n">
-        <v>428175062.72</v>
+        <v>429617724.08</v>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>73045404</t>
+          <t>66323490</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>-24953620.01166701</t>
+          <t>-19681845.34470924</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>9412143.48629275</t>
+          <t>9312915.32355851</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>400332973.0</t>
+          <t>287225273.0</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2312,7 +2312,7 @@
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="CI4" t="inlineStr">
         <is>
-          <t>75.86</t>
+          <t>73.91</t>
         </is>
       </c>
       <c r="CJ4" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>26.91</t>
+          <t>26.63</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
         <is>
-          <t>462485</t>
+          <t>450578</t>
         </is>
       </c>
       <c r="CN4" t="inlineStr">
@@ -2362,17 +2362,17 @@
       </c>
       <c r="CQ4" t="inlineStr">
         <is>
-          <t>48.05</t>
+          <t>48.3</t>
         </is>
       </c>
       <c r="CR4" t="inlineStr">
         <is>
-          <t>49.35</t>
+          <t>49.15</t>
         </is>
       </c>
       <c r="CS4" t="inlineStr">
         <is>
-          <t>47.6</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="CT4" t="inlineStr">
@@ -2409,12 +2409,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8500.423</t>
+          <t>8255.567</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>47.7</t>
+          <t>47.6</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2434,17 +2434,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>34.38</t>
+          <t>33.83</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2509,7 +2509,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-8.45</t>
+          <t>-8.64</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -2584,17 +2584,17 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>22.53</t>
+          <t>21.88</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-3.68</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
@@ -2605,66 +2605,66 @@
       <c r="AP5" t="inlineStr"/>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>48</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>3709</t>
+          <t>6393</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>45.83</t>
+          <t>41.67</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>25.15</t>
+          <t>32.87</t>
         </is>
       </c>
       <c r="AU5" t="n">
-        <v>1.02</v>
+        <v>0.89</v>
       </c>
       <c r="AV5" t="n">
-        <v>-2.83</v>
+        <v>-2.55</v>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>-2.89</t>
+          <t>-3.32</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>7.35</t>
+          <t>7.22</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>47.22</t>
+          <t>47.18</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>48.6</v>
+        <v>48.42</v>
       </c>
       <c r="BA5" t="n">
-        <v>50.04</v>
+        <v>50.08</v>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>46.61</t>
+          <t>46.71</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-31.89</t>
+          <t>-21.48</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>-0.8</v>
+        <v>-0.78</v>
       </c>
       <c r="BE5" t="n">
-        <v>-0.61</v>
+        <v>-0.64</v>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
@@ -2673,7 +2673,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-120.44</t>
+          <t>-121.60</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2683,43 +2683,43 @@
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>504922909.0967413</t>
+          <t>504818691.2743902</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>409067878.0</t>
+          <t>400332973.0</t>
         </is>
       </c>
       <c r="BK5" t="n">
-        <v>266799022.6</v>
+        <v>288987178.4</v>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>198544932.4</t>
+          <t>215941774.0</t>
         </is>
       </c>
       <c r="BM5" t="n">
-        <v>426998591.06</v>
+        <v>428175062.72</v>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>68254090</t>
+          <t>73045404</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>-31201940.6476597</t>
+          <t>-24953620.01166701</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>-2900932.120025873</t>
+          <t>9412143.48629275</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>409067878.0</t>
+          <t>400332973.0</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2739,7 +2739,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>8.78</t>
+          <t>8.55</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2784,12 +2784,12 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
@@ -2799,7 +2799,7 @@
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="CI5" t="inlineStr">
         <is>
-          <t>75.86</t>
+          <t>73.91</t>
         </is>
       </c>
       <c r="CJ5" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>26.91</t>
+          <t>26.63</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
         <is>
-          <t>462485</t>
+          <t>450578</t>
         </is>
       </c>
       <c r="CN5" t="inlineStr">
@@ -2849,22 +2849,22 @@
       </c>
       <c r="CQ5" t="inlineStr">
         <is>
-          <t>47.15</t>
+          <t>48.05</t>
         </is>
       </c>
       <c r="CR5" t="inlineStr">
         <is>
-          <t>48.75</t>
+          <t>49.35</t>
         </is>
       </c>
       <c r="CS5" t="inlineStr">
         <is>
-          <t>47.15</t>
+          <t>47.6</t>
         </is>
       </c>
       <c r="CT5" t="inlineStr">
         <is>
-          <t>47.7</t>
+          <t>47.6</t>
         </is>
       </c>
       <c r="CU5" t="inlineStr">
@@ -2896,12 +2896,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>3638.546</t>
+          <t>8500.423</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>46.9</t>
+          <t>47.7</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2921,17 +2921,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>16.80</t>
+          <t>34.38</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-9.98</t>
+          <t>-8.45</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -3071,17 +3071,17 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>9.64</t>
+          <t>22.53</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -3092,66 +3092,66 @@
       <c r="AP6" t="inlineStr"/>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>48</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>3709</t>
+          <t>6393</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>45.83</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>9.88</t>
+          <t>25.15</t>
         </is>
       </c>
       <c r="AU6" t="n">
-        <v>-1.22</v>
+        <v>1.02</v>
       </c>
       <c r="AV6" t="n">
-        <v>-2.68</v>
+        <v>-2.83</v>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>-2.43</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>7.48</t>
+          <t>7.35</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>47.48</t>
+          <t>47.22</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>48.78</v>
+        <v>48.6</v>
       </c>
       <c r="BA6" t="n">
-        <v>50</v>
+        <v>50.04</v>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>46.52</t>
+          <t>46.61</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-47.93</t>
+          <t>-31.89</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>-0.83</v>
+        <v>-0.8</v>
       </c>
       <c r="BE6" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.61</v>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
@@ -3160,7 +3160,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-118.81</t>
+          <t>-120.44</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -3170,43 +3170,43 @@
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>504922909.0967413</t>
+          <t>504818691.2743902</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
         <is>
-          <t>171620168.0</t>
+          <t>409067878.0</t>
         </is>
       </c>
       <c r="BK6" t="n">
-        <v>205560214.4</v>
+        <v>266799022.6</v>
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>175992316.4</t>
+          <t>198544932.4</t>
         </is>
       </c>
       <c r="BM6" t="n">
-        <v>429198766.1</v>
+        <v>426998591.06</v>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>29567898</t>
+          <t>68254090</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>-36347578.56177494</t>
+          <t>-31201940.6476597</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>-21323318.08905157</t>
+          <t>-2900932.120025873</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>171620168.0</t>
+          <t>409067878.0</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>6.96</t>
+          <t>8.78</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -3271,22 +3271,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="CI6" t="inlineStr">
         <is>
-          <t>75.86</t>
+          <t>73.91</t>
         </is>
       </c>
       <c r="CJ6" t="inlineStr">
@@ -3311,12 +3311,12 @@
       </c>
       <c r="CL6" t="inlineStr">
         <is>
-          <t>26.91</t>
+          <t>26.63</t>
         </is>
       </c>
       <c r="CM6" t="inlineStr">
         <is>
-          <t>462485</t>
+          <t>450578</t>
         </is>
       </c>
       <c r="CN6" t="inlineStr">
@@ -3336,22 +3336,22 @@
       </c>
       <c r="CQ6" t="inlineStr">
         <is>
-          <t>47.25</t>
+          <t>47.15</t>
         </is>
       </c>
       <c r="CR6" t="inlineStr">
         <is>
-          <t>47.95</t>
+          <t>48.75</t>
         </is>
       </c>
       <c r="CS6" t="inlineStr">
         <is>
-          <t>46.85</t>
+          <t>47.15</t>
         </is>
       </c>
       <c r="CT6" t="inlineStr">
         <is>
-          <t>46.9</t>
+          <t>47.7</t>
         </is>
       </c>
       <c r="CU6" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>4700.034</t>
+          <t>3638.546</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>46.9</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3408,17 +3408,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2.99</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>4.37</t>
+          <t>16.80</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3483,7 +3483,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-9.60</t>
+          <t>-9.98</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -3558,17 +3558,17 @@
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>12.46</t>
+          <t>9.64</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -3579,66 +3579,66 @@
       <c r="AP7" t="inlineStr"/>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>48</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>3709</t>
+          <t>6393</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>18.52</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>6.17</t>
+          <t>9.88</t>
         </is>
       </c>
       <c r="AU7" t="n">
-        <v>-1.67</v>
+        <v>-1.22</v>
       </c>
       <c r="AV7" t="n">
-        <v>-2.27</v>
+        <v>-2.68</v>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>-2.43</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>7.68</t>
+          <t>7.48</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>47.9</t>
+          <t>47.48</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>49.02</v>
+        <v>48.78</v>
       </c>
       <c r="BA7" t="n">
-        <v>49.99</v>
+        <v>50</v>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>46.43</t>
+          <t>46.52</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-55.75</t>
+          <t>-47.93</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>-0.77</v>
+        <v>-0.83</v>
       </c>
       <c r="BE7" t="n">
-        <v>-0.49</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
@@ -3647,7 +3647,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-116.56</t>
+          <t>-118.81</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3657,43 +3657,43 @@
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>504922909.0967413</t>
+          <t>504818691.2743902</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
         <is>
-          <t>222017076.0</t>
+          <t>171620168.0</t>
         </is>
       </c>
       <c r="BK7" t="n">
-        <v>196981396.8</v>
+        <v>205560214.4</v>
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>188729985.6</t>
+          <t>175992316.4</t>
         </is>
       </c>
       <c r="BM7" t="n">
-        <v>441739824.86</v>
+        <v>429198766.1</v>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>8251411</t>
+          <t>29567898</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>-39079262.28408828</t>
+          <t>-36347578.56177494</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>-21438639.1844793</t>
+          <t>-21323318.08905157</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>222017076.0</t>
+          <t>171620168.0</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3713,7 +3713,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>7.41</t>
+          <t>6.96</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3763,7 +3763,7 @@
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
@@ -3773,7 +3773,7 @@
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="CI7" t="inlineStr">
         <is>
-          <t>75.86</t>
+          <t>73.91</t>
         </is>
       </c>
       <c r="CJ7" t="inlineStr">
@@ -3798,12 +3798,12 @@
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>26.91</t>
+          <t>26.63</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
         <is>
-          <t>462485</t>
+          <t>450578</t>
         </is>
       </c>
       <c r="CN7" t="inlineStr">
@@ -3823,22 +3823,22 @@
       </c>
       <c r="CQ7" t="inlineStr">
         <is>
-          <t>47.4</t>
+          <t>47.25</t>
         </is>
       </c>
       <c r="CR7" t="inlineStr">
         <is>
-          <t>47.7</t>
+          <t>47.95</t>
         </is>
       </c>
       <c r="CS7" t="inlineStr">
         <is>
-          <t>46.95</t>
+          <t>46.85</t>
         </is>
       </c>
       <c r="CT7" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>46.9</t>
         </is>
       </c>
       <c r="CU7" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>5142.181</t>
+          <t>4700.034</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3885,7 +3885,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>46.6</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3895,17 +3895,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>4.02</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-11.15</t>
+          <t>4.37</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3970,7 +3970,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-10.56</t>
+          <t>-9.60</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>13.63</t>
+          <t>12.46</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>-3.22</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -4066,66 +4066,66 @@
       <c r="AP8" t="inlineStr"/>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>48</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>3709</t>
+          <t>6393</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>18.52</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>26.44</t>
+          <t>6.17</t>
         </is>
       </c>
       <c r="AU8" t="n">
-        <v>-3.36</v>
+        <v>-1.67</v>
       </c>
       <c r="AV8" t="n">
-        <v>-2.25</v>
+        <v>-2.27</v>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>-1.96</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>7.78</t>
+          <t>7.68</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>48.22</t>
+          <t>47.9</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>49.33</v>
+        <v>49.02</v>
       </c>
       <c r="BA8" t="n">
-        <v>49.94</v>
+        <v>49.99</v>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>46.33</t>
+          <t>46.43</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-64.87</t>
+          <t>-55.75</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>-0.7</v>
+        <v>-0.77</v>
       </c>
       <c r="BE8" t="n">
-        <v>-0.42</v>
+        <v>-0.49</v>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
@@ -4134,7 +4134,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-114.25</t>
+          <t>-116.56</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -4144,43 +4144,43 @@
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>504922909.0967413</t>
+          <t>504818691.2743902</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
         <is>
-          <t>241897797.0</t>
+          <t>222017076.0</t>
         </is>
       </c>
       <c r="BK8" t="n">
-        <v>165405692.4</v>
+        <v>196981396.8</v>
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>186159307.5</t>
+          <t>188729985.6</t>
         </is>
       </c>
       <c r="BM8" t="n">
-        <v>443312295.6</v>
+        <v>441739824.86</v>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>-20753615</t>
+          <t>8251411</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>-42286648.30219901</t>
+          <t>-39079262.28408828</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>-26237386.63564461</t>
+          <t>-21438639.1844793</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>241897797.0</t>
+          <t>222017076.0</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -4200,7 +4200,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>6.27</t>
+          <t>7.41</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -4245,7 +4245,7 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="CI8" t="inlineStr">
         <is>
-          <t>75.86</t>
+          <t>73.91</t>
         </is>
       </c>
       <c r="CJ8" t="inlineStr">
@@ -4285,12 +4285,12 @@
       </c>
       <c r="CL8" t="inlineStr">
         <is>
-          <t>26.91</t>
+          <t>26.63</t>
         </is>
       </c>
       <c r="CM8" t="inlineStr">
         <is>
-          <t>462485</t>
+          <t>450578</t>
         </is>
       </c>
       <c r="CN8" t="inlineStr">
@@ -4310,22 +4310,22 @@
       </c>
       <c r="CQ8" t="inlineStr">
         <is>
-          <t>48.1</t>
+          <t>47.4</t>
         </is>
       </c>
       <c r="CR8" t="inlineStr">
         <is>
-          <t>48.1</t>
+          <t>47.7</t>
         </is>
       </c>
       <c r="CS8" t="inlineStr">
         <is>
-          <t>46.6</t>
+          <t>46.95</t>
         </is>
       </c>
       <c r="CT8" t="inlineStr">
         <is>
-          <t>46.6</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="CU8" t="inlineStr">
@@ -4357,12 +4357,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-2.45</t>
+          <t>-2.49</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>6031.976</t>
+          <t>5142.181</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4372,159 +4372,159 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
+          <t>46.6</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>-2.41</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>-11.15</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2025-11-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>2025-11-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>2025-09-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>2025-11-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>47.85</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>52.1</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>40.15</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>44.5</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>-10.56</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>7.53</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025/07/28</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>40.4</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>-0.08</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>2025/12/31</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
           <t>47.8</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>1.54</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>-2.72</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>-26.27</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>2025-11-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>2025-11-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>2025-09-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>2025-11-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>47.85</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>2025/09/19</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>38.9</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>2025/11/25</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
         <is>
           <t>52.1</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>40.15</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>2025/11/04</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
         <is>
           <t>44.5</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>-8.25</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>7.53</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>2025/07/28</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>40.4</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>-0.03</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>2025/12/31</t>
-        </is>
-      </c>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>47.8</t>
-        </is>
-      </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>2025/09/19</t>
-        </is>
-      </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>38.9</t>
-        </is>
-      </c>
-      <c r="AG9" t="inlineStr">
-        <is>
-          <t>2025/11/25</t>
-        </is>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>52.1</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>2025/11/04</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>44.5</t>
-        </is>
-      </c>
       <c r="AK9" t="inlineStr">
         <is>
           <t>2025-11-10 00:00:00</t>
@@ -4532,17 +4532,17 @@
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>15.99</t>
+          <t>13.63</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>-2.30</t>
+          <t>-3.22</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
@@ -4553,12 +4553,12 @@
       <c r="AP9" t="inlineStr"/>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>48</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>3709</t>
+          <t>6393</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4568,51 +4568,51 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>52.87</t>
+          <t>26.44</t>
         </is>
       </c>
       <c r="AU9" t="n">
-        <v>-1.71</v>
+        <v>-3.36</v>
       </c>
       <c r="AV9" t="n">
-        <v>-2.08</v>
+        <v>-2.25</v>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>7.85</t>
+          <t>7.78</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>48.63</t>
+          <t>48.22</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>49.66</v>
+        <v>49.33</v>
       </c>
       <c r="BA9" t="n">
-        <v>49.88</v>
+        <v>49.94</v>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>46.25</t>
+          <t>46.33</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-55.03</t>
+          <t>-64.87</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>-0.55</v>
+        <v>-0.7</v>
       </c>
       <c r="BE9" t="n">
-        <v>-0.35</v>
+        <v>-0.42</v>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
@@ -4621,7 +4621,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-111.94</t>
+          <t>-114.25</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4631,43 +4631,43 @@
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>504922909.0967413</t>
+          <t>504818691.2743902</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
         <is>
-          <t>289392194.0</t>
+          <t>241897797.0</t>
         </is>
       </c>
       <c r="BK9" t="n">
-        <v>142896369.6</v>
+        <v>165405692.4</v>
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>193812739.5</t>
+          <t>186159307.5</t>
         </is>
       </c>
       <c r="BM9" t="n">
-        <v>442436106.5</v>
+        <v>443312295.6</v>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>-50916369</t>
+          <t>-20753615</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>-45204695.87793616</t>
+          <t>-42286648.30219901</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>-34285767.86460775</t>
+          <t>-26237386.63564461</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>289392194.0</t>
+          <t>241897797.0</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4687,7 +4687,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>9.01</t>
+          <t>6.27</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4732,22 +4732,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4757,7 +4757,7 @@
       </c>
       <c r="CI9" t="inlineStr">
         <is>
-          <t>75.86</t>
+          <t>73.91</t>
         </is>
       </c>
       <c r="CJ9" t="inlineStr">
@@ -4772,12 +4772,12 @@
       </c>
       <c r="CL9" t="inlineStr">
         <is>
-          <t>26.91</t>
+          <t>26.63</t>
         </is>
       </c>
       <c r="CM9" t="inlineStr">
         <is>
-          <t>462485</t>
+          <t>450578</t>
         </is>
       </c>
       <c r="CN9" t="inlineStr">
@@ -4797,22 +4797,22 @@
       </c>
       <c r="CQ9" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>48.1</t>
         </is>
       </c>
       <c r="CR9" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>48.1</t>
         </is>
       </c>
       <c r="CS9" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>46.6</t>
         </is>
       </c>
       <c r="CT9" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>46.6</t>
         </is>
       </c>
       <c r="CU9" t="inlineStr">
@@ -4834,7 +4834,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4844,12 +4844,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-2.45</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2103.849</t>
+          <t>6031.976</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4859,7 +4859,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>47.8</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4869,17 +4869,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-32.52</t>
+          <t>-26.27</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4944,7 +4944,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-5.95</t>
+          <t>-8.25</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4964,12 +4964,12 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -5019,17 +5019,17 @@
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>5.58</t>
+          <t>15.99</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>-2.30</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
@@ -5040,66 +5040,66 @@
       <c r="AP10" t="inlineStr"/>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>48</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>3709</t>
+          <t>6393</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>79.31</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>64.93</t>
+          <t>52.87</t>
         </is>
       </c>
       <c r="AU10" t="n">
-        <v>0.14</v>
+        <v>-1.71</v>
       </c>
       <c r="AV10" t="n">
         <v>-2.08</v>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>7.93</t>
+          <t>7.85</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>48.92999999999999</t>
+          <t>48.63</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>49.97</v>
+        <v>49.66</v>
       </c>
       <c r="BA10" t="n">
-        <v>49.8</v>
+        <v>49.88</v>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>46.14</t>
+          <t>46.25</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-55.33</t>
+          <t>-55.03</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>-0.47</v>
+        <v>-0.55</v>
       </c>
       <c r="BE10" t="n">
-        <v>-0.31</v>
+        <v>-0.35</v>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
@@ -5108,7 +5108,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-110.30</t>
+          <t>-111.94</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -5118,43 +5118,43 @@
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>504922909.0967413</t>
+          <t>504818691.2743902</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
         <is>
-          <t>102873837.0</t>
+          <t>289392194.0</t>
         </is>
       </c>
       <c r="BK10" t="n">
-        <v>130290842.2</v>
+        <v>142896369.6</v>
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>193069761.9</t>
+          <t>193812739.5</t>
         </is>
       </c>
       <c r="BM10" t="n">
-        <v>440991024.68</v>
+        <v>442436106.5</v>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>-62778919</t>
+          <t>-50916369</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>-47189955.51672314</t>
+          <t>-45204695.87793616</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>-49647649.01796198</t>
+          <t>-34285767.86460775</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>102873837.0</t>
+          <t>289392194.0</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -5174,7 +5174,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>11.74</t>
+          <t>9.01</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -5219,7 +5219,7 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
@@ -5229,12 +5229,12 @@
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -5244,7 +5244,7 @@
       </c>
       <c r="CI10" t="inlineStr">
         <is>
-          <t>75.86</t>
+          <t>73.91</t>
         </is>
       </c>
       <c r="CJ10" t="inlineStr">
@@ -5259,12 +5259,12 @@
       </c>
       <c r="CL10" t="inlineStr">
         <is>
-          <t>26.91</t>
+          <t>26.63</t>
         </is>
       </c>
       <c r="CM10" t="inlineStr">
         <is>
-          <t>462485</t>
+          <t>450578</t>
         </is>
       </c>
       <c r="CN10" t="inlineStr">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="CQ10" t="inlineStr">
         <is>
+          <t>49.0</t>
+        </is>
+      </c>
+      <c r="CR10" t="inlineStr">
+        <is>
           <t>49.2</t>
         </is>
       </c>
-      <c r="CR10" t="inlineStr">
-        <is>
-          <t>49.35</t>
-        </is>
-      </c>
       <c r="CS10" t="inlineStr">
         <is>
-          <t>48.35</t>
+          <t>47.5</t>
         </is>
       </c>
       <c r="CT10" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>47.8</t>
         </is>
       </c>
       <c r="CU10" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2623.606</t>
+          <t>2103.849</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5356,17 +5356,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-3.59</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-31.27</t>
+          <t>-32.52</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -5506,17 +5506,17 @@
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>6.95</t>
+          <t>5.58</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
@@ -5527,12 +5527,12 @@
       <c r="AP11" t="inlineStr"/>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>48</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>3709</t>
+          <t>6393</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -5542,51 +5542,51 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>49.84</t>
+          <t>64.93</t>
         </is>
       </c>
       <c r="AU11" t="n">
-        <v>0.35</v>
+        <v>0.14</v>
       </c>
       <c r="AV11" t="n">
-        <v>-2.61</v>
+        <v>-2.08</v>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>7.98</t>
+          <t>7.93</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>48.83</t>
+          <t>48.92999999999999</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>50.14</v>
+        <v>49.97</v>
       </c>
       <c r="BA11" t="n">
-        <v>49.69</v>
+        <v>49.8</v>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>46.02</t>
+          <t>46.14</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-87.85</t>
+          <t>-55.33</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>-0.49</v>
+        <v>-0.47</v>
       </c>
       <c r="BE11" t="n">
-        <v>-0.26</v>
+        <v>-0.31</v>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-108.87</t>
+          <t>-110.30</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5605,43 +5605,43 @@
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>504922909.0967413</t>
+          <t>504818691.2743902</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
         <is>
-          <t>128726080.0</t>
+          <t>102873837.0</t>
         </is>
       </c>
       <c r="BK11" t="n">
-        <v>146424418.4</v>
+        <v>130290842.2</v>
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>213035188.0</t>
+          <t>193069761.9</t>
         </is>
       </c>
       <c r="BM11" t="n">
-        <v>446858256.1</v>
+        <v>440991024.68</v>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>-66610769</t>
+          <t>-62778919</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>-46743102.15286153</t>
+          <t>-47189955.51672314</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>-49835953.52211222</t>
+          <t>-49647649.01796198</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>128726080.0</t>
+          <t>102873837.0</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5706,7 +5706,7 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
@@ -5721,7 +5721,7 @@
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5731,7 +5731,7 @@
       </c>
       <c r="CI11" t="inlineStr">
         <is>
-          <t>75.86</t>
+          <t>73.91</t>
         </is>
       </c>
       <c r="CJ11" t="inlineStr">
@@ -5746,12 +5746,12 @@
       </c>
       <c r="CL11" t="inlineStr">
         <is>
-          <t>26.91</t>
+          <t>26.63</t>
         </is>
       </c>
       <c r="CM11" t="inlineStr">
         <is>
-          <t>462485</t>
+          <t>450578</t>
         </is>
       </c>
       <c r="CN11" t="inlineStr">
@@ -5771,17 +5771,17 @@
       </c>
       <c r="CQ11" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="CR11" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>49.35</t>
         </is>
       </c>
       <c r="CS11" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>48.35</t>
         </is>
       </c>
       <c r="CT11" t="inlineStr">
@@ -5818,12 +5818,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>558.268</t>
+          <t>333.587</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5833,7 +5833,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>70.4</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5848,12 +5848,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-4.71</t>
+          <t>-4.15</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5943,7 +5943,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -5993,17 +5993,17 @@
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>29.66</t>
+          <t>17.73</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
@@ -6014,66 +6014,66 @@
       <c r="AP12" t="inlineStr"/>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>558</t>
+          <t>334</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>96.77</t>
+          <t>97.26</t>
         </is>
       </c>
       <c r="AU12" t="n">
-        <v>1.82</v>
+        <v>0.63</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.96</v>
+        <v>1.81</v>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>-6.06</t>
+          <t>-5.72</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>-5.03</t>
+          <t>-5.14</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>69.14000000000001</t>
+          <t>69.76</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>68.48</v>
+        <v>68.52</v>
       </c>
       <c r="BA12" t="n">
-        <v>72.90000000000001</v>
+        <v>72.68000000000001</v>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>76.77</t>
+          <t>76.62</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>39.55</t>
+          <t>45.71</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-0.76</v>
       </c>
       <c r="BE12" t="n">
-        <v>-1.55</v>
+        <v>-1.4</v>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
@@ -6082,7 +6082,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-194.71</t>
+          <t>-184.99</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -6092,43 +6092,43 @@
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>67902833.3706721</t>
+          <t>67835936.7652439</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
         <is>
-          <t>39008562.0</t>
+          <t>23326469.0</t>
         </is>
       </c>
       <c r="BK12" t="n">
-        <v>34989274.2</v>
+        <v>33150026.6</v>
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>36718827.1</t>
+          <t>34585798.3</t>
         </is>
       </c>
       <c r="BM12" t="n">
-        <v>39943524.72</v>
+        <v>39554243.3</v>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>-1729552</t>
+          <t>-1435771</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>-907679.5131158077</t>
+          <t>-943167.3675451955</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>-235706.7779135033</t>
+          <t>-1138350.566906828</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>39008562.0</t>
+          <t>23326469.0</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -6148,7 +6148,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>-21.16</t>
+          <t>-21.39</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -6193,7 +6193,7 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
@@ -6203,12 +6203,12 @@
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>6.39</t>
+          <t>6.41</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -6218,7 +6218,7 @@
       </c>
       <c r="CI12" t="inlineStr">
         <is>
-          <t>22.21</t>
+          <t>22.15</t>
         </is>
       </c>
       <c r="CJ12" t="inlineStr">
@@ -6233,12 +6233,12 @@
       </c>
       <c r="CL12" t="inlineStr">
         <is>
-          <t>55.22</t>
+          <t>56.04</t>
         </is>
       </c>
       <c r="CM12" t="inlineStr">
         <is>
-          <t>16678</t>
+          <t>16631</t>
         </is>
       </c>
       <c r="CN12" t="inlineStr">
@@ -6258,22 +6258,22 @@
       </c>
       <c r="CQ12" t="inlineStr">
         <is>
-          <t>69.4</t>
+          <t>70.3</t>
         </is>
       </c>
       <c r="CR12" t="inlineStr">
         <is>
-          <t>70.4</t>
+          <t>70.3</t>
         </is>
       </c>
       <c r="CS12" t="inlineStr">
         <is>
-          <t>69.1</t>
+          <t>69.5</t>
         </is>
       </c>
       <c r="CT12" t="inlineStr">
         <is>
-          <t>70.4</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="CU12" t="inlineStr">
@@ -6295,7 +6295,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -6305,12 +6305,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>520.602</t>
+          <t>558.268</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -6320,7 +6320,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>69.4</t>
+          <t>70.4</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -6330,17 +6330,17 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-7.09</t>
+          <t>-4.71</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -6430,7 +6430,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -6480,17 +6480,17 @@
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>27.66</t>
+          <t>29.66</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>-1.30</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
@@ -6501,66 +6501,66 @@
       <c r="AP13" t="inlineStr"/>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>558</t>
+          <t>334</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr">
+        <is>
           <t>96.77</t>
         </is>
       </c>
-      <c r="AT13" t="inlineStr">
-        <is>
-          <t>96.77</t>
-        </is>
-      </c>
       <c r="AU13" t="n">
-        <v>1.55</v>
+        <v>1.82</v>
       </c>
       <c r="AV13" t="n">
-        <v>-0.13</v>
+        <v>0.96</v>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>-6.43</t>
+          <t>-6.06</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>-4.91</t>
+          <t>-5.03</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>68.34</t>
+          <t>69.14000000000001</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>68.43000000000001</v>
+        <v>68.48</v>
       </c>
       <c r="BA13" t="n">
-        <v>73.13</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>76.91</t>
+          <t>76.77</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>30.99</t>
+          <t>39.55</t>
         </is>
       </c>
       <c r="BD13" t="n">
-        <v>-1.18</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="BE13" t="n">
-        <v>-1.71</v>
+        <v>-1.55</v>
       </c>
       <c r="BF13" t="inlineStr">
         <is>
@@ -6569,7 +6569,7 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>-204.07</t>
+          <t>-194.71</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -6579,43 +6579,43 @@
       </c>
       <c r="BI13" t="inlineStr">
         <is>
-          <t>67902833.3706721</t>
+          <t>67835936.7652439</t>
         </is>
       </c>
       <c r="BJ13" t="inlineStr">
         <is>
-          <t>36375938.0</t>
+          <t>39008562.0</t>
         </is>
       </c>
       <c r="BK13" t="n">
-        <v>35739941.4</v>
+        <v>34989274.2</v>
       </c>
       <c r="BL13" t="inlineStr">
         <is>
-          <t>38465909.2</t>
+          <t>36718827.1</t>
         </is>
       </c>
       <c r="BM13" t="n">
-        <v>39551314.52</v>
+        <v>39943524.72</v>
       </c>
       <c r="BN13" t="inlineStr">
         <is>
-          <t>-2725967</t>
+          <t>-1729552</t>
         </is>
       </c>
       <c r="BO13" t="inlineStr">
         <is>
-          <t>-1029856.374061681</t>
+          <t>-907679.5131158077</t>
         </is>
       </c>
       <c r="BP13" t="inlineStr">
         <is>
-          <t>-618021.801568985</t>
+          <t>-235706.7779135033</t>
         </is>
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>36375938.0</t>
+          <t>39008562.0</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -6635,7 +6635,7 @@
       </c>
       <c r="BU13" t="inlineStr">
         <is>
-          <t>-22.28</t>
+          <t>-21.16</t>
         </is>
       </c>
       <c r="BV13" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
@@ -6690,12 +6690,12 @@
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>6.39</t>
+          <t>6.41</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6705,7 +6705,7 @@
       </c>
       <c r="CI13" t="inlineStr">
         <is>
-          <t>22.21</t>
+          <t>22.15</t>
         </is>
       </c>
       <c r="CJ13" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="CL13" t="inlineStr">
         <is>
-          <t>55.22</t>
+          <t>56.04</t>
         </is>
       </c>
       <c r="CM13" t="inlineStr">
         <is>
-          <t>16678</t>
+          <t>16631</t>
         </is>
       </c>
       <c r="CN13" t="inlineStr">
@@ -6750,17 +6750,17 @@
       </c>
       <c r="CR13" t="inlineStr">
         <is>
-          <t>70.3</t>
+          <t>70.4</t>
         </is>
       </c>
       <c r="CS13" t="inlineStr">
         <is>
-          <t>69.4</t>
+          <t>69.1</t>
         </is>
       </c>
       <c r="CT13" t="inlineStr">
         <is>
-          <t>69.4</t>
+          <t>70.4</t>
         </is>
       </c>
       <c r="CU13" t="inlineStr">
@@ -6792,12 +6792,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>350.741</t>
+          <t>520.602</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6807,7 +6807,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>69.3</t>
+          <t>69.4</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6817,17 +6817,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-7.09</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6917,7 +6917,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -6967,17 +6967,17 @@
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>18.64</t>
+          <t>27.66</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-1.30</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
@@ -6988,66 +6988,66 @@
       <c r="AP14" t="inlineStr"/>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>558</t>
+          <t>334</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>93.55</t>
+          <t>96.77</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>74.66</t>
+          <t>96.77</t>
         </is>
       </c>
       <c r="AU14" t="n">
-        <v>2.09</v>
+        <v>1.55</v>
       </c>
       <c r="AV14" t="n">
-        <v>-0.74</v>
+        <v>-0.13</v>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>-6.82</t>
+          <t>-6.43</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>-4.76</t>
+          <t>-4.91</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>67.88</t>
+          <t>68.34</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>68.39</v>
+        <v>68.43000000000001</v>
       </c>
       <c r="BA14" t="n">
-        <v>73.39</v>
+        <v>73.13</v>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>77.06</t>
+          <t>76.91</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>25.82</t>
+          <t>30.99</t>
         </is>
       </c>
       <c r="BD14" t="n">
-        <v>-1.37</v>
+        <v>-1.18</v>
       </c>
       <c r="BE14" t="n">
-        <v>-1.84</v>
+        <v>-1.71</v>
       </c>
       <c r="BF14" t="inlineStr">
         <is>
@@ -7056,7 +7056,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>-212.13</t>
+          <t>-204.07</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -7066,43 +7066,43 @@
       </c>
       <c r="BI14" t="inlineStr">
         <is>
-          <t>67902833.3706721</t>
+          <t>67835936.7652439</t>
         </is>
       </c>
       <c r="BJ14" t="inlineStr">
         <is>
-          <t>24325351.0</t>
+          <t>36375938.0</t>
         </is>
       </c>
       <c r="BK14" t="n">
-        <v>36038654.2</v>
+        <v>35739941.4</v>
       </c>
       <c r="BL14" t="inlineStr">
         <is>
-          <t>36553536.0</t>
+          <t>38465909.2</t>
         </is>
       </c>
       <c r="BM14" t="n">
-        <v>39196138.46</v>
+        <v>39551314.52</v>
       </c>
       <c r="BN14" t="inlineStr">
         <is>
-          <t>-514881</t>
+          <t>-2725967</t>
         </is>
       </c>
       <c r="BO14" t="inlineStr">
         <is>
-          <t>-1104735.387242171</t>
+          <t>-1029856.374061681</t>
         </is>
       </c>
       <c r="BP14" t="inlineStr">
         <is>
-          <t>-860047.0567350611</t>
+          <t>-618021.801568985</t>
         </is>
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>24325351.0</t>
+          <t>36375938.0</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -7122,7 +7122,7 @@
       </c>
       <c r="BU14" t="inlineStr">
         <is>
-          <t>-22.40</t>
+          <t>-22.28</t>
         </is>
       </c>
       <c r="BV14" t="inlineStr">
@@ -7167,22 +7167,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>6.39</t>
+          <t>6.41</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -7192,7 +7192,7 @@
       </c>
       <c r="CI14" t="inlineStr">
         <is>
-          <t>22.21</t>
+          <t>22.15</t>
         </is>
       </c>
       <c r="CJ14" t="inlineStr">
@@ -7207,12 +7207,12 @@
       </c>
       <c r="CL14" t="inlineStr">
         <is>
-          <t>55.22</t>
+          <t>56.04</t>
         </is>
       </c>
       <c r="CM14" t="inlineStr">
         <is>
-          <t>16678</t>
+          <t>16631</t>
         </is>
       </c>
       <c r="CN14" t="inlineStr">
@@ -7232,22 +7232,22 @@
       </c>
       <c r="CQ14" t="inlineStr">
         <is>
-          <t>69.8</t>
+          <t>69.4</t>
         </is>
       </c>
       <c r="CR14" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>70.3</t>
         </is>
       </c>
       <c r="CS14" t="inlineStr">
         <is>
-          <t>68.9</t>
+          <t>69.4</t>
         </is>
       </c>
       <c r="CT14" t="inlineStr">
         <is>
-          <t>69.3</t>
+          <t>69.4</t>
         </is>
       </c>
       <c r="CU14" t="inlineStr">
@@ -7279,12 +7279,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>3.57</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>621.714</t>
+          <t>350.741</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -7294,7 +7294,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>69.5</t>
+          <t>69.3</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -7309,12 +7309,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -7404,7 +7404,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -7454,17 +7454,17 @@
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>33.03</t>
+          <t>18.64</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>3.43</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
@@ -7475,66 +7475,66 @@
       <c r="AP15" t="inlineStr"/>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>558</t>
+          <t>334</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>93.55</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>43.48</t>
+          <t>74.66</t>
         </is>
       </c>
       <c r="AU15" t="n">
-        <v>2.75</v>
+        <v>2.09</v>
       </c>
       <c r="AV15" t="n">
-        <v>-1.02</v>
+        <v>-0.74</v>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>-7.21</t>
+          <t>-6.82</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>-4.62</t>
+          <t>-4.76</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>67.64</t>
+          <t>67.88</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>68.34</v>
+        <v>68.39</v>
       </c>
       <c r="BA15" t="n">
-        <v>73.65000000000001</v>
+        <v>73.39</v>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>77.22</t>
+          <t>77.06</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>19.71</t>
+          <t>25.82</t>
         </is>
       </c>
       <c r="BD15" t="n">
-        <v>-1.57</v>
+        <v>-1.37</v>
       </c>
       <c r="BE15" t="n">
-        <v>-1.96</v>
+        <v>-1.84</v>
       </c>
       <c r="BF15" t="inlineStr">
         <is>
@@ -7543,7 +7543,7 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>-219.37</t>
+          <t>-212.13</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -7553,43 +7553,43 @@
       </c>
       <c r="BI15" t="inlineStr">
         <is>
-          <t>67902833.3706721</t>
+          <t>67835936.7652439</t>
         </is>
       </c>
       <c r="BJ15" t="inlineStr">
         <is>
-          <t>42713813.0</t>
+          <t>24325351.0</t>
         </is>
       </c>
       <c r="BK15" t="n">
-        <v>35506149.2</v>
+        <v>36038654.2</v>
       </c>
       <c r="BL15" t="inlineStr">
         <is>
-          <t>35911688.6</t>
+          <t>36553536.0</t>
         </is>
       </c>
       <c r="BM15" t="n">
-        <v>39258237.54</v>
+        <v>39196138.46</v>
       </c>
       <c r="BN15" t="inlineStr">
         <is>
-          <t>-405539</t>
+          <t>-514881</t>
         </is>
       </c>
       <c r="BO15" t="inlineStr">
         <is>
-          <t>-1149224.1746071</t>
+          <t>-1104735.387242171</t>
         </is>
       </c>
       <c r="BP15" t="inlineStr">
         <is>
-          <t>116052.8664825112</t>
+          <t>-860047.0567350611</t>
         </is>
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>42713813.0</t>
+          <t>24325351.0</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
@@ -7609,7 +7609,7 @@
       </c>
       <c r="BU15" t="inlineStr">
         <is>
-          <t>-22.17</t>
+          <t>-22.40</t>
         </is>
       </c>
       <c r="BV15" t="inlineStr">
@@ -7654,22 +7654,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>6.39</t>
+          <t>6.41</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -7679,7 +7679,7 @@
       </c>
       <c r="CI15" t="inlineStr">
         <is>
-          <t>22.21</t>
+          <t>22.15</t>
         </is>
       </c>
       <c r="CJ15" t="inlineStr">
@@ -7694,12 +7694,12 @@
       </c>
       <c r="CL15" t="inlineStr">
         <is>
-          <t>55.22</t>
+          <t>56.04</t>
         </is>
       </c>
       <c r="CM15" t="inlineStr">
         <is>
-          <t>16678</t>
+          <t>16631</t>
         </is>
       </c>
       <c r="CN15" t="inlineStr">
@@ -7719,22 +7719,22 @@
       </c>
       <c r="CQ15" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>69.8</t>
         </is>
       </c>
       <c r="CR15" t="inlineStr">
         <is>
-          <t>69.6</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="CS15" t="inlineStr">
         <is>
-          <t>67.1</t>
+          <t>68.9</t>
         </is>
       </c>
       <c r="CT15" t="inlineStr">
         <is>
-          <t>69.5</t>
+          <t>69.3</t>
         </is>
       </c>
       <c r="CU15" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>3.57</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>485.313</t>
+          <t>621.714</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -7781,7 +7781,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>67.1</t>
+          <t>69.5</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -7791,17 +7791,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>4.69</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>6.33</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7891,7 +7891,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -7941,17 +7941,17 @@
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>25.79</t>
+          <t>33.03</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>3.43</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
@@ -7962,66 +7962,66 @@
       <c r="AP16" t="inlineStr"/>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>558</t>
+          <t>334</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>30.43</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>10.14</t>
+          <t>43.48</t>
         </is>
       </c>
       <c r="AU16" t="n">
-        <v>-0.5</v>
+        <v>2.75</v>
       </c>
       <c r="AV16" t="n">
-        <v>-1.35</v>
+        <v>-1.02</v>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>-7.52</t>
+          <t>-7.21</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>-4.47</t>
+          <t>-4.62</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>67.44</t>
+          <t>67.64</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>68.36</v>
+        <v>68.34</v>
       </c>
       <c r="BA16" t="n">
-        <v>73.92</v>
+        <v>73.65000000000001</v>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>77.39</t>
+          <t>77.22</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>10.70</t>
+          <t>19.71</t>
         </is>
       </c>
       <c r="BD16" t="n">
-        <v>-1.84</v>
+        <v>-1.57</v>
       </c>
       <c r="BE16" t="n">
-        <v>-2.06</v>
+        <v>-1.96</v>
       </c>
       <c r="BF16" t="inlineStr">
         <is>
@@ -8030,7 +8030,7 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>-225.25</t>
+          <t>-219.37</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -8040,43 +8040,43 @@
       </c>
       <c r="BI16" t="inlineStr">
         <is>
-          <t>67902833.3706721</t>
+          <t>67835936.7652439</t>
         </is>
       </c>
       <c r="BJ16" t="inlineStr">
         <is>
-          <t>32522707.0</t>
+          <t>42713813.0</t>
         </is>
       </c>
       <c r="BK16" t="n">
-        <v>36021570</v>
+        <v>35506149.2</v>
       </c>
       <c r="BL16" t="inlineStr">
         <is>
-          <t>33877169.8</t>
+          <t>35911688.6</t>
         </is>
       </c>
       <c r="BM16" t="n">
-        <v>39098673.78</v>
+        <v>39258237.54</v>
       </c>
       <c r="BN16" t="inlineStr">
         <is>
-          <t>2144400</t>
+          <t>-405539</t>
         </is>
       </c>
       <c r="BO16" t="inlineStr">
         <is>
-          <t>-1379274.545714302</t>
+          <t>-1149224.1746071</t>
         </is>
       </c>
       <c r="BP16" t="inlineStr">
         <is>
-          <t>-463855.7741524726</t>
+          <t>116052.8664825112</t>
         </is>
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>32522707.0</t>
+          <t>42713813.0</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
@@ -8096,7 +8096,7 @@
       </c>
       <c r="BU16" t="inlineStr">
         <is>
-          <t>-24.86</t>
+          <t>-22.17</t>
         </is>
       </c>
       <c r="BV16" t="inlineStr">
@@ -8141,22 +8141,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>6.39</t>
+          <t>6.41</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -8166,7 +8166,7 @@
       </c>
       <c r="CI16" t="inlineStr">
         <is>
-          <t>22.21</t>
+          <t>22.15</t>
         </is>
       </c>
       <c r="CJ16" t="inlineStr">
@@ -8181,12 +8181,12 @@
       </c>
       <c r="CL16" t="inlineStr">
         <is>
-          <t>55.22</t>
+          <t>56.04</t>
         </is>
       </c>
       <c r="CM16" t="inlineStr">
         <is>
-          <t>16678</t>
+          <t>16631</t>
         </is>
       </c>
       <c r="CN16" t="inlineStr">
@@ -8206,22 +8206,22 @@
       </c>
       <c r="CQ16" t="inlineStr">
         <is>
-          <t>66.2</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="CR16" t="inlineStr">
         <is>
-          <t>67.6</t>
+          <t>69.6</t>
         </is>
       </c>
       <c r="CS16" t="inlineStr">
         <is>
-          <t>66.2</t>
+          <t>67.1</t>
         </is>
       </c>
       <c r="CT16" t="inlineStr">
         <is>
-          <t>67.1</t>
+          <t>69.5</t>
         </is>
       </c>
       <c r="CU16" t="inlineStr">
@@ -8253,12 +8253,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>643.584</t>
+          <t>485.313</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -8268,7 +8268,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>66.4</t>
+          <t>67.1</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -8278,17 +8278,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>5.68</t>
+          <t>4.42</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>11.71</t>
+          <t>6.33</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -8378,7 +8378,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -8428,17 +8428,17 @@
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>34.20</t>
+          <t>25.79</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
@@ -8449,66 +8449,66 @@
       <c r="AP17" t="inlineStr"/>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>558</t>
+          <t>334</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>30.43</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>20.83</t>
+          <t>10.14</t>
         </is>
       </c>
       <c r="AU17" t="n">
-        <v>-1.75</v>
+        <v>-0.5</v>
       </c>
       <c r="AV17" t="n">
-        <v>-1.42</v>
+        <v>-1.35</v>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>-7.68</t>
+          <t>-7.52</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>-4.29</t>
+          <t>-4.47</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>67.58</t>
+          <t>67.44</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>68.55</v>
+        <v>68.36</v>
       </c>
       <c r="BA17" t="n">
-        <v>74.26000000000001</v>
+        <v>73.92</v>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>77.59</t>
+          <t>77.39</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>9.97</t>
+          <t>10.70</t>
         </is>
       </c>
       <c r="BD17" t="n">
-        <v>-1.9</v>
+        <v>-1.84</v>
       </c>
       <c r="BE17" t="n">
-        <v>-2.11</v>
+        <v>-2.06</v>
       </c>
       <c r="BF17" t="inlineStr">
         <is>
@@ -8517,7 +8517,7 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>-228.60</t>
+          <t>-225.25</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -8527,43 +8527,43 @@
       </c>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>67902833.3706721</t>
+          <t>67835936.7652439</t>
         </is>
       </c>
       <c r="BJ17" t="inlineStr">
         <is>
-          <t>42761898.0</t>
+          <t>32522707.0</t>
         </is>
       </c>
       <c r="BK17" t="n">
-        <v>38448380</v>
+        <v>36021570</v>
       </c>
       <c r="BL17" t="inlineStr">
         <is>
-          <t>34418020.0</t>
+          <t>33877169.8</t>
         </is>
       </c>
       <c r="BM17" t="n">
-        <v>38733021.6</v>
+        <v>39098673.78</v>
       </c>
       <c r="BN17" t="inlineStr">
         <is>
-          <t>4030360</t>
+          <t>2144400</t>
         </is>
       </c>
       <c r="BO17" t="inlineStr">
         <is>
-          <t>-1545714.322361908</t>
+          <t>-1379274.545714302</t>
         </is>
       </c>
       <c r="BP17" t="inlineStr">
         <is>
-          <t>-183826.1974112913</t>
+          <t>-463855.7741524726</t>
         </is>
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>42761898.0</t>
+          <t>32522707.0</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
@@ -8583,7 +8583,7 @@
       </c>
       <c r="BU17" t="inlineStr">
         <is>
-          <t>-25.64</t>
+          <t>-24.86</t>
         </is>
       </c>
       <c r="BV17" t="inlineStr">
@@ -8633,17 +8633,17 @@
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>6.39</t>
+          <t>6.41</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -8653,7 +8653,7 @@
       </c>
       <c r="CI17" t="inlineStr">
         <is>
-          <t>22.21</t>
+          <t>22.15</t>
         </is>
       </c>
       <c r="CJ17" t="inlineStr">
@@ -8668,12 +8668,12 @@
       </c>
       <c r="CL17" t="inlineStr">
         <is>
-          <t>55.22</t>
+          <t>56.04</t>
         </is>
       </c>
       <c r="CM17" t="inlineStr">
         <is>
-          <t>16678</t>
+          <t>16631</t>
         </is>
       </c>
       <c r="CN17" t="inlineStr">
@@ -8693,22 +8693,22 @@
       </c>
       <c r="CQ17" t="inlineStr">
         <is>
+          <t>66.2</t>
+        </is>
+      </c>
+      <c r="CR17" t="inlineStr">
+        <is>
+          <t>67.6</t>
+        </is>
+      </c>
+      <c r="CS17" t="inlineStr">
+        <is>
+          <t>66.2</t>
+        </is>
+      </c>
+      <c r="CT17" t="inlineStr">
+        <is>
           <t>67.1</t>
-        </is>
-      </c>
-      <c r="CR17" t="inlineStr">
-        <is>
-          <t>67.3</t>
-        </is>
-      </c>
-      <c r="CS17" t="inlineStr">
-        <is>
-          <t>66.0</t>
-        </is>
-      </c>
-      <c r="CT17" t="inlineStr">
-        <is>
-          <t>66.4</t>
         </is>
       </c>
       <c r="CU17" t="inlineStr">
@@ -8740,12 +8740,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>561.716</t>
+          <t>643.584</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -8755,7 +8755,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>67.1</t>
+          <t>66.4</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -8765,17 +8765,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>4.69</t>
+          <t>5.41</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>19.23</t>
+          <t>11.71</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -8865,7 +8865,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -8915,17 +8915,17 @@
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>29.85</t>
+          <t>34.20</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
@@ -8936,12 +8936,12 @@
       <c r="AP18" t="inlineStr"/>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>558</t>
+          <t>334</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -8951,51 +8951,51 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>45.39</t>
+          <t>20.83</t>
         </is>
       </c>
       <c r="AU18" t="n">
-        <v>-0.92</v>
+        <v>-1.75</v>
       </c>
       <c r="AV18" t="n">
-        <v>-1.6</v>
+        <v>-1.42</v>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>-7.76</t>
+          <t>-7.68</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>-4.10</t>
+          <t>-4.29</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>67.72</t>
+          <t>67.58</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>68.81999999999999</v>
+        <v>68.55</v>
       </c>
       <c r="BA18" t="n">
-        <v>74.61</v>
+        <v>74.26000000000001</v>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>77.79</t>
+          <t>77.59</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>12.93</t>
+          <t>9.97</t>
         </is>
       </c>
       <c r="BD18" t="n">
-        <v>-1.88</v>
+        <v>-1.9</v>
       </c>
       <c r="BE18" t="n">
-        <v>-2.16</v>
+        <v>-2.11</v>
       </c>
       <c r="BF18" t="inlineStr">
         <is>
@@ -9004,7 +9004,7 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>-231.81</t>
+          <t>-228.60</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -9014,43 +9014,43 @@
       </c>
       <c r="BI18" t="inlineStr">
         <is>
-          <t>67902833.3706721</t>
+          <t>67835936.7652439</t>
         </is>
       </c>
       <c r="BJ18" t="inlineStr">
         <is>
-          <t>37869502.0</t>
+          <t>42761898.0</t>
         </is>
       </c>
       <c r="BK18" t="n">
-        <v>41191877</v>
+        <v>38448380</v>
       </c>
       <c r="BL18" t="inlineStr">
         <is>
-          <t>34549396.1</t>
+          <t>34418020.0</t>
         </is>
       </c>
       <c r="BM18" t="n">
-        <v>38283283.38</v>
+        <v>38733021.6</v>
       </c>
       <c r="BN18" t="inlineStr">
         <is>
-          <t>6642480</t>
+          <t>4030360</t>
         </is>
       </c>
       <c r="BO18" t="inlineStr">
         <is>
-          <t>-1793330.345080202</t>
+          <t>-1545714.322361908</t>
         </is>
       </c>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>-874274.9021591917</t>
+          <t>-183826.1974112913</t>
         </is>
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>37869502.0</t>
+          <t>42761898.0</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
@@ -9070,7 +9070,7 @@
       </c>
       <c r="BU18" t="inlineStr">
         <is>
-          <t>-24.86</t>
+          <t>-25.64</t>
         </is>
       </c>
       <c r="BV18" t="inlineStr">
@@ -9115,7 +9115,7 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
@@ -9125,12 +9125,12 @@
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>6.39</t>
+          <t>6.41</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -9140,7 +9140,7 @@
       </c>
       <c r="CI18" t="inlineStr">
         <is>
-          <t>22.21</t>
+          <t>22.15</t>
         </is>
       </c>
       <c r="CJ18" t="inlineStr">
@@ -9155,12 +9155,12 @@
       </c>
       <c r="CL18" t="inlineStr">
         <is>
-          <t>55.22</t>
+          <t>56.04</t>
         </is>
       </c>
       <c r="CM18" t="inlineStr">
         <is>
-          <t>16678</t>
+          <t>16631</t>
         </is>
       </c>
       <c r="CN18" t="inlineStr">
@@ -9180,22 +9180,22 @@
       </c>
       <c r="CQ18" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>67.1</t>
         </is>
       </c>
       <c r="CR18" t="inlineStr">
         <is>
-          <t>68.4</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="CS18" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="CT18" t="inlineStr">
         <is>
-          <t>67.1</t>
+          <t>66.4</t>
         </is>
       </c>
       <c r="CU18" t="inlineStr">
@@ -9227,12 +9227,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>316.85</t>
+          <t>561.716</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -9242,7 +9242,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>68.1</t>
+          <t>67.1</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -9252,17 +9252,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>3.27</t>
+          <t>4.42</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>14.26</t>
+          <t>19.23</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -9352,7 +9352,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -9402,17 +9402,17 @@
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>16.84</t>
+          <t>29.85</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
@@ -9423,66 +9423,66 @@
       <c r="AP19" t="inlineStr"/>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>558</t>
+          <t>334</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>62.5</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>56.0</t>
+          <t>45.39</t>
         </is>
       </c>
       <c r="AU19" t="n">
-        <v>0.15</v>
+        <v>-0.92</v>
       </c>
       <c r="AV19" t="n">
-        <v>-1.47</v>
+        <v>-1.6</v>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>-7.91</t>
+          <t>-7.76</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>-3.92</t>
+          <t>-4.10</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>67.99999999999999</t>
+          <t>67.72</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>69.02</v>
+        <v>68.81999999999999</v>
       </c>
       <c r="BA19" t="n">
-        <v>74.94</v>
+        <v>74.61</v>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>77.99</t>
+          <t>77.79</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>14.65</t>
+          <t>12.93</t>
         </is>
       </c>
       <c r="BD19" t="n">
-        <v>-1.91</v>
+        <v>-1.88</v>
       </c>
       <c r="BE19" t="n">
-        <v>-2.23</v>
+        <v>-2.16</v>
       </c>
       <c r="BF19" t="inlineStr">
         <is>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>-236.07</t>
+          <t>-231.81</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -9501,43 +9501,43 @@
       </c>
       <c r="BI19" t="inlineStr">
         <is>
-          <t>67902833.3706721</t>
+          <t>67835936.7652439</t>
         </is>
       </c>
       <c r="BJ19" t="inlineStr">
         <is>
-          <t>21662826.0</t>
+          <t>37869502.0</t>
         </is>
       </c>
       <c r="BK19" t="n">
-        <v>37068417.8</v>
+        <v>41191877</v>
       </c>
       <c r="BL19" t="inlineStr">
         <is>
-          <t>32440889.4</t>
+          <t>34549396.1</t>
         </is>
       </c>
       <c r="BM19" t="n">
-        <v>37992857.32</v>
+        <v>38283283.38</v>
       </c>
       <c r="BN19" t="inlineStr">
         <is>
-          <t>4627528</t>
+          <t>6642480</t>
         </is>
       </c>
       <c r="BO19" t="inlineStr">
         <is>
-          <t>-1960431.334702203</t>
+          <t>-1793330.345080202</t>
         </is>
       </c>
       <c r="BP19" t="inlineStr">
         <is>
-          <t>-1305220.805293366</t>
+          <t>-874274.9021591917</t>
         </is>
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>21662826.0</t>
+          <t>37869502.0</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
@@ -9557,7 +9557,7 @@
       </c>
       <c r="BU19" t="inlineStr">
         <is>
-          <t>-23.74</t>
+          <t>-24.86</t>
         </is>
       </c>
       <c r="BV19" t="inlineStr">
@@ -9602,7 +9602,7 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
@@ -9612,12 +9612,12 @@
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>6.39</t>
+          <t>6.41</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -9627,7 +9627,7 @@
       </c>
       <c r="CI19" t="inlineStr">
         <is>
-          <t>22.21</t>
+          <t>22.15</t>
         </is>
       </c>
       <c r="CJ19" t="inlineStr">
@@ -9642,12 +9642,12 @@
       </c>
       <c r="CL19" t="inlineStr">
         <is>
-          <t>55.22</t>
+          <t>56.04</t>
         </is>
       </c>
       <c r="CM19" t="inlineStr">
         <is>
-          <t>16678</t>
+          <t>16631</t>
         </is>
       </c>
       <c r="CN19" t="inlineStr">
@@ -9667,22 +9667,22 @@
       </c>
       <c r="CQ19" t="inlineStr">
         <is>
-          <t>68.1</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="CR19" t="inlineStr">
         <is>
-          <t>69.1</t>
+          <t>68.4</t>
         </is>
       </c>
       <c r="CS19" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="CT19" t="inlineStr">
         <is>
-          <t>68.1</t>
+          <t>67.1</t>
         </is>
       </c>
       <c r="CU19" t="inlineStr">
@@ -9714,12 +9714,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>673.593</t>
+          <t>316.85</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -9729,7 +9729,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>68.5</t>
+          <t>68.1</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -9739,17 +9739,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>12.26</t>
+          <t>14.26</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -9839,7 +9839,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -9889,17 +9889,17 @@
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>35.79</t>
+          <t>16.84</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>3.01</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
@@ -9910,66 +9910,66 @@
       <c r="AP20" t="inlineStr"/>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>558</t>
+          <t>334</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
         <is>
-          <t>73.68</t>
+          <t>62.5</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>35.17</t>
+          <t>56.0</t>
         </is>
       </c>
       <c r="AU20" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.15</v>
       </c>
       <c r="AV20" t="n">
-        <v>-1.55</v>
+        <v>-1.47</v>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>-8.07</t>
+          <t>-7.91</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>-3.71</t>
+          <t>-3.92</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>68.12</t>
+          <t>67.99999999999999</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>69.19</v>
+        <v>69.02</v>
       </c>
       <c r="BA20" t="n">
-        <v>75.27</v>
+        <v>74.94</v>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>78.16</t>
+          <t>77.99</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>13.22</t>
+          <t>14.65</t>
         </is>
       </c>
       <c r="BD20" t="n">
-        <v>-2.01</v>
+        <v>-1.91</v>
       </c>
       <c r="BE20" t="n">
-        <v>-2.32</v>
+        <v>-2.23</v>
       </c>
       <c r="BF20" t="inlineStr">
         <is>
@@ -9978,7 +9978,7 @@
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>-241.05</t>
+          <t>-236.07</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
@@ -9988,43 +9988,43 @@
       </c>
       <c r="BI20" t="inlineStr">
         <is>
-          <t>67902833.3706721</t>
+          <t>67835936.7652439</t>
         </is>
       </c>
       <c r="BJ20" t="inlineStr">
         <is>
-          <t>45290917.0</t>
+          <t>21662826.0</t>
         </is>
       </c>
       <c r="BK20" t="n">
-        <v>36317228</v>
+        <v>37068417.8</v>
       </c>
       <c r="BL20" t="inlineStr">
         <is>
-          <t>32350796.3</t>
+          <t>32440889.4</t>
         </is>
       </c>
       <c r="BM20" t="n">
-        <v>38135166.56</v>
+        <v>37992857.32</v>
       </c>
       <c r="BN20" t="inlineStr">
         <is>
-          <t>3966431</t>
+          <t>4627528</t>
         </is>
       </c>
       <c r="BO20" t="inlineStr">
         <is>
-          <t>-2079560.521867446</t>
+          <t>-1960431.334702203</t>
         </is>
       </c>
       <c r="BP20" t="inlineStr">
         <is>
-          <t>-137813.2095817178</t>
+          <t>-1305220.805293366</t>
         </is>
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>45290917.0</t>
+          <t>21662826.0</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
@@ -10044,7 +10044,7 @@
       </c>
       <c r="BU20" t="inlineStr">
         <is>
-          <t>-23.29</t>
+          <t>-23.74</t>
         </is>
       </c>
       <c r="BV20" t="inlineStr">
@@ -10089,7 +10089,7 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
@@ -10099,12 +10099,12 @@
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>6.39</t>
+          <t>6.41</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -10114,7 +10114,7 @@
       </c>
       <c r="CI20" t="inlineStr">
         <is>
-          <t>22.21</t>
+          <t>22.15</t>
         </is>
       </c>
       <c r="CJ20" t="inlineStr">
@@ -10129,12 +10129,12 @@
       </c>
       <c r="CL20" t="inlineStr">
         <is>
-          <t>55.22</t>
+          <t>56.04</t>
         </is>
       </c>
       <c r="CM20" t="inlineStr">
         <is>
-          <t>16678</t>
+          <t>16631</t>
         </is>
       </c>
       <c r="CN20" t="inlineStr">
@@ -10154,22 +10154,22 @@
       </c>
       <c r="CQ20" t="inlineStr">
         <is>
-          <t>67.5</t>
+          <t>68.1</t>
         </is>
       </c>
       <c r="CR20" t="inlineStr">
         <is>
-          <t>68.5</t>
+          <t>69.1</t>
         </is>
       </c>
       <c r="CS20" t="inlineStr">
         <is>
-          <t>66.5</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="CT20" t="inlineStr">
         <is>
-          <t>68.5</t>
+          <t>68.1</t>
         </is>
       </c>
       <c r="CU20" t="inlineStr">
@@ -10206,7 +10206,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>658.104</t>
+          <t>673.593</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -10216,7 +10216,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>68.5</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -10226,17 +10226,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>3.69</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>5.11</t>
+          <t>12.26</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -10326,7 +10326,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -10376,17 +10376,17 @@
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>34.97</t>
+          <t>35.79</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>3.01</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
@@ -10397,66 +10397,66 @@
       <c r="AP21" t="inlineStr"/>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>558</t>
+          <t>334</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
         <is>
-          <t>31.82</t>
+          <t>73.68</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>23.57</t>
+          <t>35.17</t>
         </is>
       </c>
       <c r="AU21" t="n">
-        <v>-0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AV21" t="n">
-        <v>-1.72</v>
+        <v>-1.55</v>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>-8.29</t>
+          <t>-8.07</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>-3.49</t>
+          <t>-3.71</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>68.14</t>
+          <t>68.12</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>69.33</v>
+        <v>69.19</v>
       </c>
       <c r="BA21" t="n">
-        <v>75.59999999999999</v>
+        <v>75.27</v>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>78.33</t>
+          <t>78.16</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>10.03</t>
+          <t>13.22</t>
         </is>
       </c>
       <c r="BD21" t="n">
-        <v>-2.15</v>
+        <v>-2.01</v>
       </c>
       <c r="BE21" t="n">
-        <v>-2.39</v>
+        <v>-2.32</v>
       </c>
       <c r="BF21" t="inlineStr">
         <is>
@@ -10465,7 +10465,7 @@
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>-245.71</t>
+          <t>-241.05</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
@@ -10475,43 +10475,43 @@
       </c>
       <c r="BI21" t="inlineStr">
         <is>
-          <t>67902833.3706721</t>
+          <t>67835936.7652439</t>
         </is>
       </c>
       <c r="BJ21" t="inlineStr">
         <is>
-          <t>44656757.0</t>
+          <t>45290917.0</t>
         </is>
       </c>
       <c r="BK21" t="n">
-        <v>31732769.6</v>
+        <v>36317228</v>
       </c>
       <c r="BL21" t="inlineStr">
         <is>
-          <t>30190352.0</t>
+          <t>32350796.3</t>
         </is>
       </c>
       <c r="BM21" t="n">
-        <v>37849613.32</v>
+        <v>38135166.56</v>
       </c>
       <c r="BN21" t="inlineStr">
         <is>
-          <t>1542417</t>
+          <t>3966431</t>
         </is>
       </c>
       <c r="BO21" t="inlineStr">
         <is>
-          <t>-2432605.487737579</t>
+          <t>-2079560.521867446</t>
         </is>
       </c>
       <c r="BP21" t="inlineStr">
         <is>
-          <t>-996747.3510800153</t>
+          <t>-137813.2095817178</t>
         </is>
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>44656757.0</t>
+          <t>45290917.0</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -10531,7 +10531,7 @@
       </c>
       <c r="BU21" t="inlineStr">
         <is>
-          <t>-24.08</t>
+          <t>-23.29</t>
         </is>
       </c>
       <c r="BV21" t="inlineStr">
@@ -10576,7 +10576,7 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
@@ -10586,12 +10586,12 @@
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>6.39</t>
+          <t>6.41</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -10601,7 +10601,7 @@
       </c>
       <c r="CI21" t="inlineStr">
         <is>
-          <t>22.21</t>
+          <t>22.15</t>
         </is>
       </c>
       <c r="CJ21" t="inlineStr">
@@ -10616,12 +10616,12 @@
       </c>
       <c r="CL21" t="inlineStr">
         <is>
-          <t>55.22</t>
+          <t>56.04</t>
         </is>
       </c>
       <c r="CM21" t="inlineStr">
         <is>
-          <t>16678</t>
+          <t>16631</t>
         </is>
       </c>
       <c r="CN21" t="inlineStr">
@@ -10641,22 +10641,22 @@
       </c>
       <c r="CQ21" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>67.5</t>
         </is>
       </c>
       <c r="CR21" t="inlineStr">
         <is>
-          <t>68.4</t>
+          <t>68.5</t>
         </is>
       </c>
       <c r="CS21" t="inlineStr">
         <is>
-          <t>66.8</t>
+          <t>66.5</t>
         </is>
       </c>
       <c r="CT21" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>68.5</t>
         </is>
       </c>
       <c r="CU21" t="inlineStr">
@@ -10678,7 +10678,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>價_量;【b1】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -10688,12 +10688,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>4.44</t>
+          <t>-3.85</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>88763.068</t>
+          <t>89876.199</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -10703,7 +10703,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>64.7</t>
+          <t>62.2</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -10718,12 +10718,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>43.21</t>
+          <t>41.45</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -10733,7 +10733,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -10743,7 +10743,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>2026-01-13 00:00:00</t>
+          <t>2026-01-14 00:00:00</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -10783,7 +10783,7 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>-3.43</t>
+          <t>-7.16</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
@@ -10813,7 +10813,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -10863,87 +10863,87 @@
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>26.34</t>
+          <t>26.67</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>3.44</t>
+          <t>-4.18</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr"/>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>629</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>88763</t>
+          <t>89876</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
         <is>
-          <t>79.82</t>
+          <t>57.89</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>78.36</t>
+          <t>64.33</t>
         </is>
       </c>
       <c r="AU22" t="n">
-        <v>1.99</v>
+        <v>-2.96</v>
       </c>
       <c r="AV22" t="n">
-        <v>6.06</v>
+        <v>7.07</v>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>6.42</t>
+          <t>5.73</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>11.73</t>
+          <t>11.86</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>63.44</t>
+          <t>64.1</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>59.82</v>
+        <v>59.87</v>
       </c>
       <c r="BA22" t="n">
-        <v>56.21</v>
+        <v>56.62</v>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>50.31</t>
+          <t>50.62</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>26.54</t>
+          <t>16.96</t>
         </is>
       </c>
       <c r="BD22" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="BF22" t="inlineStr">
         <is>
@@ -10952,7 +10952,7 @@
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>-69.35</t>
+          <t>-67.99</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
@@ -10962,24 +10962,24 @@
       </c>
       <c r="BI22" t="inlineStr">
         <is>
-          <t>2291712942.699593</t>
+          <t>2304365558.54878</t>
         </is>
       </c>
       <c r="BJ22" t="inlineStr">
         <is>
-          <t>5656658024.0</t>
+          <t>5677866627.0</t>
         </is>
       </c>
       <c r="BK22" t="n">
-        <v>10584236598.2</v>
+        <v>10746815073.2</v>
       </c>
       <c r="BL22" t="inlineStr">
         <is>
-          <t>7390674180.3</t>
+          <t>7597601892.7</t>
         </is>
       </c>
       <c r="BM22" t="n">
-        <v>6810415500.54</v>
+        <v>6885227144.88</v>
       </c>
       <c r="BN22" t="inlineStr">
         <is>
@@ -10988,22 +10988,22 @@
       </c>
       <c r="BO22" t="inlineStr">
         <is>
-          <t>249193046.8320053</t>
+          <t>306359047.8425348</t>
         </is>
       </c>
       <c r="BP22" t="inlineStr">
         <is>
-          <t>942700615.7325144</t>
+          <t>620772053.4004469</t>
         </is>
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>5656658024.0</t>
+          <t>5677866627.0</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="BS22" t="inlineStr">
@@ -11018,7 +11018,7 @@
       </c>
       <c r="BU22" t="inlineStr">
         <is>
-          <t>54.42</t>
+          <t>48.45</t>
         </is>
       </c>
       <c r="BV22" t="inlineStr">
@@ -11063,7 +11063,7 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
@@ -11073,12 +11073,12 @@
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -11103,12 +11103,12 @@
       </c>
       <c r="CL22" t="inlineStr">
         <is>
-          <t>62.08</t>
+          <t>62.1</t>
         </is>
       </c>
       <c r="CM22" t="inlineStr">
         <is>
-          <t>513124</t>
+          <t>493297</t>
         </is>
       </c>
       <c r="CN22" t="inlineStr">
@@ -11128,22 +11128,22 @@
       </c>
       <c r="CQ22" t="inlineStr">
         <is>
-          <t>63.1</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="CR22" t="inlineStr">
         <is>
-          <t>65.4</t>
+          <t>65.2</t>
         </is>
       </c>
       <c r="CS22" t="inlineStr">
         <is>
-          <t>61.9</t>
+          <t>61.8</t>
         </is>
       </c>
       <c r="CT22" t="inlineStr">
         <is>
-          <t>64.7</t>
+          <t>62.2</t>
         </is>
       </c>
       <c r="CU22" t="inlineStr">
@@ -11175,12 +11175,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-7.45</t>
+          <t>4.44</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>182653.667</t>
+          <t>88763.068</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -11190,7 +11190,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>61.9</t>
+          <t>64.7</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -11200,17 +11200,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>-4.02</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>47.28</t>
+          <t>43.21</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -11220,7 +11220,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -11230,7 +11230,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>2026-01-13 00:00:00</t>
+          <t>2026-01-14 00:00:00</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -11270,7 +11270,7 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>-7.61</t>
+          <t>-3.43</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
@@ -11300,7 +11300,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -11350,17 +11350,17 @@
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>54.21</t>
+          <t>26.34</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>-12.44</t>
+          <t>3.44</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
@@ -11371,66 +11371,66 @@
       <c r="AP23" t="inlineStr"/>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>629</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>88763</t>
+          <t>89876</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
         <is>
-          <t>55.26</t>
+          <t>79.82</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>85.09</t>
+          <t>78.36</t>
         </is>
       </c>
       <c r="AU23" t="n">
-        <v>0.45</v>
+        <v>1.99</v>
       </c>
       <c r="AV23" t="n">
-        <v>3.43</v>
+        <v>6.06</v>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>6.85</t>
+          <t>6.42</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>11.57</t>
+          <t>11.73</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>61.62</t>
+          <t>63.44</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>59.58</v>
+        <v>59.82</v>
       </c>
       <c r="BA23" t="n">
-        <v>55.75</v>
+        <v>56.21</v>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>49.97</t>
+          <t>50.31</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>19.85</t>
+          <t>26.54</t>
         </is>
       </c>
       <c r="BD23" t="n">
-        <v>1.55</v>
+        <v>1.75</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="BF23" t="inlineStr">
         <is>
@@ -11439,7 +11439,7 @@
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>-71.38</t>
+          <t>-69.35</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
@@ -11449,24 +11449,24 @@
       </c>
       <c r="BI23" t="inlineStr">
         <is>
-          <t>2291712942.699593</t>
+          <t>2304365558.54878</t>
         </is>
       </c>
       <c r="BJ23" t="inlineStr">
         <is>
-          <t>11804253718.0</t>
+          <t>5656658024.0</t>
         </is>
       </c>
       <c r="BK23" t="n">
-        <v>10376727113</v>
+        <v>10584236598.2</v>
       </c>
       <c r="BL23" t="inlineStr">
         <is>
-          <t>7045506054.6</t>
+          <t>7390674180.3</t>
         </is>
       </c>
       <c r="BM23" t="n">
-        <v>6715236405.64</v>
+        <v>6810415500.54</v>
       </c>
       <c r="BN23" t="inlineStr">
         <is>
@@ -11475,22 +11475,22 @@
       </c>
       <c r="BO23" t="inlineStr">
         <is>
-          <t>123100761.5773672</t>
+          <t>249193046.8320053</t>
         </is>
       </c>
       <c r="BP23" t="inlineStr">
         <is>
-          <t>1371203033.109304</t>
+          <t>942700615.7325144</t>
         </is>
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>11804253718.0</t>
+          <t>5656658024.0</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="BS23" t="inlineStr">
@@ -11505,7 +11505,7 @@
       </c>
       <c r="BU23" t="inlineStr">
         <is>
-          <t>47.73</t>
+          <t>54.42</t>
         </is>
       </c>
       <c r="BV23" t="inlineStr">
@@ -11550,22 +11550,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">
@@ -11590,12 +11590,12 @@
       </c>
       <c r="CL23" t="inlineStr">
         <is>
-          <t>62.08</t>
+          <t>62.1</t>
         </is>
       </c>
       <c r="CM23" t="inlineStr">
         <is>
-          <t>513124</t>
+          <t>493297</t>
         </is>
       </c>
       <c r="CN23" t="inlineStr">
@@ -11615,22 +11615,22 @@
       </c>
       <c r="CQ23" t="inlineStr">
         <is>
-          <t>68.5</t>
+          <t>63.1</t>
         </is>
       </c>
       <c r="CR23" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>65.4</t>
         </is>
       </c>
       <c r="CS23" t="inlineStr">
         <is>
-          <t>61.5</t>
+          <t>61.9</t>
         </is>
       </c>
       <c r="CT23" t="inlineStr">
         <is>
-          <t>61.9</t>
+          <t>64.7</t>
         </is>
       </c>
       <c r="CU23" t="inlineStr">
@@ -11662,12 +11662,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>3.47</t>
+          <t>-7.45</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>258690.382</t>
+          <t>182653.667</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -11677,74 +11677,74 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
+          <t>61.9</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>0.48</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>47.28</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>2026-01-08</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>2026-01-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>2026-01-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>2025-11-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>2025-12-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
           <t>67.0</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>-3.55</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>3.02</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>48.91</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>2026-01-08</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>95.0</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>2026-01-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>2026-01-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>2025-11-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>2025-12-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q24" t="inlineStr">
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
         <is>
           <t>67.0</t>
         </is>
       </c>
-      <c r="R24" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
       <c r="T24" t="inlineStr">
         <is>
           <t>56.2</t>
@@ -11757,7 +11757,7 @@
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-7.61</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
@@ -11787,7 +11787,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -11837,17 +11837,17 @@
       </c>
       <c r="AL24" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>76.77</t>
+          <t>54.21</t>
         </is>
       </c>
       <c r="AN24" t="inlineStr">
         <is>
-          <t>-2.22</t>
+          <t>-12.44</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
@@ -11858,66 +11858,66 @@
       <c r="AP24" t="inlineStr"/>
       <c r="AQ24" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>629</t>
         </is>
       </c>
       <c r="AR24" t="inlineStr">
         <is>
-          <t>88763</t>
+          <t>89876</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>55.26</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr">
         <is>
-          <t>90.58</t>
+          <t>85.09</t>
         </is>
       </c>
       <c r="AU24" t="n">
-        <v>10.49</v>
+        <v>0.45</v>
       </c>
       <c r="AV24" t="n">
-        <v>1.83</v>
+        <v>3.43</v>
       </c>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>7.58</t>
+          <t>6.85</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>11.46</t>
+          <t>11.57</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
-          <t>60.64000000000001</t>
+          <t>61.62</t>
         </is>
       </c>
       <c r="AZ24" t="n">
-        <v>59.55</v>
+        <v>59.58</v>
       </c>
       <c r="BA24" t="n">
-        <v>55.36</v>
+        <v>55.75</v>
       </c>
       <c r="BB24" t="inlineStr">
         <is>
-          <t>49.67</t>
+          <t>49.97</t>
         </is>
       </c>
       <c r="BC24" t="inlineStr">
         <is>
-          <t>26.46</t>
+          <t>19.85</t>
         </is>
       </c>
       <c r="BD24" t="n">
         <v>1.55</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="BF24" t="inlineStr">
         <is>
@@ -11926,7 +11926,7 @@
       </c>
       <c r="BG24" t="inlineStr">
         <is>
-          <t>-72.80</t>
+          <t>-71.38</t>
         </is>
       </c>
       <c r="BH24" t="inlineStr">
@@ -11936,24 +11936,24 @@
       </c>
       <c r="BI24" t="inlineStr">
         <is>
-          <t>2291712942.699593</t>
+          <t>2304365558.54878</t>
         </is>
       </c>
       <c r="BJ24" t="inlineStr">
         <is>
-          <t>17488494279.0</t>
+          <t>11804253718.0</t>
         </is>
       </c>
       <c r="BK24" t="n">
-        <v>9186543148.799999</v>
+        <v>10376727113</v>
       </c>
       <c r="BL24" t="inlineStr">
         <is>
-          <t>6169134567.4</t>
+          <t>7045506054.6</t>
         </is>
       </c>
       <c r="BM24" t="n">
-        <v>6503604913.66</v>
+        <v>6715236405.64</v>
       </c>
       <c r="BN24" t="inlineStr">
         <is>
@@ -11962,22 +11962,22 @@
       </c>
       <c r="BO24" t="inlineStr">
         <is>
-          <t>-103826924.1557122</t>
+          <t>123100761.5773672</t>
         </is>
       </c>
       <c r="BP24" t="inlineStr">
         <is>
-          <t>1275706839.536532</t>
+          <t>1371203033.109304</t>
         </is>
       </c>
       <c r="BQ24" t="inlineStr">
         <is>
-          <t>17488494279.0</t>
+          <t>11804253718.0</t>
         </is>
       </c>
       <c r="BR24" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="BS24" t="inlineStr">
@@ -11992,7 +11992,7 @@
       </c>
       <c r="BU24" t="inlineStr">
         <is>
-          <t>59.90</t>
+          <t>47.73</t>
         </is>
       </c>
       <c r="BV24" t="inlineStr">
@@ -12037,22 +12037,22 @@
       </c>
       <c r="CD24" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE24" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="CF24" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="CG24" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="CH24" t="inlineStr">
@@ -12077,12 +12077,12 @@
       </c>
       <c r="CL24" t="inlineStr">
         <is>
-          <t>62.08</t>
+          <t>62.1</t>
         </is>
       </c>
       <c r="CM24" t="inlineStr">
         <is>
-          <t>513124</t>
+          <t>493297</t>
         </is>
       </c>
       <c r="CN24" t="inlineStr">
@@ -12102,22 +12102,22 @@
       </c>
       <c r="CQ24" t="inlineStr">
         <is>
-          <t>66.2</t>
+          <t>68.5</t>
         </is>
       </c>
       <c r="CR24" t="inlineStr">
         <is>
-          <t>69.5</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="CS24" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>61.5</t>
         </is>
       </c>
       <c r="CT24" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>61.9</t>
         </is>
       </c>
       <c r="CU24" t="inlineStr">
@@ -12139,7 +12139,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -12149,12 +12149,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>9.65</t>
+          <t>3.47</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>206471.229</t>
+          <t>258690.382</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -12164,7 +12164,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>64.7</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -12174,27 +12174,27 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-7.72</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>41.18</t>
+          <t>48.91</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -12204,7 +12204,7 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>2026-01-13 00:00:00</t>
+          <t>2026-01-14 00:00:00</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -12229,7 +12229,7 @@
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
@@ -12244,7 +12244,7 @@
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
@@ -12274,7 +12274,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -12324,33 +12324,33 @@
       </c>
       <c r="AL25" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>61.28</t>
+          <t>76.77</t>
         </is>
       </c>
       <c r="AN25" t="inlineStr">
         <is>
-          <t>7.83</t>
+          <t>-2.22</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AP25" t="inlineStr"/>
       <c r="AQ25" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>629</t>
         </is>
       </c>
       <c r="AR25" t="inlineStr">
         <is>
-          <t>88763</t>
+          <t>89876</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr">
@@ -12360,51 +12360,51 @@
       </c>
       <c r="AT25" t="inlineStr">
         <is>
-          <t>57.25</t>
+          <t>90.58</t>
         </is>
       </c>
       <c r="AU25" t="n">
-        <v>9.140000000000001</v>
+        <v>10.49</v>
       </c>
       <c r="AV25" t="n">
-        <v>-0.04</v>
+        <v>1.83</v>
       </c>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>7.58</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>11.26</t>
+          <t>11.46</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
-          <t>59.27999999999999</t>
+          <t>60.64000000000001</t>
         </is>
       </c>
       <c r="AZ25" t="n">
-        <v>59.31</v>
+        <v>59.55</v>
       </c>
       <c r="BA25" t="n">
-        <v>54.86</v>
+        <v>55.36</v>
       </c>
       <c r="BB25" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>49.67</t>
         </is>
       </c>
       <c r="BC25" t="inlineStr">
         <is>
-          <t>-11.42</t>
+          <t>26.46</t>
         </is>
       </c>
       <c r="BD25" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.14</v>
+        <v>1.23</v>
       </c>
       <c r="BF25" t="inlineStr">
         <is>
@@ -12413,7 +12413,7 @@
       </c>
       <c r="BG25" t="inlineStr">
         <is>
-          <t>-74.60</t>
+          <t>-72.80</t>
         </is>
       </c>
       <c r="BH25" t="inlineStr">
@@ -12423,48 +12423,48 @@
       </c>
       <c r="BI25" t="inlineStr">
         <is>
-          <t>2291712942.699593</t>
+          <t>2304365558.54878</t>
         </is>
       </c>
       <c r="BJ25" t="inlineStr">
         <is>
-          <t>13106802718.0</t>
+          <t>17488494279.0</t>
         </is>
       </c>
       <c r="BK25" t="n">
-        <v>6760564103.4</v>
+        <v>9186543148.799999</v>
       </c>
       <c r="BL25" t="inlineStr">
         <is>
-          <t>4788669988.6</t>
+          <t>6169134567.4</t>
         </is>
       </c>
       <c r="BM25" t="n">
-        <v>6193703510.44</v>
+        <v>6503604913.66</v>
       </c>
       <c r="BN25" t="inlineStr">
         <is>
-          <t>1971894114</t>
+          <t>-2147483648</t>
         </is>
       </c>
       <c r="BO25" t="inlineStr">
         <is>
-          <t>-354651244.8270295</t>
+          <t>-103826924.1557122</t>
         </is>
       </c>
       <c r="BP25" t="inlineStr">
         <is>
-          <t>484696972.9134083</t>
+          <t>1275706839.536532</t>
         </is>
       </c>
       <c r="BQ25" t="inlineStr">
         <is>
-          <t>13106802718.0</t>
+          <t>17488494279.0</t>
         </is>
       </c>
       <c r="BR25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="BS25" t="inlineStr">
@@ -12479,7 +12479,7 @@
       </c>
       <c r="BU25" t="inlineStr">
         <is>
-          <t>54.42</t>
+          <t>59.90</t>
         </is>
       </c>
       <c r="BV25" t="inlineStr">
@@ -12524,7 +12524,7 @@
       </c>
       <c r="CD25" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="CE25" t="inlineStr">
@@ -12534,12 +12534,12 @@
       </c>
       <c r="CF25" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="CG25" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="CH25" t="inlineStr">
@@ -12564,12 +12564,12 @@
       </c>
       <c r="CL25" t="inlineStr">
         <is>
-          <t>62.08</t>
+          <t>62.1</t>
         </is>
       </c>
       <c r="CM25" t="inlineStr">
         <is>
-          <t>513124</t>
+          <t>493297</t>
         </is>
       </c>
       <c r="CN25" t="inlineStr">
@@ -12589,22 +12589,22 @@
       </c>
       <c r="CQ25" t="inlineStr">
         <is>
-          <t>60.1</t>
+          <t>66.2</t>
         </is>
       </c>
       <c r="CR25" t="inlineStr">
         <is>
-          <t>64.7</t>
+          <t>69.5</t>
         </is>
       </c>
       <c r="CS25" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="CT25" t="inlineStr">
         <is>
-          <t>64.7</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="CU25" t="inlineStr">
@@ -12636,12 +12636,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>5.86</t>
+          <t>9.65</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>83828.18</t>
+          <t>206471.229</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -12651,7 +12651,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>58.9</t>
+          <t>64.7</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -12661,17 +12661,17 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>8.96</t>
+          <t>-4.02</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>13.99</t>
+          <t>41.18</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -12681,7 +12681,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -12691,7 +12691,7 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>2026-01-13 00:00:00</t>
+          <t>2026-01-14 00:00:00</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -12761,7 +12761,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -12811,17 +12811,17 @@
       </c>
       <c r="AL26" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>24.88</t>
+          <t>61.28</t>
         </is>
       </c>
       <c r="AN26" t="inlineStr">
         <is>
-          <t>3.77</t>
+          <t>7.83</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
@@ -12832,66 +12832,66 @@
       <c r="AP26" t="inlineStr"/>
       <c r="AQ26" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>629</t>
         </is>
       </c>
       <c r="AR26" t="inlineStr">
         <is>
-          <t>88763</t>
+          <t>89876</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr">
         <is>
-          <t>71.74</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr">
         <is>
-          <t>23.91</t>
+          <t>57.25</t>
         </is>
       </c>
       <c r="AU26" t="n">
-        <v>1.55</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="AV26" t="n">
-        <v>-2.09</v>
+        <v>-0.04</v>
       </c>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>8.85</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>11.12</t>
+          <t>11.26</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
-          <t>58.0</t>
+          <t>59.27999999999999</t>
         </is>
       </c>
       <c r="AZ26" t="n">
-        <v>59.24</v>
+        <v>59.31</v>
       </c>
       <c r="BA26" t="n">
-        <v>54.42</v>
+        <v>54.86</v>
       </c>
       <c r="BB26" t="inlineStr">
         <is>
-          <t>48.98</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="BC26" t="inlineStr">
         <is>
-          <t>-53.37</t>
+          <t>-11.42</t>
         </is>
       </c>
       <c r="BD26" t="n">
-        <v>0.55</v>
+        <v>1.01</v>
       </c>
       <c r="BE26" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="BF26" t="inlineStr">
         <is>
@@ -12900,7 +12900,7 @@
       </c>
       <c r="BG26" t="inlineStr">
         <is>
-          <t>-73.88</t>
+          <t>-74.60</t>
         </is>
       </c>
       <c r="BH26" t="inlineStr">
@@ -12910,43 +12910,43 @@
       </c>
       <c r="BI26" t="inlineStr">
         <is>
-          <t>2291712942.699593</t>
+          <t>2304365558.54878</t>
         </is>
       </c>
       <c r="BJ26" t="inlineStr">
         <is>
-          <t>4864974252.0</t>
+          <t>13106802718.0</t>
         </is>
       </c>
       <c r="BK26" t="n">
-        <v>4448388712.2</v>
+        <v>6760564103.4</v>
       </c>
       <c r="BL26" t="inlineStr">
         <is>
-          <t>3902292857.5</t>
+          <t>4788669988.6</t>
         </is>
       </c>
       <c r="BM26" t="n">
-        <v>5988755892.86</v>
+        <v>6193703510.44</v>
       </c>
       <c r="BN26" t="inlineStr">
         <is>
-          <t>546095854</t>
+          <t>1971894114</t>
         </is>
       </c>
       <c r="BO26" t="inlineStr">
         <is>
-          <t>-507260011.6889273</t>
+          <t>-354651244.8270295</t>
         </is>
       </c>
       <c r="BP26" t="inlineStr">
         <is>
-          <t>-193160775.4736757</t>
+          <t>484696972.9134083</t>
         </is>
       </c>
       <c r="BQ26" t="inlineStr">
         <is>
-          <t>4864974252.0</t>
+          <t>13106802718.0</t>
         </is>
       </c>
       <c r="BR26" t="inlineStr">
@@ -12966,7 +12966,7 @@
       </c>
       <c r="BU26" t="inlineStr">
         <is>
-          <t>40.57</t>
+          <t>54.42</t>
         </is>
       </c>
       <c r="BV26" t="inlineStr">
@@ -13011,22 +13011,22 @@
       </c>
       <c r="CD26" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE26" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="CF26" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="CG26" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="CH26" t="inlineStr">
@@ -13051,12 +13051,12 @@
       </c>
       <c r="CL26" t="inlineStr">
         <is>
-          <t>62.08</t>
+          <t>62.1</t>
         </is>
       </c>
       <c r="CM26" t="inlineStr">
         <is>
-          <t>513124</t>
+          <t>493297</t>
         </is>
       </c>
       <c r="CN26" t="inlineStr">
@@ -13076,22 +13076,22 @@
       </c>
       <c r="CQ26" t="inlineStr">
         <is>
-          <t>56.3</t>
+          <t>60.1</t>
         </is>
       </c>
       <c r="CR26" t="inlineStr">
         <is>
-          <t>59.4</t>
+          <t>64.7</t>
         </is>
       </c>
       <c r="CS26" t="inlineStr">
         <is>
-          <t>56.3</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="CT26" t="inlineStr">
         <is>
-          <t>58.9</t>
+          <t>64.7</t>
         </is>
       </c>
       <c r="CU26" t="inlineStr">
@@ -13123,12 +13123,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>-2.45</t>
+          <t>5.86</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>82573.213</t>
+          <t>83828.18</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -13138,7 +13138,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>55.6</t>
+          <t>58.9</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -13148,17 +13148,17 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>14.06</t>
+          <t>5.31</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>13.99</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -13168,7 +13168,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -13178,7 +13178,7 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>2026-01-13 00:00:00</t>
+          <t>2026-01-14 00:00:00</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -13248,7 +13248,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -13298,17 +13298,17 @@
       </c>
       <c r="AL27" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>24.51</t>
+          <t>24.88</t>
         </is>
       </c>
       <c r="AN27" t="inlineStr">
         <is>
-          <t>-2.69</t>
+          <t>3.77</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
@@ -13319,66 +13319,66 @@
       <c r="AP27" t="inlineStr"/>
       <c r="AQ27" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>629</t>
         </is>
       </c>
       <c r="AR27" t="inlineStr">
         <is>
-          <t>88763</t>
+          <t>89876</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>71.74</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr">
         <is>
-          <t>31.11</t>
+          <t>23.91</t>
         </is>
       </c>
       <c r="AU27" t="n">
-        <v>-4.07</v>
+        <v>1.55</v>
       </c>
       <c r="AV27" t="n">
-        <v>-2.53</v>
+        <v>-2.09</v>
       </c>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>9.89</t>
+          <t>8.85</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>11.07</t>
+          <t>11.12</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
-          <t>57.96</t>
+          <t>58.0</t>
         </is>
       </c>
       <c r="AZ27" t="n">
-        <v>59.46</v>
+        <v>59.24</v>
       </c>
       <c r="BA27" t="n">
-        <v>54.12</v>
+        <v>54.42</v>
       </c>
       <c r="BB27" t="inlineStr">
         <is>
-          <t>48.72</t>
+          <t>48.98</t>
         </is>
       </c>
       <c r="BC27" t="inlineStr">
         <is>
-          <t>-59.69</t>
+          <t>-53.37</t>
         </is>
       </c>
       <c r="BD27" t="n">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="BE27" t="n">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="BF27" t="inlineStr">
         <is>
@@ -13387,7 +13387,7 @@
       </c>
       <c r="BG27" t="inlineStr">
         <is>
-          <t>-70.39</t>
+          <t>-73.88</t>
         </is>
       </c>
       <c r="BH27" t="inlineStr">
@@ -13397,43 +13397,43 @@
       </c>
       <c r="BI27" t="inlineStr">
         <is>
-          <t>2291712942.699593</t>
+          <t>2304365558.54878</t>
         </is>
       </c>
       <c r="BJ27" t="inlineStr">
         <is>
-          <t>4619110598.0</t>
+          <t>4864974252.0</t>
         </is>
       </c>
       <c r="BK27" t="n">
-        <v>4197111762.4</v>
+        <v>4448388712.2</v>
       </c>
       <c r="BL27" t="inlineStr">
         <is>
-          <t>4175836369.4</t>
+          <t>3902292857.5</t>
         </is>
       </c>
       <c r="BM27" t="n">
-        <v>5968956549.88</v>
+        <v>5988755892.86</v>
       </c>
       <c r="BN27" t="inlineStr">
         <is>
-          <t>21275393</t>
+          <t>546095854</t>
         </is>
       </c>
       <c r="BO27" t="inlineStr">
         <is>
-          <t>-564368963.728064</t>
+          <t>-507260011.6889273</t>
         </is>
       </c>
       <c r="BP27" t="inlineStr">
         <is>
-          <t>-271577338.4025931</t>
+          <t>-193160775.4736757</t>
         </is>
       </c>
       <c r="BQ27" t="inlineStr">
         <is>
-          <t>4619110598.0</t>
+          <t>4864974252.0</t>
         </is>
       </c>
       <c r="BR27" t="inlineStr">
@@ -13453,7 +13453,7 @@
       </c>
       <c r="BU27" t="inlineStr">
         <is>
-          <t>32.70</t>
+          <t>40.57</t>
         </is>
       </c>
       <c r="BV27" t="inlineStr">
@@ -13498,22 +13498,22 @@
       </c>
       <c r="CD27" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE27" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="CF27" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="CG27" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="CH27" t="inlineStr">
@@ -13538,12 +13538,12 @@
       </c>
       <c r="CL27" t="inlineStr">
         <is>
-          <t>62.08</t>
+          <t>62.1</t>
         </is>
       </c>
       <c r="CM27" t="inlineStr">
         <is>
-          <t>513124</t>
+          <t>493297</t>
         </is>
       </c>
       <c r="CN27" t="inlineStr">
@@ -13563,22 +13563,22 @@
       </c>
       <c r="CQ27" t="inlineStr">
         <is>
-          <t>57.2</t>
+          <t>56.3</t>
         </is>
       </c>
       <c r="CR27" t="inlineStr">
         <is>
-          <t>57.6</t>
+          <t>59.4</t>
         </is>
       </c>
       <c r="CS27" t="inlineStr">
         <is>
-          <t>55.1</t>
+          <t>56.3</t>
         </is>
       </c>
       <c r="CT27" t="inlineStr">
         <is>
-          <t>55.6</t>
+          <t>58.9</t>
         </is>
       </c>
       <c r="CU27" t="inlineStr">
@@ -13610,12 +13610,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>-5.32</t>
+          <t>-2.45</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>101489.286</t>
+          <t>82573.213</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -13625,7 +13625,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>57.0</t>
+          <t>55.6</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -13635,17 +13635,17 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>10.61</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>-6.64</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -13655,7 +13655,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -13665,7 +13665,7 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>2026-01-13 00:00:00</t>
+          <t>2026-01-14 00:00:00</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
@@ -13735,7 +13735,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -13785,17 +13785,17 @@
       </c>
       <c r="AL28" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>30.12</t>
+          <t>24.51</t>
         </is>
       </c>
       <c r="AN28" t="inlineStr">
         <is>
-          <t>-5.61</t>
+          <t>-2.69</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
@@ -13806,12 +13806,12 @@
       <c r="AP28" t="inlineStr"/>
       <c r="AQ28" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>629</t>
         </is>
       </c>
       <c r="AR28" t="inlineStr">
         <is>
-          <t>88763</t>
+          <t>89876</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr">
@@ -13821,51 +13821,51 @@
       </c>
       <c r="AT28" t="inlineStr">
         <is>
-          <t>41.11</t>
+          <t>31.11</t>
         </is>
       </c>
       <c r="AU28" t="n">
-        <v>-2.3</v>
+        <v>-4.07</v>
       </c>
       <c r="AV28" t="n">
         <v>-2.53</v>
       </c>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>11.15</t>
+          <t>9.89</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>11.01</t>
+          <t>11.07</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
-          <t>58.34</t>
+          <t>57.96</t>
         </is>
       </c>
       <c r="AZ28" t="n">
-        <v>59.86</v>
+        <v>59.46</v>
       </c>
       <c r="BA28" t="n">
-        <v>53.85</v>
+        <v>54.12</v>
       </c>
       <c r="BB28" t="inlineStr">
         <is>
-          <t>48.51</t>
+          <t>48.72</t>
         </is>
       </c>
       <c r="BC28" t="inlineStr">
         <is>
-          <t>-44.45</t>
+          <t>-59.69</t>
         </is>
       </c>
       <c r="BD28" t="n">
-        <v>0.85</v>
+        <v>0.54</v>
       </c>
       <c r="BE28" t="n">
-        <v>1.53</v>
+        <v>1.33</v>
       </c>
       <c r="BF28" t="inlineStr">
         <is>
@@ -13874,7 +13874,7 @@
       </c>
       <c r="BG28" t="inlineStr">
         <is>
-          <t>-65.97</t>
+          <t>-70.39</t>
         </is>
       </c>
       <c r="BH28" t="inlineStr">
@@ -13884,43 +13884,43 @@
       </c>
       <c r="BI28" t="inlineStr">
         <is>
-          <t>2291712942.699593</t>
+          <t>2304365558.54878</t>
         </is>
       </c>
       <c r="BJ28" t="inlineStr">
         <is>
-          <t>5853333897.0</t>
+          <t>4619110598.0</t>
         </is>
       </c>
       <c r="BK28" t="n">
-        <v>3714284996.2</v>
+        <v>4197111762.4</v>
       </c>
       <c r="BL28" t="inlineStr">
         <is>
-          <t>3978274860.9</t>
+          <t>4175836369.4</t>
         </is>
       </c>
       <c r="BM28" t="n">
-        <v>5935432936.84</v>
+        <v>5968956549.88</v>
       </c>
       <c r="BN28" t="inlineStr">
         <is>
-          <t>-263989864</t>
+          <t>21275393</t>
         </is>
       </c>
       <c r="BO28" t="inlineStr">
         <is>
-          <t>-617603804.6963314</t>
+          <t>-564368963.728064</t>
         </is>
       </c>
       <c r="BP28" t="inlineStr">
         <is>
-          <t>-347559274.7152386</t>
+          <t>-271577338.4025931</t>
         </is>
       </c>
       <c r="BQ28" t="inlineStr">
         <is>
-          <t>5853333897.0</t>
+          <t>4619110598.0</t>
         </is>
       </c>
       <c r="BR28" t="inlineStr">
@@ -13940,7 +13940,7 @@
       </c>
       <c r="BU28" t="inlineStr">
         <is>
-          <t>36.04</t>
+          <t>32.70</t>
         </is>
       </c>
       <c r="BV28" t="inlineStr">
@@ -13985,22 +13985,22 @@
       </c>
       <c r="CD28" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE28" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF28" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="CG28" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="CH28" t="inlineStr">
@@ -14025,12 +14025,12 @@
       </c>
       <c r="CL28" t="inlineStr">
         <is>
-          <t>62.08</t>
+          <t>62.1</t>
         </is>
       </c>
       <c r="CM28" t="inlineStr">
         <is>
-          <t>513124</t>
+          <t>493297</t>
         </is>
       </c>
       <c r="CN28" t="inlineStr">
@@ -14050,22 +14050,22 @@
       </c>
       <c r="CQ28" t="inlineStr">
         <is>
-          <t>60.2</t>
+          <t>57.2</t>
         </is>
       </c>
       <c r="CR28" t="inlineStr">
         <is>
-          <t>60.2</t>
+          <t>57.6</t>
         </is>
       </c>
       <c r="CS28" t="inlineStr">
         <is>
-          <t>57.0</t>
+          <t>55.1</t>
         </is>
       </c>
       <c r="CT28" t="inlineStr">
         <is>
-          <t>57.0</t>
+          <t>55.6</t>
         </is>
       </c>
       <c r="CU28" t="inlineStr">
@@ -14097,12 +14097,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>-5.32</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>90915.325</t>
+          <t>101489.286</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -14112,7 +14112,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>60.2</t>
+          <t>57.0</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -14122,17 +14122,17 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>6.96</t>
+          <t>8.36</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>-15.89</t>
+          <t>-6.64</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -14142,7 +14142,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -14152,7 +14152,7 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>2026-01-13 00:00:00</t>
+          <t>2026-01-14 00:00:00</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
@@ -14222,7 +14222,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
@@ -14272,17 +14272,17 @@
       </c>
       <c r="AL29" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>26.98</t>
+          <t>30.12</t>
         </is>
       </c>
       <c r="AN29" t="inlineStr">
         <is>
-          <t>4.16</t>
+          <t>-5.61</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
@@ -14293,66 +14293,66 @@
       <c r="AP29" t="inlineStr"/>
       <c r="AQ29" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>629</t>
         </is>
       </c>
       <c r="AR29" t="inlineStr">
         <is>
-          <t>88763</t>
+          <t>89876</t>
         </is>
       </c>
       <c r="AS29" t="inlineStr">
         <is>
-          <t>93.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr">
         <is>
-          <t>55.56</t>
+          <t>41.11</t>
         </is>
       </c>
       <c r="AU29" t="n">
-        <v>2.8</v>
+        <v>-2.3</v>
       </c>
       <c r="AV29" t="n">
-        <v>-3.03</v>
+        <v>-2.53</v>
       </c>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>12.78</t>
+          <t>11.15</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>10.91</t>
+          <t>11.01</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
-          <t>58.56</t>
+          <t>58.34</t>
         </is>
       </c>
       <c r="AZ29" t="n">
-        <v>60.39</v>
+        <v>59.86</v>
       </c>
       <c r="BA29" t="n">
-        <v>53.55</v>
+        <v>53.85</v>
       </c>
       <c r="BB29" t="inlineStr">
         <is>
-          <t>48.28</t>
+          <t>48.51</t>
         </is>
       </c>
       <c r="BC29" t="inlineStr">
         <is>
-          <t>-35.58</t>
+          <t>-44.45</t>
         </is>
       </c>
       <c r="BD29" t="n">
-        <v>1.1</v>
+        <v>0.85</v>
       </c>
       <c r="BE29" t="n">
-        <v>1.7</v>
+        <v>1.53</v>
       </c>
       <c r="BF29" t="inlineStr">
         <is>
@@ -14361,7 +14361,7 @@
       </c>
       <c r="BG29" t="inlineStr">
         <is>
-          <t>-62.19</t>
+          <t>-65.97</t>
         </is>
       </c>
       <c r="BH29" t="inlineStr">
@@ -14371,43 +14371,43 @@
       </c>
       <c r="BI29" t="inlineStr">
         <is>
-          <t>2291712942.699593</t>
+          <t>2304365558.54878</t>
         </is>
       </c>
       <c r="BJ29" t="inlineStr">
         <is>
-          <t>5358599052.0</t>
+          <t>5853333897.0</t>
         </is>
       </c>
       <c r="BK29" t="n">
-        <v>3151725986</v>
+        <v>3714284996.2</v>
       </c>
       <c r="BL29" t="inlineStr">
         <is>
-          <t>3746963129.5</t>
+          <t>3978274860.9</t>
         </is>
       </c>
       <c r="BM29" t="n">
-        <v>5841022551.14</v>
+        <v>5935432936.84</v>
       </c>
       <c r="BN29" t="inlineStr">
         <is>
-          <t>-595237143</t>
+          <t>-263989864</t>
         </is>
       </c>
       <c r="BO29" t="inlineStr">
         <is>
-          <t>-666702810.1474391</t>
+          <t>-617603804.6963314</t>
         </is>
       </c>
       <c r="BP29" t="inlineStr">
         <is>
-          <t>-575930277.3863311</t>
+          <t>-347559274.7152386</t>
         </is>
       </c>
       <c r="BQ29" t="inlineStr">
         <is>
-          <t>5358599052.0</t>
+          <t>5853333897.0</t>
         </is>
       </c>
       <c r="BR29" t="inlineStr">
@@ -14427,7 +14427,7 @@
       </c>
       <c r="BU29" t="inlineStr">
         <is>
-          <t>43.68</t>
+          <t>36.04</t>
         </is>
       </c>
       <c r="BV29" t="inlineStr">
@@ -14472,22 +14472,22 @@
       </c>
       <c r="CD29" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE29" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF29" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="CG29" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="CH29" t="inlineStr">
@@ -14512,12 +14512,12 @@
       </c>
       <c r="CL29" t="inlineStr">
         <is>
-          <t>62.08</t>
+          <t>62.1</t>
         </is>
       </c>
       <c r="CM29" t="inlineStr">
         <is>
-          <t>513124</t>
+          <t>493297</t>
         </is>
       </c>
       <c r="CN29" t="inlineStr">
@@ -14537,22 +14537,22 @@
       </c>
       <c r="CQ29" t="inlineStr">
         <is>
-          <t>58.4</t>
+          <t>60.2</t>
         </is>
       </c>
       <c r="CR29" t="inlineStr">
         <is>
-          <t>61.3</t>
+          <t>60.2</t>
         </is>
       </c>
       <c r="CS29" t="inlineStr">
         <is>
-          <t>56.8</t>
+          <t>57.0</t>
         </is>
       </c>
       <c r="CT29" t="inlineStr">
         <is>
-          <t>60.2</t>
+          <t>57.0</t>
         </is>
       </c>
       <c r="CU29" t="inlineStr">
@@ -14584,12 +14584,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>26487.92</t>
+          <t>90915.325</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -14599,7 +14599,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>58.3</t>
+          <t>60.2</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -14609,17 +14609,17 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>9.89</t>
+          <t>3.22</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>-19.23</t>
+          <t>-15.89</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -14629,7 +14629,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -14639,7 +14639,7 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>2026-01-13 00:00:00</t>
+          <t>2026-01-14 00:00:00</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
@@ -14709,7 +14709,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
@@ -14759,17 +14759,17 @@
       </c>
       <c r="AL30" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>7.86</t>
+          <t>26.98</t>
         </is>
       </c>
       <c r="AN30" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>4.16</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
@@ -14780,66 +14780,66 @@
       <c r="AP30" t="inlineStr"/>
       <c r="AQ30" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>629</t>
         </is>
       </c>
       <c r="AR30" t="inlineStr">
         <is>
-          <t>88763</t>
+          <t>89876</t>
         </is>
       </c>
       <c r="AS30" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>93.33</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr">
         <is>
-          <t>25.52</t>
+          <t>55.56</t>
         </is>
       </c>
       <c r="AU30" t="n">
-        <v>0.03</v>
+        <v>2.8</v>
       </c>
       <c r="AV30" t="n">
-        <v>-3.83</v>
+        <v>-3.03</v>
       </c>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>13.94</t>
+          <t>12.78</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>10.75</t>
+          <t>10.91</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
-          <t>58.27999999999999</t>
+          <t>58.56</t>
         </is>
       </c>
       <c r="AZ30" t="n">
-        <v>60.6</v>
+        <v>60.39</v>
       </c>
       <c r="BA30" t="n">
-        <v>53.18</v>
+        <v>53.55</v>
       </c>
       <c r="BB30" t="inlineStr">
         <is>
-          <t>48.02</t>
+          <t>48.28</t>
         </is>
       </c>
       <c r="BC30" t="inlineStr">
         <is>
-          <t>-42.35</t>
+          <t>-35.58</t>
         </is>
       </c>
       <c r="BD30" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="BE30" t="n">
-        <v>1.86</v>
+        <v>1.7</v>
       </c>
       <c r="BF30" t="inlineStr">
         <is>
@@ -14848,7 +14848,7 @@
       </c>
       <c r="BG30" t="inlineStr">
         <is>
-          <t>-58.82</t>
+          <t>-62.19</t>
         </is>
       </c>
       <c r="BH30" t="inlineStr">
@@ -14858,43 +14858,43 @@
       </c>
       <c r="BI30" t="inlineStr">
         <is>
-          <t>2291712942.699593</t>
+          <t>2304365558.54878</t>
         </is>
       </c>
       <c r="BJ30" t="inlineStr">
         <is>
-          <t>1545925762.0</t>
+          <t>5358599052.0</t>
         </is>
       </c>
       <c r="BK30" t="n">
-        <v>2816775873.8</v>
+        <v>3151725986</v>
       </c>
       <c r="BL30" t="inlineStr">
         <is>
-          <t>3487467287.4</t>
+          <t>3746963129.5</t>
         </is>
       </c>
       <c r="BM30" t="n">
-        <v>5761704538.5</v>
+        <v>5841022551.14</v>
       </c>
       <c r="BN30" t="inlineStr">
         <is>
-          <t>-670691413</t>
+          <t>-595237143</t>
         </is>
       </c>
       <c r="BO30" t="inlineStr">
         <is>
-          <t>-683206907.0130951</t>
+          <t>-666702810.1474391</t>
         </is>
       </c>
       <c r="BP30" t="inlineStr">
         <is>
-          <t>-828598323.6169515</t>
+          <t>-575930277.3863311</t>
         </is>
       </c>
       <c r="BQ30" t="inlineStr">
         <is>
-          <t>1545925762.0</t>
+          <t>5358599052.0</t>
         </is>
       </c>
       <c r="BR30" t="inlineStr">
@@ -14914,7 +14914,7 @@
       </c>
       <c r="BU30" t="inlineStr">
         <is>
-          <t>39.14</t>
+          <t>43.68</t>
         </is>
       </c>
       <c r="BV30" t="inlineStr">
@@ -14959,7 +14959,7 @@
       </c>
       <c r="CD30" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE30" t="inlineStr">
@@ -14969,12 +14969,12 @@
       </c>
       <c r="CF30" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="CG30" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="CH30" t="inlineStr">
@@ -14999,12 +14999,12 @@
       </c>
       <c r="CL30" t="inlineStr">
         <is>
-          <t>62.08</t>
+          <t>62.1</t>
         </is>
       </c>
       <c r="CM30" t="inlineStr">
         <is>
-          <t>513124</t>
+          <t>493297</t>
         </is>
       </c>
       <c r="CN30" t="inlineStr">
@@ -15024,22 +15024,22 @@
       </c>
       <c r="CQ30" t="inlineStr">
         <is>
-          <t>58.7</t>
+          <t>58.4</t>
         </is>
       </c>
       <c r="CR30" t="inlineStr">
         <is>
-          <t>59.0</t>
+          <t>61.3</t>
         </is>
       </c>
       <c r="CS30" t="inlineStr">
         <is>
-          <t>58.0</t>
+          <t>56.8</t>
         </is>
       </c>
       <c r="CT30" t="inlineStr">
         <is>
-          <t>58.3</t>
+          <t>60.2</t>
         </is>
       </c>
       <c r="CU30" t="inlineStr">
@@ -15071,12 +15071,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>60874.354</t>
+          <t>26487.92</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -15086,7 +15086,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>58.7</t>
+          <t>58.3</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -15096,17 +15096,17 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>9.27</t>
+          <t>6.27</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>-4.90</t>
+          <t>-19.23</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -15116,7 +15116,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -15126,7 +15126,7 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>2026-01-13 00:00:00</t>
+          <t>2026-01-14 00:00:00</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
@@ -15196,7 +15196,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
@@ -15246,17 +15246,17 @@
       </c>
       <c r="AL31" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>18.07</t>
+          <t>7.86</t>
         </is>
       </c>
       <c r="AN31" t="inlineStr">
         <is>
-          <t>-1.69</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
@@ -15267,266 +15267,266 @@
       <c r="AP31" t="inlineStr"/>
       <c r="AQ31" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>629</t>
         </is>
       </c>
       <c r="AR31" t="inlineStr">
         <is>
-          <t>88763</t>
+          <t>89876</t>
         </is>
       </c>
       <c r="AS31" t="inlineStr">
         <is>
-          <t>43.33</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr">
         <is>
-          <t>21.83</t>
+          <t>25.52</t>
         </is>
       </c>
       <c r="AU31" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="AV31" t="n">
-        <v>-3.36</v>
+        <v>-3.83</v>
       </c>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>14.91</t>
+          <t>13.94</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>10.60</t>
+          <t>10.75</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
+          <t>58.27999999999999</t>
+        </is>
+      </c>
+      <c r="AZ31" t="n">
+        <v>60.6</v>
+      </c>
+      <c r="BA31" t="n">
+        <v>53.18</v>
+      </c>
+      <c r="BB31" t="inlineStr">
+        <is>
+          <t>48.02</t>
+        </is>
+      </c>
+      <c r="BC31" t="inlineStr">
+        <is>
+          <t>-42.35</t>
+        </is>
+      </c>
+      <c r="BD31" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="BE31" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="BF31" t="inlineStr">
+        <is>
+          <t>4.51</t>
+        </is>
+      </c>
+      <c r="BG31" t="inlineStr">
+        <is>
+          <t>-58.82</t>
+        </is>
+      </c>
+      <c r="BH31" t="inlineStr">
+        <is>
+          <t>2026/01/08</t>
+        </is>
+      </c>
+      <c r="BI31" t="inlineStr">
+        <is>
+          <t>2304365558.54878</t>
+        </is>
+      </c>
+      <c r="BJ31" t="inlineStr">
+        <is>
+          <t>1545925762.0</t>
+        </is>
+      </c>
+      <c r="BK31" t="n">
+        <v>2816775873.8</v>
+      </c>
+      <c r="BL31" t="inlineStr">
+        <is>
+          <t>3487467287.4</t>
+        </is>
+      </c>
+      <c r="BM31" t="n">
+        <v>5761704538.5</v>
+      </c>
+      <c r="BN31" t="inlineStr">
+        <is>
+          <t>-670691413</t>
+        </is>
+      </c>
+      <c r="BO31" t="inlineStr">
+        <is>
+          <t>-683206907.0130951</t>
+        </is>
+      </c>
+      <c r="BP31" t="inlineStr">
+        <is>
+          <t>-828598323.6169515</t>
+        </is>
+      </c>
+      <c r="BQ31" t="inlineStr">
+        <is>
+          <t>1545925762.0</t>
+        </is>
+      </c>
+      <c r="BR31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BS31" t="inlineStr">
+        <is>
+          <t>41.9</t>
+        </is>
+      </c>
+      <c r="BT31" t="inlineStr">
+        <is>
+          <t>2025/10/21</t>
+        </is>
+      </c>
+      <c r="BU31" t="inlineStr">
+        <is>
+          <t>39.14</t>
+        </is>
+      </c>
+      <c r="BV31" t="inlineStr">
+        <is>
+          <t>南亞</t>
+        </is>
+      </c>
+      <c r="BW31" t="inlineStr">
+        <is>
+          <t>南亞</t>
+        </is>
+      </c>
+      <c r="BX31" t="inlineStr">
+        <is>
+          <t>塑膠工業</t>
+        </is>
+      </c>
+      <c r="BY31" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BZ31" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="CA31" t="inlineStr">
+        <is>
+          <t>-0.4646396463764443</t>
+        </is>
+      </c>
+      <c r="CB31" t="inlineStr">
+        <is>
+          <t>-3.800318800328133</t>
+        </is>
+      </c>
+      <c r="CC31" t="inlineStr">
+        <is>
+          <t>0.6866519744403886</t>
+        </is>
+      </c>
+      <c r="CD31" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="CE31" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="CF31" t="inlineStr">
+        <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="CG31" t="inlineStr">
+        <is>
+          <t>1.13</t>
+        </is>
+      </c>
+      <c r="CH31" t="inlineStr">
+        <is>
+          <t>8.09</t>
+        </is>
+      </c>
+      <c r="CI31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CJ31" t="inlineStr">
+        <is>
+          <t>8.29%</t>
+        </is>
+      </c>
+      <c r="CK31" t="inlineStr">
+        <is>
+          <t>1.61%</t>
+        </is>
+      </c>
+      <c r="CL31" t="inlineStr">
+        <is>
+          <t>62.1</t>
+        </is>
+      </c>
+      <c r="CM31" t="inlineStr">
+        <is>
+          <t>493297</t>
+        </is>
+      </c>
+      <c r="CN31" t="inlineStr">
+        <is>
+          <t>聚酯纖維16.60%、其他16.28%、印刷電路板(PCB)12.09%、銅箔基板(CCL)10.47%、環氧樹脂8.29%、丙二酚(BPA)5.67%、乙二醇(EG)5.60%、銅箔5.01%、可塑劑(DOP)及硬化劑3.38%、硬質管2.55%、硬質膠布2.48%、塑膠門窗2.20%、軟質膠布1.85%、麩酸酐(PA)1.55%、玻璃纖維布1.32%、聚酯薄膜1.30%、膠乳皮0.92%、PU合成皮(人造皮)0.69%、BOPP膜0.64%、玻璃纖維絲0.60%、丁二醇(BDO)0.54% (2024年)</t>
+        </is>
+      </c>
+      <c r="CO31" t="inlineStr">
+        <is>
+          <t>南亞-塑膠工業-上市</t>
+        </is>
+      </c>
+      <c r="CP31" t="inlineStr">
+        <is>
+          <t>塑膠工業右上上市</t>
+        </is>
+      </c>
+      <c r="CQ31" t="inlineStr">
+        <is>
           <t>58.7</t>
         </is>
       </c>
-      <c r="AZ31" t="n">
-        <v>60.74</v>
-      </c>
-      <c r="BA31" t="n">
-        <v>52.86</v>
-      </c>
-      <c r="BB31" t="inlineStr">
-        <is>
-          <t>47.79</t>
-        </is>
-      </c>
-      <c r="BC31" t="inlineStr">
-        <is>
-          <t>-40.94</t>
-        </is>
-      </c>
-      <c r="BD31" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="BE31" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="BF31" t="inlineStr">
-        <is>
-          <t>4.51</t>
-        </is>
-      </c>
-      <c r="BG31" t="inlineStr">
-        <is>
-          <t>-54.47</t>
-        </is>
-      </c>
-      <c r="BH31" t="inlineStr">
-        <is>
-          <t>2026/01/08</t>
-        </is>
-      </c>
-      <c r="BI31" t="inlineStr">
-        <is>
-          <t>2291712942.699593</t>
-        </is>
-      </c>
-      <c r="BJ31" t="inlineStr">
-        <is>
-          <t>3608589503.0</t>
-        </is>
-      </c>
-      <c r="BK31" t="n">
-        <v>3356197002.8</v>
-      </c>
-      <c r="BL31" t="inlineStr">
-        <is>
-          <t>3528975051.7</t>
-        </is>
-      </c>
-      <c r="BM31" t="n">
-        <v>5761226342.04</v>
-      </c>
-      <c r="BN31" t="inlineStr">
-        <is>
-          <t>-172778048</t>
-        </is>
-      </c>
-      <c r="BO31" t="inlineStr">
-        <is>
-          <t>-656772103.9942122</t>
-        </is>
-      </c>
-      <c r="BP31" t="inlineStr">
-        <is>
-          <t>-751459168.4600897</t>
-        </is>
-      </c>
-      <c r="BQ31" t="inlineStr">
-        <is>
-          <t>3608589503.0</t>
-        </is>
-      </c>
-      <c r="BR31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BS31" t="inlineStr">
-        <is>
-          <t>41.9</t>
-        </is>
-      </c>
-      <c r="BT31" t="inlineStr">
-        <is>
-          <t>2025/10/21</t>
-        </is>
-      </c>
-      <c r="BU31" t="inlineStr">
-        <is>
-          <t>40.10</t>
-        </is>
-      </c>
-      <c r="BV31" t="inlineStr">
-        <is>
-          <t>南亞</t>
-        </is>
-      </c>
-      <c r="BW31" t="inlineStr">
-        <is>
-          <t>南亞</t>
-        </is>
-      </c>
-      <c r="BX31" t="inlineStr">
-        <is>
-          <t>塑膠工業</t>
-        </is>
-      </c>
-      <c r="BY31" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BZ31" t="inlineStr">
-        <is>
-          <t>0.9</t>
-        </is>
-      </c>
-      <c r="CA31" t="inlineStr">
-        <is>
-          <t>-0.4646396463764443</t>
-        </is>
-      </c>
-      <c r="CB31" t="inlineStr">
-        <is>
-          <t>-3.800318800328133</t>
-        </is>
-      </c>
-      <c r="CC31" t="inlineStr">
-        <is>
-          <t>0.6866519744403886</t>
-        </is>
-      </c>
-      <c r="CD31" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="CE31" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="CF31" t="inlineStr">
-        <is>
-          <t>1.42</t>
-        </is>
-      </c>
-      <c r="CG31" t="inlineStr">
-        <is>
-          <t>1.08</t>
-        </is>
-      </c>
-      <c r="CH31" t="inlineStr">
-        <is>
-          <t>8.09</t>
-        </is>
-      </c>
-      <c r="CI31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CJ31" t="inlineStr">
-        <is>
-          <t>8.29%</t>
-        </is>
-      </c>
-      <c r="CK31" t="inlineStr">
-        <is>
-          <t>1.61%</t>
-        </is>
-      </c>
-      <c r="CL31" t="inlineStr">
-        <is>
-          <t>62.08</t>
-        </is>
-      </c>
-      <c r="CM31" t="inlineStr">
-        <is>
-          <t>513124</t>
-        </is>
-      </c>
-      <c r="CN31" t="inlineStr">
-        <is>
-          <t>聚酯纖維16.60%、其他16.28%、印刷電路板(PCB)12.09%、銅箔基板(CCL)10.47%、環氧樹脂8.29%、丙二酚(BPA)5.67%、乙二醇(EG)5.60%、銅箔5.01%、可塑劑(DOP)及硬化劑3.38%、硬質管2.55%、硬質膠布2.48%、塑膠門窗2.20%、軟質膠布1.85%、麩酸酐(PA)1.55%、玻璃纖維布1.32%、聚酯薄膜1.30%、膠乳皮0.92%、PU合成皮(人造皮)0.69%、BOPP膜0.64%、玻璃纖維絲0.60%、丁二醇(BDO)0.54% (2024年)</t>
-        </is>
-      </c>
-      <c r="CO31" t="inlineStr">
-        <is>
-          <t>南亞-塑膠工業-上市</t>
-        </is>
-      </c>
-      <c r="CP31" t="inlineStr">
-        <is>
-          <t>塑膠工業右上上市</t>
-        </is>
-      </c>
-      <c r="CQ31" t="inlineStr">
-        <is>
-          <t>58.2</t>
-        </is>
-      </c>
       <c r="CR31" t="inlineStr">
         <is>
-          <t>60.3</t>
+          <t>59.0</t>
         </is>
       </c>
       <c r="CS31" t="inlineStr">
         <is>
-          <t>58.1</t>
+          <t>58.0</t>
         </is>
       </c>
       <c r="CT31" t="inlineStr">
         <is>
-          <t>58.7</t>
+          <t>58.3</t>
         </is>
       </c>
       <c r="CU31" t="inlineStr">

--- a/Result/checksun_type/石化上游原料及相關鑽探設備.xlsx
+++ b/Result/checksun_type/石化上游原料及相關鑽探設備.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CX34"/>
+  <dimension ref="A1:CY33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -939,6 +939,11 @@
           <t>盤整震盪_前15日次數</t>
         </is>
       </c>
+      <c r="CY1" s="1" t="inlineStr">
+        <is>
+          <t>多頭排列_前5日次數</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -978,12 +983,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -998,7 +1003,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -1008,7 +1013,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2026-02-04 00:00:00</t>
+          <t>2026-02-05 00:00:00</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -1123,7 +1128,7 @@
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>2026-01-26 00:00:00</t>
+          <t>2026-01-27 00:00:00</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
@@ -1149,12 +1154,12 @@
       <c r="AP2" t="inlineStr"/>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>64</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>9081</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1227,7 +1232,7 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>519314816.3905326</t>
+          <t>523657208.8559999</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
@@ -1253,12 +1258,12 @@
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>71049833.53916088</t>
+          <t>71049833.53915913</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>57377992.83427048</t>
+          <t>57377992.83427024</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
@@ -1268,7 +1273,7 @@
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
@@ -1343,7 +1348,7 @@
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1353,7 +1358,7 @@
       </c>
       <c r="CI2" t="inlineStr">
         <is>
-          <t>76.17</t>
+          <t>77.81</t>
         </is>
       </c>
       <c r="CJ2" t="inlineStr">
@@ -1368,12 +1373,12 @@
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>27.12</t>
+          <t>27.38</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
         <is>
-          <t>464391</t>
+          <t>474393</t>
         </is>
       </c>
       <c r="CN2" t="inlineStr">
@@ -1388,7 +1393,7 @@
       </c>
       <c r="CP2" t="inlineStr">
         <is>
-          <t>油電燃氣業平上市</t>
+          <t>油電燃氣業右上上市</t>
         </is>
       </c>
       <c r="CQ2" t="inlineStr">
@@ -1428,7 +1433,12 @@
       </c>
       <c r="CX2" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="CY2" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -1470,12 +1480,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -1490,7 +1500,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1500,7 +1510,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2026-02-04 00:00:00</t>
+          <t>2026-02-05 00:00:00</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1615,7 +1625,7 @@
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>2026-01-26 00:00:00</t>
+          <t>2026-01-27 00:00:00</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
@@ -1641,12 +1651,12 @@
       <c r="AP3" t="inlineStr"/>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>64</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>9081</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1719,7 +1729,7 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>519314816.3905326</t>
+          <t>523657208.8559999</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
@@ -1745,12 +1755,12 @@
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>73535622.75823185</t>
+          <t>73535622.75822984</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>93480846.44011259</t>
+          <t>93480846.44011223</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
@@ -1760,7 +1770,7 @@
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
@@ -1835,7 +1845,7 @@
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1845,7 +1855,7 @@
       </c>
       <c r="CI3" t="inlineStr">
         <is>
-          <t>76.17</t>
+          <t>77.81</t>
         </is>
       </c>
       <c r="CJ3" t="inlineStr">
@@ -1860,12 +1870,12 @@
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>27.12</t>
+          <t>27.38</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
         <is>
-          <t>464391</t>
+          <t>474393</t>
         </is>
       </c>
       <c r="CN3" t="inlineStr">
@@ -1880,7 +1890,7 @@
       </c>
       <c r="CP3" t="inlineStr">
         <is>
-          <t>油電燃氣業平上市</t>
+          <t>油電燃氣業右上上市</t>
         </is>
       </c>
       <c r="CQ3" t="inlineStr">
@@ -1920,7 +1930,12 @@
       </c>
       <c r="CX3" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="CY3" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -1962,12 +1977,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-9.54</t>
+          <t>-7.23</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1982,7 +1997,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1992,7 +2007,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2026-02-04 00:00:00</t>
+          <t>2026-02-05 00:00:00</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -2107,7 +2122,7 @@
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>2026-01-26 00:00:00</t>
+          <t>2026-01-27 00:00:00</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
@@ -2133,12 +2148,12 @@
       <c r="AP4" t="inlineStr"/>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>64</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>9081</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -2211,7 +2226,7 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>519314816.3905326</t>
+          <t>523657208.8559999</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
@@ -2237,12 +2252,12 @@
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>69909218.45243534</t>
+          <t>69909218.45243303</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>112247222.7184541</t>
+          <t>112247222.7184538</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
@@ -2252,7 +2267,7 @@
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
@@ -2327,7 +2342,7 @@
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2337,7 +2352,7 @@
       </c>
       <c r="CI4" t="inlineStr">
         <is>
-          <t>76.17</t>
+          <t>77.81</t>
         </is>
       </c>
       <c r="CJ4" t="inlineStr">
@@ -2352,12 +2367,12 @@
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>27.12</t>
+          <t>27.38</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
         <is>
-          <t>464391</t>
+          <t>474393</t>
         </is>
       </c>
       <c r="CN4" t="inlineStr">
@@ -2372,7 +2387,7 @@
       </c>
       <c r="CP4" t="inlineStr">
         <is>
-          <t>油電燃氣業平上市</t>
+          <t>油電燃氣業右上上市</t>
         </is>
       </c>
       <c r="CQ4" t="inlineStr">
@@ -2412,7 +2427,12 @@
       </c>
       <c r="CX4" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="CY4" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -2454,12 +2474,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-7.49</t>
+          <t>-5.22</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -2474,7 +2494,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2484,7 +2504,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2026-02-04 00:00:00</t>
+          <t>2026-02-05 00:00:00</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -2599,7 +2619,7 @@
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>2026-01-26 00:00:00</t>
+          <t>2026-01-27 00:00:00</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
@@ -2625,12 +2645,12 @@
       <c r="AP5" t="inlineStr"/>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>64</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>9081</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2677,7 +2697,7 @@
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>3357.21</t>
+          <t>3357.22</t>
         </is>
       </c>
       <c r="BD5" t="n">
@@ -2703,7 +2723,7 @@
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>519314816.3905326</t>
+          <t>523657208.8559999</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
@@ -2729,12 +2749,12 @@
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>62211399.49497739</t>
+          <t>62211399.49497472</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>100908756.1975689</t>
+          <t>100908756.1975684</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
@@ -2819,7 +2839,7 @@
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2829,7 +2849,7 @@
       </c>
       <c r="CI5" t="inlineStr">
         <is>
-          <t>76.17</t>
+          <t>77.81</t>
         </is>
       </c>
       <c r="CJ5" t="inlineStr">
@@ -2844,12 +2864,12 @@
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>27.12</t>
+          <t>27.38</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
         <is>
-          <t>464391</t>
+          <t>474393</t>
         </is>
       </c>
       <c r="CN5" t="inlineStr">
@@ -2864,7 +2884,7 @@
       </c>
       <c r="CP5" t="inlineStr">
         <is>
-          <t>油電燃氣業平上市</t>
+          <t>油電燃氣業右上上市</t>
         </is>
       </c>
       <c r="CQ5" t="inlineStr">
@@ -2904,7 +2924,12 @@
       </c>
       <c r="CX5" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="CY5" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -2946,12 +2971,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-8.1</t>
+          <t>-5.82</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -2966,7 +2991,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2976,7 +3001,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2026-02-04 00:00:00</t>
+          <t>2026-02-05 00:00:00</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -3091,7 +3116,7 @@
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>2026-01-26 00:00:00</t>
+          <t>2026-01-27 00:00:00</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
@@ -3117,12 +3142,12 @@
       <c r="AP6" t="inlineStr"/>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>64</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>9081</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -3132,7 +3157,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>96.87</t>
+          <t>96.88</t>
         </is>
       </c>
       <c r="AU6" t="n">
@@ -3195,7 +3220,7 @@
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>519314816.3905326</t>
+          <t>523657208.8559999</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
@@ -3221,12 +3246,12 @@
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>55175516.45814257</t>
+          <t>55175516.45813949</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>110208399.446391</t>
+          <t>110208399.4463904</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
@@ -3311,7 +3336,7 @@
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3321,7 +3346,7 @@
       </c>
       <c r="CI6" t="inlineStr">
         <is>
-          <t>76.17</t>
+          <t>77.81</t>
         </is>
       </c>
       <c r="CJ6" t="inlineStr">
@@ -3336,12 +3361,12 @@
       </c>
       <c r="CL6" t="inlineStr">
         <is>
-          <t>27.12</t>
+          <t>27.38</t>
         </is>
       </c>
       <c r="CM6" t="inlineStr">
         <is>
-          <t>464391</t>
+          <t>474393</t>
         </is>
       </c>
       <c r="CN6" t="inlineStr">
@@ -3356,7 +3381,7 @@
       </c>
       <c r="CP6" t="inlineStr">
         <is>
-          <t>油電燃氣業平上市</t>
+          <t>油電燃氣業右上上市</t>
         </is>
       </c>
       <c r="CQ6" t="inlineStr">
@@ -3396,7 +3421,12 @@
       </c>
       <c r="CX6" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="CY6" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -3438,12 +3468,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-5.85</t>
+          <t>-3.61</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -3458,7 +3488,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3468,7 +3498,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2026-02-04 00:00:00</t>
+          <t>2026-02-05 00:00:00</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -3583,7 +3613,7 @@
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>2026-01-26 00:00:00</t>
+          <t>2026-01-27 00:00:00</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
@@ -3609,12 +3639,12 @@
       <c r="AP7" t="inlineStr"/>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>64</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>9081</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3687,7 +3717,7 @@
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>519314816.3905326</t>
+          <t>523657208.8559999</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
@@ -3713,12 +3743,12 @@
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>45169537.73300649</t>
+          <t>45169537.73300298</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>125961421.321623</t>
+          <t>125961421.3216223</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
@@ -3803,7 +3833,7 @@
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3813,7 +3843,7 @@
       </c>
       <c r="CI7" t="inlineStr">
         <is>
-          <t>76.17</t>
+          <t>77.81</t>
         </is>
       </c>
       <c r="CJ7" t="inlineStr">
@@ -3828,12 +3858,12 @@
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>27.12</t>
+          <t>27.38</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
         <is>
-          <t>464391</t>
+          <t>474393</t>
         </is>
       </c>
       <c r="CN7" t="inlineStr">
@@ -3848,7 +3878,7 @@
       </c>
       <c r="CP7" t="inlineStr">
         <is>
-          <t>油電燃氣業平上市</t>
+          <t>油電燃氣業右上上市</t>
         </is>
       </c>
       <c r="CQ7" t="inlineStr">
@@ -3888,7 +3918,12 @@
       </c>
       <c r="CX7" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="CY7" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -3930,12 +3965,12 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-7.08</t>
+          <t>-4.82</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -3950,7 +3985,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3960,7 +3995,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2026-02-04 00:00:00</t>
+          <t>2026-02-05 00:00:00</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -4075,7 +4110,7 @@
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>2026-01-26 00:00:00</t>
+          <t>2026-01-27 00:00:00</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
@@ -4101,12 +4136,12 @@
       <c r="AP8" t="inlineStr"/>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>64</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>9081</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -4179,7 +4214,7 @@
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>519314816.3905326</t>
+          <t>523657208.8559999</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
@@ -4205,12 +4240,12 @@
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>30480104.35325804</t>
+          <t>30480104.35325402</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>58969667.73903918</t>
+          <t>58969667.73903829</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
@@ -4295,7 +4330,7 @@
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -4305,7 +4340,7 @@
       </c>
       <c r="CI8" t="inlineStr">
         <is>
-          <t>76.17</t>
+          <t>77.81</t>
         </is>
       </c>
       <c r="CJ8" t="inlineStr">
@@ -4320,12 +4355,12 @@
       </c>
       <c r="CL8" t="inlineStr">
         <is>
-          <t>27.12</t>
+          <t>27.38</t>
         </is>
       </c>
       <c r="CM8" t="inlineStr">
         <is>
-          <t>464391</t>
+          <t>474393</t>
         </is>
       </c>
       <c r="CN8" t="inlineStr">
@@ -4340,7 +4375,7 @@
       </c>
       <c r="CP8" t="inlineStr">
         <is>
-          <t>油電燃氣業平上市</t>
+          <t>油電燃氣業右上上市</t>
         </is>
       </c>
       <c r="CQ8" t="inlineStr">
@@ -4380,7 +4415,12 @@
       </c>
       <c r="CX8" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="CY8" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -4422,12 +4462,12 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>4.62</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -4442,7 +4482,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -4452,7 +4492,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2026-02-04 00:00:00</t>
+          <t>2026-02-05 00:00:00</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -4567,7 +4607,7 @@
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>2026-01-26 00:00:00</t>
+          <t>2026-01-27 00:00:00</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
@@ -4593,12 +4633,12 @@
       <c r="AP9" t="inlineStr"/>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>64</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>9081</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4671,7 +4711,7 @@
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>519314816.3905326</t>
+          <t>523657208.8559999</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
@@ -4697,12 +4737,12 @@
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>25300183.73766147</t>
+          <t>25300183.73765688</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>13844440.23752534</t>
+          <t>13844440.23752433</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
@@ -4777,7 +4817,7 @@
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
@@ -4787,7 +4827,7 @@
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4797,7 +4837,7 @@
       </c>
       <c r="CI9" t="inlineStr">
         <is>
-          <t>76.17</t>
+          <t>77.81</t>
         </is>
       </c>
       <c r="CJ9" t="inlineStr">
@@ -4812,12 +4852,12 @@
       </c>
       <c r="CL9" t="inlineStr">
         <is>
-          <t>27.12</t>
+          <t>27.38</t>
         </is>
       </c>
       <c r="CM9" t="inlineStr">
         <is>
-          <t>464391</t>
+          <t>474393</t>
         </is>
       </c>
       <c r="CN9" t="inlineStr">
@@ -4832,7 +4872,7 @@
       </c>
       <c r="CP9" t="inlineStr">
         <is>
-          <t>油電燃氣業平上市</t>
+          <t>油電燃氣業右上上市</t>
         </is>
       </c>
       <c r="CQ9" t="inlineStr">
@@ -4872,7 +4912,12 @@
       </c>
       <c r="CX9" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="CY9" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -4914,12 +4959,12 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>3.28</t>
+          <t>5.32</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -4934,7 +4979,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4944,7 +4989,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2026-02-04 00:00:00</t>
+          <t>2026-02-05 00:00:00</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -5059,7 +5104,7 @@
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>2026-01-26 00:00:00</t>
+          <t>2026-01-27 00:00:00</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
@@ -5085,12 +5130,12 @@
       <c r="AP10" t="inlineStr"/>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>64</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>9081</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -5121,7 +5166,7 @@
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>47.17</t>
+          <t>47.16999999999999</t>
         </is>
       </c>
       <c r="AZ10" t="n">
@@ -5163,7 +5208,7 @@
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>519314816.3905326</t>
+          <t>523657208.8559999</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
@@ -5189,12 +5234,12 @@
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>27383046.19223167</t>
+          <t>27383046.19222644</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>38407809.2268796</t>
+          <t>38407809.22687846</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -5269,7 +5314,7 @@
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
@@ -5279,7 +5324,7 @@
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -5289,7 +5334,7 @@
       </c>
       <c r="CI10" t="inlineStr">
         <is>
-          <t>76.17</t>
+          <t>77.81</t>
         </is>
       </c>
       <c r="CJ10" t="inlineStr">
@@ -5304,12 +5349,12 @@
       </c>
       <c r="CL10" t="inlineStr">
         <is>
-          <t>27.12</t>
+          <t>27.38</t>
         </is>
       </c>
       <c r="CM10" t="inlineStr">
         <is>
-          <t>464391</t>
+          <t>474393</t>
         </is>
       </c>
       <c r="CN10" t="inlineStr">
@@ -5324,7 +5369,7 @@
       </c>
       <c r="CP10" t="inlineStr">
         <is>
-          <t>油電燃氣業平上市</t>
+          <t>油電燃氣業右上上市</t>
         </is>
       </c>
       <c r="CQ10" t="inlineStr">
@@ -5364,7 +5409,12 @@
       </c>
       <c r="CX10" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="CY10" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -5406,12 +5456,12 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>6.05</t>
+          <t>8.03</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -5426,7 +5476,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -5436,7 +5486,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2026-02-04 00:00:00</t>
+          <t>2026-02-05 00:00:00</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -5551,7 +5601,7 @@
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>2026-01-26 00:00:00</t>
+          <t>2026-01-27 00:00:00</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
@@ -5577,12 +5627,12 @@
       <c r="AP11" t="inlineStr"/>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>64</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>9081</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -5655,7 +5705,7 @@
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>519314816.3905326</t>
+          <t>523657208.8559999</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
@@ -5681,12 +5731,12 @@
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>25378543.82229569</t>
+          <t>25378543.82228971</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>50793807.70356852</t>
+          <t>50793807.70356727</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5771,7 +5821,7 @@
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5781,7 +5831,7 @@
       </c>
       <c r="CI11" t="inlineStr">
         <is>
-          <t>76.17</t>
+          <t>77.81</t>
         </is>
       </c>
       <c r="CJ11" t="inlineStr">
@@ -5796,12 +5846,12 @@
       </c>
       <c r="CL11" t="inlineStr">
         <is>
-          <t>27.12</t>
+          <t>27.38</t>
         </is>
       </c>
       <c r="CM11" t="inlineStr">
         <is>
-          <t>464391</t>
+          <t>474393</t>
         </is>
       </c>
       <c r="CN11" t="inlineStr">
@@ -5816,7 +5866,7 @@
       </c>
       <c r="CP11" t="inlineStr">
         <is>
-          <t>油電燃氣業平上市</t>
+          <t>油電燃氣業右上上市</t>
         </is>
       </c>
       <c r="CQ11" t="inlineStr">
@@ -5856,29 +5906,34 @@
       </c>
       <c r="CX11" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="CY11" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>【d1】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>6505</t>
+          <t>1723</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-3.95</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>14562.265</t>
+          <t>267.935</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5888,7 +5943,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>46.35</t>
+          <t>73.4</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5898,17 +5953,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>4.92</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>27.98</t>
+          <t>-10.96</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5918,32 +5973,32 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-01-30 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2026-02-04 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>2025-11-07 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2025-11-25 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>53.4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -5958,12 +6013,12 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -5978,17 +6033,17 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025/07/28</t>
+          <t>2025/10/15</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>40.4</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -5998,67 +6053,67 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>2025/12/31</t>
+          <t>2025/11/13</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>79.9</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>2025/09/19</t>
+          <t>2025/06/20</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>38.9</t>
+          <t>90.1</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>2026/01/21</t>
+          <t>2025/10/23</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>45.8</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>2025/11/25</t>
+          <t>2025/07/31</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>86.9</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>2026-01-26 00:00:00</t>
+          <t>2025-12-08 00:00:00</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>38.60</t>
+          <t>14.24</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>-3.78</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
@@ -6069,121 +6124,121 @@
       <c r="AP12" t="inlineStr"/>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>9081</t>
+          <t>268</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>58.82</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>26.78</t>
+          <t>46.4</t>
         </is>
       </c>
       <c r="AU12" t="n">
-        <v>-3.76</v>
+        <v>0.14</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.22</v>
+        <v>1.97</v>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>-4.71</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>5.89</t>
+          <t>-5.63</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>48.16</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>48.06</v>
+        <v>71.88</v>
       </c>
       <c r="BA12" t="n">
-        <v>50.43</v>
+        <v>70.45999999999999</v>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>47.63</t>
+          <t>74.67</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>7.28</t>
+          <t>27.20</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>-0.47</v>
+        <v>0.8</v>
       </c>
       <c r="BE12" t="n">
-        <v>-0.5</v>
+        <v>0.63</v>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>2.97</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-116.90</t>
+          <t>-61.32</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026/01/26</t>
+          <t>2025/12/15</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>519314816.3905326</t>
+          <t>43899810.6812749</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
         <is>
-          <t>683297183.0</t>
+          <t>19642714.0</t>
         </is>
       </c>
       <c r="BK12" t="n">
-        <v>560940581.8</v>
+        <v>26269154.8</v>
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>438310515.0</t>
+          <t>29501746.5</t>
         </is>
       </c>
       <c r="BM12" t="n">
-        <v>438095262.3</v>
+        <v>38311289.88</v>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>122630066</t>
+          <t>-3232591</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>20757586.75297336</t>
+          <t>-797555.6572213848</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>70372116.50228238</t>
+          <t>-1738753.044416409</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>683297183.0</t>
+          <t>19642714.0</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -6193,32 +6248,32 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>43.85</t>
+          <t>74.1</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>2025/10/20</t>
+          <t>2026/01/29</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>5.70</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>台塑化</t>
+          <t>中碳</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
         <is>
-          <t>台塑化</t>
+          <t>中碳</t>
         </is>
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>油電燃氣業</t>
+          <t>化學工業</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
@@ -6228,117 +6283,117 @@
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
         <is>
-          <t>13.10069405245257</t>
+          <t>30.99363452064579</t>
         </is>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>1.558209746667079</t>
+          <t>-16.66279631185816</t>
         </is>
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>-5.675322107259221</t>
+          <t>-23.39857080035468</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>6.13</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
         <is>
-          <t>17.17</t>
+          <t>5.94</t>
         </is>
       </c>
       <c r="CI12" t="inlineStr">
         <is>
-          <t>76.17</t>
+          <t>23.15</t>
         </is>
       </c>
       <c r="CJ12" t="inlineStr">
         <is>
-          <t>7.31%</t>
+          <t>17.52%</t>
         </is>
       </c>
       <c r="CK12" t="inlineStr">
         <is>
-          <t>5.68%</t>
+          <t>6.35%</t>
         </is>
       </c>
       <c r="CL12" t="inlineStr">
         <is>
-          <t>27.12</t>
+          <t>53.58</t>
         </is>
       </c>
       <c r="CM12" t="inlineStr">
         <is>
-          <t>464391</t>
+          <t>17389</t>
         </is>
       </c>
       <c r="CN12" t="inlineStr">
         <is>
-          <t>汽油,柴油等各項石油製品75.50%、乙烯,丙烯等石油化學品18.10%、電力,蒸汽6.00%、其他0.40% (2024年)</t>
+          <t>煤焦油及化學品系列產品53.20%、輕油及油品系列產品29.03%、精碳材料9.72%、焦碳製品6.62%、其他1.43% (2024年)</t>
         </is>
       </c>
       <c r="CO12" t="inlineStr">
         <is>
-          <t>台塑化-油電燃氣業-上市</t>
+          <t>中碳-化學工業-上市</t>
         </is>
       </c>
       <c r="CP12" t="inlineStr">
         <is>
-          <t>油電燃氣業平上市</t>
+          <t>化學工業右下上市</t>
         </is>
       </c>
       <c r="CQ12" t="inlineStr">
         <is>
-          <t>48.1</t>
+          <t>73.4</t>
         </is>
       </c>
       <c r="CR12" t="inlineStr">
         <is>
-          <t>48.1</t>
+          <t>73.7</t>
         </is>
       </c>
       <c r="CS12" t="inlineStr">
         <is>
-          <t>46.35</t>
+          <t>72.7</t>
         </is>
       </c>
       <c r="CT12" t="inlineStr">
         <is>
-          <t>46.35</t>
+          <t>73.4</t>
         </is>
       </c>
       <c r="CU12" t="inlineStr">
         <is>
-          <t>32.21</t>
+          <t>33.12</t>
         </is>
       </c>
       <c r="CV12" t="inlineStr">
         <is>
-          <t>** 石化及塑橡膠 - 石化上游原料及相關鑽探設備** 油電燃氣 - 加油站、汽電共生</t>
+          <t>** 石化及塑橡膠 - 石化上游原料及相關鑽探設備** 電動車輛產業 - 鋰電池材料** 能源元件 - 原材料</t>
         </is>
       </c>
       <c r="CW12" t="inlineStr">
@@ -6348,7 +6403,12 @@
       </c>
       <c r="CX12" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CY12" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -6390,12 +6450,12 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -6410,7 +6470,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -6535,7 +6595,7 @@
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>2025-11-28 00:00:00</t>
+          <t>2025-12-08 00:00:00</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
@@ -6561,12 +6621,12 @@
       <c r="AP13" t="inlineStr"/>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>268</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -6624,12 +6684,12 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>-64.14</t>
+          <t>-63.95</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -6639,7 +6699,7 @@
       </c>
       <c r="BI13" t="inlineStr">
         <is>
-          <t>67132084.28106509</t>
+          <t>43899810.6812749</t>
         </is>
       </c>
       <c r="BJ13" t="inlineStr">
@@ -6665,12 +6725,12 @@
       </c>
       <c r="BO13" t="inlineStr">
         <is>
-          <t>-626428.8595494754</t>
+          <t>-626428.8595495621</t>
         </is>
       </c>
       <c r="BP13" t="inlineStr">
         <is>
-          <t>-1231831.403425679</t>
+          <t>-1231831.403425697</t>
         </is>
       </c>
       <c r="BQ13" t="inlineStr">
@@ -6755,7 +6815,7 @@
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>6.22</t>
+          <t>6.13</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6765,7 +6825,7 @@
       </c>
       <c r="CI13" t="inlineStr">
         <is>
-          <t>22.84</t>
+          <t>23.15</t>
         </is>
       </c>
       <c r="CJ13" t="inlineStr">
@@ -6780,12 +6840,12 @@
       </c>
       <c r="CL13" t="inlineStr">
         <is>
-          <t>52.42</t>
+          <t>53.58</t>
         </is>
       </c>
       <c r="CM13" t="inlineStr">
         <is>
-          <t>17152</t>
+          <t>17389</t>
         </is>
       </c>
       <c r="CN13" t="inlineStr">
@@ -6840,7 +6900,12 @@
       </c>
       <c r="CX13" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CY13" t="inlineStr">
+        <is>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -6882,12 +6947,12 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -6902,7 +6967,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -7027,7 +7092,7 @@
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>2025-11-28 00:00:00</t>
+          <t>2025-12-08 00:00:00</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
@@ -7053,12 +7118,12 @@
       <c r="AP14" t="inlineStr"/>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>268</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -7116,12 +7181,12 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>-67.18</t>
+          <t>-67.00</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -7131,7 +7196,7 @@
       </c>
       <c r="BI14" t="inlineStr">
         <is>
-          <t>67132084.28106509</t>
+          <t>43899810.6812749</t>
         </is>
       </c>
       <c r="BJ14" t="inlineStr">
@@ -7157,12 +7222,12 @@
       </c>
       <c r="BO14" t="inlineStr">
         <is>
-          <t>-516355.6697538021</t>
+          <t>-516355.6697539011</t>
         </is>
       </c>
       <c r="BP14" t="inlineStr">
         <is>
-          <t>-53394.58045945317</t>
+          <t>-53394.58045947179</t>
         </is>
       </c>
       <c r="BQ14" t="inlineStr">
@@ -7247,7 +7312,7 @@
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>6.22</t>
+          <t>6.13</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -7257,7 +7322,7 @@
       </c>
       <c r="CI14" t="inlineStr">
         <is>
-          <t>22.84</t>
+          <t>23.15</t>
         </is>
       </c>
       <c r="CJ14" t="inlineStr">
@@ -7272,12 +7337,12 @@
       </c>
       <c r="CL14" t="inlineStr">
         <is>
-          <t>52.42</t>
+          <t>53.58</t>
         </is>
       </c>
       <c r="CM14" t="inlineStr">
         <is>
-          <t>17152</t>
+          <t>17389</t>
         </is>
       </c>
       <c r="CN14" t="inlineStr">
@@ -7332,7 +7397,12 @@
       </c>
       <c r="CX14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CY14" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -7374,12 +7444,12 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-2.35</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -7394,7 +7464,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -7519,7 +7589,7 @@
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>2025-11-28 00:00:00</t>
+          <t>2025-12-08 00:00:00</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
@@ -7545,12 +7615,12 @@
       <c r="AP15" t="inlineStr"/>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>268</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -7608,12 +7678,12 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>-72.05</t>
+          <t>-71.90</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -7623,7 +7693,7 @@
       </c>
       <c r="BI15" t="inlineStr">
         <is>
-          <t>67132084.28106509</t>
+          <t>43899810.6812749</t>
         </is>
       </c>
       <c r="BJ15" t="inlineStr">
@@ -7649,12 +7719,12 @@
       </c>
       <c r="BO15" t="inlineStr">
         <is>
-          <t>-600530.4132618655</t>
+          <t>-600530.4132619792</t>
         </is>
       </c>
       <c r="BP15" t="inlineStr">
         <is>
-          <t>458683.9016515687</t>
+          <t>458683.9016515464</t>
         </is>
       </c>
       <c r="BQ15" t="inlineStr">
@@ -7739,7 +7809,7 @@
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>6.22</t>
+          <t>6.13</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -7749,7 +7819,7 @@
       </c>
       <c r="CI15" t="inlineStr">
         <is>
-          <t>22.84</t>
+          <t>23.15</t>
         </is>
       </c>
       <c r="CJ15" t="inlineStr">
@@ -7764,12 +7834,12 @@
       </c>
       <c r="CL15" t="inlineStr">
         <is>
-          <t>52.42</t>
+          <t>53.58</t>
         </is>
       </c>
       <c r="CM15" t="inlineStr">
         <is>
-          <t>17152</t>
+          <t>17389</t>
         </is>
       </c>
       <c r="CN15" t="inlineStr">
@@ -7824,7 +7894,12 @@
       </c>
       <c r="CX15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CY15" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -7866,12 +7941,12 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-2.35</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -7886,7 +7961,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -8011,7 +8086,7 @@
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>2025-11-28 00:00:00</t>
+          <t>2025-12-08 00:00:00</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
@@ -8037,12 +8112,12 @@
       <c r="AP16" t="inlineStr"/>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>268</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -8100,12 +8175,12 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>-79.16</t>
+          <t>-79.05</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -8115,7 +8190,7 @@
       </c>
       <c r="BI16" t="inlineStr">
         <is>
-          <t>67132084.28106509</t>
+          <t>43899810.6812749</t>
         </is>
       </c>
       <c r="BJ16" t="inlineStr">
@@ -8141,12 +8216,12 @@
       </c>
       <c r="BO16" t="inlineStr">
         <is>
-          <t>-793114.8341552172</t>
+          <t>-793114.8341553474</t>
         </is>
       </c>
       <c r="BP16" t="inlineStr">
         <is>
-          <t>167480.2724654712</t>
+          <t>167480.2724654451</t>
         </is>
       </c>
       <c r="BQ16" t="inlineStr">
@@ -8231,7 +8306,7 @@
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>6.22</t>
+          <t>6.13</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -8241,7 +8316,7 @@
       </c>
       <c r="CI16" t="inlineStr">
         <is>
-          <t>22.84</t>
+          <t>23.15</t>
         </is>
       </c>
       <c r="CJ16" t="inlineStr">
@@ -8256,12 +8331,12 @@
       </c>
       <c r="CL16" t="inlineStr">
         <is>
-          <t>52.42</t>
+          <t>53.58</t>
         </is>
       </c>
       <c r="CM16" t="inlineStr">
         <is>
-          <t>17152</t>
+          <t>17389</t>
         </is>
       </c>
       <c r="CN16" t="inlineStr">
@@ -8316,7 +8391,12 @@
       </c>
       <c r="CX16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CY16" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -8358,12 +8438,12 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -8378,7 +8458,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -8503,7 +8583,7 @@
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>2025-11-28 00:00:00</t>
+          <t>2025-12-08 00:00:00</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
@@ -8529,12 +8609,12 @@
       <c r="AP17" t="inlineStr"/>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>268</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -8565,7 +8645,7 @@
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>72.82000000000001</t>
+          <t>72.82</t>
         </is>
       </c>
       <c r="AZ17" t="n">
@@ -8592,12 +8672,12 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>-86.68</t>
+          <t>-86.61</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -8607,7 +8687,7 @@
       </c>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>67132084.28106509</t>
+          <t>43899810.6812749</t>
         </is>
       </c>
       <c r="BJ17" t="inlineStr">
@@ -8633,12 +8713,12 @@
       </c>
       <c r="BO17" t="inlineStr">
         <is>
-          <t>-967768.4899044333</t>
+          <t>-967768.4899045824</t>
         </is>
       </c>
       <c r="BP17" t="inlineStr">
         <is>
-          <t>87192.79246870428</t>
+          <t>87192.79246867448</t>
         </is>
       </c>
       <c r="BQ17" t="inlineStr">
@@ -8723,7 +8803,7 @@
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>6.22</t>
+          <t>6.13</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -8733,7 +8813,7 @@
       </c>
       <c r="CI17" t="inlineStr">
         <is>
-          <t>22.84</t>
+          <t>23.15</t>
         </is>
       </c>
       <c r="CJ17" t="inlineStr">
@@ -8748,12 +8828,12 @@
       </c>
       <c r="CL17" t="inlineStr">
         <is>
-          <t>52.42</t>
+          <t>53.58</t>
         </is>
       </c>
       <c r="CM17" t="inlineStr">
         <is>
-          <t>17152</t>
+          <t>17389</t>
         </is>
       </c>
       <c r="CN17" t="inlineStr">
@@ -8808,7 +8888,12 @@
       </c>
       <c r="CX17" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="CY17" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -8850,12 +8935,12 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -8870,7 +8955,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -8995,7 +9080,7 @@
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>2025-11-28 00:00:00</t>
+          <t>2025-12-08 00:00:00</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
@@ -9021,12 +9106,12 @@
       <c r="AP18" t="inlineStr"/>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>268</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -9084,12 +9169,12 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>-94.14</t>
+          <t>-94.11</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -9099,7 +9184,7 @@
       </c>
       <c r="BI18" t="inlineStr">
         <is>
-          <t>67132084.28106509</t>
+          <t>43899810.6812749</t>
         </is>
       </c>
       <c r="BJ18" t="inlineStr">
@@ -9125,12 +9210,12 @@
       </c>
       <c r="BO18" t="inlineStr">
         <is>
-          <t>-1159579.632154095</t>
+          <t>-1159579.632154265</t>
         </is>
       </c>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>-291937.8858291283</t>
+          <t>-291937.8858291619</t>
         </is>
       </c>
       <c r="BQ18" t="inlineStr">
@@ -9215,7 +9300,7 @@
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>6.22</t>
+          <t>6.13</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -9225,7 +9310,7 @@
       </c>
       <c r="CI18" t="inlineStr">
         <is>
-          <t>22.84</t>
+          <t>23.15</t>
         </is>
       </c>
       <c r="CJ18" t="inlineStr">
@@ -9240,12 +9325,12 @@
       </c>
       <c r="CL18" t="inlineStr">
         <is>
-          <t>52.42</t>
+          <t>53.58</t>
         </is>
       </c>
       <c r="CM18" t="inlineStr">
         <is>
-          <t>17152</t>
+          <t>17389</t>
         </is>
       </c>
       <c r="CN18" t="inlineStr">
@@ -9300,7 +9385,12 @@
       </c>
       <c r="CX18" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="CY18" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -9342,12 +9432,12 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-1.52</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -9362,7 +9452,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -9487,7 +9577,7 @@
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>2025-11-28 00:00:00</t>
+          <t>2025-12-08 00:00:00</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
@@ -9513,12 +9603,12 @@
       <c r="AP19" t="inlineStr"/>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>268</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -9576,12 +9666,12 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>-101.61</t>
+          <t>-101.62</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -9591,7 +9681,7 @@
       </c>
       <c r="BI19" t="inlineStr">
         <is>
-          <t>67132084.28106509</t>
+          <t>43899810.6812749</t>
         </is>
       </c>
       <c r="BJ19" t="inlineStr">
@@ -9617,12 +9707,12 @@
       </c>
       <c r="BO19" t="inlineStr">
         <is>
-          <t>-1317332.676940452</t>
+          <t>-1317332.676940648</t>
         </is>
       </c>
       <c r="BP19" t="inlineStr">
         <is>
-          <t>-228155.5374749973</t>
+          <t>-228155.5374750346</t>
         </is>
       </c>
       <c r="BQ19" t="inlineStr">
@@ -9707,7 +9797,7 @@
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>6.22</t>
+          <t>6.13</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -9717,7 +9807,7 @@
       </c>
       <c r="CI19" t="inlineStr">
         <is>
-          <t>22.84</t>
+          <t>23.15</t>
         </is>
       </c>
       <c r="CJ19" t="inlineStr">
@@ -9732,12 +9822,12 @@
       </c>
       <c r="CL19" t="inlineStr">
         <is>
-          <t>52.42</t>
+          <t>53.58</t>
         </is>
       </c>
       <c r="CM19" t="inlineStr">
         <is>
-          <t>17152</t>
+          <t>17389</t>
         </is>
       </c>
       <c r="CN19" t="inlineStr">
@@ -9792,7 +9882,12 @@
       </c>
       <c r="CX19" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="CY19" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -9834,12 +9929,12 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -9854,7 +9949,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -9979,7 +10074,7 @@
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>2025-11-28 00:00:00</t>
+          <t>2025-12-08 00:00:00</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
@@ -10005,12 +10100,12 @@
       <c r="AP20" t="inlineStr"/>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>268</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -10068,12 +10163,12 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>-109.84</t>
+          <t>-109.89</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
@@ -10083,7 +10178,7 @@
       </c>
       <c r="BI20" t="inlineStr">
         <is>
-          <t>67132084.28106509</t>
+          <t>43899810.6812749</t>
         </is>
       </c>
       <c r="BJ20" t="inlineStr">
@@ -10109,12 +10204,12 @@
       </c>
       <c r="BO20" t="inlineStr">
         <is>
-          <t>-1515364.88411599</t>
+          <t>-1515364.884116214</t>
         </is>
       </c>
       <c r="BP20" t="inlineStr">
         <is>
-          <t>-1901949.91348784</t>
+          <t>-1901949.913487885</t>
         </is>
       </c>
       <c r="BQ20" t="inlineStr">
@@ -10189,7 +10284,7 @@
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
@@ -10199,7 +10294,7 @@
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>6.22</t>
+          <t>6.13</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -10209,7 +10304,7 @@
       </c>
       <c r="CI20" t="inlineStr">
         <is>
-          <t>22.84</t>
+          <t>23.15</t>
         </is>
       </c>
       <c r="CJ20" t="inlineStr">
@@ -10224,12 +10319,12 @@
       </c>
       <c r="CL20" t="inlineStr">
         <is>
-          <t>52.42</t>
+          <t>53.58</t>
         </is>
       </c>
       <c r="CM20" t="inlineStr">
         <is>
-          <t>17152</t>
+          <t>17389</t>
         </is>
       </c>
       <c r="CN20" t="inlineStr">
@@ -10284,7 +10379,12 @@
       </c>
       <c r="CX20" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="CY20" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -10326,12 +10426,12 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>2.18</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -10346,7 +10446,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -10471,7 +10571,7 @@
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>2025-11-28 00:00:00</t>
+          <t>2025-12-08 00:00:00</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
@@ -10497,12 +10597,12 @@
       <c r="AP21" t="inlineStr"/>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>268</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -10533,7 +10633,7 @@
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>71.34</t>
+          <t>71.33999999999999</t>
         </is>
       </c>
       <c r="AZ21" t="n">
@@ -10560,12 +10660,12 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>-117.36</t>
+          <t>-117.46</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
@@ -10575,7 +10675,7 @@
       </c>
       <c r="BI21" t="inlineStr">
         <is>
-          <t>67132084.28106509</t>
+          <t>43899810.6812749</t>
         </is>
       </c>
       <c r="BJ21" t="inlineStr">
@@ -10601,12 +10701,12 @@
       </c>
       <c r="BO21" t="inlineStr">
         <is>
-          <t>-1445076.696957472</t>
+          <t>-1445076.696957728</t>
         </is>
       </c>
       <c r="BP21" t="inlineStr">
         <is>
-          <t>-1811882.95373876</t>
+          <t>-1811882.953738812</t>
         </is>
       </c>
       <c r="BQ21" t="inlineStr">
@@ -10681,7 +10781,7 @@
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
@@ -10691,7 +10791,7 @@
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>6.22</t>
+          <t>6.13</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -10701,7 +10801,7 @@
       </c>
       <c r="CI21" t="inlineStr">
         <is>
-          <t>22.84</t>
+          <t>23.15</t>
         </is>
       </c>
       <c r="CJ21" t="inlineStr">
@@ -10716,12 +10816,12 @@
       </c>
       <c r="CL21" t="inlineStr">
         <is>
-          <t>52.42</t>
+          <t>53.58</t>
         </is>
       </c>
       <c r="CM21" t="inlineStr">
         <is>
-          <t>17152</t>
+          <t>17389</t>
         </is>
       </c>
       <c r="CN21" t="inlineStr">
@@ -10776,7 +10876,12 @@
       </c>
       <c r="CX21" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="CY21" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -10818,12 +10923,12 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>3.81</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -10838,7 +10943,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -10963,7 +11068,7 @@
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>2025-11-28 00:00:00</t>
+          <t>2025-12-08 00:00:00</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
@@ -10989,12 +11094,12 @@
       <c r="AP22" t="inlineStr"/>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>268</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -11029,7 +11134,7 @@
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>69.29000000000001</v>
+        <v>69.3</v>
       </c>
       <c r="BA22" t="n">
         <v>71.56</v>
@@ -11052,12 +11157,12 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>-124.72</t>
+          <t>-124.85</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
@@ -11067,7 +11172,7 @@
       </c>
       <c r="BI22" t="inlineStr">
         <is>
-          <t>67132084.28106509</t>
+          <t>43899810.6812749</t>
         </is>
       </c>
       <c r="BJ22" t="inlineStr">
@@ -11093,12 +11198,12 @@
       </c>
       <c r="BO22" t="inlineStr">
         <is>
-          <t>-1378384.650269964</t>
+          <t>-1378384.650270259</t>
         </is>
       </c>
       <c r="BP22" t="inlineStr">
         <is>
-          <t>-2074007.44146369</t>
+          <t>-2074007.441463754</t>
         </is>
       </c>
       <c r="BQ22" t="inlineStr">
@@ -11183,7 +11288,7 @@
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>6.22</t>
+          <t>6.13</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -11193,7 +11298,7 @@
       </c>
       <c r="CI22" t="inlineStr">
         <is>
-          <t>22.84</t>
+          <t>23.15</t>
         </is>
       </c>
       <c r="CJ22" t="inlineStr">
@@ -11208,12 +11313,12 @@
       </c>
       <c r="CL22" t="inlineStr">
         <is>
-          <t>52.42</t>
+          <t>53.58</t>
         </is>
       </c>
       <c r="CM22" t="inlineStr">
         <is>
-          <t>17152</t>
+          <t>17389</t>
         </is>
       </c>
       <c r="CN22" t="inlineStr">
@@ -11268,29 +11373,34 @@
       </c>
       <c r="CX22" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="CY22" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>【d1】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>1723</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>6.29</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>284.335</t>
+          <t>76143.132</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -11300,7 +11410,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>71.2</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -11310,17 +11420,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-8.46</t>
+          <t>-37.18</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -11330,37 +11440,37 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2026-01-08 00:00:00</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2026-02-02 00:00:00</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-01 00:00:00</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-10 00:00:00</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>70.6</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -11370,12 +11480,12 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>61.1</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>61.4</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
@@ -11385,22 +11495,22 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9.92</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9.12</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025/10/15</t>
+          <t>2025/07/28</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>37.0</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -11410,67 +11520,67 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>2025/11/13</t>
+          <t>2025/09/26</t>
         </is>
       </c>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>79.9</t>
+          <t>39.6</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>2025/06/20</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>90.1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>2025/10/23</t>
+          <t>2026/02/02</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>70.6</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>2025/07/31</t>
+          <t>2025/12/10</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>86.9</t>
+          <t>61.4</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>2025-11-28 00:00:00</t>
+          <t>2026-01-07 00:00:00</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>15.11</t>
+          <t>20.57</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>6.68</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
@@ -11481,121 +11591,121 @@
       <c r="AP23" t="inlineStr"/>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>666</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>76143</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>63.06</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>87.21</t>
+          <t>28.23</t>
         </is>
       </c>
       <c r="AU23" t="n">
-        <v>-0.34</v>
+        <v>3.69</v>
       </c>
       <c r="AV23" t="n">
-        <v>3.24</v>
+        <v>2.3</v>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>-3.54</t>
+          <t>12.5</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>-5.57</t>
+          <t>12.48</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>71.44</t>
+          <t>74.84</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>69.2</v>
+        <v>73.16</v>
       </c>
       <c r="BA23" t="n">
-        <v>71.73999999999999</v>
+        <v>65.03</v>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>75.97</t>
+          <t>57.81</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>115.63</t>
+          <t>-13.69</t>
         </is>
       </c>
       <c r="BD23" t="n">
-        <v>0.08</v>
+        <v>3.78</v>
       </c>
       <c r="BE23" t="n">
-        <v>-0.53</v>
+        <v>4.38</v>
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>4.82</t>
         </is>
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>-132.33</t>
+          <t>-9.14</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2025/12/15</t>
+          <t>2026/01/08</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
         <is>
-          <t>67132084.28106509</t>
+          <t>4781639005.834661</t>
         </is>
       </c>
       <c r="BJ23" t="inlineStr">
         <is>
-          <t>20245703.0</t>
+          <t>5810696045.0</t>
         </is>
       </c>
       <c r="BK23" t="n">
-        <v>27975889.4</v>
+        <v>5332113616.6</v>
       </c>
       <c r="BL23" t="inlineStr">
         <is>
-          <t>30562958.0</t>
+          <t>8487679653.7</t>
         </is>
       </c>
       <c r="BM23" t="n">
-        <v>39329467.96</v>
+        <v>8402507681.12</v>
       </c>
       <c r="BN23" t="inlineStr">
         <is>
-          <t>-2587068</t>
+          <t>-2147483648</t>
         </is>
       </c>
       <c r="BO23" t="inlineStr">
         <is>
-          <t>-1251907.779143833</t>
+          <t>-30517724.78436583</t>
         </is>
       </c>
       <c r="BP23" t="inlineStr">
         <is>
-          <t>-2060807.158161316</t>
+          <t>-1133539726.649557</t>
         </is>
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>20245703.0</t>
+          <t>5810696045.0</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -11605,32 +11715,32 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>74.1</t>
+          <t>41.9</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>2026/01/29</t>
+          <t>2025/10/21</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
         <is>
-          <t>-3.91</t>
+          <t>85.20</t>
         </is>
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>中碳</t>
+          <t>南亞</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
         <is>
-          <t>中碳</t>
+          <t>南亞</t>
         </is>
       </c>
       <c r="BX23" t="inlineStr">
         <is>
-          <t>化學工業</t>
+          <t>塑膠工業</t>
         </is>
       </c>
       <c r="BY23" t="inlineStr">
@@ -11640,127 +11750,132 @@
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
         <is>
-          <t>30.99363452064579</t>
+          <t>4.576300423341094</t>
         </is>
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>-16.66279631185816</t>
+          <t>-5.666405408220591</t>
         </is>
       </c>
       <c r="CC23" t="inlineStr">
         <is>
-          <t>-23.39857080035468</t>
+          <t>0.1134007627940262</t>
         </is>
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>6.22</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">
         <is>
-          <t>5.94</t>
+          <t>8.09</t>
         </is>
       </c>
       <c r="CI23" t="inlineStr">
         <is>
-          <t>22.84</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CJ23" t="inlineStr">
         <is>
-          <t>17.52%</t>
+          <t>8.29%</t>
         </is>
       </c>
       <c r="CK23" t="inlineStr">
         <is>
-          <t>6.35%</t>
+          <t>1.61%</t>
         </is>
       </c>
       <c r="CL23" t="inlineStr">
         <is>
-          <t>52.42</t>
+          <t>60.96</t>
         </is>
       </c>
       <c r="CM23" t="inlineStr">
         <is>
-          <t>17152</t>
+          <t>615432</t>
         </is>
       </c>
       <c r="CN23" t="inlineStr">
         <is>
-          <t>煤焦油及化學品系列產品53.20%、輕油及油品系列產品29.03%、精碳材料9.72%、焦碳製品6.62%、其他1.43% (2024年)</t>
+          <t>聚酯纖維16.60%、其他16.28%、印刷電路板(PCB)12.09%、銅箔基板(CCL)10.47%、環氧樹脂8.29%、丙二酚(BPA)5.67%、乙二醇(EG)5.60%、銅箔5.01%、可塑劑(DOP)及硬化劑3.38%、硬質管2.55%、硬質膠布2.48%、塑膠門窗2.20%、軟質膠布1.85%、麩酸酐(PA)1.55%、玻璃纖維布1.32%、聚酯薄膜1.30%、膠乳皮0.92%、PU合成皮(人造皮)0.69%、BOPP膜0.64%、玻璃纖維絲0.60%、丁二醇(BDO)0.54% (2024年)</t>
         </is>
       </c>
       <c r="CO23" t="inlineStr">
         <is>
-          <t>中碳-化學工業-上市</t>
+          <t>南亞-塑膠工業-上市</t>
         </is>
       </c>
       <c r="CP23" t="inlineStr">
         <is>
-          <t>化學工業右下上市</t>
+          <t>塑膠工業右上上市</t>
         </is>
       </c>
       <c r="CQ23" t="inlineStr">
         <is>
-          <t>71.6</t>
+          <t>73.1</t>
         </is>
       </c>
       <c r="CR23" t="inlineStr">
         <is>
-          <t>71.6</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="CS23" t="inlineStr">
         <is>
-          <t>70.9</t>
+          <t>71.7</t>
         </is>
       </c>
       <c r="CT23" t="inlineStr">
         <is>
-          <t>71.2</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="CU23" t="inlineStr">
         <is>
-          <t>33.12</t>
+          <t>41.48</t>
         </is>
       </c>
       <c r="CV23" t="inlineStr">
         <is>
-          <t>** 石化及塑橡膠 - 石化上游原料及相關鑽探設備** 電動車輛產業 - 鋰電池材料** 能源元件 - 原材料</t>
+          <t>** 印刷電路板 - 玻璃纖維/玻纖布、環氧樹脂、酚醛樹脂、銅箔、銅箔基板** 石化及塑橡膠 - 石化上游原料及相關鑽探設備、人造纖維** 紡織 - 石化原料(例如純對苯二甲酸、乙二醇、己內醯胺、丙烯腈等)、人造纖維產品(例如尼龍纖維、聚酯纖維、嫘縈纖維等)、染整** 電機機械 - 電控元件、機械設備之沖壓零組件</t>
         </is>
       </c>
       <c r="CW23" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="CX23" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CY23" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -11802,12 +11917,12 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.93</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -11822,7 +11937,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -11917,12 +12032,12 @@
       </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>2025/04/08</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>28.85</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AG24" t="inlineStr">
@@ -11947,7 +12062,7 @@
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>2025-12-19 00:00:00</t>
+          <t>2026-01-07 00:00:00</t>
         </is>
       </c>
       <c r="AL24" t="inlineStr">
@@ -11973,12 +12088,12 @@
       <c r="AP24" t="inlineStr"/>
       <c r="AQ24" t="inlineStr">
         <is>
-          <t>450</t>
+          <t>666</t>
         </is>
       </c>
       <c r="AR24" t="inlineStr">
         <is>
-          <t>62847</t>
+          <t>76143</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr">
@@ -12051,7 +12166,7 @@
       </c>
       <c r="BI24" t="inlineStr">
         <is>
-          <t>2764003009.408284</t>
+          <t>4781639005.834661</t>
         </is>
       </c>
       <c r="BJ24" t="inlineStr">
@@ -12077,7 +12192,7 @@
       </c>
       <c r="BO24" t="inlineStr">
         <is>
-          <t>170031730.1002147</t>
+          <t>170031730.1002144</t>
         </is>
       </c>
       <c r="BP24" t="inlineStr">
@@ -12167,7 +12282,7 @@
       </c>
       <c r="CG24" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="CH24" t="inlineStr">
@@ -12192,12 +12307,12 @@
       </c>
       <c r="CL24" t="inlineStr">
         <is>
-          <t>60.85</t>
+          <t>60.96</t>
         </is>
       </c>
       <c r="CM24" t="inlineStr">
         <is>
-          <t>578950</t>
+          <t>615432</t>
         </is>
       </c>
       <c r="CN24" t="inlineStr">
@@ -12252,7 +12367,12 @@
       </c>
       <c r="CX24" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CY24" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -12294,12 +12414,12 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>3.29</t>
+          <t>9.02</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -12314,7 +12434,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -12409,12 +12529,12 @@
       </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>2025/04/08</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>28.85</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AG25" t="inlineStr">
@@ -12439,7 +12559,7 @@
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>2025-12-19 00:00:00</t>
+          <t>2026-01-07 00:00:00</t>
         </is>
       </c>
       <c r="AL25" t="inlineStr">
@@ -12465,12 +12585,12 @@
       <c r="AP25" t="inlineStr"/>
       <c r="AQ25" t="inlineStr">
         <is>
-          <t>450</t>
+          <t>666</t>
         </is>
       </c>
       <c r="AR25" t="inlineStr">
         <is>
-          <t>62847</t>
+          <t>76143</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr">
@@ -12505,7 +12625,7 @@
         </is>
       </c>
       <c r="AZ25" t="n">
-        <v>71.81</v>
+        <v>71.8</v>
       </c>
       <c r="BA25" t="n">
         <v>64.16</v>
@@ -12543,7 +12663,7 @@
       </c>
       <c r="BI25" t="inlineStr">
         <is>
-          <t>2764003009.408284</t>
+          <t>4781639005.834661</t>
         </is>
       </c>
       <c r="BJ25" t="inlineStr">
@@ -12569,7 +12689,7 @@
       </c>
       <c r="BO25" t="inlineStr">
         <is>
-          <t>402127393.5617278</t>
+          <t>402127393.5617275</t>
         </is>
       </c>
       <c r="BP25" t="inlineStr">
@@ -12659,7 +12779,7 @@
       </c>
       <c r="CG25" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="CH25" t="inlineStr">
@@ -12684,12 +12804,12 @@
       </c>
       <c r="CL25" t="inlineStr">
         <is>
-          <t>60.85</t>
+          <t>60.96</t>
         </is>
       </c>
       <c r="CM25" t="inlineStr">
         <is>
-          <t>578950</t>
+          <t>615432</t>
         </is>
       </c>
       <c r="CN25" t="inlineStr">
@@ -12744,7 +12864,12 @@
       </c>
       <c r="CX25" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CY25" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -12786,12 +12911,12 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-3.97</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -12806,7 +12931,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -12901,12 +13026,12 @@
       </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>2025/04/08</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>28.85</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AG26" t="inlineStr">
@@ -12931,7 +13056,7 @@
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>2025-12-19 00:00:00</t>
+          <t>2026-01-07 00:00:00</t>
         </is>
       </c>
       <c r="AL26" t="inlineStr">
@@ -12957,12 +13082,12 @@
       <c r="AP26" t="inlineStr"/>
       <c r="AQ26" t="inlineStr">
         <is>
-          <t>450</t>
+          <t>666</t>
         </is>
       </c>
       <c r="AR26" t="inlineStr">
         <is>
-          <t>62847</t>
+          <t>76143</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr">
@@ -13035,7 +13160,7 @@
       </c>
       <c r="BI26" t="inlineStr">
         <is>
-          <t>2764003009.408284</t>
+          <t>4781639005.834661</t>
         </is>
       </c>
       <c r="BJ26" t="inlineStr">
@@ -13061,7 +13186,7 @@
       </c>
       <c r="BO26" t="inlineStr">
         <is>
-          <t>639260934.1630217</t>
+          <t>639260934.1630212</t>
         </is>
       </c>
       <c r="BP26" t="inlineStr">
@@ -13151,7 +13276,7 @@
       </c>
       <c r="CG26" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="CH26" t="inlineStr">
@@ -13176,12 +13301,12 @@
       </c>
       <c r="CL26" t="inlineStr">
         <is>
-          <t>60.85</t>
+          <t>60.96</t>
         </is>
       </c>
       <c r="CM26" t="inlineStr">
         <is>
-          <t>578950</t>
+          <t>615432</t>
         </is>
       </c>
       <c r="CN26" t="inlineStr">
@@ -13236,7 +13361,12 @@
       </c>
       <c r="CX26" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CY26" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -13278,12 +13408,12 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-5.62</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -13298,7 +13428,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -13393,12 +13523,12 @@
       </c>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>2025/04/08</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>28.85</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AG27" t="inlineStr">
@@ -13423,7 +13553,7 @@
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>2025-12-19 00:00:00</t>
+          <t>2026-01-07 00:00:00</t>
         </is>
       </c>
       <c r="AL27" t="inlineStr">
@@ -13449,12 +13579,12 @@
       <c r="AP27" t="inlineStr"/>
       <c r="AQ27" t="inlineStr">
         <is>
-          <t>450</t>
+          <t>666</t>
         </is>
       </c>
       <c r="AR27" t="inlineStr">
         <is>
-          <t>62847</t>
+          <t>76143</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr">
@@ -13527,7 +13657,7 @@
       </c>
       <c r="BI27" t="inlineStr">
         <is>
-          <t>2764003009.408284</t>
+          <t>4781639005.834661</t>
         </is>
       </c>
       <c r="BJ27" t="inlineStr">
@@ -13553,7 +13683,7 @@
       </c>
       <c r="BO27" t="inlineStr">
         <is>
-          <t>866532702.6239393</t>
+          <t>866532702.6239387</t>
         </is>
       </c>
       <c r="BP27" t="inlineStr">
@@ -13643,7 +13773,7 @@
       </c>
       <c r="CG27" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="CH27" t="inlineStr">
@@ -13668,12 +13798,12 @@
       </c>
       <c r="CL27" t="inlineStr">
         <is>
-          <t>60.85</t>
+          <t>60.96</t>
         </is>
       </c>
       <c r="CM27" t="inlineStr">
         <is>
-          <t>578950</t>
+          <t>615432</t>
         </is>
       </c>
       <c r="CN27" t="inlineStr">
@@ -13728,7 +13858,12 @@
       </c>
       <c r="CX27" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CY27" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -13770,12 +13905,12 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-10.27</t>
+          <t>-3.74</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -13790,7 +13925,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -13885,12 +14020,12 @@
       </c>
       <c r="AE28" t="inlineStr">
         <is>
-          <t>2025/04/08</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>28.85</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AG28" t="inlineStr">
@@ -13915,7 +14050,7 @@
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>2025-12-19 00:00:00</t>
+          <t>2026-01-07 00:00:00</t>
         </is>
       </c>
       <c r="AL28" t="inlineStr">
@@ -13941,12 +14076,12 @@
       <c r="AP28" t="inlineStr"/>
       <c r="AQ28" t="inlineStr">
         <is>
-          <t>450</t>
+          <t>666</t>
         </is>
       </c>
       <c r="AR28" t="inlineStr">
         <is>
-          <t>62847</t>
+          <t>76143</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr">
@@ -14019,7 +14154,7 @@
       </c>
       <c r="BI28" t="inlineStr">
         <is>
-          <t>2764003009.408284</t>
+          <t>4781639005.834661</t>
         </is>
       </c>
       <c r="BJ28" t="inlineStr">
@@ -14045,7 +14180,7 @@
       </c>
       <c r="BO28" t="inlineStr">
         <is>
-          <t>1049896627.348488</t>
+          <t>1049896627.348487</t>
         </is>
       </c>
       <c r="BP28" t="inlineStr">
@@ -14135,7 +14270,7 @@
       </c>
       <c r="CG28" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="CH28" t="inlineStr">
@@ -14160,12 +14295,12 @@
       </c>
       <c r="CL28" t="inlineStr">
         <is>
-          <t>60.85</t>
+          <t>60.96</t>
         </is>
       </c>
       <c r="CM28" t="inlineStr">
         <is>
-          <t>578950</t>
+          <t>615432</t>
         </is>
       </c>
       <c r="CN28" t="inlineStr">
@@ -14220,7 +14355,12 @@
       </c>
       <c r="CX28" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CY28" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -14262,12 +14402,12 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-9.04</t>
+          <t>-2.58</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -14282,7 +14422,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -14377,12 +14517,12 @@
       </c>
       <c r="AE29" t="inlineStr">
         <is>
-          <t>2025/04/08</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>28.85</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AG29" t="inlineStr">
@@ -14407,7 +14547,7 @@
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>2025-12-19 00:00:00</t>
+          <t>2026-01-07 00:00:00</t>
         </is>
       </c>
       <c r="AL29" t="inlineStr">
@@ -14433,12 +14573,12 @@
       <c r="AP29" t="inlineStr"/>
       <c r="AQ29" t="inlineStr">
         <is>
-          <t>450</t>
+          <t>666</t>
         </is>
       </c>
       <c r="AR29" t="inlineStr">
         <is>
-          <t>62847</t>
+          <t>76143</t>
         </is>
       </c>
       <c r="AS29" t="inlineStr">
@@ -14511,7 +14651,7 @@
       </c>
       <c r="BI29" t="inlineStr">
         <is>
-          <t>2764003009.408284</t>
+          <t>4781639005.834661</t>
         </is>
       </c>
       <c r="BJ29" t="inlineStr">
@@ -14537,7 +14677,7 @@
       </c>
       <c r="BO29" t="inlineStr">
         <is>
-          <t>1182371602.91387</t>
+          <t>1182371602.913869</t>
         </is>
       </c>
       <c r="BP29" t="inlineStr">
@@ -14627,7 +14767,7 @@
       </c>
       <c r="CG29" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="CH29" t="inlineStr">
@@ -14652,12 +14792,12 @@
       </c>
       <c r="CL29" t="inlineStr">
         <is>
-          <t>60.85</t>
+          <t>60.96</t>
         </is>
       </c>
       <c r="CM29" t="inlineStr">
         <is>
-          <t>578950</t>
+          <t>615432</t>
         </is>
       </c>
       <c r="CN29" t="inlineStr">
@@ -14712,7 +14852,12 @@
       </c>
       <c r="CX29" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CY29" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -14754,12 +14899,12 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-11.92</t>
+          <t>-5.28</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -14774,7 +14919,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -14869,12 +15014,12 @@
       </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>2025/04/08</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>28.85</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AG30" t="inlineStr">
@@ -14899,7 +15044,7 @@
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>2025-12-19 00:00:00</t>
+          <t>2026-01-07 00:00:00</t>
         </is>
       </c>
       <c r="AL30" t="inlineStr">
@@ -14925,12 +15070,12 @@
       <c r="AP30" t="inlineStr"/>
       <c r="AQ30" t="inlineStr">
         <is>
-          <t>450</t>
+          <t>666</t>
         </is>
       </c>
       <c r="AR30" t="inlineStr">
         <is>
-          <t>62847</t>
+          <t>76143</t>
         </is>
       </c>
       <c r="AS30" t="inlineStr">
@@ -14972,7 +15117,7 @@
       </c>
       <c r="BB30" t="inlineStr">
         <is>
-          <t>54.66</t>
+          <t>54.65</t>
         </is>
       </c>
       <c r="BC30" t="inlineStr">
@@ -15003,7 +15148,7 @@
       </c>
       <c r="BI30" t="inlineStr">
         <is>
-          <t>2764003009.408284</t>
+          <t>4781639005.834661</t>
         </is>
       </c>
       <c r="BJ30" t="inlineStr">
@@ -15029,7 +15174,7 @@
       </c>
       <c r="BO30" t="inlineStr">
         <is>
-          <t>1301117726.866078</t>
+          <t>1301117726.866077</t>
         </is>
       </c>
       <c r="BP30" t="inlineStr">
@@ -15119,7 +15264,7 @@
       </c>
       <c r="CG30" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="CH30" t="inlineStr">
@@ -15144,12 +15289,12 @@
       </c>
       <c r="CL30" t="inlineStr">
         <is>
-          <t>60.85</t>
+          <t>60.96</t>
         </is>
       </c>
       <c r="CM30" t="inlineStr">
         <is>
-          <t>578950</t>
+          <t>615432</t>
         </is>
       </c>
       <c r="CN30" t="inlineStr">
@@ -15204,7 +15349,12 @@
       </c>
       <c r="CX30" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="CY30" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -15246,12 +15396,12 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>-5.62</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -15266,7 +15416,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -15361,12 +15511,12 @@
       </c>
       <c r="AE31" t="inlineStr">
         <is>
-          <t>2025/04/08</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF31" t="inlineStr">
         <is>
-          <t>28.85</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AG31" t="inlineStr">
@@ -15391,7 +15541,7 @@
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>2025-12-19 00:00:00</t>
+          <t>2026-01-07 00:00:00</t>
         </is>
       </c>
       <c r="AL31" t="inlineStr">
@@ -15417,12 +15567,12 @@
       <c r="AP31" t="inlineStr"/>
       <c r="AQ31" t="inlineStr">
         <is>
-          <t>450</t>
+          <t>666</t>
         </is>
       </c>
       <c r="AR31" t="inlineStr">
         <is>
-          <t>62847</t>
+          <t>76143</t>
         </is>
       </c>
       <c r="AS31" t="inlineStr">
@@ -15495,7 +15645,7 @@
       </c>
       <c r="BI31" t="inlineStr">
         <is>
-          <t>2764003009.408284</t>
+          <t>4781639005.834661</t>
         </is>
       </c>
       <c r="BJ31" t="inlineStr">
@@ -15521,7 +15671,7 @@
       </c>
       <c r="BO31" t="inlineStr">
         <is>
-          <t>1350822801.567148</t>
+          <t>1350822801.567147</t>
         </is>
       </c>
       <c r="BP31" t="inlineStr">
@@ -15601,7 +15751,7 @@
       </c>
       <c r="CE31" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF31" t="inlineStr">
@@ -15611,7 +15761,7 @@
       </c>
       <c r="CG31" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="CH31" t="inlineStr">
@@ -15636,12 +15786,12 @@
       </c>
       <c r="CL31" t="inlineStr">
         <is>
-          <t>60.85</t>
+          <t>60.96</t>
         </is>
       </c>
       <c r="CM31" t="inlineStr">
         <is>
-          <t>578950</t>
+          <t>615432</t>
         </is>
       </c>
       <c r="CN31" t="inlineStr">
@@ -15696,7 +15846,12 @@
       </c>
       <c r="CX31" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="CY31" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -15738,12 +15893,12 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-6.58</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -15758,7 +15913,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -15853,12 +16008,12 @@
       </c>
       <c r="AE32" t="inlineStr">
         <is>
-          <t>2025/04/08</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF32" t="inlineStr">
         <is>
-          <t>28.85</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AG32" t="inlineStr">
@@ -15883,7 +16038,7 @@
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>2025-12-19 00:00:00</t>
+          <t>2026-01-07 00:00:00</t>
         </is>
       </c>
       <c r="AL32" t="inlineStr">
@@ -15909,12 +16064,12 @@
       <c r="AP32" t="inlineStr"/>
       <c r="AQ32" t="inlineStr">
         <is>
-          <t>450</t>
+          <t>666</t>
         </is>
       </c>
       <c r="AR32" t="inlineStr">
         <is>
-          <t>62847</t>
+          <t>76143</t>
         </is>
       </c>
       <c r="AS32" t="inlineStr">
@@ -15987,7 +16142,7 @@
       </c>
       <c r="BI32" t="inlineStr">
         <is>
-          <t>2764003009.408284</t>
+          <t>4781639005.834661</t>
         </is>
       </c>
       <c r="BJ32" t="inlineStr">
@@ -16013,7 +16168,7 @@
       </c>
       <c r="BO32" t="inlineStr">
         <is>
-          <t>1404163122.003943</t>
+          <t>1404163122.003942</t>
         </is>
       </c>
       <c r="BP32" t="inlineStr">
@@ -16093,7 +16248,7 @@
       </c>
       <c r="CE32" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF32" t="inlineStr">
@@ -16103,7 +16258,7 @@
       </c>
       <c r="CG32" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="CH32" t="inlineStr">
@@ -16128,12 +16283,12 @@
       </c>
       <c r="CL32" t="inlineStr">
         <is>
-          <t>60.85</t>
+          <t>60.96</t>
         </is>
       </c>
       <c r="CM32" t="inlineStr">
         <is>
-          <t>578950</t>
+          <t>615432</t>
         </is>
       </c>
       <c r="CN32" t="inlineStr">
@@ -16188,7 +16343,12 @@
       </c>
       <c r="CX32" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="CY32" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -16230,12 +16390,12 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>5.03</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -16250,7 +16410,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -16345,12 +16505,12 @@
       </c>
       <c r="AE33" t="inlineStr">
         <is>
-          <t>2025/04/08</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF33" t="inlineStr">
         <is>
-          <t>28.85</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AG33" t="inlineStr">
@@ -16375,7 +16535,7 @@
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>2025-12-19 00:00:00</t>
+          <t>2026-01-07 00:00:00</t>
         </is>
       </c>
       <c r="AL33" t="inlineStr">
@@ -16401,12 +16561,12 @@
       <c r="AP33" t="inlineStr"/>
       <c r="AQ33" t="inlineStr">
         <is>
-          <t>450</t>
+          <t>666</t>
         </is>
       </c>
       <c r="AR33" t="inlineStr">
         <is>
-          <t>62847</t>
+          <t>76143</t>
         </is>
       </c>
       <c r="AS33" t="inlineStr">
@@ -16479,7 +16639,7 @@
       </c>
       <c r="BI33" t="inlineStr">
         <is>
-          <t>2764003009.408284</t>
+          <t>4781639005.834661</t>
         </is>
       </c>
       <c r="BJ33" t="inlineStr">
@@ -16505,7 +16665,7 @@
       </c>
       <c r="BO33" t="inlineStr">
         <is>
-          <t>1365520284.34471</t>
+          <t>1365520284.344708</t>
         </is>
       </c>
       <c r="BP33" t="inlineStr">
@@ -16595,7 +16755,7 @@
       </c>
       <c r="CG33" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="CH33" t="inlineStr">
@@ -16620,12 +16780,12 @@
       </c>
       <c r="CL33" t="inlineStr">
         <is>
-          <t>60.85</t>
+          <t>60.96</t>
         </is>
       </c>
       <c r="CM33" t="inlineStr">
         <is>
-          <t>578950</t>
+          <t>615432</t>
         </is>
       </c>
       <c r="CN33" t="inlineStr">
@@ -16680,499 +16840,12 @@
       </c>
       <c r="CX33" t="inlineStr">
         <is>
-          <t>2.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>【b1】</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>1303</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>-3.99</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>229688.124</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>76.4</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>-4.66</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>-1.64</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>26.13</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>2026-01-08</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>99.0</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>2026-01-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>2026-02-02 00:00:00</t>
-        </is>
-      </c>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t>2025-12-01 00:00:00</t>
-        </is>
-      </c>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>2025-12-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q34" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="R34" t="inlineStr">
-        <is>
-          <t>70.6</t>
-        </is>
-      </c>
-      <c r="S34" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="T34" t="inlineStr">
-        <is>
-          <t>61.1</t>
-        </is>
-      </c>
-      <c r="U34" t="inlineStr">
-        <is>
-          <t>61.4</t>
-        </is>
-      </c>
-      <c r="V34" t="inlineStr">
-        <is>
-          <t>14.03</t>
-        </is>
-      </c>
-      <c r="W34" t="inlineStr">
-        <is>
-          <t>8.22</t>
-        </is>
-      </c>
-      <c r="X34" t="inlineStr">
-        <is>
-          <t>9.12</t>
-        </is>
-      </c>
-      <c r="Y34" t="inlineStr">
-        <is>
-          <t>2025/07/28</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>37.0</t>
-        </is>
-      </c>
-      <c r="AA34" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>0.06</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>2025/09/26</t>
-        </is>
-      </c>
-      <c r="AD34" t="inlineStr">
-        <is>
-          <t>39.6</t>
-        </is>
-      </c>
-      <c r="AE34" t="inlineStr">
-        <is>
-          <t>2025/04/08</t>
-        </is>
-      </c>
-      <c r="AF34" t="inlineStr">
-        <is>
-          <t>28.85</t>
-        </is>
-      </c>
-      <c r="AG34" t="inlineStr">
-        <is>
-          <t>2026/02/02</t>
-        </is>
-      </c>
-      <c r="AH34" t="inlineStr">
-        <is>
-          <t>70.6</t>
-        </is>
-      </c>
-      <c r="AI34" t="inlineStr">
-        <is>
-          <t>2025/12/10</t>
-        </is>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>61.4</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>2025-12-19 00:00:00</t>
-        </is>
-      </c>
-      <c r="AL34" t="inlineStr">
-        <is>
-          <t>2026-01-20</t>
-        </is>
-      </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>62.05</t>
-        </is>
-      </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>-0.68</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AP34" t="inlineStr"/>
-      <c r="AQ34" t="inlineStr">
-        <is>
-          <t>450</t>
-        </is>
-      </c>
-      <c r="AR34" t="inlineStr">
-        <is>
-          <t>62847</t>
-        </is>
-      </c>
-      <c r="AS34" t="inlineStr">
-        <is>
-          <t>82.86</t>
-        </is>
-      </c>
-      <c r="AT34" t="inlineStr">
-        <is>
-          <t>94.29</t>
-        </is>
-      </c>
-      <c r="AU34" t="n">
-        <v>5.32</v>
-      </c>
-      <c r="AV34" t="n">
-        <v>14.53</v>
-      </c>
-      <c r="AW34" t="inlineStr">
-        <is>
-          <t>6.06</t>
-        </is>
-      </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>13.18</t>
-        </is>
-      </c>
-      <c r="AY34" t="inlineStr">
-        <is>
-          <t>72.53999999999999</t>
-        </is>
-      </c>
-      <c r="AZ34" t="n">
-        <v>63.34</v>
-      </c>
-      <c r="BA34" t="n">
-        <v>59.72</v>
-      </c>
-      <c r="BB34" t="inlineStr">
-        <is>
-          <t>52.76</t>
-        </is>
-      </c>
-      <c r="BC34" t="inlineStr">
-        <is>
-          <t>60.75</t>
-        </is>
-      </c>
-      <c r="BD34" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="BE34" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="BF34" t="inlineStr">
-        <is>
-          <t>4.82</t>
-        </is>
-      </c>
-      <c r="BG34" t="inlineStr">
-        <is>
-          <t>-43.83</t>
-        </is>
-      </c>
-      <c r="BH34" t="inlineStr">
-        <is>
-          <t>2026/01/08</t>
-        </is>
-      </c>
-      <c r="BI34" t="inlineStr">
-        <is>
-          <t>2764003009.408284</t>
-        </is>
-      </c>
-      <c r="BJ34" t="inlineStr">
-        <is>
-          <t>17712677893.0</t>
-        </is>
-      </c>
-      <c r="BK34" t="n">
-        <v>18350574605.6</v>
-      </c>
-      <c r="BL34" t="inlineStr">
-        <is>
-          <t>14548694839.4</t>
-        </is>
-      </c>
-      <c r="BM34" t="n">
-        <v>8579593877.62</v>
-      </c>
-      <c r="BN34" t="inlineStr">
-        <is>
-          <t>-2147483648</t>
-        </is>
-      </c>
-      <c r="BO34" t="inlineStr">
-        <is>
-          <t>1281303516.887251</t>
-        </is>
-      </c>
-      <c r="BP34" t="inlineStr">
-        <is>
-          <t>2806216507.820721</t>
-        </is>
-      </c>
-      <c r="BQ34" t="inlineStr">
-        <is>
-          <t>17712677893.0</t>
-        </is>
-      </c>
-      <c r="BR34" t="inlineStr">
-        <is>
-          <t>2026-02-02</t>
-        </is>
-      </c>
-      <c r="BS34" t="inlineStr">
-        <is>
-          <t>41.9</t>
-        </is>
-      </c>
-      <c r="BT34" t="inlineStr">
-        <is>
-          <t>2025/10/21</t>
-        </is>
-      </c>
-      <c r="BU34" t="inlineStr">
-        <is>
-          <t>82.34</t>
-        </is>
-      </c>
-      <c r="BV34" t="inlineStr">
-        <is>
-          <t>南亞</t>
-        </is>
-      </c>
-      <c r="BW34" t="inlineStr">
-        <is>
-          <t>南亞</t>
-        </is>
-      </c>
-      <c r="BX34" t="inlineStr">
-        <is>
-          <t>塑膠工業</t>
-        </is>
-      </c>
-      <c r="BY34" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BZ34" t="inlineStr">
-        <is>
-          <t>0.94</t>
-        </is>
-      </c>
-      <c r="CA34" t="inlineStr">
-        <is>
-          <t>4.576300423341094</t>
-        </is>
-      </c>
-      <c r="CB34" t="inlineStr">
-        <is>
-          <t>-5.666405408220591</t>
-        </is>
-      </c>
-      <c r="CC34" t="inlineStr">
-        <is>
-          <t>0.1134007627940262</t>
-        </is>
-      </c>
-      <c r="CD34" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="CE34" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="CF34" t="inlineStr">
-        <is>
-          <t>1.84</t>
-        </is>
-      </c>
-      <c r="CG34" t="inlineStr">
-        <is>
-          <t>0.96</t>
-        </is>
-      </c>
-      <c r="CH34" t="inlineStr">
-        <is>
-          <t>8.09</t>
-        </is>
-      </c>
-      <c r="CI34" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CJ34" t="inlineStr">
-        <is>
-          <t>8.29%</t>
-        </is>
-      </c>
-      <c r="CK34" t="inlineStr">
-        <is>
-          <t>1.61%</t>
-        </is>
-      </c>
-      <c r="CL34" t="inlineStr">
-        <is>
-          <t>60.85</t>
-        </is>
-      </c>
-      <c r="CM34" t="inlineStr">
-        <is>
-          <t>578950</t>
-        </is>
-      </c>
-      <c r="CN34" t="inlineStr">
-        <is>
-          <t>聚酯纖維16.60%、其他16.28%、印刷電路板(PCB)12.09%、銅箔基板(CCL)10.47%、環氧樹脂8.29%、丙二酚(BPA)5.67%、乙二醇(EG)5.60%、銅箔5.01%、可塑劑(DOP)及硬化劑3.38%、硬質管2.55%、硬質膠布2.48%、塑膠門窗2.20%、軟質膠布1.85%、麩酸酐(PA)1.55%、玻璃纖維布1.32%、聚酯薄膜1.30%、膠乳皮0.92%、PU合成皮(人造皮)0.69%、BOPP膜0.64%、玻璃纖維絲0.60%、丁二醇(BDO)0.54% (2024年)</t>
-        </is>
-      </c>
-      <c r="CO34" t="inlineStr">
-        <is>
-          <t>南亞-塑膠工業-上市</t>
-        </is>
-      </c>
-      <c r="CP34" t="inlineStr">
-        <is>
-          <t>塑膠工業右上上市</t>
-        </is>
-      </c>
-      <c r="CQ34" t="inlineStr">
-        <is>
-          <t>75.2</t>
-        </is>
-      </c>
-      <c r="CR34" t="inlineStr">
-        <is>
-          <t>79.4</t>
-        </is>
-      </c>
-      <c r="CS34" t="inlineStr">
-        <is>
-          <t>74.0</t>
-        </is>
-      </c>
-      <c r="CT34" t="inlineStr">
-        <is>
-          <t>76.4</t>
-        </is>
-      </c>
-      <c r="CU34" t="inlineStr">
-        <is>
-          <t>41.48</t>
-        </is>
-      </c>
-      <c r="CV34" t="inlineStr">
-        <is>
-          <t>** 印刷電路板 - 玻璃纖維/玻纖布、環氧樹脂、酚醛樹脂、銅箔、銅箔基板** 石化及塑橡膠 - 石化上游原料及相關鑽探設備、人造纖維** 紡織 - 石化原料(例如純對苯二甲酸、乙二醇、己內醯胺、丙烯腈等)、人造纖維產品(例如尼龍纖維、聚酯纖維、嫘縈纖維等)、染整** 電機機械 - 電控元件、機械設備之沖壓零組件</t>
-        </is>
-      </c>
-      <c r="CW34" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="CX34" t="inlineStr">
-        <is>
-          <t>2.0</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="CY33" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
     </row>
